--- a/Báo giá 2.xlsx
+++ b/Báo giá 2.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tb" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bao gia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh gia LN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1" iterateCount="1"/>
 </workbook>
@@ -21,10 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.##"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,6 +131,53 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -169,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -192,6 +242,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -199,7 +283,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -377,6 +461,76 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -775,9 +929,14 @@
     <col width="12.28515625" bestFit="1" customWidth="1" style="29" min="12" max="12"/>
     <col width="15.28515625" customWidth="1" min="13" max="13"/>
     <col width="8.85546875" customWidth="1" style="51" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -788,7 +947,9 @@
       </c>
       <c r="M1" s="3" t="n"/>
       <c r="N1" s="48" t="n"/>
-      <c r="O1" s="3" t="n"/>
+      <c r="O1" s="82" t="n"/>
+      <c r="P1" s="82" t="n"/>
+      <c r="Q1" s="82" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="59">
@@ -797,7 +958,9 @@
       </c>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="48" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="O2" s="82" t="n"/>
+      <c r="P2" s="82" t="n"/>
+      <c r="Q2" s="82" t="n"/>
     </row>
     <row r="3" ht="37.5" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="4" t="inlineStr">
@@ -850,21 +1013,17 @@
           <t>NSX</t>
         </is>
       </c>
-      <c r="O3" s="75" t="inlineStr">
-        <is>
-          <t>Giá vốn vật tư (đơn giá)</t>
-        </is>
-      </c>
-      <c r="P3" s="75" t="inlineStr">
-        <is>
-          <t>Giá vốn nhân công (đơn giá)</t>
-        </is>
-      </c>
-      <c r="Q3" s="70" t="inlineStr">
-        <is>
-          <t>Đơn giá đề xuất (trước thuế)</t>
-        </is>
-      </c>
+      <c r="O3" s="83" t="inlineStr">
+        <is>
+          <t>Giá vật tư đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="P3" s="83" t="inlineStr">
+        <is>
+          <t>Giá nhân công đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="Q3" s="82" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -889,6 +1048,9 @@
       <c r="L4" s="28" t="n"/>
       <c r="M4" s="26" t="n"/>
       <c r="N4" s="50" t="n"/>
+      <c r="O4" s="84" t="n"/>
+      <c r="P4" s="84" t="n"/>
+      <c r="Q4" s="82" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -911,7 +1073,7 @@
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5">
+      <c r="I5" s="85">
         <f>SUM(D5:H5)</f>
         <v/>
       </c>
@@ -934,15 +1096,15 @@
           <t>vn</t>
         </is>
       </c>
-      <c r="O5" s="76" t="n">
-        <v>53000</v>
-      </c>
-      <c r="P5" s="76" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Q5" s="71" t="n">
-        <v>163000</v>
-      </c>
+      <c r="O5" s="86">
+        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="P5" s="86">
+        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="82" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -967,7 +1129,7 @@
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5">
+      <c r="I6" s="85">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
@@ -990,15 +1152,15 @@
           <t>vn</t>
         </is>
       </c>
-      <c r="O6" s="76" t="n">
-        <v>137000</v>
-      </c>
-      <c r="P6" s="77" t="n">
-        <v>31538</v>
-      </c>
-      <c r="Q6" s="71" t="n">
-        <v>216000</v>
-      </c>
+      <c r="O6" s="86">
+        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="P6" s="86">
+        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="82" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -1023,7 +1185,7 @@
       </c>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5">
+      <c r="I7" s="85">
         <f>SUM(D7:H7)</f>
         <v/>
       </c>
@@ -1046,15 +1208,15 @@
           <t>vn</t>
         </is>
       </c>
-      <c r="O7" s="76" t="n">
-        <v>652000</v>
-      </c>
-      <c r="P7" s="77" t="n">
-        <v>10769</v>
-      </c>
-      <c r="Q7" s="71" t="n">
-        <v>1027000</v>
-      </c>
+      <c r="O7" s="86">
+        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="P7" s="86">
+        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="82" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -1085,7 +1247,7 @@
       <c r="H8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="85">
         <f>SUM(D8:H8)</f>
         <v/>
       </c>
@@ -1108,15 +1270,15 @@
           <t>vn</t>
         </is>
       </c>
-      <c r="O8" s="76" t="n">
-        <v>442000</v>
-      </c>
-      <c r="P8" s="76" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Q8" s="71" t="n">
-        <v>775000</v>
-      </c>
+      <c r="O8" s="86">
+        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="P8" s="86">
+        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="82" t="n"/>
     </row>
     <row r="9" ht="18.75" customFormat="1" customHeight="1" s="10">
       <c r="A9" s="35" t="n"/>
@@ -1150,18 +1312,9 @@
           <t>vn</t>
         </is>
       </c>
-      <c r="O9" s="78">
-        <f>SUMPRODUCT(I5:I8,O5:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="78">
-        <f>SUMPRODUCT(I5:I8,P5:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="72">
-        <f>SUMPRODUCT(I5:I8,Q5:Q8)</f>
-        <v/>
-      </c>
+      <c r="O9" s="84" t="n"/>
+      <c r="P9" s="84" t="n"/>
+      <c r="Q9" s="82" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="B10" s="36" t="inlineStr">
@@ -1184,15 +1337,15 @@
       <c r="L10" s="34" t="n"/>
       <c r="M10" s="27" t="n"/>
       <c r="N10" s="50" t="n"/>
-      <c r="O10" s="79" t="n"/>
-      <c r="P10" s="79" t="n"/>
-      <c r="Q10" s="73">
-        <f>Q9+SUMPRODUCT(I5:I8,Q5:Q8,L5:L8)</f>
-        <v/>
-      </c>
+      <c r="O10" s="84" t="n"/>
+      <c r="P10" s="84" t="n"/>
+      <c r="Q10" s="82" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="B11" s="36" t="n"/>
+      <c r="O11" s="82" t="n"/>
+      <c r="P11" s="82" t="n"/>
+      <c r="Q11" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1222,10 +1375,14 @@
     <col width="16" customWidth="1" style="53" min="7" max="7"/>
     <col width="15.5703125" customWidth="1" style="46" min="8" max="8"/>
     <col width="10.85546875" customWidth="1" style="1" min="9" max="9"/>
-    <col width="8.7109375" customWidth="1" style="1" min="10" max="16384"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1234,12 +1391,20 @@
           <t>BẢNG TỔNG HỢP THIẾT BỊ</t>
         </is>
       </c>
+      <c r="J1" s="82" t="n"/>
+      <c r="K1" s="82" t="n"/>
+      <c r="L1" s="82" t="n"/>
+      <c r="M1" s="82" t="n"/>
     </row>
     <row r="2" ht="44.25" customHeight="1">
       <c r="A2" s="61">
         <f>#REF!</f>
         <v/>
       </c>
+      <c r="J2" s="82" t="n"/>
+      <c r="K2" s="82" t="n"/>
+      <c r="L2" s="82" t="n"/>
+      <c r="M2" s="82" t="n"/>
     </row>
     <row r="3" ht="37.5" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -1287,21 +1452,18 @@
           <t>NSX</t>
         </is>
       </c>
-      <c r="K3" s="75" t="inlineStr">
-        <is>
-          <t>Giá vốn vật tư (đơn giá)</t>
-        </is>
-      </c>
-      <c r="L3" s="75" t="inlineStr">
-        <is>
-          <t>Giá vốn nhân công (đơn giá)</t>
-        </is>
-      </c>
-      <c r="M3" s="70" t="inlineStr">
-        <is>
-          <t>Đơn giá đề xuất (trước thuế)</t>
-        </is>
-      </c>
+      <c r="J3" s="83" t="inlineStr">
+        <is>
+          <t>Giá vật tư đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="K3" s="83" t="inlineStr">
+        <is>
+          <t>Giá nhân công đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="L3" s="82" t="n"/>
+      <c r="M3" s="82" t="n"/>
     </row>
     <row r="4" ht="37.5" customHeight="1">
       <c r="A4" s="15" t="n">
@@ -1339,15 +1501,16 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="K4" s="80" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="L4" s="80" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="M4" s="74" t="n">
-        <v>13534000</v>
-      </c>
+      <c r="J4" s="86">
+        <f>IF('Danh gia LN'!E16="","",ROUNDUP('Danh gia LN'!E16*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K4" s="86">
+        <f>IF('Danh gia LN'!F16="","",ROUNDUP('Danh gia LN'!F16*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L4" s="82" t="n"/>
+      <c r="M4" s="82" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="15" t="n">
@@ -1385,15 +1548,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K5" s="80" t="n">
-        <v>252000</v>
-      </c>
-      <c r="L5" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M5" s="74" t="n">
-        <v>397000</v>
-      </c>
+      <c r="J5" s="86">
+        <f>IF('Danh gia LN'!E17="","",ROUNDUP('Danh gia LN'!E17*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K5" s="86">
+        <f>IF('Danh gia LN'!F17="","",ROUNDUP('Danh gia LN'!F17*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L5" s="82" t="n"/>
+      <c r="M5" s="82" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="15">
@@ -1432,15 +1596,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K6" s="80" t="n">
-        <v>205000</v>
-      </c>
-      <c r="L6" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M6" s="74" t="n">
-        <v>323000</v>
-      </c>
+      <c r="J6" s="86">
+        <f>IF('Danh gia LN'!E18="","",ROUNDUP('Danh gia LN'!E18*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K6" s="86">
+        <f>IF('Danh gia LN'!F18="","",ROUNDUP('Danh gia LN'!F18*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L6" s="82" t="n"/>
+      <c r="M6" s="82" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="15">
@@ -1479,15 +1644,16 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="K7" s="80" t="n">
-        <v>242000</v>
-      </c>
-      <c r="L7" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M7" s="74" t="n">
-        <v>381000</v>
-      </c>
+      <c r="J7" s="86">
+        <f>IF('Danh gia LN'!E19="","",ROUNDUP('Danh gia LN'!E19*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K7" s="86">
+        <f>IF('Danh gia LN'!F19="","",ROUNDUP('Danh gia LN'!F19*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L7" s="82" t="n"/>
+      <c r="M7" s="82" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="15">
@@ -1526,15 +1692,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K8" s="80" t="n">
-        <v>116000</v>
-      </c>
-      <c r="L8" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M8" s="74" t="n">
-        <v>183000</v>
-      </c>
+      <c r="J8" s="86">
+        <f>IF('Danh gia LN'!E20="","",ROUNDUP('Danh gia LN'!E20*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K8" s="86">
+        <f>IF('Danh gia LN'!F20="","",ROUNDUP('Danh gia LN'!F20*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L8" s="82" t="n"/>
+      <c r="M8" s="82" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="15">
@@ -1573,15 +1740,16 @@
           <t>ấn độ</t>
         </is>
       </c>
-      <c r="K9" s="80" t="n">
-        <v>252000</v>
-      </c>
-      <c r="L9" s="80" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M9" s="74" t="n">
-        <v>397000</v>
-      </c>
+      <c r="J9" s="86">
+        <f>IF('Danh gia LN'!E21="","",ROUNDUP('Danh gia LN'!E21*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K9" s="86">
+        <f>IF('Danh gia LN'!F21="","",ROUNDUP('Danh gia LN'!F21*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="15">
@@ -1620,15 +1788,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K10" s="80" t="n">
-        <v>53000</v>
-      </c>
-      <c r="L10" s="80" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M10" s="74" t="n">
-        <v>84000</v>
-      </c>
+      <c r="J10" s="86">
+        <f>IF('Danh gia LN'!E22="","",ROUNDUP('Danh gia LN'!E22*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K10" s="86">
+        <f>IF('Danh gia LN'!F22="","",ROUNDUP('Danh gia LN'!F22*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="15">
@@ -1667,15 +1836,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K11" s="80" t="n">
-        <v>42000</v>
-      </c>
-      <c r="L11" s="80" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M11" s="74" t="n">
-        <v>67000</v>
-      </c>
+      <c r="J11" s="86">
+        <f>IF('Danh gia LN'!E23="","",ROUNDUP('Danh gia LN'!E23*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K11" s="86">
+        <f>IF('Danh gia LN'!F23="","",ROUNDUP('Danh gia LN'!F23*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="15">
@@ -1714,15 +1884,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K12" s="80" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L12" s="80" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M12" s="74" t="n">
-        <v>150000</v>
-      </c>
+      <c r="J12" s="86">
+        <f>IF('Danh gia LN'!E24="","",ROUNDUP('Danh gia LN'!E24*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K12" s="86">
+        <f>IF('Danh gia LN'!F24="","",ROUNDUP('Danh gia LN'!F24*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
     </row>
     <row r="13" ht="18.75" customFormat="1" customHeight="1" s="69">
       <c r="A13" s="62">
@@ -1761,20 +1932,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J13" s="69" t="inlineStr">
-        <is>
-          <t>Sai giá ( gấp 10 lân)</t>
-        </is>
-      </c>
-      <c r="K13" s="80" t="n">
-        <v>190000</v>
-      </c>
-      <c r="L13" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M13" s="74" t="n">
-        <v>299000</v>
-      </c>
+      <c r="J13" s="86">
+        <f>IF('Danh gia LN'!E25="","",ROUNDUP('Danh gia LN'!E25*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K13" s="86">
+        <f>IF('Danh gia LN'!F25="","",ROUNDUP('Danh gia LN'!F25*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L13" s="82" t="n"/>
+      <c r="M13" s="82" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="15">
@@ -1813,15 +1980,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K14" s="80" t="n">
-        <v>75000</v>
-      </c>
-      <c r="L14" s="80" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M14" s="74" t="n">
-        <v>119000</v>
-      </c>
+      <c r="J14" s="86">
+        <f>IF('Danh gia LN'!E26="","",ROUNDUP('Danh gia LN'!E26*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K14" s="86">
+        <f>IF('Danh gia LN'!F26="","",ROUNDUP('Danh gia LN'!F26*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L14" s="82" t="n"/>
+      <c r="M14" s="82" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="15">
@@ -1860,15 +2028,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K15" s="80" t="n">
-        <v>245000</v>
-      </c>
-      <c r="L15" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M15" s="74" t="n">
-        <v>386000</v>
-      </c>
+      <c r="J15" s="86">
+        <f>IF('Danh gia LN'!E27="","",ROUNDUP('Danh gia LN'!E27*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K15" s="86">
+        <f>IF('Danh gia LN'!F27="","",ROUNDUP('Danh gia LN'!F27*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="15">
@@ -1907,15 +2076,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K16" s="80" t="n">
-        <v>190000</v>
-      </c>
-      <c r="L16" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M16" s="74" t="n">
-        <v>299000</v>
-      </c>
+      <c r="J16" s="86">
+        <f>IF('Danh gia LN'!E28="","",ROUNDUP('Danh gia LN'!E28*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K16" s="86">
+        <f>IF('Danh gia LN'!F28="","",ROUNDUP('Danh gia LN'!F28*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L16" s="82" t="n"/>
+      <c r="M16" s="82" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="15">
@@ -1954,15 +2124,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K17" s="80" t="n">
-        <v>231000</v>
-      </c>
-      <c r="L17" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M17" s="74" t="n">
-        <v>364000</v>
-      </c>
+      <c r="J17" s="86">
+        <f>IF('Danh gia LN'!E29="","",ROUNDUP('Danh gia LN'!E29*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K17" s="86">
+        <f>IF('Danh gia LN'!F29="","",ROUNDUP('Danh gia LN'!F29*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="15">
@@ -2001,15 +2172,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K18" s="80" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L18" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M18" s="74" t="n">
-        <v>150000</v>
-      </c>
+      <c r="J18" s="86">
+        <f>IF('Danh gia LN'!E30="","",ROUNDUP('Danh gia LN'!E30*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K18" s="86">
+        <f>IF('Danh gia LN'!F30="","",ROUNDUP('Danh gia LN'!F30*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="15">
@@ -2048,15 +2220,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K19" s="80" t="n">
-        <v>17000</v>
-      </c>
-      <c r="L19" s="81" t="n">
-        <v>11538</v>
-      </c>
-      <c r="M19" s="74" t="n">
-        <v>27000</v>
-      </c>
+      <c r="J19" s="86">
+        <f>IF('Danh gia LN'!E31="","",ROUNDUP('Danh gia LN'!E31*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K19" s="86">
+        <f>IF('Danh gia LN'!F31="","",ROUNDUP('Danh gia LN'!F31*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="15">
@@ -2094,15 +2267,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K20" s="80" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L20" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M20" s="74" t="n">
-        <v>315000</v>
-      </c>
+      <c r="J20" s="86">
+        <f>IF('Danh gia LN'!E32="","",ROUNDUP('Danh gia LN'!E32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K20" s="86">
+        <f>IF('Danh gia LN'!F32="","",ROUNDUP('Danh gia LN'!F32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
     </row>
     <row r="21" ht="18.75" customFormat="1" customHeight="1" s="69">
       <c r="A21" s="62">
@@ -2139,20 +2313,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J21" s="69" t="inlineStr">
-        <is>
-          <t>Thiếu báo giá</t>
-        </is>
-      </c>
-      <c r="K21" s="80" t="n">
-        <v>2205000</v>
-      </c>
-      <c r="L21" s="80" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M21" s="74" t="n">
-        <v>3470000</v>
-      </c>
+      <c r="J21" s="86">
+        <f>IF('Danh gia LN'!E33="","",ROUNDUP('Danh gia LN'!E33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K21" s="86">
+        <f>IF('Danh gia LN'!F33="","",ROUNDUP('Danh gia LN'!F33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
     </row>
     <row r="22" ht="37.5" customHeight="1">
       <c r="A22" s="15">
@@ -2191,15 +2361,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K22" s="80" t="n">
-        <v>368000</v>
-      </c>
-      <c r="L22" s="80" t="n">
-        <v>400000</v>
-      </c>
-      <c r="M22" s="74" t="n">
-        <v>580000</v>
-      </c>
+      <c r="J22" s="86">
+        <f>IF('Danh gia LN'!E34="","",ROUNDUP('Danh gia LN'!E34*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K22" s="86">
+        <f>IF('Danh gia LN'!F34="","",ROUNDUP('Danh gia LN'!F34*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
     </row>
     <row r="23" ht="37.5" customHeight="1">
       <c r="A23" s="15">
@@ -2238,15 +2409,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K23" s="80" t="n">
-        <v>514286</v>
-      </c>
-      <c r="L23" s="81" t="n">
-        <v>58022</v>
-      </c>
-      <c r="M23" s="74" t="n">
-        <v>810000</v>
-      </c>
+      <c r="J23" s="86">
+        <f>IF('Danh gia LN'!E35="","",ROUNDUP('Danh gia LN'!E35*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K23" s="86">
+        <f>IF('Danh gia LN'!F35="","",ROUNDUP('Danh gia LN'!F35*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="15">
@@ -2285,15 +2457,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K24" s="80" t="n">
-        <v>85714</v>
-      </c>
-      <c r="L24" s="81" t="n">
-        <v>9670</v>
-      </c>
-      <c r="M24" s="74" t="n">
-        <v>135000</v>
-      </c>
+      <c r="J24" s="86">
+        <f>IF('Danh gia LN'!E36="","",ROUNDUP('Danh gia LN'!E36*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K24" s="86">
+        <f>IF('Danh gia LN'!F36="","",ROUNDUP('Danh gia LN'!F36*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="15">
@@ -2332,15 +2505,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K25" s="80" t="n">
-        <v>166000</v>
-      </c>
-      <c r="L25" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M25" s="74" t="n">
-        <v>262000</v>
-      </c>
+      <c r="J25" s="86">
+        <f>IF('Danh gia LN'!E37="","",ROUNDUP('Danh gia LN'!E37*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K25" s="86">
+        <f>IF('Danh gia LN'!F37="","",ROUNDUP('Danh gia LN'!F37*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
     </row>
     <row r="26" ht="37.5" customHeight="1">
       <c r="A26" s="15">
@@ -2380,15 +2554,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K26" s="80" t="n">
-        <v>53000</v>
-      </c>
-      <c r="L26" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M26" s="74" t="n">
-        <v>163000</v>
-      </c>
+      <c r="J26" s="86">
+        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K26" s="86">
+        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="15">
@@ -2428,15 +2603,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K27" s="80" t="n">
-        <v>137000</v>
-      </c>
-      <c r="L27" s="81" t="n">
-        <v>31538</v>
-      </c>
-      <c r="M27" s="74" t="n">
-        <v>216000</v>
-      </c>
+      <c r="J27" s="86">
+        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K27" s="86">
+        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="82" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="15">
@@ -2476,15 +2652,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K28" s="80" t="n">
-        <v>652000</v>
-      </c>
-      <c r="L28" s="81" t="n">
-        <v>10769</v>
-      </c>
-      <c r="M28" s="74" t="n">
-        <v>1027000</v>
-      </c>
+      <c r="J28" s="86">
+        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K28" s="86">
+        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L28" s="82" t="n"/>
+      <c r="M28" s="82" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="15">
@@ -2523,15 +2700,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K29" s="80" t="n">
-        <v>158000</v>
-      </c>
-      <c r="L29" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M29" s="74" t="n">
-        <v>249000</v>
-      </c>
+      <c r="J29" s="86">
+        <f>IF('Danh gia LN'!E41="","",ROUNDUP('Danh gia LN'!E41*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K29" s="86">
+        <f>IF('Danh gia LN'!F41="","",ROUNDUP('Danh gia LN'!F41*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L29" s="82" t="n"/>
+      <c r="M29" s="82" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="15">
@@ -2570,15 +2748,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K30" s="80" t="n">
-        <v>190000</v>
-      </c>
-      <c r="L30" s="80" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M30" s="74" t="n">
-        <v>299000</v>
-      </c>
+      <c r="J30" s="86">
+        <f>IF('Danh gia LN'!E42="","",ROUNDUP('Danh gia LN'!E42*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K30" s="86">
+        <f>IF('Danh gia LN'!F42="","",ROUNDUP('Danh gia LN'!F42*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L30" s="82" t="n"/>
+      <c r="M30" s="82" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="15">
@@ -2613,9 +2792,10 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K31" s="80" t="n"/>
-      <c r="L31" s="80" t="n"/>
-      <c r="M31" s="74" t="n"/>
+      <c r="J31" s="84" t="n"/>
+      <c r="K31" s="84" t="n"/>
+      <c r="L31" s="82" t="n"/>
+      <c r="M31" s="82" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="15">
@@ -2655,15 +2835,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K32" s="80" t="n">
-        <v>442000</v>
-      </c>
-      <c r="L32" s="80" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M32" s="74" t="n">
-        <v>775000</v>
-      </c>
+      <c r="J32" s="86">
+        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K32" s="86">
+        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L32" s="82" t="n"/>
+      <c r="M32" s="82" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="15">
@@ -2702,15 +2883,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K33" s="80" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="L33" s="80" t="n">
-        <v>500000</v>
-      </c>
-      <c r="M33" s="74" t="n">
-        <v>1983000</v>
-      </c>
+      <c r="J33" s="86">
+        <f>IF('Danh gia LN'!E44="","",ROUNDUP('Danh gia LN'!E44*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K33" s="86">
+        <f>IF('Danh gia LN'!F44="","",ROUNDUP('Danh gia LN'!F44*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L33" s="82" t="n"/>
+      <c r="M33" s="82" t="n"/>
     </row>
     <row r="34" customFormat="1" s="46">
       <c r="A34" s="41" t="n"/>
@@ -2732,18 +2914,10 @@
         <v/>
       </c>
       <c r="I34" s="45" t="n"/>
-      <c r="K34" s="79">
-        <f>SUMPRODUCT(D4:D33,K4:K33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="79">
-        <f>SUMPRODUCT(D4:D33,L4:L33)</f>
-        <v/>
-      </c>
-      <c r="M34" s="73">
-        <f>SUMPRODUCT(D4:D33,M4:M33)</f>
-        <v/>
-      </c>
+      <c r="J34" s="84" t="n"/>
+      <c r="K34" s="84" t="n"/>
+      <c r="L34" s="82" t="n"/>
+      <c r="M34" s="82" t="n"/>
     </row>
     <row r="35" customFormat="1" s="46">
       <c r="A35" s="41" t="n"/>
@@ -2762,12 +2936,10 @@
       <c r="G35" s="54" t="n"/>
       <c r="H35" s="45" t="n"/>
       <c r="I35" s="45" t="n"/>
-      <c r="K35" s="79" t="n"/>
-      <c r="L35" s="79" t="n"/>
-      <c r="M35" s="73">
-        <f>M34+SUMPRODUCT(D4:D33,M4:M33,G4:G33)</f>
-        <v/>
-      </c>
+      <c r="J35" s="84" t="n"/>
+      <c r="K35" s="84" t="n"/>
+      <c r="L35" s="82" t="n"/>
+      <c r="M35" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2777,4 +2949,2247 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="82" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>ĐÁNH GIÁ LỢI NHUẬN THEO GIÁ ĐỀ XUẤT – TIỂU HỌC – THCS (5 TRƯỜNG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="88" t="inlineStr">
+        <is>
+          <t>Giá vốn lấy theo sheet 'Gia von chi tiet' (file Danh gia toan goi PCCC Dong Son). Giá đề xuất = giá vốn × (1 + tỷ lệ lợi nhuận), làm tròn lên hàng nghìn. Đơn giá trước thuế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="89" t="inlineStr">
+        <is>
+          <t>Tỷ lệ lợi nhuận mong muốn trên giá vốn (sửa ô này)</t>
+        </is>
+      </c>
+      <c r="C4" s="90" t="n"/>
+      <c r="D4" s="91" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="92" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="93" t="inlineStr">
+        <is>
+          <t>Khoản</t>
+        </is>
+      </c>
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="90" t="n"/>
+      <c r="E7" s="93" t="inlineStr">
+        <is>
+          <t>Giá vốn</t>
+        </is>
+      </c>
+      <c r="F7" s="90" t="n"/>
+      <c r="G7" s="93" t="inlineStr">
+        <is>
+          <t>Giá đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="H7" s="90" t="n"/>
+      <c r="I7" s="93" t="inlineStr">
+        <is>
+          <t>Lợi nhuận</t>
+        </is>
+      </c>
+      <c r="J7" s="93" t="inlineStr">
+        <is>
+          <t>% LN / giá vốn</t>
+        </is>
+      </c>
+      <c r="K7" s="93" t="inlineStr">
+        <is>
+          <t>% LN / giá bán</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="95" t="inlineStr">
+        <is>
+          <t>Vật tư, thiết bị</t>
+        </is>
+      </c>
+      <c r="C8" s="96" t="n"/>
+      <c r="D8" s="96" t="n"/>
+      <c r="E8" s="96">
+        <f>SUMPRODUCT(--(E16:E44&lt;&gt;""),D16:D44,N(+E16:E44))</f>
+        <v/>
+      </c>
+      <c r="F8" s="96" t="n"/>
+      <c r="G8" s="96">
+        <f>SUMPRODUCT(--(G16:G44&lt;&gt;""),D16:D44,N(+G16:G44))</f>
+        <v/>
+      </c>
+      <c r="H8" s="96" t="n"/>
+      <c r="I8" s="96">
+        <f>G8-E8</f>
+        <v/>
+      </c>
+      <c r="J8" s="97">
+        <f>IF(E8=0,"",I8/E8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="97">
+        <f>IF(G8=0,"",I8/G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="95" t="inlineStr">
+        <is>
+          <t>Nhân công</t>
+        </is>
+      </c>
+      <c r="C9" s="96" t="n"/>
+      <c r="D9" s="96" t="n"/>
+      <c r="E9" s="96">
+        <f>SUMPRODUCT(--(F16:F44&lt;&gt;""),D16:D44,N(+F16:F44))</f>
+        <v/>
+      </c>
+      <c r="F9" s="96" t="n"/>
+      <c r="G9" s="96">
+        <f>SUMPRODUCT(--(H16:H44&lt;&gt;""),D16:D44,N(+H16:H44))</f>
+        <v/>
+      </c>
+      <c r="H9" s="96" t="n"/>
+      <c r="I9" s="96">
+        <f>G9-E9</f>
+        <v/>
+      </c>
+      <c r="J9" s="97">
+        <f>IF(E9=0,"",I9/E9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="97">
+        <f>IF(G9=0,"",I9/G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>Cộng trước thuế</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="n"/>
+      <c r="D10" s="99" t="n"/>
+      <c r="E10" s="99">
+        <f>E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="99" t="n"/>
+      <c r="G10" s="99">
+        <f>G8+G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="99" t="n"/>
+      <c r="I10" s="99">
+        <f>G10-E10</f>
+        <v/>
+      </c>
+      <c r="J10" s="100">
+        <f>IF(E10=0,"",I10/E10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="100">
+        <f>IF(G10=0,"",I10/G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="95" t="inlineStr">
+        <is>
+          <t>Thuế GTGT trên giá đề xuất (theo thuế suất từng dòng)</t>
+        </is>
+      </c>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="96" t="n"/>
+      <c r="F11" s="96" t="n"/>
+      <c r="G11" s="96">
+        <f>SUMPRODUCT(J16:J44,N(+M16:M44))</f>
+        <v/>
+      </c>
+      <c r="H11" s="96" t="n"/>
+      <c r="I11" s="96" t="n"/>
+      <c r="J11" s="97" t="n"/>
+      <c r="K11" s="97" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>Giá trị đề xuất sau thuế</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="n"/>
+      <c r="D12" s="99" t="n"/>
+      <c r="E12" s="99" t="n"/>
+      <c r="F12" s="99" t="n"/>
+      <c r="G12" s="99">
+        <f>G10+G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="99" t="n"/>
+      <c r="I12" s="99" t="n"/>
+      <c r="J12" s="100" t="n"/>
+      <c r="K12" s="100" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="101" t="inlineStr">
+        <is>
+          <t>Kiểm tra: tổng cộng ở bảng chi tiết (dòng 45) phải bằng dòng 'Cộng trước thuế'. % LN / giá bán = lợi nhuận ÷ giá đề xuất (40% trên giá vốn ≈ 28,6% trên giá bán).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="93" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B15" s="93" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C15" s="93" t="inlineStr">
+        <is>
+          <t>ĐVT</t>
+        </is>
+      </c>
+      <c r="D15" s="93" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E15" s="93" t="inlineStr">
+        <is>
+          <t>Giá vốn vật tư</t>
+        </is>
+      </c>
+      <c r="F15" s="93" t="inlineStr">
+        <is>
+          <t>Giá vốn nhân công</t>
+        </is>
+      </c>
+      <c r="G15" s="93" t="inlineStr">
+        <is>
+          <t>Giá vật tư đề xuất</t>
+        </is>
+      </c>
+      <c r="H15" s="93" t="inlineStr">
+        <is>
+          <t>Giá nhân công đề xuất</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="inlineStr">
+        <is>
+          <t>Thành tiền giá vốn</t>
+        </is>
+      </c>
+      <c r="J15" s="93" t="inlineStr">
+        <is>
+          <t>Thành tiền đề xuất</t>
+        </is>
+      </c>
+      <c r="K15" s="93" t="inlineStr">
+        <is>
+          <t>Lợi nhuận</t>
+        </is>
+      </c>
+      <c r="L15" s="93" t="inlineStr">
+        <is>
+          <t>% LN / giá vốn</t>
+        </is>
+      </c>
+      <c r="M15" s="93" t="inlineStr">
+        <is>
+          <t>Thuế suất</t>
+        </is>
+      </c>
+      <c r="N15" s="93" t="inlineStr">
+        <is>
+          <t>Đơn giá VT hiện tại (cột E báo giá)</t>
+        </is>
+      </c>
+      <c r="O15" s="93" t="inlineStr">
+        <is>
+          <t>Nguồn giá vốn</t>
+        </is>
+      </c>
+      <c r="P15" s="93" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="103" t="inlineStr">
+        <is>
+          <t>Trung tâm báo cháy 10 kênh bao gồm Acquy</t>
+        </is>
+      </c>
+      <c r="C16" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D16" s="104">
+        <f>'Bao gia'!D4</f>
+        <v/>
+      </c>
+      <c r="E16" s="96" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="F16" s="96" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G16" s="105">
+        <f>IF(E16="","",'Bao gia'!J4)</f>
+        <v/>
+      </c>
+      <c r="H16" s="105">
+        <f>IF(F16="","",'Bao gia'!K4)</f>
+        <v/>
+      </c>
+      <c r="I16" s="96">
+        <f>IF(E16="",0,D16*(E16+F16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="96">
+        <f>IF(E16="",0,D16*(G16+H16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="96">
+        <f>J16-I16</f>
+        <v/>
+      </c>
+      <c r="L16" s="97">
+        <f>IF(I16=0,"",K16/I16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="106">
+        <f>'Bao gia'!G4</f>
+        <v/>
+      </c>
+      <c r="N16" s="96">
+        <f>'Bao gia'!E4</f>
+        <v/>
+      </c>
+      <c r="O16" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P16" s="103" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="103" t="inlineStr">
+        <is>
+          <t>Còi đèn báo cháy kết hợp</t>
+        </is>
+      </c>
+      <c r="C17" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D17" s="104">
+        <f>'Bao gia'!D5</f>
+        <v/>
+      </c>
+      <c r="E17" s="96" t="n">
+        <v>252000</v>
+      </c>
+      <c r="F17" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G17" s="105">
+        <f>IF(E17="","",'Bao gia'!J5)</f>
+        <v/>
+      </c>
+      <c r="H17" s="105">
+        <f>IF(F17="","",'Bao gia'!K5)</f>
+        <v/>
+      </c>
+      <c r="I17" s="96">
+        <f>IF(E17="",0,D17*(E17+F17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="96">
+        <f>IF(E17="",0,D17*(G17+H17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="96">
+        <f>J17-I17</f>
+        <v/>
+      </c>
+      <c r="L17" s="97">
+        <f>IF(I17=0,"",K17/I17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="106">
+        <f>'Bao gia'!G5</f>
+        <v/>
+      </c>
+      <c r="N17" s="96">
+        <f>'Bao gia'!E5</f>
+        <v/>
+      </c>
+      <c r="O17" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P17" s="103" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="102" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="103" t="inlineStr">
+        <is>
+          <t>Nút ấn khẩn tròn lắp nổi</t>
+        </is>
+      </c>
+      <c r="C18" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D18" s="104">
+        <f>'Bao gia'!D6</f>
+        <v/>
+      </c>
+      <c r="E18" s="96" t="n">
+        <v>205000</v>
+      </c>
+      <c r="F18" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G18" s="105">
+        <f>IF(E18="","",'Bao gia'!J6)</f>
+        <v/>
+      </c>
+      <c r="H18" s="105">
+        <f>IF(F18="","",'Bao gia'!K6)</f>
+        <v/>
+      </c>
+      <c r="I18" s="96">
+        <f>IF(E18="",0,D18*(E18+F18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="96">
+        <f>IF(E18="",0,D18*(G18+H18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="96">
+        <f>J18-I18</f>
+        <v/>
+      </c>
+      <c r="L18" s="97">
+        <f>IF(I18=0,"",K18/I18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="106">
+        <f>'Bao gia'!G6</f>
+        <v/>
+      </c>
+      <c r="N18" s="96">
+        <f>'Bao gia'!E6</f>
+        <v/>
+      </c>
+      <c r="O18" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P18" s="103" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="102" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="103" t="inlineStr">
+        <is>
+          <t>Đầu báo khói quang 24VDC</t>
+        </is>
+      </c>
+      <c r="C19" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D19" s="104">
+        <f>'Bao gia'!D7</f>
+        <v/>
+      </c>
+      <c r="E19" s="96" t="n">
+        <v>242000</v>
+      </c>
+      <c r="F19" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G19" s="105">
+        <f>IF(E19="","",'Bao gia'!J7)</f>
+        <v/>
+      </c>
+      <c r="H19" s="105">
+        <f>IF(F19="","",'Bao gia'!K7)</f>
+        <v/>
+      </c>
+      <c r="I19" s="96">
+        <f>IF(E19="",0,D19*(E19+F19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="96">
+        <f>IF(E19="",0,D19*(G19+H19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="96">
+        <f>J19-I19</f>
+        <v/>
+      </c>
+      <c r="L19" s="97">
+        <f>IF(I19=0,"",K19/I19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="106">
+        <f>'Bao gia'!G7</f>
+        <v/>
+      </c>
+      <c r="N19" s="96">
+        <f>'Bao gia'!E7</f>
+        <v/>
+      </c>
+      <c r="O19" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P19" s="103" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="102" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="103" t="inlineStr">
+        <is>
+          <t>Đèn báo phòng</t>
+        </is>
+      </c>
+      <c r="C20" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D20" s="104">
+        <f>'Bao gia'!D8</f>
+        <v/>
+      </c>
+      <c r="E20" s="96" t="n">
+        <v>116000</v>
+      </c>
+      <c r="F20" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G20" s="105">
+        <f>IF(E20="","",'Bao gia'!J8)</f>
+        <v/>
+      </c>
+      <c r="H20" s="105">
+        <f>IF(F20="","",'Bao gia'!K8)</f>
+        <v/>
+      </c>
+      <c r="I20" s="96">
+        <f>IF(E20="",0,D20*(E20+F20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="96">
+        <f>IF(E20="",0,D20*(G20+H20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="96">
+        <f>J20-I20</f>
+        <v/>
+      </c>
+      <c r="L20" s="97">
+        <f>IF(I20=0,"",K20/I20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="106">
+        <f>'Bao gia'!G8</f>
+        <v/>
+      </c>
+      <c r="N20" s="96">
+        <f>'Bao gia'!E8</f>
+        <v/>
+      </c>
+      <c r="O20" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P20" s="103" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="102" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="103" t="inlineStr">
+        <is>
+          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
+        </is>
+      </c>
+      <c r="C21" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D21" s="104">
+        <f>'Bao gia'!D9</f>
+        <v/>
+      </c>
+      <c r="E21" s="96" t="n">
+        <v>252000</v>
+      </c>
+      <c r="F21" s="96" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G21" s="105">
+        <f>IF(E21="","",'Bao gia'!J9)</f>
+        <v/>
+      </c>
+      <c r="H21" s="105">
+        <f>IF(F21="","",'Bao gia'!K9)</f>
+        <v/>
+      </c>
+      <c r="I21" s="96">
+        <f>IF(E21="",0,D21*(E21+F21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="96">
+        <f>IF(E21="",0,D21*(G21+H21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="96">
+        <f>J21-I21</f>
+        <v/>
+      </c>
+      <c r="L21" s="97">
+        <f>IF(I21=0,"",K21/I21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="106">
+        <f>'Bao gia'!G9</f>
+        <v/>
+      </c>
+      <c r="N21" s="96">
+        <f>'Bao gia'!E9</f>
+        <v/>
+      </c>
+      <c r="O21" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Hệ thống tiếp địa trung tâm báo cháy'</t>
+        </is>
+      </c>
+      <c r="P21" s="103" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="102" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="103" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C22" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D22" s="104">
+        <f>'Bao gia'!D10</f>
+        <v/>
+      </c>
+      <c r="E22" s="96" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F22" s="96" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G22" s="105">
+        <f>IF(E22="","",'Bao gia'!J10)</f>
+        <v/>
+      </c>
+      <c r="H22" s="105">
+        <f>IF(F22="","",'Bao gia'!K10)</f>
+        <v/>
+      </c>
+      <c r="I22" s="96">
+        <f>IF(E22="",0,D22*(E22+F22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="96">
+        <f>IF(E22="",0,D22*(G22+H22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="96">
+        <f>J22-I22</f>
+        <v/>
+      </c>
+      <c r="L22" s="97">
+        <f>IF(I22=0,"",K22/I22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="106">
+        <f>'Bao gia'!G10</f>
+        <v/>
+      </c>
+      <c r="N22" s="96">
+        <f>'Bao gia'!E10</f>
+        <v/>
+      </c>
+      <c r="O22" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P22" s="103" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="102" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="103" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN50</t>
+        </is>
+      </c>
+      <c r="C23" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D23" s="104">
+        <f>'Bao gia'!D11</f>
+        <v/>
+      </c>
+      <c r="E23" s="96" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F23" s="96" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G23" s="105">
+        <f>IF(E23="","",'Bao gia'!J11)</f>
+        <v/>
+      </c>
+      <c r="H23" s="105">
+        <f>IF(F23="","",'Bao gia'!K11)</f>
+        <v/>
+      </c>
+      <c r="I23" s="96">
+        <f>IF(E23="",0,D23*(E23+F23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="96">
+        <f>IF(E23="",0,D23*(G23+H23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="96">
+        <f>J23-I23</f>
+        <v/>
+      </c>
+      <c r="L23" s="97">
+        <f>IF(I23=0,"",K23/I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="106">
+        <f>'Bao gia'!G11</f>
+        <v/>
+      </c>
+      <c r="N23" s="96">
+        <f>'Bao gia'!E11</f>
+        <v/>
+      </c>
+      <c r="O23" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P23" s="103" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="102" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="103" t="inlineStr">
+        <is>
+          <t>Tê thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C24" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D24" s="104">
+        <f>'Bao gia'!D12</f>
+        <v/>
+      </c>
+      <c r="E24" s="96" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F24" s="96" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G24" s="105">
+        <f>IF(E24="","",'Bao gia'!J12)</f>
+        <v/>
+      </c>
+      <c r="H24" s="105">
+        <f>IF(F24="","",'Bao gia'!K12)</f>
+        <v/>
+      </c>
+      <c r="I24" s="96">
+        <f>IF(E24="",0,D24*(E24+F24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="96">
+        <f>IF(E24="",0,D24*(G24+H24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="96">
+        <f>J24-I24</f>
+        <v/>
+      </c>
+      <c r="L24" s="97">
+        <f>IF(I24=0,"",K24/I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="106">
+        <f>'Bao gia'!G12</f>
+        <v/>
+      </c>
+      <c r="N24" s="96">
+        <f>'Bao gia'!E12</f>
+        <v/>
+      </c>
+      <c r="O24" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P24" s="103" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="102" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="103" t="inlineStr">
+        <is>
+          <t>Tê giảm thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C25" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D25" s="104">
+        <f>'Bao gia'!D13</f>
+        <v/>
+      </c>
+      <c r="E25" s="96" t="n">
+        <v>190000</v>
+      </c>
+      <c r="F25" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G25" s="105">
+        <f>IF(E25="","",'Bao gia'!J13)</f>
+        <v/>
+      </c>
+      <c r="H25" s="105">
+        <f>IF(F25="","",'Bao gia'!K13)</f>
+        <v/>
+      </c>
+      <c r="I25" s="96">
+        <f>IF(E25="",0,D25*(E25+F25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="96">
+        <f>IF(E25="",0,D25*(G25+H25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="96">
+        <f>J25-I25</f>
+        <v/>
+      </c>
+      <c r="L25" s="97">
+        <f>IF(I25=0,"",K25/I25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="106">
+        <f>'Bao gia'!G13</f>
+        <v/>
+      </c>
+      <c r="N25" s="96">
+        <f>'Bao gia'!E13</f>
+        <v/>
+      </c>
+      <c r="O25" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Tê giảm thép hàn DN65/50'</t>
+        </is>
+      </c>
+      <c r="P25" s="103" t="inlineStr">
+        <is>
+          <t>Sai giá ( gấp 10 lân)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="102" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="103" t="inlineStr">
+        <is>
+          <t>Tê thép hàn tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C26" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D26" s="104">
+        <f>'Bao gia'!D14</f>
+        <v/>
+      </c>
+      <c r="E26" s="96" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F26" s="96" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G26" s="105">
+        <f>IF(E26="","",'Bao gia'!J14)</f>
+        <v/>
+      </c>
+      <c r="H26" s="105">
+        <f>IF(F26="","",'Bao gia'!K14)</f>
+        <v/>
+      </c>
+      <c r="I26" s="96">
+        <f>IF(E26="",0,D26*(E26+F26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="96">
+        <f>IF(E26="",0,D26*(G26+H26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="96">
+        <f>J26-I26</f>
+        <v/>
+      </c>
+      <c r="L26" s="97">
+        <f>IF(I26=0,"",K26/I26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="106">
+        <f>'Bao gia'!G14</f>
+        <v/>
+      </c>
+      <c r="N26" s="96">
+        <f>'Bao gia'!E14</f>
+        <v/>
+      </c>
+      <c r="O26" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P26" s="103" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="102" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="103" t="inlineStr">
+        <is>
+          <t>Tê giảm thép hàn DN100/65</t>
+        </is>
+      </c>
+      <c r="C27" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D27" s="104">
+        <f>'Bao gia'!D15</f>
+        <v/>
+      </c>
+      <c r="E27" s="96" t="n">
+        <v>245000</v>
+      </c>
+      <c r="F27" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G27" s="105">
+        <f>IF(E27="","",'Bao gia'!J15)</f>
+        <v/>
+      </c>
+      <c r="H27" s="105">
+        <f>IF(F27="","",'Bao gia'!K15)</f>
+        <v/>
+      </c>
+      <c r="I27" s="96">
+        <f>IF(E27="",0,D27*(E27+F27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="96">
+        <f>IF(E27="",0,D27*(G27+H27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="96">
+        <f>J27-I27</f>
+        <v/>
+      </c>
+      <c r="L27" s="97">
+        <f>IF(I27=0,"",K27/I27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="106">
+        <f>'Bao gia'!G15</f>
+        <v/>
+      </c>
+      <c r="N27" s="96">
+        <f>'Bao gia'!E15</f>
+        <v/>
+      </c>
+      <c r="O27" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P27" s="103" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="102" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="103" t="inlineStr">
+        <is>
+          <t>Tê giảm thép hàn DN65/50</t>
+        </is>
+      </c>
+      <c r="C28" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D28" s="104">
+        <f>'Bao gia'!D16</f>
+        <v/>
+      </c>
+      <c r="E28" s="96" t="n">
+        <v>190000</v>
+      </c>
+      <c r="F28" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G28" s="105">
+        <f>IF(E28="","",'Bao gia'!J16)</f>
+        <v/>
+      </c>
+      <c r="H28" s="105">
+        <f>IF(F28="","",'Bao gia'!K16)</f>
+        <v/>
+      </c>
+      <c r="I28" s="96">
+        <f>IF(E28="",0,D28*(E28+F28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="96">
+        <f>IF(E28="",0,D28*(G28+H28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="96">
+        <f>J28-I28</f>
+        <v/>
+      </c>
+      <c r="L28" s="97">
+        <f>IF(I28=0,"",K28/I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="106">
+        <f>'Bao gia'!G16</f>
+        <v/>
+      </c>
+      <c r="N28" s="96">
+        <f>'Bao gia'!E16</f>
+        <v/>
+      </c>
+      <c r="O28" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P28" s="103" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="102" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="103" t="inlineStr">
+        <is>
+          <t>Côn giảm thép hàn DN80/65</t>
+        </is>
+      </c>
+      <c r="C29" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D29" s="104">
+        <f>'Bao gia'!D17</f>
+        <v/>
+      </c>
+      <c r="E29" s="96" t="n">
+        <v>231000</v>
+      </c>
+      <c r="F29" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G29" s="105">
+        <f>IF(E29="","",'Bao gia'!J17)</f>
+        <v/>
+      </c>
+      <c r="H29" s="105">
+        <f>IF(F29="","",'Bao gia'!K17)</f>
+        <v/>
+      </c>
+      <c r="I29" s="96">
+        <f>IF(E29="",0,D29*(E29+F29))</f>
+        <v/>
+      </c>
+      <c r="J29" s="96">
+        <f>IF(E29="",0,D29*(G29+H29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="96">
+        <f>J29-I29</f>
+        <v/>
+      </c>
+      <c r="L29" s="97">
+        <f>IF(I29=0,"",K29/I29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="106">
+        <f>'Bao gia'!G17</f>
+        <v/>
+      </c>
+      <c r="N29" s="96">
+        <f>'Bao gia'!E17</f>
+        <v/>
+      </c>
+      <c r="O29" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P29" s="103" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="102" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="103" t="inlineStr">
+        <is>
+          <t>Mặt bích thép DN80</t>
+        </is>
+      </c>
+      <c r="C30" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D30" s="104">
+        <f>'Bao gia'!D18</f>
+        <v/>
+      </c>
+      <c r="E30" s="96" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F30" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G30" s="105">
+        <f>IF(E30="","",'Bao gia'!J18)</f>
+        <v/>
+      </c>
+      <c r="H30" s="105">
+        <f>IF(F30="","",'Bao gia'!K18)</f>
+        <v/>
+      </c>
+      <c r="I30" s="96">
+        <f>IF(E30="",0,D30*(E30+F30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="96">
+        <f>IF(E30="",0,D30*(G30+H30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="96">
+        <f>J30-I30</f>
+        <v/>
+      </c>
+      <c r="L30" s="97">
+        <f>IF(I30=0,"",K30/I30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="106">
+        <f>'Bao gia'!G18</f>
+        <v/>
+      </c>
+      <c r="N30" s="96">
+        <f>'Bao gia'!E18</f>
+        <v/>
+      </c>
+      <c r="O30" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P30" s="103" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="102" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="103" t="inlineStr">
+        <is>
+          <t>Roăng su DN80</t>
+        </is>
+      </c>
+      <c r="C31" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D31" s="104">
+        <f>'Bao gia'!D19</f>
+        <v/>
+      </c>
+      <c r="E31" s="96" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F31" s="96" t="n">
+        <v>11538</v>
+      </c>
+      <c r="G31" s="105">
+        <f>IF(E31="","",'Bao gia'!J19)</f>
+        <v/>
+      </c>
+      <c r="H31" s="105">
+        <f>IF(F31="","",'Bao gia'!K19)</f>
+        <v/>
+      </c>
+      <c r="I31" s="96">
+        <f>IF(E31="",0,D31*(E31+F31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="96">
+        <f>IF(E31="",0,D31*(G31+H31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="96">
+        <f>J31-I31</f>
+        <v/>
+      </c>
+      <c r="L31" s="97">
+        <f>IF(I31=0,"",K31/I31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="106">
+        <f>'Bao gia'!G19</f>
+        <v/>
+      </c>
+      <c r="N31" s="96">
+        <f>'Bao gia'!E19</f>
+        <v/>
+      </c>
+      <c r="O31" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P31" s="103" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="102" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="103">
+        <f>'[1]ĐƠN GIÁ'!B53</f>
+        <v/>
+      </c>
+      <c r="C32" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D32" s="104">
+        <f>'Bao gia'!D20</f>
+        <v/>
+      </c>
+      <c r="E32" s="96" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F32" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G32" s="105">
+        <f>IF(E32="","",'Bao gia'!J20)</f>
+        <v/>
+      </c>
+      <c r="H32" s="105">
+        <f>IF(F32="","",'Bao gia'!K20)</f>
+        <v/>
+      </c>
+      <c r="I32" s="96">
+        <f>IF(E32="",0,D32*(E32+F32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="96">
+        <f>IF(E32="",0,D32*(G32+H32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="96">
+        <f>J32-I32</f>
+        <v/>
+      </c>
+      <c r="L32" s="97">
+        <f>IF(I32=0,"",K32/I32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="106">
+        <f>'Bao gia'!G20</f>
+        <v/>
+      </c>
+      <c r="N32" s="96">
+        <f>'Bao gia'!E20</f>
+        <v/>
+      </c>
+      <c r="O32" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P32" s="103" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="102" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="103" t="inlineStr">
+        <is>
+          <t>Rơ le kiểm tra mực nước</t>
+        </is>
+      </c>
+      <c r="C33" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D33" s="104">
+        <f>'Bao gia'!D21</f>
+        <v/>
+      </c>
+      <c r="E33" s="96" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="F33" s="96" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G33" s="105">
+        <f>IF(E33="","",'Bao gia'!J21)</f>
+        <v/>
+      </c>
+      <c r="H33" s="105">
+        <f>IF(F33="","",'Bao gia'!K21)</f>
+        <v/>
+      </c>
+      <c r="I33" s="96">
+        <f>IF(E33="",0,D33*(E33+F33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="96">
+        <f>IF(E33="",0,D33*(G33+H33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="96">
+        <f>J33-I33</f>
+        <v/>
+      </c>
+      <c r="L33" s="97">
+        <f>IF(I33=0,"",K33/I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="106">
+        <f>'Bao gia'!G21</f>
+        <v/>
+      </c>
+      <c r="N33" s="96">
+        <f>'Bao gia'!E21</f>
+        <v/>
+      </c>
+      <c r="O33" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P33" s="103" t="inlineStr">
+        <is>
+          <t>Thiếu báo giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="102" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="103" t="inlineStr">
+        <is>
+          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
+        </is>
+      </c>
+      <c r="C34" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D34" s="104">
+        <f>'Bao gia'!D22</f>
+        <v/>
+      </c>
+      <c r="E34" s="96" t="n">
+        <v>368000</v>
+      </c>
+      <c r="F34" s="96" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G34" s="105">
+        <f>IF(E34="","",'Bao gia'!J22)</f>
+        <v/>
+      </c>
+      <c r="H34" s="105">
+        <f>IF(F34="","",'Bao gia'!K22)</f>
+        <v/>
+      </c>
+      <c r="I34" s="96">
+        <f>IF(E34="",0,D34*(E34+F34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="96">
+        <f>IF(E34="",0,D34*(G34+H34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="96">
+        <f>J34-I34</f>
+        <v/>
+      </c>
+      <c r="L34" s="97">
+        <f>IF(I34=0,"",K34/I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="106">
+        <f>'Bao gia'!G22</f>
+        <v/>
+      </c>
+      <c r="N34" s="96">
+        <f>'Bao gia'!E22</f>
+        <v/>
+      </c>
+      <c r="O34" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P34" s="103" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="102" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="103" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
+        </is>
+      </c>
+      <c r="C35" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D35" s="104">
+        <f>'Bao gia'!D23</f>
+        <v/>
+      </c>
+      <c r="E35" s="96" t="n">
+        <v>514286</v>
+      </c>
+      <c r="F35" s="96" t="n">
+        <v>58022</v>
+      </c>
+      <c r="G35" s="105">
+        <f>IF(E35="","",'Bao gia'!J23)</f>
+        <v/>
+      </c>
+      <c r="H35" s="105">
+        <f>IF(F35="","",'Bao gia'!K23)</f>
+        <v/>
+      </c>
+      <c r="I35" s="96">
+        <f>IF(E35="",0,D35*(E35+F35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="96">
+        <f>IF(E35="",0,D35*(G35+H35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="96">
+        <f>J35-I35</f>
+        <v/>
+      </c>
+      <c r="L35" s="97">
+        <f>IF(I35=0,"",K35/I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="106">
+        <f>'Bao gia'!G23</f>
+        <v/>
+      </c>
+      <c r="N35" s="96">
+        <f>'Bao gia'!E23</f>
+        <v/>
+      </c>
+      <c r="O35" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần vòi</t>
+        </is>
+      </c>
+      <c r="P35" s="103" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="102" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="103" t="inlineStr">
+        <is>
+          <t>Lăng phun DN50</t>
+        </is>
+      </c>
+      <c r="C36" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D36" s="104">
+        <f>'Bao gia'!D24</f>
+        <v/>
+      </c>
+      <c r="E36" s="96" t="n">
+        <v>85714</v>
+      </c>
+      <c r="F36" s="96" t="n">
+        <v>9670</v>
+      </c>
+      <c r="G36" s="105">
+        <f>IF(E36="","",'Bao gia'!J24)</f>
+        <v/>
+      </c>
+      <c r="H36" s="105">
+        <f>IF(F36="","",'Bao gia'!K24)</f>
+        <v/>
+      </c>
+      <c r="I36" s="96">
+        <f>IF(E36="",0,D36*(E36+F36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="96">
+        <f>IF(E36="",0,D36*(G36+H36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="96">
+        <f>J36-I36</f>
+        <v/>
+      </c>
+      <c r="L36" s="97">
+        <f>IF(I36=0,"",K36/I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="106">
+        <f>'Bao gia'!G24</f>
+        <v/>
+      </c>
+      <c r="N36" s="96">
+        <f>'Bao gia'!E24</f>
+        <v/>
+      </c>
+      <c r="O36" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần lăng</t>
+        </is>
+      </c>
+      <c r="P36" s="103" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="102" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="103" t="inlineStr">
+        <is>
+          <t>Van góc FUJI DN50</t>
+        </is>
+      </c>
+      <c r="C37" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D37" s="104">
+        <f>'Bao gia'!D25</f>
+        <v/>
+      </c>
+      <c r="E37" s="96" t="n">
+        <v>166000</v>
+      </c>
+      <c r="F37" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G37" s="105">
+        <f>IF(E37="","",'Bao gia'!J25)</f>
+        <v/>
+      </c>
+      <c r="H37" s="105">
+        <f>IF(F37="","",'Bao gia'!K25)</f>
+        <v/>
+      </c>
+      <c r="I37" s="96">
+        <f>IF(E37="",0,D37*(E37+F37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="96">
+        <f>IF(E37="",0,D37*(G37+H37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="96">
+        <f>J37-I37</f>
+        <v/>
+      </c>
+      <c r="L37" s="97">
+        <f>IF(I37=0,"",K37/I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="106">
+        <f>'Bao gia'!G25</f>
+        <v/>
+      </c>
+      <c r="N37" s="96">
+        <f>'Bao gia'!E25</f>
+        <v/>
+      </c>
+      <c r="O37" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P37" s="103" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="102" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="103" t="inlineStr">
+        <is>
+          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
+        </is>
+      </c>
+      <c r="C38" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D38" s="104">
+        <f>'Bao gia'!D26</f>
+        <v/>
+      </c>
+      <c r="E38" s="96" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F38" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G38" s="105">
+        <f>IF(E38="","",'Bao gia'!J26)</f>
+        <v/>
+      </c>
+      <c r="H38" s="105">
+        <f>IF(F38="","",'Bao gia'!K26)</f>
+        <v/>
+      </c>
+      <c r="I38" s="96">
+        <f>IF(E38="",0,D38*(E38+F38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="96">
+        <f>IF(E38="",0,D38*(G38+H38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="96">
+        <f>J38-I38</f>
+        <v/>
+      </c>
+      <c r="L38" s="97">
+        <f>IF(I38=0,"",K38/I38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="106">
+        <f>'Bao gia'!G26</f>
+        <v/>
+      </c>
+      <c r="N38" s="96">
+        <f>'Bao gia'!E26</f>
+        <v/>
+      </c>
+      <c r="O38" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P38" s="103" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="102" t="n">
+        <v>24</v>
+      </c>
+      <c r="B39" s="103" t="inlineStr">
+        <is>
+          <t>Kệ đỡ bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="C39" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D39" s="104">
+        <f>'Bao gia'!D27</f>
+        <v/>
+      </c>
+      <c r="E39" s="96" t="n">
+        <v>137000</v>
+      </c>
+      <c r="F39" s="96" t="n">
+        <v>31538</v>
+      </c>
+      <c r="G39" s="105">
+        <f>IF(E39="","",'Bao gia'!J27)</f>
+        <v/>
+      </c>
+      <c r="H39" s="105">
+        <f>IF(F39="","",'Bao gia'!K27)</f>
+        <v/>
+      </c>
+      <c r="I39" s="96">
+        <f>IF(E39="",0,D39*(E39+F39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="96">
+        <f>IF(E39="",0,D39*(G39+H39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="96">
+        <f>J39-I39</f>
+        <v/>
+      </c>
+      <c r="L39" s="97">
+        <f>IF(I39=0,"",K39/I39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="106">
+        <f>'Bao gia'!G27</f>
+        <v/>
+      </c>
+      <c r="N39" s="96">
+        <f>'Bao gia'!E27</f>
+        <v/>
+      </c>
+      <c r="O39" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P39" s="103" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="102" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" s="103" t="inlineStr">
+        <is>
+          <t>BÌNH BỘT ABC 8KG</t>
+        </is>
+      </c>
+      <c r="C40" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D40" s="104">
+        <f>'Bao gia'!D28</f>
+        <v/>
+      </c>
+      <c r="E40" s="96" t="n">
+        <v>652000</v>
+      </c>
+      <c r="F40" s="96" t="n">
+        <v>10769</v>
+      </c>
+      <c r="G40" s="105">
+        <f>IF(E40="","",'Bao gia'!J28)</f>
+        <v/>
+      </c>
+      <c r="H40" s="105">
+        <f>IF(F40="","",'Bao gia'!K28)</f>
+        <v/>
+      </c>
+      <c r="I40" s="96">
+        <f>IF(E40="",0,D40*(E40+F40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="96">
+        <f>IF(E40="",0,D40*(G40+H40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="96">
+        <f>J40-I40</f>
+        <v/>
+      </c>
+      <c r="L40" s="97">
+        <f>IF(I40=0,"",K40/I40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="106">
+        <f>'Bao gia'!G28</f>
+        <v/>
+      </c>
+      <c r="N40" s="96">
+        <f>'Bao gia'!E28</f>
+        <v/>
+      </c>
+      <c r="O40" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P40" s="103" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="102" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="103" t="inlineStr">
+        <is>
+          <t>Đèn exit</t>
+        </is>
+      </c>
+      <c r="C41" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D41" s="104">
+        <f>'Bao gia'!D29</f>
+        <v/>
+      </c>
+      <c r="E41" s="96" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F41" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G41" s="105">
+        <f>IF(E41="","",'Bao gia'!J29)</f>
+        <v/>
+      </c>
+      <c r="H41" s="105">
+        <f>IF(F41="","",'Bao gia'!K29)</f>
+        <v/>
+      </c>
+      <c r="I41" s="96">
+        <f>IF(E41="",0,D41*(E41+F41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="96">
+        <f>IF(E41="",0,D41*(G41+H41))</f>
+        <v/>
+      </c>
+      <c r="K41" s="96">
+        <f>J41-I41</f>
+        <v/>
+      </c>
+      <c r="L41" s="97">
+        <f>IF(I41=0,"",K41/I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="106">
+        <f>'Bao gia'!G29</f>
+        <v/>
+      </c>
+      <c r="N41" s="96">
+        <f>'Bao gia'!E29</f>
+        <v/>
+      </c>
+      <c r="O41" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P41" s="103" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="102" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="103" t="inlineStr">
+        <is>
+          <t>Đèn chiếu sáng sự cố</t>
+        </is>
+      </c>
+      <c r="C42" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D42" s="104">
+        <f>'Bao gia'!D30</f>
+        <v/>
+      </c>
+      <c r="E42" s="96" t="n">
+        <v>190000</v>
+      </c>
+      <c r="F42" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G42" s="105">
+        <f>IF(E42="","",'Bao gia'!J30)</f>
+        <v/>
+      </c>
+      <c r="H42" s="105">
+        <f>IF(F42="","",'Bao gia'!K30)</f>
+        <v/>
+      </c>
+      <c r="I42" s="96">
+        <f>IF(E42="",0,D42*(E42+F42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="96">
+        <f>IF(E42="",0,D42*(G42+H42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="96">
+        <f>J42-I42</f>
+        <v/>
+      </c>
+      <c r="L42" s="97">
+        <f>IF(I42=0,"",K42/I42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="106">
+        <f>'Bao gia'!G30</f>
+        <v/>
+      </c>
+      <c r="N42" s="96">
+        <f>'Bao gia'!E30</f>
+        <v/>
+      </c>
+      <c r="O42" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P42" s="103" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="102" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="103" t="inlineStr">
+        <is>
+          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
+        </is>
+      </c>
+      <c r="C43" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D43" s="104">
+        <f>'Bao gia'!D32</f>
+        <v/>
+      </c>
+      <c r="E43" s="96" t="n">
+        <v>442000</v>
+      </c>
+      <c r="F43" s="96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G43" s="105">
+        <f>IF(E43="","",'Bao gia'!J32)</f>
+        <v/>
+      </c>
+      <c r="H43" s="105">
+        <f>IF(F43="","",'Bao gia'!K32)</f>
+        <v/>
+      </c>
+      <c r="I43" s="96">
+        <f>IF(E43="",0,D43*(E43+F43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="96">
+        <f>IF(E43="",0,D43*(G43+H43))</f>
+        <v/>
+      </c>
+      <c r="K43" s="96">
+        <f>J43-I43</f>
+        <v/>
+      </c>
+      <c r="L43" s="97">
+        <f>IF(I43=0,"",K43/I43)</f>
+        <v/>
+      </c>
+      <c r="M43" s="106">
+        <f>'Bao gia'!G32</f>
+        <v/>
+      </c>
+      <c r="N43" s="96">
+        <f>'Bao gia'!E32</f>
+        <v/>
+      </c>
+      <c r="O43" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P43" s="103" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="102" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="103" t="inlineStr">
+        <is>
+          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
+        </is>
+      </c>
+      <c r="C44" s="102" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D44" s="104">
+        <f>'Bao gia'!D33</f>
+        <v/>
+      </c>
+      <c r="E44" s="96" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="F44" s="96" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G44" s="105">
+        <f>IF(E44="","",'Bao gia'!J33)</f>
+        <v/>
+      </c>
+      <c r="H44" s="105">
+        <f>IF(F44="","",'Bao gia'!K33)</f>
+        <v/>
+      </c>
+      <c r="I44" s="96">
+        <f>IF(E44="",0,D44*(E44+F44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="96">
+        <f>IF(E44="",0,D44*(G44+H44))</f>
+        <v/>
+      </c>
+      <c r="K44" s="96">
+        <f>J44-I44</f>
+        <v/>
+      </c>
+      <c r="L44" s="97">
+        <f>IF(I44=0,"",K44/I44)</f>
+        <v/>
+      </c>
+      <c r="M44" s="106">
+        <f>'Bao gia'!G33</f>
+        <v/>
+      </c>
+      <c r="N44" s="96">
+        <f>'Bao gia'!E33</f>
+        <v/>
+      </c>
+      <c r="O44" s="103" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P44" s="103" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="107" t="n"/>
+      <c r="B45" s="107" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C45" s="107" t="n"/>
+      <c r="D45" s="107" t="n"/>
+      <c r="E45" s="107" t="n"/>
+      <c r="F45" s="107" t="n"/>
+      <c r="G45" s="107" t="n"/>
+      <c r="H45" s="107" t="n"/>
+      <c r="I45" s="99">
+        <f>SUM(I16:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="99">
+        <f>SUM(J16:J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="99">
+        <f>SUM(K16:K44)</f>
+        <v/>
+      </c>
+      <c r="L45" s="100">
+        <f>IF(I45=0,"",K45/I45)</f>
+        <v/>
+      </c>
+      <c r="M45" s="107" t="n"/>
+      <c r="N45" s="107" t="n"/>
+      <c r="O45" s="107" t="n"/>
+      <c r="P45" s="107" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="108" t="inlineStr">
+        <is>
+          <t>GHI CHÚ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="B48" s="109" t="inlineStr">
+        <is>
+          <t>Khối lượng lấy theo cột D sheet 'Bao gia'. Máy bơm, bình, kệ, nội quy, sơ đồ lấy số lượng từ cột 'Tổng số lượng' sheet tb (đã điền công thức cộng các trường). Sheet tb dùng chung giá đề xuất với sheet 'Bao gia'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="B49" s="109" t="inlineStr">
+        <is>
+          <t>Không có giá vốn nên chưa tính: Đèn báo trạm bơm</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="B50" s="109" t="inlineStr">
+        <is>
+          <t>Báo giá chỉ gồm thiết bị và phụ kiện; chưa gồm ống thép, cáp tín hiệu, ống luồn, van, vật tư phụ 5% và phần xây dựng có trong sheet 'Gia von chi tiet'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B48:P48"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B13:P13"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B49:P49"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B50:P50"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:P47"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Báo giá 2.xlsx
+++ b/Báo giá 2.xlsx
@@ -22,12 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.##"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.##"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,6 +135,10 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="15"/>
     </font>
@@ -148,7 +154,13 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <sz val="14"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -157,29 +169,16 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="14"/>
+      <i val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
+      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -216,6 +215,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -264,14 +268,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -283,7 +287,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,75 +467,119 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -913,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="12" min="1" max="1"/>
@@ -929,14 +977,9 @@
     <col width="12.28515625" bestFit="1" customWidth="1" style="29" min="12" max="12"/>
     <col width="15.28515625" customWidth="1" min="13" max="13"/>
     <col width="8.85546875" customWidth="1" style="51" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -950,6 +993,8 @@
       <c r="O1" s="82" t="n"/>
       <c r="P1" s="82" t="n"/>
       <c r="Q1" s="82" t="n"/>
+      <c r="R1" s="82" t="n"/>
+      <c r="S1" s="82" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="59">
@@ -961,6 +1006,8 @@
       <c r="O2" s="82" t="n"/>
       <c r="P2" s="82" t="n"/>
       <c r="Q2" s="82" t="n"/>
+      <c r="R2" s="82" t="n"/>
+      <c r="S2" s="82" t="n"/>
     </row>
     <row r="3" ht="37.5" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="4" t="inlineStr">
@@ -1015,15 +1062,17 @@
       </c>
       <c r="O3" s="83" t="inlineStr">
         <is>
-          <t>Giá vật tư đề xuất (trước thuế)</t>
+          <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="P3" s="83" t="inlineStr">
         <is>
-          <t>Giá nhân công đề xuất (trước thuế)</t>
+          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
       <c r="Q3" s="82" t="n"/>
+      <c r="R3" s="82" t="n"/>
+      <c r="S3" s="82" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -1051,6 +1100,8 @@
       <c r="O4" s="84" t="n"/>
       <c r="P4" s="84" t="n"/>
       <c r="Q4" s="82" t="n"/>
+      <c r="R4" s="82" t="n"/>
+      <c r="S4" s="82" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -1097,14 +1148,16 @@
         </is>
       </c>
       <c r="O5" s="86">
-        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="P5" s="86">
-        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H84</f>
+        <v/>
+      </c>
+      <c r="P5" s="87">
+        <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
       <c r="Q5" s="82" t="n"/>
+      <c r="R5" s="82" t="n"/>
+      <c r="S5" s="82" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -1153,14 +1206,16 @@
         </is>
       </c>
       <c r="O6" s="86">
-        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="P6" s="86">
-        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H85</f>
+        <v/>
+      </c>
+      <c r="P6" s="87">
+        <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
       <c r="Q6" s="82" t="n"/>
+      <c r="R6" s="82" t="n"/>
+      <c r="S6" s="82" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -1209,14 +1264,16 @@
         </is>
       </c>
       <c r="O7" s="86">
-        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="P7" s="86">
-        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H86</f>
+        <v/>
+      </c>
+      <c r="P7" s="87">
+        <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
       <c r="Q7" s="82" t="n"/>
+      <c r="R7" s="82" t="n"/>
+      <c r="S7" s="82" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -1271,14 +1328,16 @@
         </is>
       </c>
       <c r="O8" s="86">
-        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="P8" s="86">
-        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H89</f>
+        <v/>
+      </c>
+      <c r="P8" s="87">
+        <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
       <c r="Q8" s="82" t="n"/>
+      <c r="R8" s="82" t="n"/>
+      <c r="S8" s="82" t="n"/>
     </row>
     <row r="9" ht="18.75" customFormat="1" customHeight="1" s="10">
       <c r="A9" s="35" t="n"/>
@@ -1315,6 +1374,8 @@
       <c r="O9" s="84" t="n"/>
       <c r="P9" s="84" t="n"/>
       <c r="Q9" s="82" t="n"/>
+      <c r="R9" s="82" t="n"/>
+      <c r="S9" s="82" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="B10" s="36" t="inlineStr">
@@ -1340,12 +1401,16 @@
       <c r="O10" s="84" t="n"/>
       <c r="P10" s="84" t="n"/>
       <c r="Q10" s="82" t="n"/>
+      <c r="R10" s="82" t="n"/>
+      <c r="S10" s="82" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="B11" s="36" t="n"/>
       <c r="O11" s="82" t="n"/>
       <c r="P11" s="82" t="n"/>
       <c r="Q11" s="82" t="n"/>
+      <c r="R11" s="82" t="n"/>
+      <c r="S11" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1363,7 +1428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="17.25"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="18" min="1" max="1"/>
@@ -1375,14 +1440,10 @@
     <col width="16" customWidth="1" style="53" min="7" max="7"/>
     <col width="15.5703125" customWidth="1" style="46" min="8" max="8"/>
     <col width="10.85546875" customWidth="1" style="1" min="9" max="9"/>
-    <col width="20" customWidth="1" style="1" min="10" max="16384"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1395,6 +1456,7 @@
       <c r="K1" s="82" t="n"/>
       <c r="L1" s="82" t="n"/>
       <c r="M1" s="82" t="n"/>
+      <c r="N1" s="82" t="n"/>
     </row>
     <row r="2" ht="44.25" customHeight="1">
       <c r="A2" s="61">
@@ -1405,6 +1467,7 @@
       <c r="K2" s="82" t="n"/>
       <c r="L2" s="82" t="n"/>
       <c r="M2" s="82" t="n"/>
+      <c r="N2" s="82" t="n"/>
     </row>
     <row r="3" ht="37.5" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -1454,16 +1517,17 @@
       </c>
       <c r="J3" s="83" t="inlineStr">
         <is>
-          <t>Giá vật tư đề xuất (trước thuế)</t>
+          <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="K3" s="83" t="inlineStr">
         <is>
-          <t>Giá nhân công đề xuất (trước thuế)</t>
+          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
       <c r="L3" s="82" t="n"/>
       <c r="M3" s="82" t="n"/>
+      <c r="N3" s="82" t="n"/>
     </row>
     <row r="4" ht="37.5" customHeight="1">
       <c r="A4" s="15" t="n">
@@ -1502,15 +1566,16 @@
         </is>
       </c>
       <c r="J4" s="86">
-        <f>IF('Danh gia LN'!E16="","",ROUNDUP('Danh gia LN'!E16*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K4" s="86">
-        <f>IF('Danh gia LN'!F16="","",ROUNDUP('Danh gia LN'!F16*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H62</f>
+        <v/>
+      </c>
+      <c r="K4" s="87">
+        <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
       <c r="L4" s="82" t="n"/>
       <c r="M4" s="82" t="n"/>
+      <c r="N4" s="82" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="15" t="n">
@@ -1549,15 +1614,16 @@
         </is>
       </c>
       <c r="J5" s="86">
-        <f>IF('Danh gia LN'!E17="","",ROUNDUP('Danh gia LN'!E17*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K5" s="86">
-        <f>IF('Danh gia LN'!F17="","",ROUNDUP('Danh gia LN'!F17*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H63</f>
+        <v/>
+      </c>
+      <c r="K5" s="87">
+        <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
       <c r="L5" s="82" t="n"/>
       <c r="M5" s="82" t="n"/>
+      <c r="N5" s="82" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="15">
@@ -1597,15 +1663,16 @@
         </is>
       </c>
       <c r="J6" s="86">
-        <f>IF('Danh gia LN'!E18="","",ROUNDUP('Danh gia LN'!E18*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K6" s="86">
-        <f>IF('Danh gia LN'!F18="","",ROUNDUP('Danh gia LN'!F18*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H64</f>
+        <v/>
+      </c>
+      <c r="K6" s="87">
+        <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
       <c r="L6" s="82" t="n"/>
       <c r="M6" s="82" t="n"/>
+      <c r="N6" s="82" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="15">
@@ -1645,15 +1712,16 @@
         </is>
       </c>
       <c r="J7" s="86">
-        <f>IF('Danh gia LN'!E19="","",ROUNDUP('Danh gia LN'!E19*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K7" s="86">
-        <f>IF('Danh gia LN'!F19="","",ROUNDUP('Danh gia LN'!F19*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H65</f>
+        <v/>
+      </c>
+      <c r="K7" s="87">
+        <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
       <c r="L7" s="82" t="n"/>
       <c r="M7" s="82" t="n"/>
+      <c r="N7" s="82" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="15">
@@ -1693,15 +1761,16 @@
         </is>
       </c>
       <c r="J8" s="86">
-        <f>IF('Danh gia LN'!E20="","",ROUNDUP('Danh gia LN'!E20*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K8" s="86">
-        <f>IF('Danh gia LN'!F20="","",ROUNDUP('Danh gia LN'!F20*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H66</f>
+        <v/>
+      </c>
+      <c r="K8" s="87">
+        <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
       <c r="L8" s="82" t="n"/>
       <c r="M8" s="82" t="n"/>
+      <c r="N8" s="82" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="15">
@@ -1741,15 +1810,16 @@
         </is>
       </c>
       <c r="J9" s="86">
-        <f>IF('Danh gia LN'!E21="","",ROUNDUP('Danh gia LN'!E21*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K9" s="86">
-        <f>IF('Danh gia LN'!F21="","",ROUNDUP('Danh gia LN'!F21*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H67</f>
+        <v/>
+      </c>
+      <c r="K9" s="87">
+        <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
       <c r="L9" s="82" t="n"/>
       <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="15">
@@ -1789,15 +1859,16 @@
         </is>
       </c>
       <c r="J10" s="86">
-        <f>IF('Danh gia LN'!E22="","",ROUNDUP('Danh gia LN'!E22*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K10" s="86">
-        <f>IF('Danh gia LN'!F22="","",ROUNDUP('Danh gia LN'!F22*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H68</f>
+        <v/>
+      </c>
+      <c r="K10" s="87">
+        <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
       <c r="L10" s="82" t="n"/>
       <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="15">
@@ -1837,15 +1908,16 @@
         </is>
       </c>
       <c r="J11" s="86">
-        <f>IF('Danh gia LN'!E23="","",ROUNDUP('Danh gia LN'!E23*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K11" s="86">
-        <f>IF('Danh gia LN'!F23="","",ROUNDUP('Danh gia LN'!F23*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H69</f>
+        <v/>
+      </c>
+      <c r="K11" s="87">
+        <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
       <c r="L11" s="82" t="n"/>
       <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="15">
@@ -1885,15 +1957,16 @@
         </is>
       </c>
       <c r="J12" s="86">
-        <f>IF('Danh gia LN'!E24="","",ROUNDUP('Danh gia LN'!E24*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K12" s="86">
-        <f>IF('Danh gia LN'!F24="","",ROUNDUP('Danh gia LN'!F24*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H70</f>
+        <v/>
+      </c>
+      <c r="K12" s="87">
+        <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
       <c r="L12" s="82" t="n"/>
       <c r="M12" s="82" t="n"/>
+      <c r="N12" s="82" t="n"/>
     </row>
     <row r="13" ht="18.75" customFormat="1" customHeight="1" s="69">
       <c r="A13" s="62">
@@ -1933,15 +2006,16 @@
         </is>
       </c>
       <c r="J13" s="86">
-        <f>IF('Danh gia LN'!E25="","",ROUNDUP('Danh gia LN'!E25*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K13" s="86">
-        <f>IF('Danh gia LN'!F25="","",ROUNDUP('Danh gia LN'!F25*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H71</f>
+        <v/>
+      </c>
+      <c r="K13" s="87">
+        <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
       <c r="L13" s="82" t="n"/>
       <c r="M13" s="82" t="n"/>
+      <c r="N13" s="82" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="15">
@@ -1981,15 +2055,16 @@
         </is>
       </c>
       <c r="J14" s="86">
-        <f>IF('Danh gia LN'!E26="","",ROUNDUP('Danh gia LN'!E26*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K14" s="86">
-        <f>IF('Danh gia LN'!F26="","",ROUNDUP('Danh gia LN'!F26*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H72</f>
+        <v/>
+      </c>
+      <c r="K14" s="87">
+        <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
       <c r="L14" s="82" t="n"/>
       <c r="M14" s="82" t="n"/>
+      <c r="N14" s="82" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="15">
@@ -2029,15 +2104,16 @@
         </is>
       </c>
       <c r="J15" s="86">
-        <f>IF('Danh gia LN'!E27="","",ROUNDUP('Danh gia LN'!E27*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K15" s="86">
-        <f>IF('Danh gia LN'!F27="","",ROUNDUP('Danh gia LN'!F27*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H73</f>
+        <v/>
+      </c>
+      <c r="K15" s="87">
+        <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
       <c r="L15" s="82" t="n"/>
       <c r="M15" s="82" t="n"/>
+      <c r="N15" s="82" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="15">
@@ -2077,15 +2153,16 @@
         </is>
       </c>
       <c r="J16" s="86">
-        <f>IF('Danh gia LN'!E28="","",ROUNDUP('Danh gia LN'!E28*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K16" s="86">
-        <f>IF('Danh gia LN'!F28="","",ROUNDUP('Danh gia LN'!F28*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H74</f>
+        <v/>
+      </c>
+      <c r="K16" s="87">
+        <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
       <c r="L16" s="82" t="n"/>
       <c r="M16" s="82" t="n"/>
+      <c r="N16" s="82" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="15">
@@ -2125,15 +2202,16 @@
         </is>
       </c>
       <c r="J17" s="86">
-        <f>IF('Danh gia LN'!E29="","",ROUNDUP('Danh gia LN'!E29*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K17" s="86">
-        <f>IF('Danh gia LN'!F29="","",ROUNDUP('Danh gia LN'!F29*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H75</f>
+        <v/>
+      </c>
+      <c r="K17" s="87">
+        <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
       <c r="L17" s="82" t="n"/>
       <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="15">
@@ -2173,15 +2251,16 @@
         </is>
       </c>
       <c r="J18" s="86">
-        <f>IF('Danh gia LN'!E30="","",ROUNDUP('Danh gia LN'!E30*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K18" s="86">
-        <f>IF('Danh gia LN'!F30="","",ROUNDUP('Danh gia LN'!F30*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H76</f>
+        <v/>
+      </c>
+      <c r="K18" s="87">
+        <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
       <c r="L18" s="82" t="n"/>
       <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="15">
@@ -2221,15 +2300,16 @@
         </is>
       </c>
       <c r="J19" s="86">
-        <f>IF('Danh gia LN'!E31="","",ROUNDUP('Danh gia LN'!E31*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K19" s="86">
-        <f>IF('Danh gia LN'!F31="","",ROUNDUP('Danh gia LN'!F31*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H77</f>
+        <v/>
+      </c>
+      <c r="K19" s="87">
+        <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
       <c r="L19" s="82" t="n"/>
       <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="15">
@@ -2268,15 +2348,16 @@
         </is>
       </c>
       <c r="J20" s="86">
-        <f>IF('Danh gia LN'!E32="","",ROUNDUP('Danh gia LN'!E32*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K20" s="86">
-        <f>IF('Danh gia LN'!F32="","",ROUNDUP('Danh gia LN'!F32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H78</f>
+        <v/>
+      </c>
+      <c r="K20" s="87">
+        <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
       <c r="L20" s="82" t="n"/>
       <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
     </row>
     <row r="21" ht="18.75" customFormat="1" customHeight="1" s="69">
       <c r="A21" s="62">
@@ -2314,15 +2395,16 @@
         </is>
       </c>
       <c r="J21" s="86">
-        <f>IF('Danh gia LN'!E33="","",ROUNDUP('Danh gia LN'!E33*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K21" s="86">
-        <f>IF('Danh gia LN'!F33="","",ROUNDUP('Danh gia LN'!F33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H79</f>
+        <v/>
+      </c>
+      <c r="K21" s="87">
+        <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
       <c r="L21" s="82" t="n"/>
       <c r="M21" s="82" t="n"/>
+      <c r="N21" s="82" t="n"/>
     </row>
     <row r="22" ht="37.5" customHeight="1">
       <c r="A22" s="15">
@@ -2362,15 +2444,16 @@
         </is>
       </c>
       <c r="J22" s="86">
-        <f>IF('Danh gia LN'!E34="","",ROUNDUP('Danh gia LN'!E34*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K22" s="86">
-        <f>IF('Danh gia LN'!F34="","",ROUNDUP('Danh gia LN'!F34*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H80</f>
+        <v/>
+      </c>
+      <c r="K22" s="87">
+        <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
       <c r="L22" s="82" t="n"/>
       <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
     </row>
     <row r="23" ht="37.5" customHeight="1">
       <c r="A23" s="15">
@@ -2410,15 +2493,16 @@
         </is>
       </c>
       <c r="J23" s="86">
-        <f>IF('Danh gia LN'!E35="","",ROUNDUP('Danh gia LN'!E35*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K23" s="86">
-        <f>IF('Danh gia LN'!F35="","",ROUNDUP('Danh gia LN'!F35*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H81</f>
+        <v/>
+      </c>
+      <c r="K23" s="87">
+        <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
       <c r="L23" s="82" t="n"/>
       <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="15">
@@ -2458,15 +2542,16 @@
         </is>
       </c>
       <c r="J24" s="86">
-        <f>IF('Danh gia LN'!E36="","",ROUNDUP('Danh gia LN'!E36*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K24" s="86">
-        <f>IF('Danh gia LN'!F36="","",ROUNDUP('Danh gia LN'!F36*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H82</f>
+        <v/>
+      </c>
+      <c r="K24" s="87">
+        <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
       <c r="L24" s="82" t="n"/>
       <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="15">
@@ -2506,15 +2591,16 @@
         </is>
       </c>
       <c r="J25" s="86">
-        <f>IF('Danh gia LN'!E37="","",ROUNDUP('Danh gia LN'!E37*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K25" s="86">
-        <f>IF('Danh gia LN'!F37="","",ROUNDUP('Danh gia LN'!F37*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H83</f>
+        <v/>
+      </c>
+      <c r="K25" s="87">
+        <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
       <c r="L25" s="82" t="n"/>
       <c r="M25" s="82" t="n"/>
+      <c r="N25" s="82" t="n"/>
     </row>
     <row r="26" ht="37.5" customHeight="1">
       <c r="A26" s="15">
@@ -2555,15 +2641,16 @@
         </is>
       </c>
       <c r="J26" s="86">
-        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K26" s="86">
-        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H84</f>
+        <v/>
+      </c>
+      <c r="K26" s="87">
+        <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
       <c r="L26" s="82" t="n"/>
       <c r="M26" s="82" t="n"/>
+      <c r="N26" s="82" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="15">
@@ -2604,15 +2691,16 @@
         </is>
       </c>
       <c r="J27" s="86">
-        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K27" s="86">
-        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H85</f>
+        <v/>
+      </c>
+      <c r="K27" s="87">
+        <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
       <c r="L27" s="82" t="n"/>
       <c r="M27" s="82" t="n"/>
+      <c r="N27" s="82" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="15">
@@ -2653,15 +2741,16 @@
         </is>
       </c>
       <c r="J28" s="86">
-        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K28" s="86">
-        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H86</f>
+        <v/>
+      </c>
+      <c r="K28" s="87">
+        <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
       <c r="L28" s="82" t="n"/>
       <c r="M28" s="82" t="n"/>
+      <c r="N28" s="82" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="15">
@@ -2701,15 +2790,16 @@
         </is>
       </c>
       <c r="J29" s="86">
-        <f>IF('Danh gia LN'!E41="","",ROUNDUP('Danh gia LN'!E41*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K29" s="86">
-        <f>IF('Danh gia LN'!F41="","",ROUNDUP('Danh gia LN'!F41*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H87</f>
+        <v/>
+      </c>
+      <c r="K29" s="87">
+        <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
       <c r="L29" s="82" t="n"/>
       <c r="M29" s="82" t="n"/>
+      <c r="N29" s="82" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="15">
@@ -2749,15 +2839,16 @@
         </is>
       </c>
       <c r="J30" s="86">
-        <f>IF('Danh gia LN'!E42="","",ROUNDUP('Danh gia LN'!E42*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K30" s="86">
-        <f>IF('Danh gia LN'!F42="","",ROUNDUP('Danh gia LN'!F42*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H88</f>
+        <v/>
+      </c>
+      <c r="K30" s="87">
+        <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
       <c r="L30" s="82" t="n"/>
       <c r="M30" s="82" t="n"/>
+      <c r="N30" s="82" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="15">
@@ -2796,6 +2887,7 @@
       <c r="K31" s="84" t="n"/>
       <c r="L31" s="82" t="n"/>
       <c r="M31" s="82" t="n"/>
+      <c r="N31" s="82" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="15">
@@ -2836,15 +2928,16 @@
         </is>
       </c>
       <c r="J32" s="86">
-        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K32" s="86">
-        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H89</f>
+        <v/>
+      </c>
+      <c r="K32" s="87">
+        <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
       <c r="L32" s="82" t="n"/>
       <c r="M32" s="82" t="n"/>
+      <c r="N32" s="82" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="15">
@@ -2884,15 +2977,16 @@
         </is>
       </c>
       <c r="J33" s="86">
-        <f>IF('Danh gia LN'!E44="","",ROUNDUP('Danh gia LN'!E44*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K33" s="86">
-        <f>IF('Danh gia LN'!F44="","",ROUNDUP('Danh gia LN'!F44*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H90</f>
+        <v/>
+      </c>
+      <c r="K33" s="87">
+        <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
       <c r="L33" s="82" t="n"/>
       <c r="M33" s="82" t="n"/>
+      <c r="N33" s="82" t="n"/>
     </row>
     <row r="34" customFormat="1" s="46">
       <c r="A34" s="41" t="n"/>
@@ -2918,6 +3012,7 @@
       <c r="K34" s="84" t="n"/>
       <c r="L34" s="82" t="n"/>
       <c r="M34" s="82" t="n"/>
+      <c r="N34" s="82" t="n"/>
     </row>
     <row r="35" customFormat="1" s="46">
       <c r="A35" s="41" t="n"/>
@@ -2940,6 +3035,7 @@
       <c r="K35" s="84" t="n"/>
       <c r="L35" s="82" t="n"/>
       <c r="M35" s="82" t="n"/>
+      <c r="N35" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2957,2237 +3053,3627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="87" t="inlineStr">
-        <is>
-          <t>ĐÁNH GIÁ LỢI NHUẬN THEO GIÁ ĐỀ XUẤT – TIỂU HỌC – THCS (5 TRƯỜNG)</t>
+      <c r="A1" s="88" t="inlineStr">
+        <is>
+          <t>ĐÁNH GIÁ GIÁ CHỐT PHẦN PCCC – HỆ THỐNG PCCC CÁC TRƯỜNG TIỂU HỌC, THCS PHƯỜNG ĐỒNG SƠN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
-        <is>
-          <t>Giá vốn lấy theo sheet 'Gia von chi tiet' (file Danh gia toan goi PCCC Dong Son). Giá đề xuất = giá vốn × (1 + tỷ lệ lợi nhuận), làm tròn lên hàng nghìn. Đơn giá trước thuế.</t>
+      <c r="A2" s="89" t="inlineStr">
+        <is>
+          <t>Chỉ điều chỉnh đơn giá vật tư/thiết bị có trong báo giá; nhân công theo định mức, các hạng mục khác giữ đơn giá dự toán. QLDA, tư vấn, nhà tạm, dự phòng tính lại theo công thức của bảng tổng dự toán. Giá vốn theo sheet 'Gia von chi tiet'.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="89" t="inlineStr">
-        <is>
-          <t>Tỷ lệ lợi nhuận mong muốn trên giá vốn (sửa ô này)</t>
-        </is>
-      </c>
-      <c r="C4" s="90" t="n"/>
-      <c r="D4" s="91" t="n">
-        <v>0.4</v>
+      <c r="B4" s="90" t="inlineStr">
+        <is>
+          <t>Lợi nhuận tối thiểu của bên thi công trên giá vốn PCCC</t>
+        </is>
+      </c>
+      <c r="C4" s="91" t="n"/>
+      <c r="D4" s="92" t="n"/>
+      <c r="E4" s="93" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="90" t="inlineStr">
+        <is>
+          <t>Tỷ lệ trích lại chủ đầu tư (trên tổng dự toán gói sau VAT, đã làm tròn)</t>
+        </is>
+      </c>
+      <c r="C5" s="91" t="n"/>
+      <c r="D5" s="92" t="n"/>
+      <c r="E5" s="93" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="92" t="inlineStr">
-        <is>
-          <t>TỔNG HỢP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B6" s="90" t="inlineStr">
+        <is>
+          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (làm tròn lên nghìn)</t>
+        </is>
+      </c>
+      <c r="C6" s="91" t="n"/>
+      <c r="D6" s="92" t="n"/>
+      <c r="E6" s="94" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F6" s="95" t="inlineStr">
+        <is>
+          <t>← giá trị nhỏ nhất đạt lợi nhuận tối thiểu (đã tính lặp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="90" t="inlineStr">
+        <is>
+          <t>Hệ số chi phí trực tiếp → chi phí xây dựng trước thuế: (1 + 7,3% + 2,5%) × (1 + 5,5%)</t>
+        </is>
+      </c>
+      <c r="C7" s="91" t="n"/>
+      <c r="D7" s="92" t="n"/>
+      <c r="E7" s="96">
+        <f>(1+7.3%+2.5%)*(1+5.5%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – nhập bằng tổng dự toán làm tròn</t>
+        </is>
+      </c>
+      <c r="C8" s="91" t="n"/>
+      <c r="D8" s="92" t="n"/>
+      <c r="E8" s="97" t="n">
+        <v>2394000000</v>
+      </c>
+      <c r="F8" s="98">
+        <f>IF($E$8=H34,"Khớp tổng làm tròn","⚠ Nhập lại E8 = "&amp;TEXT(H34,"#,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>A. TỔNG DỰ TOÁN GÓI – HIỆN TẠI VÀ SAU KHI CHỐT GIÁ PCCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="100" t="inlineStr">
+        <is>
+          <t>Khoản mục chi phí</t>
+        </is>
+      </c>
+      <c r="C11" s="100" t="inlineStr">
+        <is>
+          <t>Ký hiệu</t>
+        </is>
+      </c>
+      <c r="D11" s="100" t="inlineStr">
+        <is>
+          <t>Cách tính</t>
+        </is>
+      </c>
+      <c r="E11" s="100" t="inlineStr">
+        <is>
+          <t>Hiện tại (sau thuế)</t>
+        </is>
+      </c>
+      <c r="F11" s="100" t="inlineStr">
+        <is>
+          <t>Mới – trước thuế</t>
+        </is>
+      </c>
+      <c r="G11" s="100" t="inlineStr">
+        <is>
+          <t>Thuế VAT 8%</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
+        <is>
+          <t>MỚI – SAU THUẾ</t>
+        </is>
+      </c>
+      <c r="I11" s="100" t="inlineStr">
+        <is>
+          <t>Chênh (sau thuế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="101" t="inlineStr">
+        <is>
+          <t>Chi phí xây dựng phần PCCC (lắp đặt)</t>
+        </is>
+      </c>
+      <c r="C12" s="102" t="inlineStr">
+        <is>
+          <t>Gxdct1</t>
+        </is>
+      </c>
+      <c r="D12" s="101" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại + hệ số × chênh VT</t>
+        </is>
+      </c>
+      <c r="E12" s="103" t="n">
+        <v>1313010000</v>
+      </c>
+      <c r="F12" s="103">
+        <f>1215750394+SUM(O62:O90)</f>
+        <v/>
+      </c>
+      <c r="G12" s="103">
+        <f>F12*8%</f>
+        <v/>
+      </c>
+      <c r="H12" s="104">
+        <f>ROUND(F12+G12,-3)</f>
+        <v/>
+      </c>
+      <c r="I12" s="103">
+        <f>IF(E12="","",H12-E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="105" t="inlineStr">
+        <is>
+          <t>Xây lắp Trường tiểu học Nghĩa Ninh</t>
+        </is>
+      </c>
+      <c r="C13" s="106" t="inlineStr">
+        <is>
+          <t>Gxdct2</t>
+        </is>
+      </c>
+      <c r="D13" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E13" s="107" t="n">
+        <v>109257000</v>
+      </c>
+      <c r="F13" s="107" t="n">
+        <v>101163519</v>
+      </c>
+      <c r="G13" s="107">
+        <f>F13*8%</f>
+        <v/>
+      </c>
+      <c r="H13" s="108">
+        <f>ROUND(F13+G13,-3)</f>
+        <v/>
+      </c>
+      <c r="I13" s="107">
+        <f>IF(E13="","",H13-E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="105" t="inlineStr">
+        <is>
+          <t>Xây lắp Trường tiểu học số 1 Đồng Sơn</t>
+        </is>
+      </c>
+      <c r="C14" s="106" t="inlineStr">
+        <is>
+          <t>Gxdct3</t>
+        </is>
+      </c>
+      <c r="D14" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E14" s="107" t="n">
+        <v>42923000</v>
+      </c>
+      <c r="F14" s="107" t="n">
+        <v>39743608</v>
+      </c>
+      <c r="G14" s="107">
+        <f>F14*8%</f>
+        <v/>
+      </c>
+      <c r="H14" s="108">
+        <f>ROUND(F14+G14,-3)</f>
+        <v/>
+      </c>
+      <c r="I14" s="107">
+        <f>IF(E14="","",H14-E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="105" t="inlineStr">
+        <is>
+          <t>Xây lắp Trường tiểu học số 2 Đồng Sơn</t>
+        </is>
+      </c>
+      <c r="C15" s="106" t="inlineStr">
+        <is>
+          <t>Gxdct4</t>
+        </is>
+      </c>
+      <c r="D15" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E15" s="107" t="n">
+        <v>86464000</v>
+      </c>
+      <c r="F15" s="107" t="n">
+        <v>80058943</v>
+      </c>
+      <c r="G15" s="107">
+        <f>F15*8%</f>
+        <v/>
+      </c>
+      <c r="H15" s="108">
+        <f>ROUND(F15+G15,-3)</f>
+        <v/>
+      </c>
+      <c r="I15" s="107">
+        <f>IF(E15="","",H15-E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="105" t="inlineStr">
+        <is>
+          <t>Xây lắp Trường THCS số 1 Đồng Sơn</t>
+        </is>
+      </c>
+      <c r="C16" s="106" t="inlineStr">
+        <is>
+          <t>Gxdct5</t>
+        </is>
+      </c>
+      <c r="D16" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E16" s="107" t="n">
+        <v>127297000</v>
+      </c>
+      <c r="F16" s="107" t="n">
+        <v>117867626</v>
+      </c>
+      <c r="G16" s="107">
+        <f>F16*8%</f>
+        <v/>
+      </c>
+      <c r="H16" s="108">
+        <f>ROUND(F16+G16,-3)</f>
+        <v/>
+      </c>
+      <c r="I16" s="107">
+        <f>IF(E16="","",H16-E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="105" t="inlineStr">
+        <is>
+          <t>Xây lắp Trường THCS Bắc Nghĩa</t>
+        </is>
+      </c>
+      <c r="C17" s="106" t="inlineStr">
+        <is>
+          <t>Gxdct6</t>
+        </is>
+      </c>
+      <c r="D17" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E17" s="107" t="n">
+        <v>43209000</v>
+      </c>
+      <c r="F17" s="107" t="n">
+        <v>40008775</v>
+      </c>
+      <c r="G17" s="107">
+        <f>F17*8%</f>
+        <v/>
+      </c>
+      <c r="H17" s="108">
+        <f>ROUND(F17+G17,-3)</f>
+        <v/>
+      </c>
+      <c r="I17" s="107">
+        <f>IF(E17="","",H17-E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="105" t="inlineStr">
+        <is>
+          <t>Chi phí xây dựng của công trình</t>
+        </is>
+      </c>
+      <c r="C18" s="106" t="inlineStr">
+        <is>
+          <t>Gxdct</t>
+        </is>
+      </c>
+      <c r="D18" s="105" t="inlineStr">
+        <is>
+          <t>Cộng</t>
+        </is>
+      </c>
+      <c r="E18" s="107" t="n"/>
+      <c r="F18" s="107">
+        <f>SUM(F12:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="107">
+        <f>F18*8%</f>
+        <v/>
+      </c>
+      <c r="H18" s="108">
+        <f>ROUND(F18+G18,-3)</f>
+        <v/>
+      </c>
+      <c r="I18" s="107">
+        <f>IF(E18="","",H18-E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="105" t="inlineStr">
+        <is>
+          <t>Chi phí nhà tạm để ở và điều hành thi công</t>
+        </is>
+      </c>
+      <c r="C19" s="106" t="inlineStr">
+        <is>
+          <t>Glt</t>
+        </is>
+      </c>
+      <c r="D19" s="105" t="inlineStr">
+        <is>
+          <t>1,1% × Gxdct</t>
+        </is>
+      </c>
+      <c r="E19" s="107" t="n"/>
+      <c r="F19" s="107">
+        <f>F18*1.1%</f>
+        <v/>
+      </c>
+      <c r="G19" s="107">
+        <f>F19*8%</f>
+        <v/>
+      </c>
+      <c r="H19" s="108">
+        <f>ROUND(F19+G19,-3)</f>
+        <v/>
+      </c>
+      <c r="I19" s="107">
+        <f>IF(E19="","",H19-E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="90" t="inlineStr">
+        <is>
+          <t>I. CHI PHÍ XÂY LẮP</t>
+        </is>
+      </c>
+      <c r="C20" s="109" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D20" s="90" t="inlineStr">
+        <is>
+          <t>Gxdct + Glt</t>
+        </is>
+      </c>
+      <c r="E20" s="108" t="n">
+        <v>1741104000</v>
+      </c>
+      <c r="F20" s="108">
+        <f>F18+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="108">
+        <f>F20*8%</f>
+        <v/>
+      </c>
+      <c r="H20" s="108">
+        <f>ROUND(F20+G20,-3)</f>
+        <v/>
+      </c>
+      <c r="I20" s="108">
+        <f>IF(E20="","",H20-E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="90" t="inlineStr">
+        <is>
+          <t>II. CHI PHÍ THIẾT BỊ</t>
+        </is>
+      </c>
+      <c r="C21" s="109" t="inlineStr">
+        <is>
+          <t>Gtb</t>
+        </is>
+      </c>
+      <c r="D21" s="90" t="inlineStr">
+        <is>
+          <t>Σ thiết bị × giá chốt</t>
+        </is>
+      </c>
+      <c r="E21" s="108" t="n">
+        <v>18954000</v>
+      </c>
+      <c r="F21" s="108">
+        <f>SUMIF(L62:L90,"Thiết bị",K62:K90)</f>
+        <v/>
+      </c>
+      <c r="G21" s="108">
+        <f>F21*8%</f>
+        <v/>
+      </c>
+      <c r="H21" s="108">
+        <f>F21*1.08</f>
+        <v/>
+      </c>
+      <c r="I21" s="108">
+        <f>IF(E21="","",H21-E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="90" t="inlineStr">
+        <is>
+          <t>III. CHI PHÍ QUẢN LÝ DỰ ÁN</t>
+        </is>
+      </c>
+      <c r="C22" s="109" t="inlineStr">
+        <is>
+          <t>QL</t>
+        </is>
+      </c>
+      <c r="D22" s="90" t="inlineStr">
+        <is>
+          <t>3,446% × (GXD + Gtb)</t>
+        </is>
+      </c>
+      <c r="E22" s="108" t="n">
+        <v>56159000</v>
+      </c>
+      <c r="F22" s="108">
+        <f>(F20+F21)*3.446%</f>
+        <v/>
+      </c>
+      <c r="G22" s="108" t="n"/>
+      <c r="H22" s="108">
+        <f>ROUND(F22,-3)</f>
+        <v/>
+      </c>
+      <c r="I22" s="108">
+        <f>IF(E22="","",H22-E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí đo vẽ hiện trạng</t>
+        </is>
+      </c>
+      <c r="C23" s="106" t="inlineStr">
+        <is>
+          <t>TV1</t>
+        </is>
+      </c>
+      <c r="D23" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E23" s="107" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F23" s="107">
+        <f>15000000/1.08</f>
+        <v/>
+      </c>
+      <c r="G23" s="107">
+        <f>F23*8%</f>
+        <v/>
+      </c>
+      <c r="H23" s="108">
+        <f>15000000</f>
+        <v/>
+      </c>
+      <c r="I23" s="107">
+        <f>IF(E23="","",H23-E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí lập báo cáo KTKT (nội suy theo quy mô)</t>
+        </is>
+      </c>
+      <c r="C24" s="106" t="inlineStr">
+        <is>
+          <t>TV2</t>
+        </is>
+      </c>
+      <c r="D24" s="105" t="inlineStr">
+        <is>
+          <t>(Gxdct + Gtb) × tỷ lệ nội suy</t>
+        </is>
+      </c>
+      <c r="E24" s="107" t="n"/>
+      <c r="F24" s="107">
+        <f>(F18+F21)*(((3-(F20+F21)/10^9)*(6.5-4.7)/(3-1)+4.7)/100)</f>
+        <v/>
+      </c>
+      <c r="G24" s="107">
+        <f>F24*8%</f>
+        <v/>
+      </c>
+      <c r="H24" s="108">
+        <f>ROUND(F24+G24,-3)</f>
+        <v/>
+      </c>
+      <c r="I24" s="107">
+        <f>IF(E24="","",H24-E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm tra thiết kế BVTC</t>
+        </is>
+      </c>
+      <c r="C25" s="106" t="inlineStr">
+        <is>
+          <t>TV3</t>
+        </is>
+      </c>
+      <c r="D25" s="105" t="inlineStr">
+        <is>
+          <t>0,258% × Gxdct</t>
+        </is>
+      </c>
+      <c r="E25" s="107" t="n"/>
+      <c r="F25" s="107">
+        <f>F18*0.258%</f>
+        <v/>
+      </c>
+      <c r="G25" s="107">
+        <f>F25*8%</f>
+        <v/>
+      </c>
+      <c r="H25" s="108">
+        <f>ROUND(F25+G25,-3)</f>
+        <v/>
+      </c>
+      <c r="I25" s="107">
+        <f>IF(E25="","",H25-E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm tra dự toán</t>
+        </is>
+      </c>
+      <c r="C26" s="106" t="inlineStr">
+        <is>
+          <t>TV4</t>
+        </is>
+      </c>
+      <c r="D26" s="105" t="inlineStr">
+        <is>
+          <t>0,25% × Gxdct</t>
+        </is>
+      </c>
+      <c r="E26" s="107" t="n"/>
+      <c r="F26" s="107">
+        <f>F18*0.25%</f>
+        <v/>
+      </c>
+      <c r="G26" s="107">
+        <f>F26*8%</f>
+        <v/>
+      </c>
+      <c r="H26" s="108">
+        <f>ROUND(F26+G26,-3)</f>
+        <v/>
+      </c>
+      <c r="I26" s="107">
+        <f>IF(E26="","",H26-E26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm định giá</t>
+        </is>
+      </c>
+      <c r="C27" s="106" t="inlineStr">
+        <is>
+          <t>TV5</t>
+        </is>
+      </c>
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E27" s="107" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F27" s="107">
+        <f>10000000/1.08</f>
+        <v/>
+      </c>
+      <c r="G27" s="107">
+        <f>F27*8%</f>
+        <v/>
+      </c>
+      <c r="H27" s="108">
+        <f>10000000</f>
+        <v/>
+      </c>
+      <c r="I27" s="107">
+        <f>IF(E27="","",H27-E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="90" t="inlineStr">
+        <is>
+          <t>IV. CHI PHÍ TƯ VẤN</t>
+        </is>
+      </c>
+      <c r="C28" s="109" t="inlineStr">
+        <is>
+          <t>GTV</t>
+        </is>
+      </c>
+      <c r="D28" s="90" t="inlineStr">
+        <is>
+          <t>Cộng TV1–TV5</t>
+        </is>
+      </c>
+      <c r="E28" s="108" t="n">
+        <v>137053000</v>
+      </c>
+      <c r="F28" s="108" t="n"/>
+      <c r="G28" s="108" t="n"/>
+      <c r="H28" s="108">
+        <f>ROUND(SUM(H23:H27),-3)</f>
+        <v/>
+      </c>
+      <c r="I28" s="108">
+        <f>IF(E28="","",H28-E28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm tra phê duyệt quyết toán</t>
+        </is>
+      </c>
+      <c r="C29" s="106" t="inlineStr">
+        <is>
+          <t>CK1</t>
+        </is>
+      </c>
+      <c r="D29" s="105" t="inlineStr">
+        <is>
+          <t>0,57% × TM (ô E8)</t>
+        </is>
+      </c>
+      <c r="E29" s="107" t="n"/>
+      <c r="F29" s="107">
+        <f>0.57%*$E$8</f>
+        <v/>
+      </c>
+      <c r="G29" s="107" t="n"/>
+      <c r="H29" s="108">
+        <f>ROUND(F29,-3)</f>
+        <v/>
+      </c>
+      <c r="I29" s="107">
+        <f>IF(E29="","",H29-E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Phí thẩm định báo cáo KTKT</t>
+        </is>
+      </c>
+      <c r="C30" s="106" t="inlineStr">
+        <is>
+          <t>CK2</t>
+        </is>
+      </c>
+      <c r="D30" s="105" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E30" s="107" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F30" s="107" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G30" s="107" t="n"/>
+      <c r="H30" s="108">
+        <f>ROUND(F30,-3)</f>
+        <v/>
+      </c>
+      <c r="I30" s="107">
+        <f>IF(E30="","",H30-E30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="90" t="inlineStr">
+        <is>
+          <t>V. CHI PHÍ KHÁC</t>
+        </is>
+      </c>
+      <c r="C31" s="109" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D31" s="90" t="inlineStr">
+        <is>
+          <t>CK1 + CK2</t>
+        </is>
+      </c>
+      <c r="E31" s="108" t="n">
+        <v>12265000</v>
+      </c>
+      <c r="F31" s="108" t="n"/>
+      <c r="G31" s="108" t="n"/>
+      <c r="H31" s="108">
+        <f>ROUND(H29+H30,-3)</f>
+        <v/>
+      </c>
+      <c r="I31" s="108">
+        <f>IF(E31="","",H31-E31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="90" t="inlineStr">
+        <is>
+          <t>VI. CHI PHÍ DỰ PHÒNG</t>
+        </is>
+      </c>
+      <c r="C32" s="109" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="D32" s="90" t="inlineStr">
+        <is>
+          <t>5% × (GXD + Gtb + QL + GTV + GK)</t>
+        </is>
+      </c>
+      <c r="E32" s="108" t="n">
+        <v>98277000</v>
+      </c>
+      <c r="F32" s="108" t="n"/>
+      <c r="G32" s="108" t="n"/>
+      <c r="H32" s="108">
+        <f>ROUND(5%*(H20+H21+H22+H28+H31),-3)</f>
+        <v/>
+      </c>
+      <c r="I32" s="108">
+        <f>IF(E32="","",H32-E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="110" t="inlineStr">
+        <is>
+          <t>TỔNG DỰ TOÁN GÓI</t>
+        </is>
+      </c>
+      <c r="C33" s="111" t="inlineStr">
+        <is>
+          <t>VTM</t>
+        </is>
+      </c>
+      <c r="D33" s="110" t="inlineStr">
+        <is>
+          <t>I + … + VI</t>
+        </is>
+      </c>
+      <c r="E33" s="112" t="n">
+        <v>2063812000</v>
+      </c>
+      <c r="F33" s="112" t="n"/>
+      <c r="G33" s="112" t="n"/>
+      <c r="H33" s="112">
+        <f>ROUND(H20+H21+H22+H28+H31+H32,-3)</f>
+        <v/>
+      </c>
+      <c r="I33" s="112">
+        <f>IF(E33="","",H33-E33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="113" t="inlineStr">
+        <is>
+          <t>TỔNG DỰ TOÁN GÓI – LÀM TRÒN (báo chủ đầu tư)</t>
+        </is>
+      </c>
+      <c r="C34" s="114" t="inlineStr"/>
+      <c r="D34" s="113" t="inlineStr">
+        <is>
+          <t>Làm tròn triệu</t>
+        </is>
+      </c>
+      <c r="E34" s="104" t="n">
+        <v>2064000000</v>
+      </c>
+      <c r="F34" s="104" t="n"/>
+      <c r="G34" s="104" t="n"/>
+      <c r="H34" s="104">
+        <f>ROUND(H33,-6)</f>
+        <v/>
+      </c>
+      <c r="I34" s="104">
+        <f>IF(E34="","",H34-E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="99" t="inlineStr">
+        <is>
+          <t>B. LỢI NHUẬN PHẦN PCCC (trước thuế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="100" t="inlineStr">
         <is>
           <t>Khoản</t>
         </is>
       </c>
-      <c r="C7" s="94" t="n"/>
-      <c r="D7" s="90" t="n"/>
-      <c r="E7" s="93" t="inlineStr">
-        <is>
-          <t>Giá vốn</t>
-        </is>
-      </c>
-      <c r="F7" s="90" t="n"/>
-      <c r="G7" s="93" t="inlineStr">
-        <is>
-          <t>Giá đề xuất (trước thuế)</t>
-        </is>
-      </c>
-      <c r="H7" s="90" t="n"/>
-      <c r="I7" s="93" t="inlineStr">
-        <is>
-          <t>Lợi nhuận</t>
-        </is>
-      </c>
-      <c r="J7" s="93" t="inlineStr">
-        <is>
-          <t>% LN / giá vốn</t>
-        </is>
-      </c>
-      <c r="K7" s="93" t="inlineStr">
-        <is>
-          <t>% LN / giá bán</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="95" t="inlineStr">
-        <is>
-          <t>Vật tư, thiết bị</t>
-        </is>
-      </c>
-      <c r="C8" s="96" t="n"/>
-      <c r="D8" s="96" t="n"/>
-      <c r="E8" s="96">
-        <f>SUMPRODUCT(--(E16:E44&lt;&gt;""),D16:D44,N(+E16:E44))</f>
-        <v/>
-      </c>
-      <c r="F8" s="96" t="n"/>
-      <c r="G8" s="96">
-        <f>SUMPRODUCT(--(G16:G44&lt;&gt;""),D16:D44,N(+G16:G44))</f>
-        <v/>
-      </c>
-      <c r="H8" s="96" t="n"/>
-      <c r="I8" s="96">
-        <f>G8-E8</f>
-        <v/>
-      </c>
-      <c r="J8" s="97">
-        <f>IF(E8=0,"",I8/E8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="97">
-        <f>IF(G8=0,"",I8/G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="95" t="inlineStr">
-        <is>
-          <t>Nhân công</t>
-        </is>
-      </c>
-      <c r="C9" s="96" t="n"/>
-      <c r="D9" s="96" t="n"/>
-      <c r="E9" s="96">
-        <f>SUMPRODUCT(--(F16:F44&lt;&gt;""),D16:D44,N(+F16:F44))</f>
-        <v/>
-      </c>
-      <c r="F9" s="96" t="n"/>
-      <c r="G9" s="96">
-        <f>SUMPRODUCT(--(H16:H44&lt;&gt;""),D16:D44,N(+H16:H44))</f>
-        <v/>
-      </c>
-      <c r="H9" s="96" t="n"/>
-      <c r="I9" s="96">
-        <f>G9-E9</f>
-        <v/>
-      </c>
-      <c r="J9" s="97">
-        <f>IF(E9=0,"",I9/E9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="97">
-        <f>IF(G9=0,"",I9/G9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="98" t="inlineStr">
-        <is>
-          <t>Cộng trước thuế</t>
-        </is>
-      </c>
-      <c r="C10" s="99" t="n"/>
-      <c r="D10" s="99" t="n"/>
-      <c r="E10" s="99">
-        <f>E8+E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="99" t="n"/>
-      <c r="G10" s="99">
-        <f>G8+G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="99" t="n"/>
-      <c r="I10" s="99">
-        <f>G10-E10</f>
-        <v/>
-      </c>
-      <c r="J10" s="100">
-        <f>IF(E10=0,"",I10/E10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="100">
-        <f>IF(G10=0,"",I10/G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="95" t="inlineStr">
-        <is>
-          <t>Thuế GTGT trên giá đề xuất (theo thuế suất từng dòng)</t>
-        </is>
-      </c>
-      <c r="C11" s="96" t="n"/>
-      <c r="D11" s="96" t="n"/>
-      <c r="E11" s="96" t="n"/>
-      <c r="F11" s="96" t="n"/>
-      <c r="G11" s="96">
-        <f>SUMPRODUCT(J16:J44,N(+M16:M44))</f>
-        <v/>
-      </c>
-      <c r="H11" s="96" t="n"/>
-      <c r="I11" s="96" t="n"/>
-      <c r="J11" s="97" t="n"/>
-      <c r="K11" s="97" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="98" t="inlineStr">
-        <is>
-          <t>Giá trị đề xuất sau thuế</t>
-        </is>
-      </c>
-      <c r="C12" s="99" t="n"/>
-      <c r="D12" s="99" t="n"/>
-      <c r="E12" s="99" t="n"/>
-      <c r="F12" s="99" t="n"/>
-      <c r="G12" s="99">
-        <f>G10+G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="99" t="n"/>
-      <c r="I12" s="99" t="n"/>
-      <c r="J12" s="100" t="n"/>
-      <c r="K12" s="100" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="101" t="inlineStr">
-        <is>
-          <t>Kiểm tra: tổng cộng ở bảng chi tiết (dòng 45) phải bằng dòng 'Cộng trước thuế'. % LN / giá bán = lợi nhuận ÷ giá đề xuất (40% trên giá vốn ≈ 28,6% trên giá bán).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="C37" s="91" t="n"/>
+      <c r="D37" s="92" t="n"/>
+      <c r="E37" s="100" t="inlineStr">
+        <is>
+          <t>Hiện tại</t>
+        </is>
+      </c>
+      <c r="F37" s="100" t="inlineStr">
+        <is>
+          <t>SAU KHI CHỐT GIÁ</t>
+        </is>
+      </c>
+      <c r="G37" s="100" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="H37" s="91" t="n"/>
+      <c r="I37" s="91" t="n"/>
+      <c r="J37" s="91" t="n"/>
+      <c r="K37" s="92" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="105" t="inlineStr">
+        <is>
+          <t>Doanh thu lắp đặt PCCC (Gxdct1)</t>
+        </is>
+      </c>
+      <c r="C38" s="115" t="n"/>
+      <c r="D38" s="115" t="n"/>
+      <c r="E38" s="107" t="n">
+        <v>1215750394</v>
+      </c>
+      <c r="F38" s="107">
+        <f>F12</f>
+        <v/>
+      </c>
+      <c r="G38" s="116" t="n"/>
+      <c r="H38" s="115" t="n"/>
+      <c r="I38" s="115" t="n"/>
+      <c r="J38" s="115" t="n"/>
+      <c r="K38" s="115" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="105" t="inlineStr">
+        <is>
+          <t>Nhà tạm phần PCCC (1,1% × Gxdct1)</t>
+        </is>
+      </c>
+      <c r="C39" s="115" t="n"/>
+      <c r="D39" s="115" t="n"/>
+      <c r="E39" s="107">
+        <f>E38*1.1%</f>
+        <v/>
+      </c>
+      <c r="F39" s="107">
+        <f>F38*1.1%</f>
+        <v/>
+      </c>
+      <c r="G39" s="116" t="n"/>
+      <c r="H39" s="115" t="n"/>
+      <c r="I39" s="115" t="n"/>
+      <c r="J39" s="115" t="n"/>
+      <c r="K39" s="115" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị (trước thuế)</t>
+        </is>
+      </c>
+      <c r="C40" s="115" t="n"/>
+      <c r="D40" s="115" t="n"/>
+      <c r="E40" s="107" t="n">
+        <v>17550000</v>
+      </c>
+      <c r="F40" s="107">
+        <f>F21</f>
+        <v/>
+      </c>
+      <c r="G40" s="116" t="n"/>
+      <c r="H40" s="115" t="n"/>
+      <c r="I40" s="115" t="n"/>
+      <c r="J40" s="115" t="n"/>
+      <c r="K40" s="115" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="90" t="inlineStr">
+        <is>
+          <t>Cộng doanh thu PCCC</t>
+        </is>
+      </c>
+      <c r="C41" s="117" t="n"/>
+      <c r="D41" s="117" t="n"/>
+      <c r="E41" s="108">
+        <f>SUM(E38:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="108">
+        <f>SUM(F38:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="116" t="n"/>
+      <c r="H41" s="117" t="n"/>
+      <c r="I41" s="117" t="n"/>
+      <c r="J41" s="117" t="n"/>
+      <c r="K41" s="117" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn – các mục trong báo giá</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="n"/>
+      <c r="D42" s="115" t="n"/>
+      <c r="E42" s="107">
+        <f>J91</f>
+        <v/>
+      </c>
+      <c r="F42" s="107">
+        <f>J91</f>
+        <v/>
+      </c>
+      <c r="G42" s="116" t="inlineStr">
+        <is>
+          <t>Bảng C: khối lượng dự toán × giá vốn</t>
+        </is>
+      </c>
+      <c r="H42" s="115" t="n"/>
+      <c r="I42" s="115" t="n"/>
+      <c r="J42" s="115" t="n"/>
+      <c r="K42" s="115" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn – ngoài báo giá (ống, cáp, van, vật tư phụ 5%…)</t>
+        </is>
+      </c>
+      <c r="C43" s="115" t="n"/>
+      <c r="D43" s="115" t="n"/>
+      <c r="E43" s="107">
+        <f>G110</f>
+        <v/>
+      </c>
+      <c r="F43" s="107">
+        <f>G110</f>
+        <v/>
+      </c>
+      <c r="G43" s="116" t="inlineStr">
+        <is>
+          <t>Bảng D: theo sheet Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="H43" s="115" t="n"/>
+      <c r="I43" s="115" t="n"/>
+      <c r="J43" s="115" t="n"/>
+      <c r="K43" s="115" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="90" t="inlineStr">
+        <is>
+          <t>Cộng giá vốn PCCC</t>
+        </is>
+      </c>
+      <c r="C44" s="117" t="n"/>
+      <c r="D44" s="117" t="n"/>
+      <c r="E44" s="108">
+        <f>E42+E43</f>
+        <v/>
+      </c>
+      <c r="F44" s="108">
+        <f>F42+F43</f>
+        <v/>
+      </c>
+      <c r="G44" s="116" t="n"/>
+      <c r="H44" s="117" t="n"/>
+      <c r="I44" s="117" t="n"/>
+      <c r="J44" s="117" t="n"/>
+      <c r="K44" s="117" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="101" t="inlineStr">
+        <is>
+          <t>Trích lại chủ đầu tư (15% × tổng dự toán làm tròn)</t>
+        </is>
+      </c>
+      <c r="C45" s="118" t="n"/>
+      <c r="D45" s="118" t="n"/>
+      <c r="E45" s="103">
+        <f>$E$5*E34</f>
+        <v/>
+      </c>
+      <c r="F45" s="103">
+        <f>$E$5*H34</f>
+        <v/>
+      </c>
+      <c r="G45" s="119" t="inlineStr">
+        <is>
+          <t>Trừ vào doanh thu trước thuế (VAT phải nộp nhà nước)</t>
+        </is>
+      </c>
+      <c r="H45" s="118" t="n"/>
+      <c r="I45" s="118" t="n"/>
+      <c r="J45" s="118" t="n"/>
+      <c r="K45" s="118" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="110" t="inlineStr">
+        <is>
+          <t>LỢI NHUẬN PCCC</t>
+        </is>
+      </c>
+      <c r="C46" s="120" t="n"/>
+      <c r="D46" s="120" t="n"/>
+      <c r="E46" s="112">
+        <f>E41-E44-E45</f>
+        <v/>
+      </c>
+      <c r="F46" s="112">
+        <f>F41-F44-F45</f>
+        <v/>
+      </c>
+      <c r="G46" s="121" t="n"/>
+      <c r="H46" s="120" t="n"/>
+      <c r="I46" s="120" t="n"/>
+      <c r="J46" s="120" t="n"/>
+      <c r="K46" s="120" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="110" t="inlineStr">
+        <is>
+          <t>% lợi nhuận / giá vốn PCCC</t>
+        </is>
+      </c>
+      <c r="C47" s="120" t="n"/>
+      <c r="D47" s="120" t="n"/>
+      <c r="E47" s="122">
+        <f>E46/E44</f>
+        <v/>
+      </c>
+      <c r="F47" s="122">
+        <f>F46/F44</f>
+        <v/>
+      </c>
+      <c r="G47" s="121" t="n"/>
+      <c r="H47" s="120" t="n"/>
+      <c r="I47" s="120" t="n"/>
+      <c r="J47" s="120" t="n"/>
+      <c r="K47" s="120" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="90" t="inlineStr">
+        <is>
+          <t>Đánh giá so với mức tối thiểu (ô E4)</t>
+        </is>
+      </c>
+      <c r="C48" s="117" t="n"/>
+      <c r="D48" s="117" t="n"/>
+      <c r="E48" s="117">
+        <f>IF(E47&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="F48" s="117">
+        <f>IF(F47&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="G48" s="116" t="n"/>
+      <c r="H48" s="117" t="n"/>
+      <c r="I48" s="117" t="n"/>
+      <c r="J48" s="117" t="n"/>
+      <c r="K48" s="117" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="105" t="inlineStr">
+        <is>
+          <t>Tham khảo – doanh thu xây dựng (xây lắp + nhà tạm, trước thuế)</t>
+        </is>
+      </c>
+      <c r="C50" s="115" t="n"/>
+      <c r="D50" s="115" t="n"/>
+      <c r="E50" s="107">
+        <f>378842471*1.011</f>
+        <v/>
+      </c>
+      <c r="F50" s="107">
+        <f>378842471*1.011</f>
+        <v/>
+      </c>
+      <c r="G50" s="116" t="inlineStr">
+        <is>
+          <t>Giữ nguyên đơn giá dự toán</t>
+        </is>
+      </c>
+      <c r="H50" s="115" t="n"/>
+      <c r="I50" s="115" t="n"/>
+      <c r="J50" s="115" t="n"/>
+      <c r="K50" s="115" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="105" t="inlineStr">
+        <is>
+          <t>Tham khảo – giá vốn xây dựng</t>
+        </is>
+      </c>
+      <c r="C51" s="115" t="n"/>
+      <c r="D51" s="115" t="n"/>
+      <c r="E51" s="107" t="n">
+        <v>110800000</v>
+      </c>
+      <c r="F51" s="107" t="n">
+        <v>110800000</v>
+      </c>
+      <c r="G51" s="116" t="inlineStr">
+        <is>
+          <t>Sheet Gia von chi tiet (khối lượng tiên lượng)</t>
+        </is>
+      </c>
+      <c r="H51" s="115" t="n"/>
+      <c r="I51" s="115" t="n"/>
+      <c r="J51" s="115" t="n"/>
+      <c r="K51" s="115" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="90" t="inlineStr">
+        <is>
+          <t>Tham khảo – lợi nhuận xây dựng (không dùng bù cho PCCC)</t>
+        </is>
+      </c>
+      <c r="C52" s="117" t="n"/>
+      <c r="D52" s="117" t="n"/>
+      <c r="E52" s="108">
+        <f>E50-E51</f>
+        <v/>
+      </c>
+      <c r="F52" s="108">
+        <f>F50-F51</f>
+        <v/>
+      </c>
+      <c r="G52" s="116" t="n"/>
+      <c r="H52" s="117" t="n"/>
+      <c r="I52" s="117" t="n"/>
+      <c r="J52" s="117" t="n"/>
+      <c r="K52" s="117" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="99" t="inlineStr">
+        <is>
+          <t>C. CHI TIẾT HẠNG MỤC TRONG BÁO GIÁ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="100" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B61" s="100" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C15" s="93" t="inlineStr">
+      <c r="C61" s="100" t="inlineStr">
         <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="D15" s="93" t="inlineStr">
+      <c r="D61" s="100" t="inlineStr">
         <is>
           <t>Khối lượng</t>
         </is>
       </c>
-      <c r="E15" s="93" t="inlineStr">
+      <c r="E61" s="100" t="inlineStr">
         <is>
           <t>Giá vốn vật tư</t>
         </is>
       </c>
-      <c r="F15" s="93" t="inlineStr">
+      <c r="F61" s="100" t="inlineStr">
         <is>
           <t>Giá vốn nhân công</t>
         </is>
       </c>
-      <c r="G15" s="93" t="inlineStr">
-        <is>
-          <t>Giá vật tư đề xuất</t>
-        </is>
-      </c>
-      <c r="H15" s="93" t="inlineStr">
-        <is>
-          <t>Giá nhân công đề xuất</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="inlineStr">
+      <c r="G61" s="100" t="inlineStr">
+        <is>
+          <t>Giá VT dự toán hiện tại</t>
+        </is>
+      </c>
+      <c r="H61" s="100" t="inlineStr">
+        <is>
+          <t>GIÁ VT ĐỀ XUẤT (CHỐT)</t>
+        </is>
+      </c>
+      <c r="I61" s="100" t="inlineStr">
+        <is>
+          <t>Nhân công theo định mức</t>
+        </is>
+      </c>
+      <c r="J61" s="100" t="inlineStr">
         <is>
           <t>Thành tiền giá vốn</t>
         </is>
       </c>
-      <c r="J15" s="93" t="inlineStr">
-        <is>
-          <t>Thành tiền đề xuất</t>
-        </is>
-      </c>
-      <c r="K15" s="93" t="inlineStr">
-        <is>
-          <t>Lợi nhuận</t>
-        </is>
-      </c>
-      <c r="L15" s="93" t="inlineStr">
-        <is>
-          <t>% LN / giá vốn</t>
-        </is>
-      </c>
-      <c r="M15" s="93" t="inlineStr">
-        <is>
-          <t>Thuế suất</t>
-        </is>
-      </c>
-      <c r="N15" s="93" t="inlineStr">
-        <is>
-          <t>Đơn giá VT hiện tại (cột E báo giá)</t>
-        </is>
-      </c>
-      <c r="O15" s="93" t="inlineStr">
-        <is>
-          <t>Nguồn giá vốn</t>
-        </is>
-      </c>
-      <c r="P15" s="93" t="inlineStr">
+      <c r="K61" s="100" t="inlineStr">
+        <is>
+          <t>Thành tiền VT đề xuất</t>
+        </is>
+      </c>
+      <c r="L61" s="100" t="inlineStr">
+        <is>
+          <t>Phần</t>
+        </is>
+      </c>
+      <c r="M61" s="100" t="inlineStr">
+        <is>
+          <t>SL quy đổi (gồm VL khác)</t>
+        </is>
+      </c>
+      <c r="N61" s="100" t="inlineStr">
+        <is>
+          <t>VL dự toán hiện tại (thành tiền)</t>
+        </is>
+      </c>
+      <c r="O61" s="100" t="inlineStr">
+        <is>
+          <t>Tăng/giảm giá trị XD trước thuế</t>
+        </is>
+      </c>
+      <c r="P61" s="100" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="102" t="n">
+    <row r="62">
+      <c r="A62" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="103" t="inlineStr">
+      <c r="B62" s="105" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 10 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C16" s="102" t="inlineStr">
+      <c r="C62" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D16" s="104">
-        <f>'Bao gia'!D4</f>
-        <v/>
-      </c>
-      <c r="E16" s="96" t="n">
+      <c r="D62" s="123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="107" t="n">
         <v>8600000</v>
       </c>
-      <c r="F16" s="96" t="n">
+      <c r="F62" s="107" t="n">
         <v>1500000</v>
       </c>
-      <c r="G16" s="105">
-        <f>IF(E16="","",'Bao gia'!J4)</f>
-        <v/>
-      </c>
-      <c r="H16" s="105">
-        <f>IF(F16="","",'Bao gia'!K4)</f>
-        <v/>
-      </c>
-      <c r="I16" s="96">
-        <f>IF(E16="",0,D16*(E16+F16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="96">
-        <f>IF(E16="",0,D16*(G16+H16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="96">
-        <f>J16-I16</f>
-        <v/>
-      </c>
-      <c r="L16" s="97">
-        <f>IF(I16=0,"",K16/I16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="106">
-        <f>'Bao gia'!G4</f>
-        <v/>
-      </c>
-      <c r="N16" s="96">
-        <f>'Bao gia'!E4</f>
-        <v/>
-      </c>
-      <c r="O16" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P16" s="103" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="102" t="n">
+      <c r="G62" s="107">
+        <f>IF(M62=0,"",N62/M62)</f>
+        <v/>
+      </c>
+      <c r="H62" s="104">
+        <f>ROUNDUP(E62*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I62" s="107" t="n">
+        <v>828880</v>
+      </c>
+      <c r="J62" s="107">
+        <f>D62*(E62+F62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="107">
+        <f>D62*H62</f>
+        <v/>
+      </c>
+      <c r="L62" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M62" s="124" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" s="107" t="n">
+        <v>17850000</v>
+      </c>
+      <c r="O62" s="107">
+        <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
+        <v/>
+      </c>
+      <c r="P62" s="105" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="106" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="103" t="inlineStr">
+      <c r="B63" s="105" t="inlineStr">
         <is>
           <t>Còi đèn báo cháy kết hợp</t>
         </is>
       </c>
-      <c r="C17" s="102" t="inlineStr">
+      <c r="C63" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D17" s="104">
-        <f>'Bao gia'!D5</f>
-        <v/>
-      </c>
-      <c r="E17" s="96" t="n">
+      <c r="D63" s="123" t="n">
+        <v>21</v>
+      </c>
+      <c r="E63" s="107" t="n">
         <v>252000</v>
       </c>
-      <c r="F17" s="96" t="n">
+      <c r="F63" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G17" s="105">
-        <f>IF(E17="","",'Bao gia'!J5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="105">
-        <f>IF(F17="","",'Bao gia'!K5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="96">
-        <f>IF(E17="",0,D17*(E17+F17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="96">
-        <f>IF(E17="",0,D17*(G17+H17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="96">
-        <f>J17-I17</f>
-        <v/>
-      </c>
-      <c r="L17" s="97">
-        <f>IF(I17=0,"",K17/I17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="106">
-        <f>'Bao gia'!G5</f>
-        <v/>
-      </c>
-      <c r="N17" s="96">
-        <f>'Bao gia'!E5</f>
-        <v/>
-      </c>
-      <c r="O17" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P17" s="103" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="102" t="n">
+      <c r="G63" s="107">
+        <f>IF(M63=0,"",N63/M63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="104">
+        <f>ROUNDUP(E63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I63" s="107" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J63" s="107">
+        <f>D63*(E63+F63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="107">
+        <f>D63*H63</f>
+        <v/>
+      </c>
+      <c r="L63" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M63" s="124" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="N63" s="107" t="n">
+        <v>5355000</v>
+      </c>
+      <c r="O63" s="107">
+        <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
+        <v/>
+      </c>
+      <c r="P63" s="105" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="106" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="103" t="inlineStr">
+      <c r="B64" s="105" t="inlineStr">
         <is>
           <t>Nút ấn khẩn tròn lắp nổi</t>
         </is>
       </c>
-      <c r="C18" s="102" t="inlineStr">
+      <c r="C64" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D18" s="104">
-        <f>'Bao gia'!D6</f>
-        <v/>
-      </c>
-      <c r="E18" s="96" t="n">
+      <c r="D64" s="123" t="n">
+        <v>21</v>
+      </c>
+      <c r="E64" s="107" t="n">
         <v>205000</v>
       </c>
-      <c r="F18" s="96" t="n">
+      <c r="F64" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G18" s="105">
-        <f>IF(E18="","",'Bao gia'!J6)</f>
-        <v/>
-      </c>
-      <c r="H18" s="105">
-        <f>IF(F18="","",'Bao gia'!K6)</f>
-        <v/>
-      </c>
-      <c r="I18" s="96">
-        <f>IF(E18="",0,D18*(E18+F18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="96">
-        <f>IF(E18="",0,D18*(G18+H18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="96">
-        <f>J18-I18</f>
-        <v/>
-      </c>
-      <c r="L18" s="97">
-        <f>IF(I18=0,"",K18/I18)</f>
-        <v/>
-      </c>
-      <c r="M18" s="106">
-        <f>'Bao gia'!G6</f>
-        <v/>
-      </c>
-      <c r="N18" s="96">
-        <f>'Bao gia'!E6</f>
-        <v/>
-      </c>
-      <c r="O18" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P18" s="103" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="102" t="n">
+      <c r="G64" s="107">
+        <f>IF(M64=0,"",N64/M64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="104">
+        <f>ROUNDUP(E64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I64" s="107" t="n">
+        <v>191280</v>
+      </c>
+      <c r="J64" s="107">
+        <f>D64*(E64+F64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="107">
+        <f>D64*H64</f>
+        <v/>
+      </c>
+      <c r="L64" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M64" s="124" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="N64" s="107" t="n">
+        <v>4284000</v>
+      </c>
+      <c r="O64" s="107">
+        <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
+        <v/>
+      </c>
+      <c r="P64" s="105" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="106" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="103" t="inlineStr">
+      <c r="B65" s="105" t="inlineStr">
         <is>
           <t>Đầu báo khói quang 24VDC</t>
         </is>
       </c>
-      <c r="C19" s="102" t="inlineStr">
+      <c r="C65" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D19" s="104">
-        <f>'Bao gia'!D7</f>
-        <v/>
-      </c>
-      <c r="E19" s="96" t="n">
+      <c r="D65" s="123" t="n">
+        <v>287</v>
+      </c>
+      <c r="E65" s="107" t="n">
         <v>242000</v>
       </c>
-      <c r="F19" s="96" t="n">
+      <c r="F65" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G19" s="105">
-        <f>IF(E19="","",'Bao gia'!J7)</f>
-        <v/>
-      </c>
-      <c r="H19" s="105">
-        <f>IF(F19="","",'Bao gia'!K7)</f>
-        <v/>
-      </c>
-      <c r="I19" s="96">
-        <f>IF(E19="",0,D19*(E19+F19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="96">
-        <f>IF(E19="",0,D19*(G19+H19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="96">
-        <f>J19-I19</f>
-        <v/>
-      </c>
-      <c r="L19" s="97">
-        <f>IF(I19=0,"",K19/I19)</f>
-        <v/>
-      </c>
-      <c r="M19" s="106">
-        <f>'Bao gia'!G7</f>
-        <v/>
-      </c>
-      <c r="N19" s="96">
-        <f>'Bao gia'!E7</f>
-        <v/>
-      </c>
-      <c r="O19" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P19" s="103" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="102" t="n">
+      <c r="G65" s="107">
+        <f>IF(M65=0,"",N65/M65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="104">
+        <f>ROUNDUP(E65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I65" s="107" t="n">
+        <v>55471</v>
+      </c>
+      <c r="J65" s="107">
+        <f>D65*(E65+F65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="107">
+        <f>D65*H65</f>
+        <v/>
+      </c>
+      <c r="L65" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M65" s="124" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="N65" s="107" t="n">
+        <v>73185000</v>
+      </c>
+      <c r="O65" s="107">
+        <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
+        <v/>
+      </c>
+      <c r="P65" s="105" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="106" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="103" t="inlineStr">
+      <c r="B66" s="105" t="inlineStr">
         <is>
           <t>Đèn báo phòng</t>
         </is>
       </c>
-      <c r="C20" s="102" t="inlineStr">
+      <c r="C66" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D20" s="104">
-        <f>'Bao gia'!D8</f>
-        <v/>
-      </c>
-      <c r="E20" s="96" t="n">
+      <c r="D66" s="123" t="n">
+        <v>70</v>
+      </c>
+      <c r="E66" s="107" t="n">
         <v>116000</v>
       </c>
-      <c r="F20" s="96" t="n">
+      <c r="F66" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G20" s="105">
-        <f>IF(E20="","",'Bao gia'!J8)</f>
-        <v/>
-      </c>
-      <c r="H20" s="105">
-        <f>IF(F20="","",'Bao gia'!K8)</f>
-        <v/>
-      </c>
-      <c r="I20" s="96">
-        <f>IF(E20="",0,D20*(E20+F20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="96">
-        <f>IF(E20="",0,D20*(G20+H20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="96">
-        <f>J20-I20</f>
-        <v/>
-      </c>
-      <c r="L20" s="97">
-        <f>IF(I20=0,"",K20/I20)</f>
-        <v/>
-      </c>
-      <c r="M20" s="106">
-        <f>'Bao gia'!G8</f>
-        <v/>
-      </c>
-      <c r="N20" s="96">
-        <f>'Bao gia'!E8</f>
-        <v/>
-      </c>
-      <c r="O20" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P20" s="103" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="102" t="n">
+      <c r="G66" s="107">
+        <f>IF(M66=0,"",N66/M66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="104">
+        <f>ROUNDUP(E66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I66" s="107" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J66" s="107">
+        <f>D66*(E66+F66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="107">
+        <f>D66*H66</f>
+        <v/>
+      </c>
+      <c r="L66" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M66" s="124" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N66" s="107" t="n">
+        <v>3570000</v>
+      </c>
+      <c r="O66" s="107">
+        <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
+        <v/>
+      </c>
+      <c r="P66" s="105" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="106" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="103" t="inlineStr">
+      <c r="B67" s="105" t="inlineStr">
         <is>
           <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
         </is>
       </c>
-      <c r="C21" s="102" t="inlineStr">
+      <c r="C67" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D21" s="104">
-        <f>'Bao gia'!D9</f>
-        <v/>
-      </c>
-      <c r="E21" s="96" t="n">
+      <c r="D67" s="123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="107" t="n">
         <v>252000</v>
       </c>
-      <c r="F21" s="96" t="n">
+      <c r="F67" s="107" t="n">
         <v>20000</v>
       </c>
-      <c r="G21" s="105">
-        <f>IF(E21="","",'Bao gia'!J9)</f>
-        <v/>
-      </c>
-      <c r="H21" s="105">
-        <f>IF(F21="","",'Bao gia'!K9)</f>
-        <v/>
-      </c>
-      <c r="I21" s="96">
-        <f>IF(E21="",0,D21*(E21+F21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="96">
-        <f>IF(E21="",0,D21*(G21+H21))</f>
-        <v/>
-      </c>
-      <c r="K21" s="96">
-        <f>J21-I21</f>
-        <v/>
-      </c>
-      <c r="L21" s="97">
-        <f>IF(I21=0,"",K21/I21)</f>
-        <v/>
-      </c>
-      <c r="M21" s="106">
-        <f>'Bao gia'!G9</f>
-        <v/>
-      </c>
-      <c r="N21" s="96">
-        <f>'Bao gia'!E9</f>
-        <v/>
-      </c>
-      <c r="O21" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Hệ thống tiếp địa trung tâm báo cháy'</t>
-        </is>
-      </c>
-      <c r="P21" s="103" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="102" t="n">
+      <c r="G67" s="107">
+        <f>IF(M67=0,"",N67/M67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="104">
+        <f>ROUNDUP(E67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I67" s="107" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J67" s="107">
+        <f>D67*(E67+F67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="107">
+        <f>D67*H67</f>
+        <v/>
+      </c>
+      <c r="L67" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M67" s="124" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N67" s="107" t="n">
+        <v>565600</v>
+      </c>
+      <c r="O67" s="107">
+        <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
+        <v/>
+      </c>
+      <c r="P67" s="105" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="106" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="103" t="inlineStr">
+      <c r="B68" s="105" t="inlineStr">
         <is>
           <t>Co thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C22" s="102" t="inlineStr">
+      <c r="C68" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D22" s="104">
-        <f>'Bao gia'!D10</f>
-        <v/>
-      </c>
-      <c r="E22" s="96" t="n">
+      <c r="D68" s="123" t="n">
+        <v>56</v>
+      </c>
+      <c r="E68" s="107" t="n">
         <v>53000</v>
       </c>
-      <c r="F22" s="96" t="n">
+      <c r="F68" s="107" t="n">
         <v>25000</v>
       </c>
-      <c r="G22" s="105">
-        <f>IF(E22="","",'Bao gia'!J10)</f>
-        <v/>
-      </c>
-      <c r="H22" s="105">
-        <f>IF(F22="","",'Bao gia'!K10)</f>
-        <v/>
-      </c>
-      <c r="I22" s="96">
-        <f>IF(E22="",0,D22*(E22+F22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="96">
-        <f>IF(E22="",0,D22*(G22+H22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="96">
-        <f>J22-I22</f>
-        <v/>
-      </c>
-      <c r="L22" s="97">
-        <f>IF(I22=0,"",K22/I22)</f>
-        <v/>
-      </c>
-      <c r="M22" s="106">
-        <f>'Bao gia'!G10</f>
-        <v/>
-      </c>
-      <c r="N22" s="96">
-        <f>'Bao gia'!E10</f>
-        <v/>
-      </c>
-      <c r="O22" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P22" s="103" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="102" t="n">
+      <c r="G68" s="107">
+        <f>IF(M68=0,"",N68/M68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="104">
+        <f>ROUNDUP(E68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I68" s="107" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J68" s="107">
+        <f>D68*(E68+F68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="107">
+        <f>D68*H68</f>
+        <v/>
+      </c>
+      <c r="L68" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M68" s="124" t="n">
+        <v>56.0056</v>
+      </c>
+      <c r="N68" s="107" t="n">
+        <v>3640364</v>
+      </c>
+      <c r="O68" s="107">
+        <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
+        <v/>
+      </c>
+      <c r="P68" s="105" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="106" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="103" t="inlineStr">
+      <c r="B69" s="105" t="inlineStr">
         <is>
           <t>Co thép đen hàn DN50</t>
         </is>
       </c>
-      <c r="C23" s="102" t="inlineStr">
+      <c r="C69" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D23" s="104">
-        <f>'Bao gia'!D11</f>
-        <v/>
-      </c>
-      <c r="E23" s="96" t="n">
+      <c r="D69" s="123" t="n">
+        <v>265</v>
+      </c>
+      <c r="E69" s="107" t="n">
         <v>42000</v>
       </c>
-      <c r="F23" s="96" t="n">
+      <c r="F69" s="107" t="n">
         <v>25000</v>
       </c>
-      <c r="G23" s="105">
-        <f>IF(E23="","",'Bao gia'!J11)</f>
-        <v/>
-      </c>
-      <c r="H23" s="105">
-        <f>IF(F23="","",'Bao gia'!K11)</f>
-        <v/>
-      </c>
-      <c r="I23" s="96">
-        <f>IF(E23="",0,D23*(E23+F23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="96">
-        <f>IF(E23="",0,D23*(G23+H23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="96">
-        <f>J23-I23</f>
-        <v/>
-      </c>
-      <c r="L23" s="97">
-        <f>IF(I23=0,"",K23/I23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="106">
-        <f>'Bao gia'!G11</f>
-        <v/>
-      </c>
-      <c r="N23" s="96">
-        <f>'Bao gia'!E11</f>
-        <v/>
-      </c>
-      <c r="O23" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P23" s="103" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="102" t="n">
+      <c r="G69" s="107">
+        <f>IF(M69=0,"",N69/M69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="104">
+        <f>ROUNDUP(E69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I69" s="107" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J69" s="107">
+        <f>D69*(E69+F69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="107">
+        <f>D69*H69</f>
+        <v/>
+      </c>
+      <c r="L69" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M69" s="124" t="n">
+        <v>265.0265</v>
+      </c>
+      <c r="N69" s="107" t="n">
+        <v>13251325</v>
+      </c>
+      <c r="O69" s="107">
+        <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
+        <v/>
+      </c>
+      <c r="P69" s="105" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="106" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="103" t="inlineStr">
+      <c r="B70" s="105" t="inlineStr">
         <is>
           <t>Tê thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C24" s="102" t="inlineStr">
+      <c r="C70" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D24" s="104">
-        <f>'Bao gia'!D12</f>
-        <v/>
-      </c>
-      <c r="E24" s="96" t="n">
+      <c r="D70" s="123" t="n">
+        <v>22</v>
+      </c>
+      <c r="E70" s="107" t="n">
         <v>95000</v>
       </c>
-      <c r="F24" s="96" t="n">
+      <c r="F70" s="107" t="n">
         <v>25000</v>
       </c>
-      <c r="G24" s="105">
-        <f>IF(E24="","",'Bao gia'!J12)</f>
-        <v/>
-      </c>
-      <c r="H24" s="105">
-        <f>IF(F24="","",'Bao gia'!K12)</f>
-        <v/>
-      </c>
-      <c r="I24" s="96">
-        <f>IF(E24="",0,D24*(E24+F24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="96">
-        <f>IF(E24="",0,D24*(G24+H24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="96">
-        <f>J24-I24</f>
-        <v/>
-      </c>
-      <c r="L24" s="97">
-        <f>IF(I24=0,"",K24/I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="106">
-        <f>'Bao gia'!G12</f>
-        <v/>
-      </c>
-      <c r="N24" s="96">
-        <f>'Bao gia'!E12</f>
-        <v/>
-      </c>
-      <c r="O24" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P24" s="103" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="102" t="n">
+      <c r="G70" s="107">
+        <f>IF(M70=0,"",N70/M70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="104">
+        <f>ROUNDUP(E70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I70" s="107" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J70" s="107">
+        <f>D70*(E70+F70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="107">
+        <f>D70*H70</f>
+        <v/>
+      </c>
+      <c r="L70" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M70" s="124" t="n">
+        <v>22.0022</v>
+      </c>
+      <c r="N70" s="107" t="n">
+        <v>3630363</v>
+      </c>
+      <c r="O70" s="107">
+        <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
+        <v/>
+      </c>
+      <c r="P70" s="105" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="106" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="103" t="inlineStr">
+      <c r="B71" s="105" t="inlineStr">
         <is>
           <t>Tê giảm thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C25" s="102" t="inlineStr">
+      <c r="C71" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D25" s="104">
-        <f>'Bao gia'!D13</f>
-        <v/>
-      </c>
-      <c r="E25" s="96" t="n">
+      <c r="D71" s="123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="107" t="n">
         <v>190000</v>
       </c>
-      <c r="F25" s="96" t="n">
+      <c r="F71" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G25" s="105">
-        <f>IF(E25="","",'Bao gia'!J13)</f>
-        <v/>
-      </c>
-      <c r="H25" s="105">
-        <f>IF(F25="","",'Bao gia'!K13)</f>
-        <v/>
-      </c>
-      <c r="I25" s="96">
-        <f>IF(E25="",0,D25*(E25+F25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="96">
-        <f>IF(E25="",0,D25*(G25+H25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="96">
-        <f>J25-I25</f>
-        <v/>
-      </c>
-      <c r="L25" s="97">
-        <f>IF(I25=0,"",K25/I25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="106">
-        <f>'Bao gia'!G13</f>
-        <v/>
-      </c>
-      <c r="N25" s="96">
-        <f>'Bao gia'!E13</f>
-        <v/>
-      </c>
-      <c r="O25" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Tê giảm thép hàn DN65/50'</t>
-        </is>
-      </c>
-      <c r="P25" s="103" t="inlineStr">
-        <is>
-          <t>Sai giá ( gấp 10 lân)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="102" t="n">
+      <c r="G71" s="107">
+        <f>IF(M71=0,"",N71/M71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="104">
+        <f>ROUNDUP(E71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I71" s="107" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J71" s="107">
+        <f>D71*(E71+F71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="107">
+        <f>D71*H71</f>
+        <v/>
+      </c>
+      <c r="L71" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M71" s="124" t="n">
+        <v>10.001</v>
+      </c>
+      <c r="N71" s="107" t="n">
+        <v>1650165</v>
+      </c>
+      <c r="O71" s="107">
+        <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
+        <v/>
+      </c>
+      <c r="P71" s="105" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="106" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="103" t="inlineStr">
+      <c r="B72" s="105" t="inlineStr">
         <is>
           <t>Tê thép hàn tráng kẽm DN50</t>
         </is>
       </c>
-      <c r="C26" s="102" t="inlineStr">
+      <c r="C72" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D26" s="104">
-        <f>'Bao gia'!D14</f>
-        <v/>
-      </c>
-      <c r="E26" s="96" t="n">
+      <c r="D72" s="123" t="n">
+        <v>52</v>
+      </c>
+      <c r="E72" s="107" t="n">
         <v>75000</v>
       </c>
-      <c r="F26" s="96" t="n">
+      <c r="F72" s="107" t="n">
         <v>25000</v>
       </c>
-      <c r="G26" s="105">
-        <f>IF(E26="","",'Bao gia'!J14)</f>
-        <v/>
-      </c>
-      <c r="H26" s="105">
-        <f>IF(F26="","",'Bao gia'!K14)</f>
-        <v/>
-      </c>
-      <c r="I26" s="96">
-        <f>IF(E26="",0,D26*(E26+F26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="96">
-        <f>IF(E26="",0,D26*(G26+H26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="96">
-        <f>J26-I26</f>
-        <v/>
-      </c>
-      <c r="L26" s="97">
-        <f>IF(I26=0,"",K26/I26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="106">
-        <f>'Bao gia'!G14</f>
-        <v/>
-      </c>
-      <c r="N26" s="96">
-        <f>'Bao gia'!E14</f>
-        <v/>
-      </c>
-      <c r="O26" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P26" s="103" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="102" t="n">
+      <c r="G72" s="107">
+        <f>IF(M72=0,"",N72/M72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="104">
+        <f>ROUNDUP(E72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I72" s="107" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J72" s="107">
+        <f>D72*(E72+F72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="107">
+        <f>D72*H72</f>
+        <v/>
+      </c>
+      <c r="L72" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M72" s="124" t="n">
+        <v>52.0052</v>
+      </c>
+      <c r="N72" s="107" t="n">
+        <v>7800780</v>
+      </c>
+      <c r="O72" s="107">
+        <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
+        <v/>
+      </c>
+      <c r="P72" s="105" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="106" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="103" t="inlineStr">
+      <c r="B73" s="105" t="inlineStr">
         <is>
           <t>Tê giảm thép hàn DN100/65</t>
         </is>
       </c>
-      <c r="C27" s="102" t="inlineStr">
+      <c r="C73" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D27" s="104">
-        <f>'Bao gia'!D15</f>
-        <v/>
-      </c>
-      <c r="E27" s="96" t="n">
+      <c r="D73" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="107" t="n">
         <v>245000</v>
       </c>
-      <c r="F27" s="96" t="n">
+      <c r="F73" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G27" s="105">
-        <f>IF(E27="","",'Bao gia'!J15)</f>
-        <v/>
-      </c>
-      <c r="H27" s="105">
-        <f>IF(F27="","",'Bao gia'!K15)</f>
-        <v/>
-      </c>
-      <c r="I27" s="96">
-        <f>IF(E27="",0,D27*(E27+F27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="96">
-        <f>IF(E27="",0,D27*(G27+H27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="96">
-        <f>J27-I27</f>
-        <v/>
-      </c>
-      <c r="L27" s="97">
-        <f>IF(I27=0,"",K27/I27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="106">
-        <f>'Bao gia'!G15</f>
-        <v/>
-      </c>
-      <c r="N27" s="96">
-        <f>'Bao gia'!E15</f>
-        <v/>
-      </c>
-      <c r="O27" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P27" s="103" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="102" t="n">
+      <c r="G73" s="107">
+        <f>IF(M73=0,"",N73/M73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="104">
+        <f>ROUNDUP(E73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I73" s="107" t="n">
+        <v>113544</v>
+      </c>
+      <c r="J73" s="107">
+        <f>D73*(E73+F73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="107">
+        <f>D73*H73</f>
+        <v/>
+      </c>
+      <c r="L73" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M73" s="124" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N73" s="107" t="n">
+        <v>180018</v>
+      </c>
+      <c r="O73" s="107">
+        <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
+        <v/>
+      </c>
+      <c r="P73" s="105" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="106" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="103" t="inlineStr">
+      <c r="B74" s="105" t="inlineStr">
         <is>
           <t>Tê giảm thép hàn DN65/50</t>
         </is>
       </c>
-      <c r="C28" s="102" t="inlineStr">
+      <c r="C74" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D28" s="104">
-        <f>'Bao gia'!D16</f>
-        <v/>
-      </c>
-      <c r="E28" s="96" t="n">
+      <c r="D74" s="123" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="107" t="n">
         <v>190000</v>
       </c>
-      <c r="F28" s="96" t="n">
+      <c r="F74" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G28" s="105">
-        <f>IF(E28="","",'Bao gia'!J16)</f>
-        <v/>
-      </c>
-      <c r="H28" s="105">
-        <f>IF(F28="","",'Bao gia'!K16)</f>
-        <v/>
-      </c>
-      <c r="I28" s="96">
-        <f>IF(E28="",0,D28*(E28+F28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="96">
-        <f>IF(E28="",0,D28*(G28+H28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="96">
-        <f>J28-I28</f>
-        <v/>
-      </c>
-      <c r="L28" s="97">
-        <f>IF(I28=0,"",K28/I28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="106">
-        <f>'Bao gia'!G16</f>
-        <v/>
-      </c>
-      <c r="N28" s="96">
-        <f>'Bao gia'!E16</f>
-        <v/>
-      </c>
-      <c r="O28" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P28" s="103" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="102" t="n">
+      <c r="G74" s="107">
+        <f>IF(M74=0,"",N74/M74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="104">
+        <f>ROUNDUP(E74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I74" s="107" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J74" s="107">
+        <f>D74*(E74+F74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="107">
+        <f>D74*H74</f>
+        <v/>
+      </c>
+      <c r="L74" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M74" s="124" t="n">
+        <v>5.0005</v>
+      </c>
+      <c r="N74" s="107" t="n">
+        <v>750075</v>
+      </c>
+      <c r="O74" s="107">
+        <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
+        <v/>
+      </c>
+      <c r="P74" s="105" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="106" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="103" t="inlineStr">
+      <c r="B75" s="105" t="inlineStr">
         <is>
           <t>Côn giảm thép hàn DN80/65</t>
         </is>
       </c>
-      <c r="C29" s="102" t="inlineStr">
+      <c r="C75" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D29" s="104">
-        <f>'Bao gia'!D17</f>
-        <v/>
-      </c>
-      <c r="E29" s="96" t="n">
+      <c r="D75" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="107" t="n">
         <v>231000</v>
       </c>
-      <c r="F29" s="96" t="n">
+      <c r="F75" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G29" s="105">
-        <f>IF(E29="","",'Bao gia'!J17)</f>
-        <v/>
-      </c>
-      <c r="H29" s="105">
-        <f>IF(F29="","",'Bao gia'!K17)</f>
-        <v/>
-      </c>
-      <c r="I29" s="96">
-        <f>IF(E29="",0,D29*(E29+F29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="96">
-        <f>IF(E29="",0,D29*(G29+H29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="96">
-        <f>J29-I29</f>
-        <v/>
-      </c>
-      <c r="L29" s="97">
-        <f>IF(I29=0,"",K29/I29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="106">
-        <f>'Bao gia'!G17</f>
-        <v/>
-      </c>
-      <c r="N29" s="96">
-        <f>'Bao gia'!E17</f>
-        <v/>
-      </c>
-      <c r="O29" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P29" s="103" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="102" t="n">
+      <c r="G75" s="107">
+        <f>IF(M75=0,"",N75/M75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="104">
+        <f>ROUNDUP(E75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I75" s="107" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J75" s="107">
+        <f>D75*(E75+F75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="107">
+        <f>D75*H75</f>
+        <v/>
+      </c>
+      <c r="L75" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M75" s="124" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N75" s="107" t="n">
+        <v>80008</v>
+      </c>
+      <c r="O75" s="107">
+        <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
+        <v/>
+      </c>
+      <c r="P75" s="105" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="106" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="103" t="inlineStr">
+      <c r="B76" s="105" t="inlineStr">
         <is>
           <t>Mặt bích thép DN80</t>
         </is>
       </c>
-      <c r="C30" s="102" t="inlineStr">
+      <c r="C76" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D30" s="104">
-        <f>'Bao gia'!D18</f>
-        <v/>
-      </c>
-      <c r="E30" s="96" t="n">
+      <c r="D76" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="107" t="n">
         <v>95000</v>
       </c>
-      <c r="F30" s="96" t="n">
+      <c r="F76" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G30" s="105">
-        <f>IF(E30="","",'Bao gia'!J18)</f>
-        <v/>
-      </c>
-      <c r="H30" s="105">
-        <f>IF(F30="","",'Bao gia'!K18)</f>
-        <v/>
-      </c>
-      <c r="I30" s="96">
-        <f>IF(E30="",0,D30*(E30+F30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="96">
-        <f>IF(E30="",0,D30*(G30+H30))</f>
-        <v/>
-      </c>
-      <c r="K30" s="96">
-        <f>J30-I30</f>
-        <v/>
-      </c>
-      <c r="L30" s="97">
-        <f>IF(I30=0,"",K30/I30)</f>
-        <v/>
-      </c>
-      <c r="M30" s="106">
-        <f>'Bao gia'!G18</f>
-        <v/>
-      </c>
-      <c r="N30" s="96">
-        <f>'Bao gia'!E18</f>
-        <v/>
-      </c>
-      <c r="O30" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P30" s="103" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="102" t="n">
+      <c r="G76" s="107">
+        <f>IF(M76=0,"",N76/M76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="104">
+        <f>ROUNDUP(E76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I76" s="107" t="n">
+        <v>59926</v>
+      </c>
+      <c r="J76" s="107">
+        <f>D76*(E76+F76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="107">
+        <f>D76*H76</f>
+        <v/>
+      </c>
+      <c r="L76" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M76" s="124" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N76" s="107" t="n">
+        <v>321032.1</v>
+      </c>
+      <c r="O76" s="107">
+        <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
+        <v/>
+      </c>
+      <c r="P76" s="105" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="106" t="n">
         <v>16</v>
       </c>
-      <c r="B31" s="103" t="inlineStr">
+      <c r="B77" s="105" t="inlineStr">
         <is>
           <t>Roăng su DN80</t>
         </is>
       </c>
-      <c r="C31" s="102" t="inlineStr">
+      <c r="C77" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D31" s="104">
-        <f>'Bao gia'!D19</f>
-        <v/>
-      </c>
-      <c r="E31" s="96" t="n">
+      <c r="D77" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="107" t="n">
         <v>17000</v>
       </c>
-      <c r="F31" s="96" t="n">
+      <c r="F77" s="107" t="n">
         <v>11538</v>
       </c>
-      <c r="G31" s="105">
-        <f>IF(E31="","",'Bao gia'!J19)</f>
-        <v/>
-      </c>
-      <c r="H31" s="105">
-        <f>IF(F31="","",'Bao gia'!K19)</f>
-        <v/>
-      </c>
-      <c r="I31" s="96">
-        <f>IF(E31="",0,D31*(E31+F31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="96">
-        <f>IF(E31="",0,D31*(G31+H31))</f>
-        <v/>
-      </c>
-      <c r="K31" s="96">
-        <f>J31-I31</f>
-        <v/>
-      </c>
-      <c r="L31" s="97">
-        <f>IF(I31=0,"",K31/I31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="106">
-        <f>'Bao gia'!G19</f>
-        <v/>
-      </c>
-      <c r="N31" s="96">
-        <f>'Bao gia'!E19</f>
-        <v/>
-      </c>
-      <c r="O31" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P31" s="103" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="102" t="n">
+      <c r="G77" s="107">
+        <f>IF(M77=0,"",N77/M77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="104">
+        <f>ROUNDUP(E77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I77" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="107">
+        <f>D77*(E77+F77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="107">
+        <f>D77*H77</f>
+        <v/>
+      </c>
+      <c r="L77" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M77" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="107" t="n">
+        <v>150000</v>
+      </c>
+      <c r="O77" s="107">
+        <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
+        <v/>
+      </c>
+      <c r="P77" s="105" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="106" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="103">
-        <f>'[1]ĐƠN GIÁ'!B53</f>
-        <v/>
-      </c>
-      <c r="C32" s="102" t="inlineStr">
+      <c r="B78" s="105" t="inlineStr">
+        <is>
+          <t>Van 1 chiều DN80</t>
+        </is>
+      </c>
+      <c r="C78" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D32" s="104">
-        <f>'Bao gia'!D20</f>
-        <v/>
-      </c>
-      <c r="E32" s="96" t="n">
+      <c r="D78" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="107" t="n">
         <v>200000</v>
       </c>
-      <c r="F32" s="96" t="n">
+      <c r="F78" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G32" s="105">
-        <f>IF(E32="","",'Bao gia'!J20)</f>
-        <v/>
-      </c>
-      <c r="H32" s="105">
-        <f>IF(F32="","",'Bao gia'!K20)</f>
-        <v/>
-      </c>
-      <c r="I32" s="96">
-        <f>IF(E32="",0,D32*(E32+F32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="96">
-        <f>IF(E32="",0,D32*(G32+H32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="96">
-        <f>J32-I32</f>
-        <v/>
-      </c>
-      <c r="L32" s="97">
-        <f>IF(I32=0,"",K32/I32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="106">
-        <f>'Bao gia'!G20</f>
-        <v/>
-      </c>
-      <c r="N32" s="96">
-        <f>'Bao gia'!E20</f>
-        <v/>
-      </c>
-      <c r="O32" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P32" s="103" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="102" t="n">
+      <c r="G78" s="107">
+        <f>IF(M78=0,"",N78/M78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="104">
+        <f>ROUNDUP(E78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I78" s="107" t="n">
+        <v>97774</v>
+      </c>
+      <c r="J78" s="107">
+        <f>D78*(E78+F78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="107">
+        <f>D78*H78</f>
+        <v/>
+      </c>
+      <c r="L78" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M78" s="124" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N78" s="107" t="n">
+        <v>350035</v>
+      </c>
+      <c r="O78" s="107">
+        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
+        <v/>
+      </c>
+      <c r="P78" s="105" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="106" t="n">
         <v>18</v>
       </c>
-      <c r="B33" s="103" t="inlineStr">
+      <c r="B79" s="105" t="inlineStr">
         <is>
           <t>Rơ le kiểm tra mực nước</t>
         </is>
       </c>
-      <c r="C33" s="102" t="inlineStr">
+      <c r="C79" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D33" s="104">
-        <f>'Bao gia'!D21</f>
-        <v/>
-      </c>
-      <c r="E33" s="96" t="n">
+      <c r="D79" s="123" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="107" t="n">
         <v>2205000</v>
       </c>
-      <c r="F33" s="96" t="n">
+      <c r="F79" s="107" t="n">
         <v>150000</v>
       </c>
-      <c r="G33" s="105">
-        <f>IF(E33="","",'Bao gia'!J21)</f>
-        <v/>
-      </c>
-      <c r="H33" s="105">
-        <f>IF(F33="","",'Bao gia'!K21)</f>
-        <v/>
-      </c>
-      <c r="I33" s="96">
-        <f>IF(E33="",0,D33*(E33+F33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="96">
-        <f>IF(E33="",0,D33*(G33+H33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="96">
-        <f>J33-I33</f>
-        <v/>
-      </c>
-      <c r="L33" s="97">
-        <f>IF(I33=0,"",K33/I33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="106">
-        <f>'Bao gia'!G21</f>
-        <v/>
-      </c>
-      <c r="N33" s="96">
-        <f>'Bao gia'!E21</f>
-        <v/>
-      </c>
-      <c r="O33" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P33" s="103" t="inlineStr">
-        <is>
-          <t>Thiếu báo giá</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="102" t="n">
+      <c r="G79" s="107">
+        <f>IF(M79=0,"",N79/M79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="104">
+        <f>ROUNDUP(E79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I79" s="107" t="n">
+        <v>31540</v>
+      </c>
+      <c r="J79" s="107">
+        <f>D79*(E79+F79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="107">
+        <f>D79*H79</f>
+        <v/>
+      </c>
+      <c r="L79" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M79" s="124" t="n">
+        <v>4.0004</v>
+      </c>
+      <c r="N79" s="107" t="n">
+        <v>4600460</v>
+      </c>
+      <c r="O79" s="107">
+        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
+        <v/>
+      </c>
+      <c r="P79" s="105" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="106" t="n">
         <v>19</v>
       </c>
-      <c r="B34" s="103" t="inlineStr">
+      <c r="B80" s="105" t="inlineStr">
         <is>
           <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
         </is>
       </c>
-      <c r="C34" s="102" t="inlineStr">
+      <c r="C80" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D34" s="104">
-        <f>'Bao gia'!D22</f>
-        <v/>
-      </c>
-      <c r="E34" s="96" t="n">
+      <c r="D80" s="123" t="n">
+        <v>57</v>
+      </c>
+      <c r="E80" s="107" t="n">
         <v>368000</v>
       </c>
-      <c r="F34" s="96" t="n">
+      <c r="F80" s="107" t="n">
         <v>400000</v>
       </c>
-      <c r="G34" s="105">
-        <f>IF(E34="","",'Bao gia'!J22)</f>
-        <v/>
-      </c>
-      <c r="H34" s="105">
-        <f>IF(F34="","",'Bao gia'!K22)</f>
-        <v/>
-      </c>
-      <c r="I34" s="96">
-        <f>IF(E34="",0,D34*(E34+F34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="96">
-        <f>IF(E34="",0,D34*(G34+H34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="96">
-        <f>J34-I34</f>
-        <v/>
-      </c>
-      <c r="L34" s="97">
-        <f>IF(I34=0,"",K34/I34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="106">
-        <f>'Bao gia'!G22</f>
-        <v/>
-      </c>
-      <c r="N34" s="96">
-        <f>'Bao gia'!E22</f>
-        <v/>
-      </c>
-      <c r="O34" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P34" s="103" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="102" t="n">
+      <c r="G80" s="107">
+        <f>IF(M80=0,"",N80/M80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="104">
+        <f>ROUNDUP(E80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I80" s="107" t="n">
+        <v>94620</v>
+      </c>
+      <c r="J80" s="107">
+        <f>D80*(E80+F80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="107">
+        <f>D80*H80</f>
+        <v/>
+      </c>
+      <c r="L80" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M80" s="124" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="N80" s="107" t="n">
+        <v>19152000</v>
+      </c>
+      <c r="O80" s="107">
+        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
+        <v/>
+      </c>
+      <c r="P80" s="105" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="106" t="n">
         <v>20</v>
       </c>
-      <c r="B35" s="103" t="inlineStr">
+      <c r="B81" s="105" t="inlineStr">
         <is>
           <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
         </is>
       </c>
-      <c r="C35" s="102" t="inlineStr">
+      <c r="C81" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D35" s="104">
-        <f>'Bao gia'!D23</f>
-        <v/>
-      </c>
-      <c r="E35" s="96" t="n">
+      <c r="D81" s="123" t="n">
+        <v>70</v>
+      </c>
+      <c r="E81" s="107" t="n">
         <v>514286</v>
       </c>
-      <c r="F35" s="96" t="n">
+      <c r="F81" s="107" t="n">
         <v>58022</v>
       </c>
-      <c r="G35" s="105">
-        <f>IF(E35="","",'Bao gia'!J23)</f>
-        <v/>
-      </c>
-      <c r="H35" s="105">
-        <f>IF(F35="","",'Bao gia'!K23)</f>
-        <v/>
-      </c>
-      <c r="I35" s="96">
-        <f>IF(E35="",0,D35*(E35+F35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="96">
-        <f>IF(E35="",0,D35*(G35+H35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="96">
-        <f>J35-I35</f>
-        <v/>
-      </c>
-      <c r="L35" s="97">
-        <f>IF(I35=0,"",K35/I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="106">
-        <f>'Bao gia'!G23</f>
-        <v/>
-      </c>
-      <c r="N35" s="96">
-        <f>'Bao gia'!E23</f>
-        <v/>
-      </c>
-      <c r="O35" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần vòi</t>
-        </is>
-      </c>
-      <c r="P35" s="103" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="102" t="n">
+      <c r="G81" s="107">
+        <f>IF(M81=0,"",N81/M81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="104">
+        <f>ROUNDUP(E81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I81" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="107">
+        <f>D81*(E81+F81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="107">
+        <f>D81*H81</f>
+        <v/>
+      </c>
+      <c r="L81" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M81" s="124" t="n">
+        <v>70</v>
+      </c>
+      <c r="N81" s="107" t="n">
+        <v>33600000</v>
+      </c>
+      <c r="O81" s="107">
+        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
+        <v/>
+      </c>
+      <c r="P81" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="106" t="n">
         <v>21</v>
       </c>
-      <c r="B36" s="103" t="inlineStr">
+      <c r="B82" s="105" t="inlineStr">
         <is>
           <t>Lăng phun DN50</t>
         </is>
       </c>
-      <c r="C36" s="102" t="inlineStr">
+      <c r="C82" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D36" s="104">
-        <f>'Bao gia'!D24</f>
-        <v/>
-      </c>
-      <c r="E36" s="96" t="n">
+      <c r="D82" s="123" t="n">
+        <v>70</v>
+      </c>
+      <c r="E82" s="107" t="n">
         <v>85714</v>
       </c>
-      <c r="F36" s="96" t="n">
+      <c r="F82" s="107" t="n">
         <v>9670</v>
       </c>
-      <c r="G36" s="105">
-        <f>IF(E36="","",'Bao gia'!J24)</f>
-        <v/>
-      </c>
-      <c r="H36" s="105">
-        <f>IF(F36="","",'Bao gia'!K24)</f>
-        <v/>
-      </c>
-      <c r="I36" s="96">
-        <f>IF(E36="",0,D36*(E36+F36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="96">
-        <f>IF(E36="",0,D36*(G36+H36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="96">
-        <f>J36-I36</f>
-        <v/>
-      </c>
-      <c r="L36" s="97">
-        <f>IF(I36=0,"",K36/I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="106">
-        <f>'Bao gia'!G24</f>
-        <v/>
-      </c>
-      <c r="N36" s="96">
-        <f>'Bao gia'!E24</f>
-        <v/>
-      </c>
-      <c r="O36" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần lăng</t>
-        </is>
-      </c>
-      <c r="P36" s="103" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="102" t="n">
+      <c r="G82" s="107">
+        <f>IF(M82=0,"",N82/M82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="104">
+        <f>ROUNDUP(E82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I82" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="107">
+        <f>D82*(E82+F82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="107">
+        <f>D82*H82</f>
+        <v/>
+      </c>
+      <c r="L82" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M82" s="124" t="n">
+        <v>70</v>
+      </c>
+      <c r="N82" s="107" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="O82" s="107">
+        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
+        <v/>
+      </c>
+      <c r="P82" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="106" t="n">
         <v>22</v>
       </c>
-      <c r="B37" s="103" t="inlineStr">
+      <c r="B83" s="105" t="inlineStr">
         <is>
           <t>Van góc FUJI DN50</t>
         </is>
       </c>
-      <c r="C37" s="102" t="inlineStr">
+      <c r="C83" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D37" s="104">
-        <f>'Bao gia'!D25</f>
-        <v/>
-      </c>
-      <c r="E37" s="96" t="n">
+      <c r="D83" s="123" t="n">
+        <v>70</v>
+      </c>
+      <c r="E83" s="107" t="n">
         <v>166000</v>
       </c>
-      <c r="F37" s="96" t="n">
+      <c r="F83" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G37" s="105">
-        <f>IF(E37="","",'Bao gia'!J25)</f>
-        <v/>
-      </c>
-      <c r="H37" s="105">
-        <f>IF(F37="","",'Bao gia'!K25)</f>
-        <v/>
-      </c>
-      <c r="I37" s="96">
-        <f>IF(E37="",0,D37*(E37+F37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="96">
-        <f>IF(E37="",0,D37*(G37+H37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="96">
-        <f>J37-I37</f>
-        <v/>
-      </c>
-      <c r="L37" s="97">
-        <f>IF(I37=0,"",K37/I37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="106">
-        <f>'Bao gia'!G25</f>
-        <v/>
-      </c>
-      <c r="N37" s="96">
-        <f>'Bao gia'!E25</f>
-        <v/>
-      </c>
-      <c r="O37" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P37" s="103" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="102" t="n">
+      <c r="G83" s="107">
+        <f>IF(M83=0,"",N83/M83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="104">
+        <f>ROUNDUP(E83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I83" s="107" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J83" s="107">
+        <f>D83*(E83+F83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="107">
+        <f>D83*H83</f>
+        <v/>
+      </c>
+      <c r="L83" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M83" s="124" t="n">
+        <v>70.00700000000001</v>
+      </c>
+      <c r="N83" s="107" t="n">
+        <v>17501750</v>
+      </c>
+      <c r="O83" s="107">
+        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
+        <v/>
+      </c>
+      <c r="P83" s="105" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="106" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="103" t="inlineStr">
+      <c r="B84" s="105" t="inlineStr">
         <is>
           <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
         </is>
       </c>
-      <c r="C38" s="102" t="inlineStr">
+      <c r="C84" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D38" s="104">
-        <f>'Bao gia'!D26</f>
-        <v/>
-      </c>
-      <c r="E38" s="96" t="n">
+      <c r="D84" s="123" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="107" t="n">
         <v>53000</v>
       </c>
-      <c r="F38" s="96" t="n">
+      <c r="F84" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G38" s="105">
-        <f>IF(E38="","",'Bao gia'!J26)</f>
-        <v/>
-      </c>
-      <c r="H38" s="105">
-        <f>IF(F38="","",'Bao gia'!K26)</f>
-        <v/>
-      </c>
-      <c r="I38" s="96">
-        <f>IF(E38="",0,D38*(E38+F38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="96">
-        <f>IF(E38="",0,D38*(G38+H38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="96">
-        <f>J38-I38</f>
-        <v/>
-      </c>
-      <c r="L38" s="97">
-        <f>IF(I38=0,"",K38/I38)</f>
-        <v/>
-      </c>
-      <c r="M38" s="106">
-        <f>'Bao gia'!G26</f>
-        <v/>
-      </c>
-      <c r="N38" s="96">
-        <f>'Bao gia'!E26</f>
-        <v/>
-      </c>
-      <c r="O38" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P38" s="103" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="102" t="n">
+      <c r="G84" s="107">
+        <f>IF(M84=0,"",N84/M84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="104">
+        <f>ROUNDUP(E84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I84" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="107">
+        <f>D84*(E84+F84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="107">
+        <f>D84*H84</f>
+        <v/>
+      </c>
+      <c r="L84" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M84" s="124" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" s="107" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O84" s="107">
+        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
+        <v/>
+      </c>
+      <c r="P84" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="106" t="n">
         <v>24</v>
       </c>
-      <c r="B39" s="103" t="inlineStr">
+      <c r="B85" s="105" t="inlineStr">
         <is>
           <t>Kệ đỡ bình chữa cháy</t>
         </is>
       </c>
-      <c r="C39" s="102" t="inlineStr">
+      <c r="C85" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D39" s="104">
-        <f>'Bao gia'!D27</f>
-        <v/>
-      </c>
-      <c r="E39" s="96" t="n">
+      <c r="D85" s="123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" s="107" t="n">
         <v>137000</v>
       </c>
-      <c r="F39" s="96" t="n">
+      <c r="F85" s="107" t="n">
         <v>31538</v>
       </c>
-      <c r="G39" s="105">
-        <f>IF(E39="","",'Bao gia'!J27)</f>
-        <v/>
-      </c>
-      <c r="H39" s="105">
-        <f>IF(F39="","",'Bao gia'!K27)</f>
-        <v/>
-      </c>
-      <c r="I39" s="96">
-        <f>IF(E39="",0,D39*(E39+F39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="96">
-        <f>IF(E39="",0,D39*(G39+H39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="96">
-        <f>J39-I39</f>
-        <v/>
-      </c>
-      <c r="L39" s="97">
-        <f>IF(I39=0,"",K39/I39)</f>
-        <v/>
-      </c>
-      <c r="M39" s="106">
-        <f>'Bao gia'!G27</f>
-        <v/>
-      </c>
-      <c r="N39" s="96">
-        <f>'Bao gia'!E27</f>
-        <v/>
-      </c>
-      <c r="O39" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P39" s="103" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="102" t="n">
+      <c r="G85" s="107">
+        <f>IF(M85=0,"",N85/M85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="104">
+        <f>ROUNDUP(E85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I85" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="107">
+        <f>D85*(E85+F85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="107">
+        <f>D85*H85</f>
+        <v/>
+      </c>
+      <c r="L85" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M85" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="N85" s="107" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="O85" s="107">
+        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
+        <v/>
+      </c>
+      <c r="P85" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="106" t="n">
         <v>25</v>
       </c>
-      <c r="B40" s="103" t="inlineStr">
+      <c r="B86" s="105" t="inlineStr">
         <is>
           <t>BÌNH BỘT ABC 8KG</t>
         </is>
       </c>
-      <c r="C40" s="102" t="inlineStr">
+      <c r="C86" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D40" s="104">
-        <f>'Bao gia'!D28</f>
-        <v/>
-      </c>
-      <c r="E40" s="96" t="n">
+      <c r="D86" s="123" t="n">
+        <v>20</v>
+      </c>
+      <c r="E86" s="107" t="n">
         <v>652000</v>
       </c>
-      <c r="F40" s="96" t="n">
+      <c r="F86" s="107" t="n">
         <v>10769</v>
       </c>
-      <c r="G40" s="105">
-        <f>IF(E40="","",'Bao gia'!J28)</f>
-        <v/>
-      </c>
-      <c r="H40" s="105">
-        <f>IF(F40="","",'Bao gia'!K28)</f>
-        <v/>
-      </c>
-      <c r="I40" s="96">
-        <f>IF(E40="",0,D40*(E40+F40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="96">
-        <f>IF(E40="",0,D40*(G40+H40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="96">
-        <f>J40-I40</f>
-        <v/>
-      </c>
-      <c r="L40" s="97">
-        <f>IF(I40=0,"",K40/I40)</f>
-        <v/>
-      </c>
-      <c r="M40" s="106">
-        <f>'Bao gia'!G28</f>
-        <v/>
-      </c>
-      <c r="N40" s="96">
-        <f>'Bao gia'!E28</f>
-        <v/>
-      </c>
-      <c r="O40" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P40" s="103" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="102" t="n">
+      <c r="G86" s="107">
+        <f>IF(M86=0,"",N86/M86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="104">
+        <f>ROUNDUP(E86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I86" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="107">
+        <f>D86*(E86+F86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="107">
+        <f>D86*H86</f>
+        <v/>
+      </c>
+      <c r="L86" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M86" s="124" t="n">
+        <v>20</v>
+      </c>
+      <c r="N86" s="107" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="O86" s="107">
+        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
+        <v/>
+      </c>
+      <c r="P86" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="106" t="n">
         <v>26</v>
       </c>
-      <c r="B41" s="103" t="inlineStr">
+      <c r="B87" s="105" t="inlineStr">
         <is>
           <t>Đèn exit</t>
         </is>
       </c>
-      <c r="C41" s="102" t="inlineStr">
+      <c r="C87" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D41" s="104">
-        <f>'Bao gia'!D29</f>
-        <v/>
-      </c>
-      <c r="E41" s="96" t="n">
+      <c r="D87" s="123" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" s="107" t="n">
         <v>158000</v>
       </c>
-      <c r="F41" s="96" t="n">
+      <c r="F87" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G41" s="105">
-        <f>IF(E41="","",'Bao gia'!J29)</f>
-        <v/>
-      </c>
-      <c r="H41" s="105">
-        <f>IF(F41="","",'Bao gia'!K29)</f>
-        <v/>
-      </c>
-      <c r="I41" s="96">
-        <f>IF(E41="",0,D41*(E41+F41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="96">
-        <f>IF(E41="",0,D41*(G41+H41))</f>
-        <v/>
-      </c>
-      <c r="K41" s="96">
-        <f>J41-I41</f>
-        <v/>
-      </c>
-      <c r="L41" s="97">
-        <f>IF(I41=0,"",K41/I41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="106">
-        <f>'Bao gia'!G29</f>
-        <v/>
-      </c>
-      <c r="N41" s="96">
-        <f>'Bao gia'!E29</f>
-        <v/>
-      </c>
-      <c r="O41" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P41" s="103" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="102" t="n">
+      <c r="G87" s="107">
+        <f>IF(M87=0,"",N87/M87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="104">
+        <f>ROUNDUP(E87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I87" s="107" t="n">
+        <v>93090</v>
+      </c>
+      <c r="J87" s="107">
+        <f>D87*(E87+F87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="107">
+        <f>D87*H87</f>
+        <v/>
+      </c>
+      <c r="L87" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M87" s="124" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="N87" s="107" t="n">
+        <v>2310000</v>
+      </c>
+      <c r="O87" s="107">
+        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
+        <v/>
+      </c>
+      <c r="P87" s="105" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="106" t="n">
         <v>27</v>
       </c>
-      <c r="B42" s="103" t="inlineStr">
+      <c r="B88" s="105" t="inlineStr">
         <is>
           <t>Đèn chiếu sáng sự cố</t>
         </is>
       </c>
-      <c r="C42" s="102" t="inlineStr">
+      <c r="C88" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D42" s="104">
-        <f>'Bao gia'!D30</f>
-        <v/>
-      </c>
-      <c r="E42" s="96" t="n">
+      <c r="D88" s="123" t="n">
+        <v>54</v>
+      </c>
+      <c r="E88" s="107" t="n">
         <v>190000</v>
       </c>
-      <c r="F42" s="96" t="n">
+      <c r="F88" s="107" t="n">
         <v>100000</v>
       </c>
-      <c r="G42" s="105">
-        <f>IF(E42="","",'Bao gia'!J30)</f>
-        <v/>
-      </c>
-      <c r="H42" s="105">
-        <f>IF(F42="","",'Bao gia'!K30)</f>
-        <v/>
-      </c>
-      <c r="I42" s="96">
-        <f>IF(E42="",0,D42*(E42+F42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="96">
-        <f>IF(E42="",0,D42*(G42+H42))</f>
-        <v/>
-      </c>
-      <c r="K42" s="96">
-        <f>J42-I42</f>
-        <v/>
-      </c>
-      <c r="L42" s="97">
-        <f>IF(I42=0,"",K42/I42)</f>
-        <v/>
-      </c>
-      <c r="M42" s="106">
-        <f>'Bao gia'!G30</f>
-        <v/>
-      </c>
-      <c r="N42" s="96">
-        <f>'Bao gia'!E30</f>
-        <v/>
-      </c>
-      <c r="O42" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P42" s="103" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="102" t="n">
+      <c r="G88" s="107">
+        <f>IF(M88=0,"",N88/M88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="104">
+        <f>ROUNDUP(E88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I88" s="107" t="n">
+        <v>93090</v>
+      </c>
+      <c r="J88" s="107">
+        <f>D88*(E88+F88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="107">
+        <f>D88*H88</f>
+        <v/>
+      </c>
+      <c r="L88" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M88" s="124" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="N88" s="107" t="n">
+        <v>11340000</v>
+      </c>
+      <c r="O88" s="107">
+        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
+        <v/>
+      </c>
+      <c r="P88" s="105" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="106" t="n">
         <v>28</v>
       </c>
-      <c r="B43" s="103" t="inlineStr">
+      <c r="B89" s="105" t="inlineStr">
         <is>
           <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
         </is>
       </c>
-      <c r="C43" s="102" t="inlineStr">
+      <c r="C89" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D43" s="104">
-        <f>'Bao gia'!D32</f>
-        <v/>
-      </c>
-      <c r="E43" s="96" t="n">
+      <c r="D89" s="123" t="n">
+        <v>35</v>
+      </c>
+      <c r="E89" s="107" t="n">
         <v>442000</v>
       </c>
-      <c r="F43" s="96" t="n">
+      <c r="F89" s="107" t="n">
         <v>50000</v>
       </c>
-      <c r="G43" s="105">
-        <f>IF(E43="","",'Bao gia'!J32)</f>
-        <v/>
-      </c>
-      <c r="H43" s="105">
-        <f>IF(F43="","",'Bao gia'!K32)</f>
-        <v/>
-      </c>
-      <c r="I43" s="96">
-        <f>IF(E43="",0,D43*(E43+F43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="96">
-        <f>IF(E43="",0,D43*(G43+H43))</f>
-        <v/>
-      </c>
-      <c r="K43" s="96">
-        <f>J43-I43</f>
-        <v/>
-      </c>
-      <c r="L43" s="97">
-        <f>IF(I43=0,"",K43/I43)</f>
-        <v/>
-      </c>
-      <c r="M43" s="106">
-        <f>'Bao gia'!G32</f>
-        <v/>
-      </c>
-      <c r="N43" s="96">
-        <f>'Bao gia'!E32</f>
-        <v/>
-      </c>
-      <c r="O43" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P43" s="103" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="102" t="n">
+      <c r="G89" s="107">
+        <f>IF(M89=0,"",N89/M89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="104">
+        <f>ROUNDUP(E89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I89" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="107">
+        <f>D89*(E89+F89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="107">
+        <f>D89*H89</f>
+        <v/>
+      </c>
+      <c r="L89" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M89" s="124" t="n">
+        <v>35</v>
+      </c>
+      <c r="N89" s="107" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="O89" s="107">
+        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
+        <v/>
+      </c>
+      <c r="P89" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="106" t="n">
         <v>29</v>
       </c>
-      <c r="B44" s="103" t="inlineStr">
+      <c r="B90" s="105" t="inlineStr">
         <is>
           <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
         </is>
       </c>
-      <c r="C44" s="102" t="inlineStr">
+      <c r="C90" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D44" s="104">
-        <f>'Bao gia'!D33</f>
-        <v/>
-      </c>
-      <c r="E44" s="96" t="n">
+      <c r="D90" s="123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" s="107" t="n">
         <v>1260000</v>
       </c>
-      <c r="F44" s="96" t="n">
+      <c r="F90" s="107" t="n">
         <v>500000</v>
       </c>
-      <c r="G44" s="105">
-        <f>IF(E44="","",'Bao gia'!J33)</f>
-        <v/>
-      </c>
-      <c r="H44" s="105">
-        <f>IF(F44="","",'Bao gia'!K33)</f>
-        <v/>
-      </c>
-      <c r="I44" s="96">
-        <f>IF(E44="",0,D44*(E44+F44))</f>
-        <v/>
-      </c>
-      <c r="J44" s="96">
-        <f>IF(E44="",0,D44*(G44+H44))</f>
-        <v/>
-      </c>
-      <c r="K44" s="96">
-        <f>J44-I44</f>
-        <v/>
-      </c>
-      <c r="L44" s="97">
-        <f>IF(I44=0,"",K44/I44)</f>
-        <v/>
-      </c>
-      <c r="M44" s="106">
-        <f>'Bao gia'!G33</f>
-        <v/>
-      </c>
-      <c r="N44" s="96">
-        <f>'Bao gia'!E33</f>
-        <v/>
-      </c>
-      <c r="O44" s="103" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P44" s="103" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="107" t="n"/>
-      <c r="B45" s="107" t="inlineStr">
+      <c r="G90" s="107">
+        <f>IF(M90=0,"",N90/M90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="104">
+        <f>ROUNDUP(E90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I90" s="107" t="n">
+        <v>110390</v>
+      </c>
+      <c r="J90" s="107">
+        <f>D90*(E90+F90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="107">
+        <f>D90*H90</f>
+        <v/>
+      </c>
+      <c r="L90" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M90" s="124" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="N90" s="107" t="n">
+        <v>2852850</v>
+      </c>
+      <c r="O90" s="107">
+        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
+        <v/>
+      </c>
+      <c r="P90" s="105" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="120" t="n"/>
+      <c r="B91" s="120" t="inlineStr">
         <is>
           <t>CỘNG</t>
         </is>
       </c>
-      <c r="C45" s="107" t="n"/>
-      <c r="D45" s="107" t="n"/>
-      <c r="E45" s="107" t="n"/>
-      <c r="F45" s="107" t="n"/>
-      <c r="G45" s="107" t="n"/>
-      <c r="H45" s="107" t="n"/>
-      <c r="I45" s="99">
-        <f>SUM(I16:I44)</f>
-        <v/>
-      </c>
-      <c r="J45" s="99">
-        <f>SUM(J16:J44)</f>
-        <v/>
-      </c>
-      <c r="K45" s="99">
-        <f>SUM(K16:K44)</f>
-        <v/>
-      </c>
-      <c r="L45" s="100">
-        <f>IF(I45=0,"",K45/I45)</f>
-        <v/>
-      </c>
-      <c r="M45" s="107" t="n"/>
-      <c r="N45" s="107" t="n"/>
-      <c r="O45" s="107" t="n"/>
-      <c r="P45" s="107" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="108" t="inlineStr">
-        <is>
-          <t>GHI CHÚ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="B48" s="109" t="inlineStr">
-        <is>
-          <t>Khối lượng lấy theo cột D sheet 'Bao gia'. Máy bơm, bình, kệ, nội quy, sơ đồ lấy số lượng từ cột 'Tổng số lượng' sheet tb (đã điền công thức cộng các trường). Sheet tb dùng chung giá đề xuất với sheet 'Bao gia'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="B49" s="109" t="inlineStr">
-        <is>
-          <t>Không có giá vốn nên chưa tính: Đèn báo trạm bơm</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="B50" s="109" t="inlineStr">
-        <is>
-          <t>Báo giá chỉ gồm thiết bị và phụ kiện; chưa gồm ống thép, cáp tín hiệu, ống luồn, van, vật tư phụ 5% và phần xây dựng có trong sheet 'Gia von chi tiet'.</t>
-        </is>
+      <c r="C91" s="120" t="n"/>
+      <c r="D91" s="120" t="n"/>
+      <c r="E91" s="120" t="n"/>
+      <c r="F91" s="120" t="n"/>
+      <c r="G91" s="120" t="n"/>
+      <c r="H91" s="120" t="n"/>
+      <c r="I91" s="120" t="n"/>
+      <c r="J91" s="112">
+        <f>SUM(J62:J90)</f>
+        <v/>
+      </c>
+      <c r="K91" s="112">
+        <f>SUM(K62:K90)</f>
+        <v/>
+      </c>
+      <c r="L91" s="120" t="n"/>
+      <c r="M91" s="120" t="n"/>
+      <c r="N91" s="112">
+        <f>SUM(N62:N90)</f>
+        <v/>
+      </c>
+      <c r="O91" s="112">
+        <f>SUM(O62:O90)</f>
+        <v/>
+      </c>
+      <c r="P91" s="120" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="99" t="inlineStr">
+        <is>
+          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="100" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B94" s="100" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C94" s="100" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D94" s="100" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E94" s="100" t="inlineStr">
+        <is>
+          <t>Giá vốn VT</t>
+        </is>
+      </c>
+      <c r="F94" s="100" t="inlineStr">
+        <is>
+          <t>Giá vốn NC</t>
+        </is>
+      </c>
+      <c r="G94" s="100" t="inlineStr">
+        <is>
+          <t>Thành tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="115" t="n">
+        <v>1</v>
+      </c>
+      <c r="B95" s="105" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN65</t>
+        </is>
+      </c>
+      <c r="C95" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D95" s="123" t="n">
+        <v>860</v>
+      </c>
+      <c r="E95" s="107" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F95" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G95" s="107" t="n">
+        <v>206400000</v>
+      </c>
+      <c r="H95" s="89" t="inlineStr">
+        <is>
+          <t>Trong đó vật tư phụ 5%:</t>
+        </is>
+      </c>
+      <c r="J95" s="125">
+        <f>SUMIF(C95:C109,"Vật tư phụ",G95:G109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" s="105" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C96" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D96" s="123" t="n">
+        <v>570</v>
+      </c>
+      <c r="E96" s="107" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F96" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G96" s="107" t="n">
+        <v>125400000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="115" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="105" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN80</t>
+        </is>
+      </c>
+      <c r="C97" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D97" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="107" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F97" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G97" s="107" t="n">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C98" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D98" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="107" t="n"/>
+      <c r="F98" s="107" t="n"/>
+      <c r="G98" s="107" t="n">
+        <v>5345662</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="115" t="n">
+        <v>5</v>
+      </c>
+      <c r="B99" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C99" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D99" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="107" t="n"/>
+      <c r="F99" s="107" t="n"/>
+      <c r="G99" s="107" t="n">
+        <v>4422065</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="115" t="n">
+        <v>6</v>
+      </c>
+      <c r="B100" s="105" t="inlineStr">
+        <is>
+          <t>Dây nguồn đèn exit sự cố 2x0.75mm</t>
+        </is>
+      </c>
+      <c r="C100" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D100" s="123" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="107" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F100" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G100" s="107" t="n">
+        <v>21250000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="115" t="n">
+        <v>7</v>
+      </c>
+      <c r="B101" s="105" t="inlineStr">
+        <is>
+          <t>Ống luồn dây PVC D20</t>
+        </is>
+      </c>
+      <c r="C101" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D101" s="123" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E101" s="107" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F101" s="107" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G101" s="107" t="n">
+        <v>117000000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="115" t="n">
+        <v>8</v>
+      </c>
+      <c r="B102" s="105" t="inlineStr">
+        <is>
+          <t>Cáp tín hiệu 2x2x0,5mm2</t>
+        </is>
+      </c>
+      <c r="C102" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D102" s="123" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E102" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F102" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G102" s="107" t="n">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="115" t="n">
+        <v>9</v>
+      </c>
+      <c r="B103" s="105" t="inlineStr">
+        <is>
+          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
+        </is>
+      </c>
+      <c r="C103" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D103" s="123" t="n">
+        <v>130</v>
+      </c>
+      <c r="E103" s="107" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F103" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G103" s="107" t="n">
+        <v>1625000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="115" t="n">
+        <v>10</v>
+      </c>
+      <c r="B104" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C104" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D104" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="107" t="n"/>
+      <c r="F104" s="107" t="n"/>
+      <c r="G104" s="107" t="n">
+        <v>7726450</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="115" t="n">
+        <v>11</v>
+      </c>
+      <c r="B105" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C105" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D105" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="107" t="n"/>
+      <c r="F105" s="107" t="n"/>
+      <c r="G105" s="107" t="n">
+        <v>6964392</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="115" t="n">
+        <v>12</v>
+      </c>
+      <c r="B106" s="105" t="inlineStr">
+        <is>
+          <t>Ống nhựa xoắn HDPE 40/30</t>
+        </is>
+      </c>
+      <c r="C106" s="115" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D106" s="123" t="n">
+        <v>200</v>
+      </c>
+      <c r="E106" s="107" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F106" s="107" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G106" s="107" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="115" t="n">
+        <v>13</v>
+      </c>
+      <c r="B107" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C107" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D107" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="107" t="n"/>
+      <c r="F107" s="107" t="n"/>
+      <c r="G107" s="107" t="n">
+        <v>6135550</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="115" t="n">
+        <v>14</v>
+      </c>
+      <c r="B108" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C108" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D108" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="107" t="n"/>
+      <c r="F108" s="107" t="n"/>
+      <c r="G108" s="107" t="n">
+        <v>5017119</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="115" t="n">
+        <v>15</v>
+      </c>
+      <c r="B109" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C109" s="115" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D109" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="107" t="n"/>
+      <c r="F109" s="107" t="n"/>
+      <c r="G109" s="107" t="n">
+        <v>4482900</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="120" t="n"/>
+      <c r="B110" s="120" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C110" s="120" t="n"/>
+      <c r="D110" s="120" t="n"/>
+      <c r="E110" s="120" t="n"/>
+      <c r="F110" s="120" t="n"/>
+      <c r="G110" s="112">
+        <f>SUM(G95:G109)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B48:P48"/>
+  <mergeCells count="36">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="G43:K43"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B13:P13"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B49:P49"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B50:P50"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="G45:K45"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:P47"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G46:K46"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Báo giá 2.xlsx
+++ b/Báo giá 2.xlsx
@@ -14,7 +14,7 @@
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$L$35</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1" iterateCount="1"/>
 </workbook>
@@ -22,14 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="#,##0.##"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -175,6 +176,17 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
       <sz val="14"/>
     </font>
   </fonts>
@@ -287,7 +299,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,7 +479,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -476,14 +488,21 @@
     <xf numFmtId="3" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -492,14 +511,15 @@
     <xf numFmtId="9" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -531,9 +551,11 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -979,7 +1001,7 @@
     <col width="8.85546875" customWidth="1" style="51" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1062,15 +1084,19 @@
       </c>
       <c r="O3" s="83" t="inlineStr">
         <is>
+          <t>Giá vốn vật tư, thiết bị (lấy từ sheet Bao gia)</t>
+        </is>
+      </c>
+      <c r="P3" s="83" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="P3" s="83" t="inlineStr">
+      <c r="Q3" s="83" t="inlineStr">
         <is>
           <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
-      <c r="Q3" s="82" t="n"/>
       <c r="R3" s="82" t="n"/>
       <c r="S3" s="82" t="n"/>
     </row>
@@ -1099,7 +1125,7 @@
       <c r="N4" s="50" t="n"/>
       <c r="O4" s="84" t="n"/>
       <c r="P4" s="84" t="n"/>
-      <c r="Q4" s="82" t="n"/>
+      <c r="Q4" s="84" t="n"/>
       <c r="R4" s="82" t="n"/>
       <c r="S4" s="82" t="n"/>
     </row>
@@ -1148,14 +1174,17 @@
         </is>
       </c>
       <c r="O5" s="86">
+        <f>'Bao gia'!J26</f>
+        <v/>
+      </c>
+      <c r="P5" s="87">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="P5" s="87">
+      <c r="Q5" s="88">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
-      <c r="Q5" s="82" t="n"/>
       <c r="R5" s="82" t="n"/>
       <c r="S5" s="82" t="n"/>
     </row>
@@ -1206,14 +1235,17 @@
         </is>
       </c>
       <c r="O6" s="86">
+        <f>'Bao gia'!J27</f>
+        <v/>
+      </c>
+      <c r="P6" s="87">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="P6" s="87">
+      <c r="Q6" s="88">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
-      <c r="Q6" s="82" t="n"/>
       <c r="R6" s="82" t="n"/>
       <c r="S6" s="82" t="n"/>
     </row>
@@ -1264,14 +1296,17 @@
         </is>
       </c>
       <c r="O7" s="86">
+        <f>'Bao gia'!J28</f>
+        <v/>
+      </c>
+      <c r="P7" s="87">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="P7" s="87">
+      <c r="Q7" s="88">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
-      <c r="Q7" s="82" t="n"/>
       <c r="R7" s="82" t="n"/>
       <c r="S7" s="82" t="n"/>
     </row>
@@ -1328,14 +1363,17 @@
         </is>
       </c>
       <c r="O8" s="86">
-        <f>'Danh gia LN'!H89</f>
+        <f>'Bao gia'!J32</f>
         <v/>
       </c>
       <c r="P8" s="87">
-        <f>'Danh gia LN'!I89</f>
-        <v/>
-      </c>
-      <c r="Q8" s="82" t="n"/>
+        <f>'Danh gia LN'!H90</f>
+        <v/>
+      </c>
+      <c r="Q8" s="88">
+        <f>'Danh gia LN'!I90</f>
+        <v/>
+      </c>
       <c r="R8" s="82" t="n"/>
       <c r="S8" s="82" t="n"/>
     </row>
@@ -1373,7 +1411,7 @@
       </c>
       <c r="O9" s="84" t="n"/>
       <c r="P9" s="84" t="n"/>
-      <c r="Q9" s="82" t="n"/>
+      <c r="Q9" s="84" t="n"/>
       <c r="R9" s="82" t="n"/>
       <c r="S9" s="82" t="n"/>
     </row>
@@ -1400,7 +1438,7 @@
       <c r="N10" s="50" t="n"/>
       <c r="O10" s="84" t="n"/>
       <c r="P10" s="84" t="n"/>
-      <c r="Q10" s="82" t="n"/>
+      <c r="Q10" s="84" t="n"/>
       <c r="R10" s="82" t="n"/>
       <c r="S10" s="82" t="n"/>
     </row>
@@ -1442,7 +1480,7 @@
     <col width="10.85546875" customWidth="1" style="1" min="9" max="9"/>
     <col width="22" customWidth="1" style="1" min="10" max="16384"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -1517,15 +1555,19 @@
       </c>
       <c r="J3" s="83" t="inlineStr">
         <is>
+          <t>Giá vốn vật tư, thiết bị (điền giá chuẩn)</t>
+        </is>
+      </c>
+      <c r="K3" s="83" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="K3" s="83" t="inlineStr">
+      <c r="L3" s="83" t="inlineStr">
         <is>
           <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
-      <c r="L3" s="82" t="n"/>
       <c r="M3" s="82" t="n"/>
       <c r="N3" s="82" t="n"/>
     </row>
@@ -1565,15 +1607,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J4" s="86">
+      <c r="J4" s="89" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="K4" s="87">
         <f>'Danh gia LN'!H62</f>
         <v/>
       </c>
-      <c r="K4" s="87">
+      <c r="L4" s="88">
         <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
-      <c r="L4" s="82" t="n"/>
       <c r="M4" s="82" t="n"/>
       <c r="N4" s="82" t="n"/>
     </row>
@@ -1613,15 +1657,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J5" s="86">
+      <c r="J5" s="89" t="n">
+        <v>252000</v>
+      </c>
+      <c r="K5" s="87">
         <f>'Danh gia LN'!H63</f>
         <v/>
       </c>
-      <c r="K5" s="87">
+      <c r="L5" s="88">
         <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
-      <c r="L5" s="82" t="n"/>
       <c r="M5" s="82" t="n"/>
       <c r="N5" s="82" t="n"/>
     </row>
@@ -1662,15 +1708,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J6" s="86">
+      <c r="J6" s="89" t="n">
+        <v>205000</v>
+      </c>
+      <c r="K6" s="87">
         <f>'Danh gia LN'!H64</f>
         <v/>
       </c>
-      <c r="K6" s="87">
+      <c r="L6" s="88">
         <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
-      <c r="L6" s="82" t="n"/>
       <c r="M6" s="82" t="n"/>
       <c r="N6" s="82" t="n"/>
     </row>
@@ -1711,15 +1759,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J7" s="86">
+      <c r="J7" s="89" t="n">
+        <v>242000</v>
+      </c>
+      <c r="K7" s="87">
         <f>'Danh gia LN'!H65</f>
         <v/>
       </c>
-      <c r="K7" s="87">
+      <c r="L7" s="88">
         <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
-      <c r="L7" s="82" t="n"/>
       <c r="M7" s="82" t="n"/>
       <c r="N7" s="82" t="n"/>
     </row>
@@ -1760,15 +1810,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="89" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K8" s="87">
         <f>'Danh gia LN'!H66</f>
         <v/>
       </c>
-      <c r="K8" s="87">
+      <c r="L8" s="88">
         <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
-      <c r="L8" s="82" t="n"/>
       <c r="M8" s="82" t="n"/>
       <c r="N8" s="82" t="n"/>
     </row>
@@ -1809,15 +1861,17 @@
           <t>ấn độ</t>
         </is>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="89" t="n">
+        <v>252000</v>
+      </c>
+      <c r="K9" s="87">
         <f>'Danh gia LN'!H67</f>
         <v/>
       </c>
-      <c r="K9" s="87">
+      <c r="L9" s="88">
         <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
-      <c r="L9" s="82" t="n"/>
       <c r="M9" s="82" t="n"/>
       <c r="N9" s="82" t="n"/>
     </row>
@@ -1858,15 +1912,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J10" s="86">
+      <c r="J10" s="89" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K10" s="87">
         <f>'Danh gia LN'!H68</f>
         <v/>
       </c>
-      <c r="K10" s="87">
+      <c r="L10" s="88">
         <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
-      <c r="L10" s="82" t="n"/>
       <c r="M10" s="82" t="n"/>
       <c r="N10" s="82" t="n"/>
     </row>
@@ -1907,15 +1963,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J11" s="86">
+      <c r="J11" s="89" t="n">
+        <v>42000</v>
+      </c>
+      <c r="K11" s="87">
         <f>'Danh gia LN'!H69</f>
         <v/>
       </c>
-      <c r="K11" s="87">
+      <c r="L11" s="88">
         <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
-      <c r="L11" s="82" t="n"/>
       <c r="M11" s="82" t="n"/>
       <c r="N11" s="82" t="n"/>
     </row>
@@ -1956,15 +2014,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J12" s="86">
+      <c r="J12" s="89" t="n">
+        <v>95000</v>
+      </c>
+      <c r="K12" s="87">
         <f>'Danh gia LN'!H70</f>
         <v/>
       </c>
-      <c r="K12" s="87">
+      <c r="L12" s="88">
         <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
-      <c r="L12" s="82" t="n"/>
       <c r="M12" s="82" t="n"/>
       <c r="N12" s="82" t="n"/>
     </row>
@@ -2005,15 +2065,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J13" s="86">
+      <c r="J13" s="89" t="n">
+        <v>190000</v>
+      </c>
+      <c r="K13" s="87">
         <f>'Danh gia LN'!H71</f>
         <v/>
       </c>
-      <c r="K13" s="87">
+      <c r="L13" s="88">
         <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
-      <c r="L13" s="82" t="n"/>
       <c r="M13" s="82" t="n"/>
       <c r="N13" s="82" t="n"/>
     </row>
@@ -2054,15 +2116,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J14" s="86">
+      <c r="J14" s="89" t="n">
+        <v>75000</v>
+      </c>
+      <c r="K14" s="87">
         <f>'Danh gia LN'!H72</f>
         <v/>
       </c>
-      <c r="K14" s="87">
+      <c r="L14" s="88">
         <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
-      <c r="L14" s="82" t="n"/>
       <c r="M14" s="82" t="n"/>
       <c r="N14" s="82" t="n"/>
     </row>
@@ -2103,15 +2167,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J15" s="86">
+      <c r="J15" s="89" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K15" s="87">
         <f>'Danh gia LN'!H73</f>
         <v/>
       </c>
-      <c r="K15" s="87">
+      <c r="L15" s="88">
         <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
-      <c r="L15" s="82" t="n"/>
       <c r="M15" s="82" t="n"/>
       <c r="N15" s="82" t="n"/>
     </row>
@@ -2152,15 +2218,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J16" s="86">
+      <c r="J16" s="89" t="n">
+        <v>190000</v>
+      </c>
+      <c r="K16" s="87">
         <f>'Danh gia LN'!H74</f>
         <v/>
       </c>
-      <c r="K16" s="87">
+      <c r="L16" s="88">
         <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
-      <c r="L16" s="82" t="n"/>
       <c r="M16" s="82" t="n"/>
       <c r="N16" s="82" t="n"/>
     </row>
@@ -2201,15 +2269,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J17" s="86">
+      <c r="J17" s="89" t="n">
+        <v>231000</v>
+      </c>
+      <c r="K17" s="87">
         <f>'Danh gia LN'!H75</f>
         <v/>
       </c>
-      <c r="K17" s="87">
+      <c r="L17" s="88">
         <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
-      <c r="L17" s="82" t="n"/>
       <c r="M17" s="82" t="n"/>
       <c r="N17" s="82" t="n"/>
     </row>
@@ -2250,15 +2320,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J18" s="86">
+      <c r="J18" s="89" t="n">
+        <v>95000</v>
+      </c>
+      <c r="K18" s="87">
         <f>'Danh gia LN'!H76</f>
         <v/>
       </c>
-      <c r="K18" s="87">
+      <c r="L18" s="88">
         <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
-      <c r="L18" s="82" t="n"/>
       <c r="M18" s="82" t="n"/>
       <c r="N18" s="82" t="n"/>
     </row>
@@ -2299,15 +2371,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J19" s="86">
+      <c r="J19" s="89" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K19" s="87">
         <f>'Danh gia LN'!H77</f>
         <v/>
       </c>
-      <c r="K19" s="87">
+      <c r="L19" s="88">
         <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
-      <c r="L19" s="82" t="n"/>
       <c r="M19" s="82" t="n"/>
       <c r="N19" s="82" t="n"/>
     </row>
@@ -2347,15 +2421,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J20" s="86">
+      <c r="J20" s="89" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K20" s="87">
         <f>'Danh gia LN'!H78</f>
         <v/>
       </c>
-      <c r="K20" s="87">
+      <c r="L20" s="88">
         <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
-      <c r="L20" s="82" t="n"/>
       <c r="M20" s="82" t="n"/>
       <c r="N20" s="82" t="n"/>
     </row>
@@ -2394,15 +2470,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J21" s="86">
+      <c r="J21" s="89" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="K21" s="87">
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="K21" s="87">
+      <c r="L21" s="88">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
-      <c r="L21" s="82" t="n"/>
       <c r="M21" s="82" t="n"/>
       <c r="N21" s="82" t="n"/>
     </row>
@@ -2443,15 +2521,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J22" s="86">
+      <c r="J22" s="89" t="n">
+        <v>368000</v>
+      </c>
+      <c r="K22" s="87">
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="K22" s="87">
+      <c r="L22" s="88">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
-      <c r="L22" s="82" t="n"/>
       <c r="M22" s="82" t="n"/>
       <c r="N22" s="82" t="n"/>
     </row>
@@ -2492,15 +2572,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J23" s="86">
+      <c r="J23" s="89" t="n">
+        <v>514286</v>
+      </c>
+      <c r="K23" s="87">
         <f>'Danh gia LN'!H81</f>
         <v/>
       </c>
-      <c r="K23" s="87">
+      <c r="L23" s="88">
         <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
-      <c r="L23" s="82" t="n"/>
       <c r="M23" s="82" t="n"/>
       <c r="N23" s="82" t="n"/>
     </row>
@@ -2541,15 +2623,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J24" s="86">
+      <c r="J24" s="89" t="n">
+        <v>85714</v>
+      </c>
+      <c r="K24" s="87">
         <f>'Danh gia LN'!H82</f>
         <v/>
       </c>
-      <c r="K24" s="87">
+      <c r="L24" s="88">
         <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
-      <c r="L24" s="82" t="n"/>
       <c r="M24" s="82" t="n"/>
       <c r="N24" s="82" t="n"/>
     </row>
@@ -2590,15 +2674,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J25" s="86">
+      <c r="J25" s="89" t="n">
+        <v>166000</v>
+      </c>
+      <c r="K25" s="87">
         <f>'Danh gia LN'!H83</f>
         <v/>
       </c>
-      <c r="K25" s="87">
+      <c r="L25" s="88">
         <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
-      <c r="L25" s="82" t="n"/>
       <c r="M25" s="82" t="n"/>
       <c r="N25" s="82" t="n"/>
     </row>
@@ -2640,15 +2726,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J26" s="86">
+      <c r="J26" s="89" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K26" s="87">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="K26" s="87">
+      <c r="L26" s="88">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
-      <c r="L26" s="82" t="n"/>
       <c r="M26" s="82" t="n"/>
       <c r="N26" s="82" t="n"/>
     </row>
@@ -2690,15 +2778,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J27" s="86">
+      <c r="J27" s="89" t="n">
+        <v>137000</v>
+      </c>
+      <c r="K27" s="87">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="K27" s="87">
+      <c r="L27" s="88">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
-      <c r="L27" s="82" t="n"/>
       <c r="M27" s="82" t="n"/>
       <c r="N27" s="82" t="n"/>
     </row>
@@ -2740,15 +2830,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J28" s="86">
+      <c r="J28" s="89" t="n">
+        <v>652000</v>
+      </c>
+      <c r="K28" s="87">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="K28" s="87">
+      <c r="L28" s="88">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
-      <c r="L28" s="82" t="n"/>
       <c r="M28" s="82" t="n"/>
       <c r="N28" s="82" t="n"/>
     </row>
@@ -2789,15 +2881,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J29" s="86">
+      <c r="J29" s="89" t="n">
+        <v>158000</v>
+      </c>
+      <c r="K29" s="87">
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="K29" s="87">
+      <c r="L29" s="88">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
-      <c r="L29" s="82" t="n"/>
       <c r="M29" s="82" t="n"/>
       <c r="N29" s="82" t="n"/>
     </row>
@@ -2838,15 +2932,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J30" s="86">
+      <c r="J30" s="89" t="n">
+        <v>190000</v>
+      </c>
+      <c r="K30" s="87">
         <f>'Danh gia LN'!H88</f>
         <v/>
       </c>
-      <c r="K30" s="87">
+      <c r="L30" s="88">
         <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
-      <c r="L30" s="82" t="n"/>
       <c r="M30" s="82" t="n"/>
       <c r="N30" s="82" t="n"/>
     </row>
@@ -2883,9 +2979,15 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="84" t="n"/>
-      <c r="L31" s="82" t="n"/>
+      <c r="J31" s="89" t="n"/>
+      <c r="K31" s="87">
+        <f>'Danh gia LN'!H89</f>
+        <v/>
+      </c>
+      <c r="L31" s="88">
+        <f>'Danh gia LN'!I89</f>
+        <v/>
+      </c>
       <c r="M31" s="82" t="n"/>
       <c r="N31" s="82" t="n"/>
     </row>
@@ -2927,15 +3029,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J32" s="86">
-        <f>'Danh gia LN'!H89</f>
-        <v/>
+      <c r="J32" s="89" t="n">
+        <v>442000</v>
       </c>
       <c r="K32" s="87">
-        <f>'Danh gia LN'!I89</f>
-        <v/>
-      </c>
-      <c r="L32" s="82" t="n"/>
+        <f>'Danh gia LN'!H90</f>
+        <v/>
+      </c>
+      <c r="L32" s="88">
+        <f>'Danh gia LN'!I90</f>
+        <v/>
+      </c>
       <c r="M32" s="82" t="n"/>
       <c r="N32" s="82" t="n"/>
     </row>
@@ -2976,15 +3080,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J33" s="86">
-        <f>'Danh gia LN'!H90</f>
-        <v/>
+      <c r="J33" s="89" t="n">
+        <v>1260000</v>
       </c>
       <c r="K33" s="87">
-        <f>'Danh gia LN'!I90</f>
-        <v/>
-      </c>
-      <c r="L33" s="82" t="n"/>
+        <f>'Danh gia LN'!H91</f>
+        <v/>
+      </c>
+      <c r="L33" s="88">
+        <f>'Danh gia LN'!I91</f>
+        <v/>
+      </c>
       <c r="M33" s="82" t="n"/>
       <c r="N33" s="82" t="n"/>
     </row>
@@ -3010,7 +3116,7 @@
       <c r="I34" s="45" t="n"/>
       <c r="J34" s="84" t="n"/>
       <c r="K34" s="84" t="n"/>
-      <c r="L34" s="82" t="n"/>
+      <c r="L34" s="84" t="n"/>
       <c r="M34" s="82" t="n"/>
       <c r="N34" s="82" t="n"/>
     </row>
@@ -3033,7 +3139,7 @@
       <c r="I35" s="45" t="n"/>
       <c r="J35" s="84" t="n"/>
       <c r="K35" s="84" t="n"/>
-      <c r="L35" s="82" t="n"/>
+      <c r="L35" s="84" t="n"/>
       <c r="M35" s="82" t="n"/>
       <c r="N35" s="82" t="n"/>
     </row>
@@ -3053,7 +3159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P110"/>
+  <dimension ref="A1:W111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3072,3568 +3178,4000 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="90" t="inlineStr">
         <is>
           <t>ĐÁNH GIÁ GIÁ CHỐT PHẦN PCCC – HỆ THỐNG PCCC CÁC TRƯỜNG TIỂU HỌC, THCS PHƯỜNG ĐỒNG SƠN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>Chỉ điều chỉnh đơn giá vật tư/thiết bị có trong báo giá; nhân công theo định mức, các hạng mục khác giữ đơn giá dự toán. QLDA, tư vấn, nhà tạm, dự phòng tính lại theo công thức của bảng tổng dự toán. Giá vốn theo sheet 'Gia von chi tiet'.</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="R3" s="92" t="inlineStr">
+        <is>
+          <t>VÙNG TÍNH HỆ SỐ TỰ ĐỘNG (không cần sửa)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="B4" s="90" t="inlineStr">
+      <c r="B4" s="93" t="inlineStr">
         <is>
           <t>Lợi nhuận tối thiểu của bên thi công trên giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C4" s="91" t="n"/>
-      <c r="D4" s="92" t="n"/>
-      <c r="E4" s="93" t="n">
+      <c r="C4" s="94" t="n"/>
+      <c r="D4" s="95" t="n"/>
+      <c r="E4" s="96" t="n">
         <v>0.25</v>
       </c>
+      <c r="R4" s="92" t="inlineStr">
+        <is>
+          <t>Σ SL quy đổi × giá vốn VT – lắp đặt</t>
+        </is>
+      </c>
+      <c r="S4" s="97">
+        <f>SUMPRODUCT((L62:L91="Lắp đặt")*M62:M91*N(+E62:E91))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="90" t="inlineStr">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>Tỷ lệ trích lại chủ đầu tư (trên tổng dự toán gói sau VAT, đã làm tròn)</t>
         </is>
       </c>
-      <c r="C5" s="91" t="n"/>
-      <c r="D5" s="92" t="n"/>
-      <c r="E5" s="93" t="n">
+      <c r="C5" s="94" t="n"/>
+      <c r="D5" s="95" t="n"/>
+      <c r="E5" s="96" t="n">
         <v>0.15</v>
       </c>
+      <c r="R5" s="92" t="inlineStr">
+        <is>
+          <t>Σ SL × giá vốn – thiết bị</t>
+        </is>
+      </c>
+      <c r="S5" s="97">
+        <f>SUMPRODUCT((L62:L91="Thiết bị")*D62:D91*N(+E62:E91))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="90" t="inlineStr">
-        <is>
-          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (làm tròn lên nghìn)</t>
-        </is>
-      </c>
-      <c r="C6" s="91" t="n"/>
-      <c r="D6" s="92" t="n"/>
-      <c r="E6" s="94" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="F6" s="95" t="inlineStr">
-        <is>
-          <t>← giá trị nhỏ nhất đạt lợi nhuận tối thiểu (đã tính lặp)</t>
-        </is>
+      <c r="B6" s="93" t="inlineStr">
+        <is>
+          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (tự tính – hệ số nhỏ nhất đạt lợi nhuận ô E4)</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="n"/>
+      <c r="D6" s="95" t="n"/>
+      <c r="E6" s="98">
+        <f>ROUNDUP(MAX(1,$W$27),3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="99" t="inlineStr">
+        <is>
+          <t>← tự tính lại khi sửa giá vốn ở sheet Bao gia hoặc sửa ô E4, E5 (vùng tính phụ ở cột R–W)</t>
+        </is>
+      </c>
+      <c r="R6" s="92" t="inlineStr">
+        <is>
+          <t>VL dự toán hiện tại – lắp đặt</t>
+        </is>
+      </c>
+      <c r="S6" s="97">
+        <f>SUMIF(L62:L91,"Lắp đặt",N62:N91)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="90" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>Hệ số chi phí trực tiếp → chi phí xây dựng trước thuế: (1 + 7,3% + 2,5%) × (1 + 5,5%)</t>
         </is>
       </c>
-      <c r="C7" s="91" t="n"/>
-      <c r="D7" s="92" t="n"/>
-      <c r="E7" s="96">
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="95" t="n"/>
+      <c r="E7" s="100">
         <f>(1+7.3%+2.5%)*(1+5.5%)</f>
         <v/>
       </c>
+      <c r="R7" s="92" t="inlineStr">
+        <is>
+          <t>Giá vốn PCCC (C)</t>
+        </is>
+      </c>
+      <c r="S7" s="97">
+        <f>J92+G111</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="90" t="inlineStr">
-        <is>
-          <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – nhập bằng tổng dự toán làm tròn</t>
-        </is>
-      </c>
-      <c r="C8" s="91" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="97" t="n">
-        <v>2394000000</v>
-      </c>
-      <c r="F8" s="98">
-        <f>IF($E$8=H34,"Khớp tổng làm tròn","⚠ Nhập lại E8 = "&amp;TEXT(H34,"#,##0"))</f>
-        <v/>
+      <c r="B8" s="93" t="inlineStr">
+        <is>
+          <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – tự tính</t>
+        </is>
+      </c>
+      <c r="C8" s="94" t="n"/>
+      <c r="D8" s="95" t="n"/>
+      <c r="E8" s="101">
+        <f>ROUND(1.05*(H20+H21+H22+H28+500000)/(1-1.05*0.57%),-6)</f>
+        <v/>
+      </c>
+      <c r="F8" s="102">
+        <f>IF($E$8=H34,"Khớp tổng làm tròn","⚠ Lệch do làm tròn: tổng = "&amp;TEXT(H34,"#,##0"))</f>
+        <v/>
+      </c>
+      <c r="R8" s="92" t="inlineStr">
+        <is>
+          <t>Gxdct1 hiện tại</t>
+        </is>
+      </c>
+      <c r="S8" s="97" t="n">
+        <v>1215750394</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="R9" s="92" t="inlineStr">
+        <is>
+          <t>Xây lắp các trường (giữ nguyên)</t>
+        </is>
+      </c>
+      <c r="S9" s="97" t="n">
+        <v>378842471</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="103" t="inlineStr">
         <is>
           <t>A. TỔNG DỰ TOÁN GÓI – HIỆN TẠI VÀ SAU KHI CHỐT GIÁ PCCC</t>
         </is>
       </c>
+      <c r="R10" s="92" t="inlineStr">
+        <is>
+          <t>Đệm an toàn cho sai số làm tròn (đ)</t>
+        </is>
+      </c>
+      <c r="S10" s="97" t="n">
+        <v>300000</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="100" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>Khoản mục chi phí</t>
         </is>
       </c>
-      <c r="C11" s="100" t="inlineStr">
+      <c r="C11" s="104" t="inlineStr">
         <is>
           <t>Ký hiệu</t>
         </is>
       </c>
-      <c r="D11" s="100" t="inlineStr">
+      <c r="D11" s="104" t="inlineStr">
         <is>
           <t>Cách tính</t>
         </is>
       </c>
-      <c r="E11" s="100" t="inlineStr">
+      <c r="E11" s="104" t="inlineStr">
         <is>
           <t>Hiện tại (sau thuế)</t>
         </is>
       </c>
-      <c r="F11" s="100" t="inlineStr">
+      <c r="F11" s="104" t="inlineStr">
         <is>
           <t>Mới – trước thuế</t>
         </is>
       </c>
-      <c r="G11" s="100" t="inlineStr">
+      <c r="G11" s="104" t="inlineStr">
         <is>
           <t>Thuế VAT 8%</t>
         </is>
       </c>
-      <c r="H11" s="100" t="inlineStr">
+      <c r="H11" s="104" t="inlineStr">
         <is>
           <t>MỚI – SAU THUẾ</t>
         </is>
       </c>
-      <c r="I11" s="100" t="inlineStr">
+      <c r="I11" s="104" t="inlineStr">
         <is>
           <t>Chênh (sau thuế)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="101" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>Chi phí xây dựng phần PCCC (lắp đặt)</t>
         </is>
       </c>
-      <c r="C12" s="102" t="inlineStr">
+      <c r="C12" s="106" t="inlineStr">
         <is>
           <t>Gxdct1</t>
         </is>
       </c>
-      <c r="D12" s="101" t="inlineStr">
+      <c r="D12" s="105" t="inlineStr">
         <is>
           <t>Dự toán hiện tại + hệ số × chênh VT</t>
         </is>
       </c>
-      <c r="E12" s="103" t="n">
+      <c r="E12" s="107" t="n">
         <v>1313010000</v>
       </c>
-      <c r="F12" s="103">
-        <f>1215750394+SUM(O62:O90)</f>
-        <v/>
-      </c>
-      <c r="G12" s="103">
+      <c r="F12" s="107">
+        <f>1215750394+SUM(O62:O91)</f>
+        <v/>
+      </c>
+      <c r="G12" s="107">
         <f>F12*8%</f>
         <v/>
       </c>
-      <c r="H12" s="104">
+      <c r="H12" s="108">
         <f>ROUND(F12+G12,-3)</f>
         <v/>
       </c>
-      <c r="I12" s="103">
+      <c r="I12" s="107">
         <f>IF(E12="","",H12-E12)</f>
         <v/>
       </c>
+      <c r="R12" s="92" t="inlineStr">
+        <is>
+          <t>Điểm thử</t>
+        </is>
+      </c>
+      <c r="S12" s="92" t="inlineStr">
+        <is>
+          <t>m = 1</t>
+        </is>
+      </c>
+      <c r="T12" s="92" t="inlineStr">
+        <is>
+          <t>m = 3</t>
+        </is>
+      </c>
+      <c r="U12" s="92" t="inlineStr">
+        <is>
+          <t>m₃ (dây cung 1)</t>
+        </is>
+      </c>
+      <c r="V12" s="92" t="inlineStr">
+        <is>
+          <t>m₃ + 0,01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="105" t="inlineStr">
+      <c r="B13" s="109" t="inlineStr">
         <is>
           <t>Xây lắp Trường tiểu học Nghĩa Ninh</t>
         </is>
       </c>
-      <c r="C13" s="106" t="inlineStr">
+      <c r="C13" s="110" t="inlineStr">
         <is>
           <t>Gxdct2</t>
         </is>
       </c>
-      <c r="D13" s="105" t="inlineStr">
+      <c r="D13" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E13" s="107" t="n">
+      <c r="E13" s="111" t="n">
         <v>109257000</v>
       </c>
-      <c r="F13" s="107" t="n">
+      <c r="F13" s="111" t="n">
         <v>101163519</v>
       </c>
-      <c r="G13" s="107">
+      <c r="G13" s="111">
         <f>F13*8%</f>
         <v/>
       </c>
-      <c r="H13" s="108">
+      <c r="H13" s="112">
         <f>ROUND(F13+G13,-3)</f>
         <v/>
       </c>
-      <c r="I13" s="107">
+      <c r="I13" s="111">
         <f>IF(E13="","",H13-E13)</f>
         <v/>
       </c>
+      <c r="R13" s="92" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="S13" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="113" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" s="113">
+        <f>T13-T23*(T13-S13)/(T23-S23)</f>
+        <v/>
+      </c>
+      <c r="V13" s="113">
+        <f>U13+0.01</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="105" t="inlineStr">
+      <c r="B14" s="109" t="inlineStr">
         <is>
           <t>Xây lắp Trường tiểu học số 1 Đồng Sơn</t>
         </is>
       </c>
-      <c r="C14" s="106" t="inlineStr">
+      <c r="C14" s="110" t="inlineStr">
         <is>
           <t>Gxdct3</t>
         </is>
       </c>
-      <c r="D14" s="105" t="inlineStr">
+      <c r="D14" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E14" s="107" t="n">
+      <c r="E14" s="111" t="n">
         <v>42923000</v>
       </c>
-      <c r="F14" s="107" t="n">
+      <c r="F14" s="111" t="n">
         <v>39743608</v>
       </c>
-      <c r="G14" s="107">
+      <c r="G14" s="111">
         <f>F14*8%</f>
         <v/>
       </c>
-      <c r="H14" s="108">
+      <c r="H14" s="112">
         <f>ROUND(F14+G14,-3)</f>
         <v/>
       </c>
-      <c r="I14" s="107">
+      <c r="I14" s="111">
         <f>IF(E14="","",H14-E14)</f>
         <v/>
       </c>
+      <c r="R14" s="92" t="inlineStr">
+        <is>
+          <t>Gxdct1</t>
+        </is>
+      </c>
+      <c r="S14" s="97">
+        <f>$S$8+$E$7*(S13*$S$4-$S$6)</f>
+        <v/>
+      </c>
+      <c r="T14" s="97">
+        <f>$S$8+$E$7*(T13*$S$4-$S$6)</f>
+        <v/>
+      </c>
+      <c r="U14" s="97">
+        <f>$S$8+$E$7*(U13*$S$4-$S$6)</f>
+        <v/>
+      </c>
+      <c r="V14" s="97">
+        <f>$S$8+$E$7*(V13*$S$4-$S$6)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="105" t="inlineStr">
+      <c r="B15" s="109" t="inlineStr">
         <is>
           <t>Xây lắp Trường tiểu học số 2 Đồng Sơn</t>
         </is>
       </c>
-      <c r="C15" s="106" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr">
         <is>
           <t>Gxdct4</t>
         </is>
       </c>
-      <c r="D15" s="105" t="inlineStr">
+      <c r="D15" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E15" s="107" t="n">
+      <c r="E15" s="111" t="n">
         <v>86464000</v>
       </c>
-      <c r="F15" s="107" t="n">
+      <c r="F15" s="111" t="n">
         <v>80058943</v>
       </c>
-      <c r="G15" s="107">
+      <c r="G15" s="111">
         <f>F15*8%</f>
         <v/>
       </c>
-      <c r="H15" s="108">
+      <c r="H15" s="112">
         <f>ROUND(F15+G15,-3)</f>
         <v/>
       </c>
-      <c r="I15" s="107">
+      <c r="I15" s="111">
         <f>IF(E15="","",H15-E15)</f>
         <v/>
       </c>
+      <c r="R15" s="92" t="inlineStr">
+        <is>
+          <t>Gxdct</t>
+        </is>
+      </c>
+      <c r="S15" s="97">
+        <f>S14+$S$9</f>
+        <v/>
+      </c>
+      <c r="T15" s="97">
+        <f>T14+$S$9</f>
+        <v/>
+      </c>
+      <c r="U15" s="97">
+        <f>U14+$S$9</f>
+        <v/>
+      </c>
+      <c r="V15" s="97">
+        <f>V14+$S$9</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="105" t="inlineStr">
+      <c r="B16" s="109" t="inlineStr">
         <is>
           <t>Xây lắp Trường THCS số 1 Đồng Sơn</t>
         </is>
       </c>
-      <c r="C16" s="106" t="inlineStr">
+      <c r="C16" s="110" t="inlineStr">
         <is>
           <t>Gxdct5</t>
         </is>
       </c>
-      <c r="D16" s="105" t="inlineStr">
+      <c r="D16" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E16" s="107" t="n">
+      <c r="E16" s="111" t="n">
         <v>127297000</v>
       </c>
-      <c r="F16" s="107" t="n">
+      <c r="F16" s="111" t="n">
         <v>117867626</v>
       </c>
-      <c r="G16" s="107">
+      <c r="G16" s="111">
         <f>F16*8%</f>
         <v/>
       </c>
-      <c r="H16" s="108">
+      <c r="H16" s="112">
         <f>ROUND(F16+G16,-3)</f>
         <v/>
       </c>
-      <c r="I16" s="107">
+      <c r="I16" s="111">
         <f>IF(E16="","",H16-E16)</f>
         <v/>
       </c>
+      <c r="R16" s="92" t="inlineStr">
+        <is>
+          <t>GXD trước thuế</t>
+        </is>
+      </c>
+      <c r="S16" s="97">
+        <f>S15*1.011</f>
+        <v/>
+      </c>
+      <c r="T16" s="97">
+        <f>T15*1.011</f>
+        <v/>
+      </c>
+      <c r="U16" s="97">
+        <f>U15*1.011</f>
+        <v/>
+      </c>
+      <c r="V16" s="97">
+        <f>V15*1.011</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="105" t="inlineStr">
+      <c r="B17" s="109" t="inlineStr">
         <is>
           <t>Xây lắp Trường THCS Bắc Nghĩa</t>
         </is>
       </c>
-      <c r="C17" s="106" t="inlineStr">
+      <c r="C17" s="110" t="inlineStr">
         <is>
           <t>Gxdct6</t>
         </is>
       </c>
-      <c r="D17" s="105" t="inlineStr">
+      <c r="D17" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E17" s="107" t="n">
+      <c r="E17" s="111" t="n">
         <v>43209000</v>
       </c>
-      <c r="F17" s="107" t="n">
+      <c r="F17" s="111" t="n">
         <v>40008775</v>
       </c>
-      <c r="G17" s="107">
+      <c r="G17" s="111">
         <f>F17*8%</f>
         <v/>
       </c>
-      <c r="H17" s="108">
+      <c r="H17" s="112">
         <f>ROUND(F17+G17,-3)</f>
         <v/>
       </c>
-      <c r="I17" s="107">
+      <c r="I17" s="111">
         <f>IF(E17="","",H17-E17)</f>
         <v/>
       </c>
+      <c r="R17" s="92" t="inlineStr">
+        <is>
+          <t>Thiết bị trước thuế</t>
+        </is>
+      </c>
+      <c r="S17" s="97">
+        <f>S13*$S$5</f>
+        <v/>
+      </c>
+      <c r="T17" s="97">
+        <f>T13*$S$5</f>
+        <v/>
+      </c>
+      <c r="U17" s="97">
+        <f>U13*$S$5</f>
+        <v/>
+      </c>
+      <c r="V17" s="97">
+        <f>V13*$S$5</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="105" t="inlineStr">
+      <c r="B18" s="109" t="inlineStr">
         <is>
           <t>Chi phí xây dựng của công trình</t>
         </is>
       </c>
-      <c r="C18" s="106" t="inlineStr">
+      <c r="C18" s="110" t="inlineStr">
         <is>
           <t>Gxdct</t>
         </is>
       </c>
-      <c r="D18" s="105" t="inlineStr">
+      <c r="D18" s="109" t="inlineStr">
         <is>
           <t>Cộng</t>
         </is>
       </c>
-      <c r="E18" s="107" t="n"/>
-      <c r="F18" s="107">
+      <c r="E18" s="111" t="n"/>
+      <c r="F18" s="111">
         <f>SUM(F12:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="107">
+      <c r="G18" s="111">
         <f>F18*8%</f>
         <v/>
       </c>
-      <c r="H18" s="108">
+      <c r="H18" s="112">
         <f>ROUND(F18+G18,-3)</f>
         <v/>
       </c>
-      <c r="I18" s="107">
+      <c r="I18" s="111">
         <f>IF(E18="","",H18-E18)</f>
         <v/>
       </c>
+      <c r="R18" s="92" t="inlineStr">
+        <is>
+          <t>QLDA</t>
+        </is>
+      </c>
+      <c r="S18" s="97">
+        <f>(S16+S17)*3.446%</f>
+        <v/>
+      </c>
+      <c r="T18" s="97">
+        <f>(T16+T17)*3.446%</f>
+        <v/>
+      </c>
+      <c r="U18" s="97">
+        <f>(U16+U17)*3.446%</f>
+        <v/>
+      </c>
+      <c r="V18" s="97">
+        <f>(V16+V17)*3.446%</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="105" t="inlineStr">
+      <c r="B19" s="109" t="inlineStr">
         <is>
           <t>Chi phí nhà tạm để ở và điều hành thi công</t>
         </is>
       </c>
-      <c r="C19" s="106" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr">
         <is>
           <t>Glt</t>
         </is>
       </c>
-      <c r="D19" s="105" t="inlineStr">
+      <c r="D19" s="109" t="inlineStr">
         <is>
           <t>1,1% × Gxdct</t>
         </is>
       </c>
-      <c r="E19" s="107" t="n"/>
-      <c r="F19" s="107">
+      <c r="E19" s="111" t="n"/>
+      <c r="F19" s="111">
         <f>F18*1.1%</f>
         <v/>
       </c>
-      <c r="G19" s="107">
+      <c r="G19" s="111">
         <f>F19*8%</f>
         <v/>
       </c>
-      <c r="H19" s="108">
+      <c r="H19" s="112">
         <f>ROUND(F19+G19,-3)</f>
         <v/>
       </c>
-      <c r="I19" s="107">
+      <c r="I19" s="111">
         <f>IF(E19="","",H19-E19)</f>
         <v/>
       </c>
+      <c r="R19" s="92" t="inlineStr">
+        <is>
+          <t>Tư vấn (sau thuế)</t>
+        </is>
+      </c>
+      <c r="S19" s="97">
+        <f>25000000+1.08*((S15+S17)*((3-(S16+S17)/10^9)*0.9+4.7)/100+S15*0.508%)</f>
+        <v/>
+      </c>
+      <c r="T19" s="97">
+        <f>25000000+1.08*((T15+T17)*((3-(T16+T17)/10^9)*0.9+4.7)/100+T15*0.508%)</f>
+        <v/>
+      </c>
+      <c r="U19" s="97">
+        <f>25000000+1.08*((U15+U17)*((3-(U16+U17)/10^9)*0.9+4.7)/100+U15*0.508%)</f>
+        <v/>
+      </c>
+      <c r="V19" s="97">
+        <f>25000000+1.08*((V15+V17)*((3-(V16+V17)/10^9)*0.9+4.7)/100+V15*0.508%)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="90" t="inlineStr">
+      <c r="B20" s="93" t="inlineStr">
         <is>
           <t>I. CHI PHÍ XÂY LẮP</t>
         </is>
       </c>
-      <c r="C20" s="109" t="inlineStr">
+      <c r="C20" s="114" t="inlineStr">
         <is>
           <t>GXD</t>
         </is>
       </c>
-      <c r="D20" s="90" t="inlineStr">
+      <c r="D20" s="93" t="inlineStr">
         <is>
           <t>Gxdct + Glt</t>
         </is>
       </c>
-      <c r="E20" s="108" t="n">
+      <c r="E20" s="112" t="n">
         <v>1741104000</v>
       </c>
-      <c r="F20" s="108">
+      <c r="F20" s="112">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="112">
         <f>F20*8%</f>
         <v/>
       </c>
-      <c r="H20" s="108">
+      <c r="H20" s="112">
         <f>ROUND(F20+G20,-3)</f>
         <v/>
       </c>
-      <c r="I20" s="108">
+      <c r="I20" s="112">
         <f>IF(E20="","",H20-E20)</f>
         <v/>
       </c>
+      <c r="R20" s="92" t="inlineStr">
+        <is>
+          <t>Tổng gói (ước)</t>
+        </is>
+      </c>
+      <c r="S20" s="97">
+        <f>1.05*(1.08*S16+1.08*S17+S18+S19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
+      <c r="T20" s="97">
+        <f>1.05*(1.08*T16+1.08*T17+T18+T19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
+      <c r="U20" s="97">
+        <f>1.05*(1.08*U16+1.08*U17+U18+U19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
+      <c r="V20" s="97">
+        <f>1.05*(1.08*V16+1.08*V17+V18+V19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="90" t="inlineStr">
+      <c r="B21" s="93" t="inlineStr">
         <is>
           <t>II. CHI PHÍ THIẾT BỊ</t>
         </is>
       </c>
-      <c r="C21" s="109" t="inlineStr">
+      <c r="C21" s="114" t="inlineStr">
         <is>
           <t>Gtb</t>
         </is>
       </c>
-      <c r="D21" s="90" t="inlineStr">
+      <c r="D21" s="93" t="inlineStr">
         <is>
           <t>Σ thiết bị × giá chốt</t>
         </is>
       </c>
-      <c r="E21" s="108" t="n">
+      <c r="E21" s="112" t="n">
         <v>18954000</v>
       </c>
-      <c r="F21" s="108">
-        <f>SUMIF(L62:L90,"Thiết bị",K62:K90)</f>
-        <v/>
-      </c>
-      <c r="G21" s="108">
+      <c r="F21" s="112">
+        <f>SUMIF(L62:L91,"Thiết bị",K62:K91)</f>
+        <v/>
+      </c>
+      <c r="G21" s="112">
         <f>F21*8%</f>
         <v/>
       </c>
-      <c r="H21" s="108">
+      <c r="H21" s="112">
         <f>F21*1.08</f>
         <v/>
       </c>
-      <c r="I21" s="108">
+      <c r="I21" s="112">
         <f>IF(E21="","",H21-E21)</f>
         <v/>
       </c>
+      <c r="R21" s="92" t="inlineStr">
+        <is>
+          <t>Doanh thu PCCC</t>
+        </is>
+      </c>
+      <c r="S21" s="97">
+        <f>S14*1.011+S17</f>
+        <v/>
+      </c>
+      <c r="T21" s="97">
+        <f>T14*1.011+T17</f>
+        <v/>
+      </c>
+      <c r="U21" s="97">
+        <f>U14*1.011+U17</f>
+        <v/>
+      </c>
+      <c r="V21" s="97">
+        <f>V14*1.011+V17</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="90" t="inlineStr">
+      <c r="B22" s="93" t="inlineStr">
         <is>
           <t>III. CHI PHÍ QUẢN LÝ DỰ ÁN</t>
         </is>
       </c>
-      <c r="C22" s="109" t="inlineStr">
+      <c r="C22" s="114" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="D22" s="90" t="inlineStr">
+      <c r="D22" s="93" t="inlineStr">
         <is>
           <t>3,446% × (GXD + Gtb)</t>
         </is>
       </c>
-      <c r="E22" s="108" t="n">
+      <c r="E22" s="112" t="n">
         <v>56159000</v>
       </c>
-      <c r="F22" s="108">
+      <c r="F22" s="112">
         <f>(F20+F21)*3.446%</f>
         <v/>
       </c>
-      <c r="G22" s="108" t="n"/>
-      <c r="H22" s="108">
+      <c r="G22" s="112" t="n"/>
+      <c r="H22" s="112">
         <f>ROUND(F22,-3)</f>
         <v/>
       </c>
-      <c r="I22" s="108">
+      <c r="I22" s="112">
         <f>IF(E22="","",H22-E22)</f>
         <v/>
       </c>
+      <c r="R22" s="92" t="inlineStr">
+        <is>
+          <t>Trích CĐT</t>
+        </is>
+      </c>
+      <c r="S22" s="97">
+        <f>$E$5*S20</f>
+        <v/>
+      </c>
+      <c r="T22" s="97">
+        <f>$E$5*T20</f>
+        <v/>
+      </c>
+      <c r="U22" s="97">
+        <f>$E$5*U20</f>
+        <v/>
+      </c>
+      <c r="V22" s="97">
+        <f>$E$5*V20</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="105" t="inlineStr">
+      <c r="B23" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí đo vẽ hiện trạng</t>
         </is>
       </c>
-      <c r="C23" s="106" t="inlineStr">
+      <c r="C23" s="110" t="inlineStr">
         <is>
           <t>TV1</t>
         </is>
       </c>
-      <c r="D23" s="105" t="inlineStr">
+      <c r="D23" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E23" s="107" t="n">
+      <c r="E23" s="111" t="n">
         <v>15000000</v>
       </c>
-      <c r="F23" s="107">
+      <c r="F23" s="111">
         <f>15000000/1.08</f>
         <v/>
       </c>
-      <c r="G23" s="107">
+      <c r="G23" s="111">
         <f>F23*8%</f>
         <v/>
       </c>
-      <c r="H23" s="108">
+      <c r="H23" s="112">
         <f>15000000</f>
         <v/>
       </c>
-      <c r="I23" s="107">
+      <c r="I23" s="111">
         <f>IF(E23="","",H23-E23)</f>
         <v/>
       </c>
+      <c r="R23" s="92" t="inlineStr">
+        <is>
+          <t>f(m) = DT − C − trích − LN tối thiểu</t>
+        </is>
+      </c>
+      <c r="S23" s="97">
+        <f>S21-$S$7-S22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
+      <c r="T23" s="97">
+        <f>T21-$S$7-T22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
+      <c r="U23" s="97">
+        <f>U21-$S$7-U22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
+      <c r="V23" s="97">
+        <f>V21-$S$7-V22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="105" t="inlineStr">
+      <c r="B24" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí lập báo cáo KTKT (nội suy theo quy mô)</t>
         </is>
       </c>
-      <c r="C24" s="106" t="inlineStr">
+      <c r="C24" s="110" t="inlineStr">
         <is>
           <t>TV2</t>
         </is>
       </c>
-      <c r="D24" s="105" t="inlineStr">
+      <c r="D24" s="109" t="inlineStr">
         <is>
           <t>(Gxdct + Gtb) × tỷ lệ nội suy</t>
         </is>
       </c>
-      <c r="E24" s="107" t="n"/>
-      <c r="F24" s="107">
+      <c r="E24" s="111" t="n"/>
+      <c r="F24" s="111">
         <f>(F18+F21)*(((3-(F20+F21)/10^9)*(6.5-4.7)/(3-1)+4.7)/100)</f>
         <v/>
       </c>
-      <c r="G24" s="107">
+      <c r="G24" s="111">
         <f>F24*8%</f>
         <v/>
       </c>
-      <c r="H24" s="108">
+      <c r="H24" s="112">
         <f>ROUND(F24+G24,-3)</f>
         <v/>
       </c>
-      <c r="I24" s="107">
+      <c r="I24" s="111">
         <f>IF(E24="","",H24-E24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="105" t="inlineStr">
+      <c r="B25" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra thiết kế BVTC</t>
         </is>
       </c>
-      <c r="C25" s="106" t="inlineStr">
+      <c r="C25" s="110" t="inlineStr">
         <is>
           <t>TV3</t>
         </is>
       </c>
-      <c r="D25" s="105" t="inlineStr">
+      <c r="D25" s="109" t="inlineStr">
         <is>
           <t>0,258% × Gxdct</t>
         </is>
       </c>
-      <c r="E25" s="107" t="n"/>
-      <c r="F25" s="107">
+      <c r="E25" s="111" t="n"/>
+      <c r="F25" s="111">
         <f>F18*0.258%</f>
         <v/>
       </c>
-      <c r="G25" s="107">
+      <c r="G25" s="111">
         <f>F25*8%</f>
         <v/>
       </c>
-      <c r="H25" s="108">
+      <c r="H25" s="112">
         <f>ROUND(F25+G25,-3)</f>
         <v/>
       </c>
-      <c r="I25" s="107">
+      <c r="I25" s="111">
         <f>IF(E25="","",H25-E25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="105" t="inlineStr">
+      <c r="B26" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra dự toán</t>
         </is>
       </c>
-      <c r="C26" s="106" t="inlineStr">
+      <c r="C26" s="110" t="inlineStr">
         <is>
           <t>TV4</t>
         </is>
       </c>
-      <c r="D26" s="105" t="inlineStr">
+      <c r="D26" s="109" t="inlineStr">
         <is>
           <t>0,25% × Gxdct</t>
         </is>
       </c>
-      <c r="E26" s="107" t="n"/>
-      <c r="F26" s="107">
+      <c r="E26" s="111" t="n"/>
+      <c r="F26" s="111">
         <f>F18*0.25%</f>
         <v/>
       </c>
-      <c r="G26" s="107">
+      <c r="G26" s="111">
         <f>F26*8%</f>
         <v/>
       </c>
-      <c r="H26" s="108">
+      <c r="H26" s="112">
         <f>ROUND(F26+G26,-3)</f>
         <v/>
       </c>
-      <c r="I26" s="107">
+      <c r="I26" s="111">
         <f>IF(E26="","",H26-E26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="105" t="inlineStr">
+      <c r="B27" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm định giá</t>
         </is>
       </c>
-      <c r="C27" s="106" t="inlineStr">
+      <c r="C27" s="110" t="inlineStr">
         <is>
           <t>TV5</t>
         </is>
       </c>
-      <c r="D27" s="105" t="inlineStr">
+      <c r="D27" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E27" s="107" t="n">
+      <c r="E27" s="111" t="n">
         <v>10000000</v>
       </c>
-      <c r="F27" s="107">
+      <c r="F27" s="111">
         <f>10000000/1.08</f>
         <v/>
       </c>
-      <c r="G27" s="107">
+      <c r="G27" s="111">
         <f>F27*8%</f>
         <v/>
       </c>
-      <c r="H27" s="108">
+      <c r="H27" s="112">
         <f>10000000</f>
         <v/>
       </c>
-      <c r="I27" s="107">
+      <c r="I27" s="111">
         <f>IF(E27="","",H27-E27)</f>
         <v/>
       </c>
+      <c r="R27" s="92" t="inlineStr">
+        <is>
+          <t>Hệ số tối thiểu (dây cung lần 2)</t>
+        </is>
+      </c>
+      <c r="W27" s="115">
+        <f>U13-U23*(V13-U13)/(V23-U23)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="90" t="inlineStr">
+      <c r="B28" s="93" t="inlineStr">
         <is>
           <t>IV. CHI PHÍ TƯ VẤN</t>
         </is>
       </c>
-      <c r="C28" s="109" t="inlineStr">
+      <c r="C28" s="114" t="inlineStr">
         <is>
           <t>GTV</t>
         </is>
       </c>
-      <c r="D28" s="90" t="inlineStr">
+      <c r="D28" s="93" t="inlineStr">
         <is>
           <t>Cộng TV1–TV5</t>
         </is>
       </c>
-      <c r="E28" s="108" t="n">
+      <c r="E28" s="112" t="n">
         <v>137053000</v>
       </c>
-      <c r="F28" s="108" t="n"/>
-      <c r="G28" s="108" t="n"/>
-      <c r="H28" s="108">
+      <c r="F28" s="112" t="n"/>
+      <c r="G28" s="112" t="n"/>
+      <c r="H28" s="112">
         <f>ROUND(SUM(H23:H27),-3)</f>
         <v/>
       </c>
-      <c r="I28" s="108">
+      <c r="I28" s="112">
         <f>IF(E28="","",H28-E28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="105" t="inlineStr">
+      <c r="B29" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra phê duyệt quyết toán</t>
         </is>
       </c>
-      <c r="C29" s="106" t="inlineStr">
+      <c r="C29" s="110" t="inlineStr">
         <is>
           <t>CK1</t>
         </is>
       </c>
-      <c r="D29" s="105" t="inlineStr">
+      <c r="D29" s="109" t="inlineStr">
         <is>
           <t>0,57% × TM (ô E8)</t>
         </is>
       </c>
-      <c r="E29" s="107" t="n"/>
-      <c r="F29" s="107">
+      <c r="E29" s="111" t="n"/>
+      <c r="F29" s="111">
         <f>0.57%*$E$8</f>
         <v/>
       </c>
-      <c r="G29" s="107" t="n"/>
-      <c r="H29" s="108">
+      <c r="G29" s="111" t="n"/>
+      <c r="H29" s="112">
         <f>ROUND(F29,-3)</f>
         <v/>
       </c>
-      <c r="I29" s="107">
+      <c r="I29" s="111">
         <f>IF(E29="","",H29-E29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="105" t="inlineStr">
+      <c r="B30" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">   Phí thẩm định báo cáo KTKT</t>
         </is>
       </c>
-      <c r="C30" s="106" t="inlineStr">
+      <c r="C30" s="110" t="inlineStr">
         <is>
           <t>CK2</t>
         </is>
       </c>
-      <c r="D30" s="105" t="inlineStr">
+      <c r="D30" s="109" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E30" s="107" t="n">
+      <c r="E30" s="111" t="n">
         <v>500000</v>
       </c>
-      <c r="F30" s="107" t="n">
+      <c r="F30" s="111" t="n">
         <v>500000</v>
       </c>
-      <c r="G30" s="107" t="n"/>
-      <c r="H30" s="108">
+      <c r="G30" s="111" t="n"/>
+      <c r="H30" s="112">
         <f>ROUND(F30,-3)</f>
         <v/>
       </c>
-      <c r="I30" s="107">
+      <c r="I30" s="111">
         <f>IF(E30="","",H30-E30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="90" t="inlineStr">
+      <c r="B31" s="93" t="inlineStr">
         <is>
           <t>V. CHI PHÍ KHÁC</t>
         </is>
       </c>
-      <c r="C31" s="109" t="inlineStr">
+      <c r="C31" s="114" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="D31" s="90" t="inlineStr">
+      <c r="D31" s="93" t="inlineStr">
         <is>
           <t>CK1 + CK2</t>
         </is>
       </c>
-      <c r="E31" s="108" t="n">
+      <c r="E31" s="112" t="n">
         <v>12265000</v>
       </c>
-      <c r="F31" s="108" t="n"/>
-      <c r="G31" s="108" t="n"/>
-      <c r="H31" s="108">
+      <c r="F31" s="112" t="n"/>
+      <c r="G31" s="112" t="n"/>
+      <c r="H31" s="112">
         <f>ROUND(H29+H30,-3)</f>
         <v/>
       </c>
-      <c r="I31" s="108">
+      <c r="I31" s="112">
         <f>IF(E31="","",H31-E31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="90" t="inlineStr">
+      <c r="B32" s="93" t="inlineStr">
         <is>
           <t>VI. CHI PHÍ DỰ PHÒNG</t>
         </is>
       </c>
-      <c r="C32" s="109" t="inlineStr">
+      <c r="C32" s="114" t="inlineStr">
         <is>
           <t>GDP</t>
         </is>
       </c>
-      <c r="D32" s="90" t="inlineStr">
+      <c r="D32" s="93" t="inlineStr">
         <is>
           <t>5% × (GXD + Gtb + QL + GTV + GK)</t>
         </is>
       </c>
-      <c r="E32" s="108" t="n">
+      <c r="E32" s="112" t="n">
         <v>98277000</v>
       </c>
-      <c r="F32" s="108" t="n"/>
-      <c r="G32" s="108" t="n"/>
-      <c r="H32" s="108">
+      <c r="F32" s="112" t="n"/>
+      <c r="G32" s="112" t="n"/>
+      <c r="H32" s="112">
         <f>ROUND(5%*(H20+H21+H22+H28+H31),-3)</f>
         <v/>
       </c>
-      <c r="I32" s="108">
+      <c r="I32" s="112">
         <f>IF(E32="","",H32-E32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="110" t="inlineStr">
+      <c r="B33" s="116" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI</t>
         </is>
       </c>
-      <c r="C33" s="111" t="inlineStr">
+      <c r="C33" s="117" t="inlineStr">
         <is>
           <t>VTM</t>
         </is>
       </c>
-      <c r="D33" s="110" t="inlineStr">
+      <c r="D33" s="116" t="inlineStr">
         <is>
           <t>I + … + VI</t>
         </is>
       </c>
-      <c r="E33" s="112" t="n">
+      <c r="E33" s="118" t="n">
         <v>2063812000</v>
       </c>
-      <c r="F33" s="112" t="n"/>
-      <c r="G33" s="112" t="n"/>
-      <c r="H33" s="112">
+      <c r="F33" s="118" t="n"/>
+      <c r="G33" s="118" t="n"/>
+      <c r="H33" s="118">
         <f>ROUND(H20+H21+H22+H28+H31+H32,-3)</f>
         <v/>
       </c>
-      <c r="I33" s="112">
+      <c r="I33" s="118">
         <f>IF(E33="","",H33-E33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="113" t="inlineStr">
+      <c r="B34" s="119" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI – LÀM TRÒN (báo chủ đầu tư)</t>
         </is>
       </c>
-      <c r="C34" s="114" t="inlineStr"/>
-      <c r="D34" s="113" t="inlineStr">
+      <c r="C34" s="120" t="inlineStr"/>
+      <c r="D34" s="119" t="inlineStr">
         <is>
           <t>Làm tròn triệu</t>
         </is>
       </c>
-      <c r="E34" s="104" t="n">
+      <c r="E34" s="108" t="n">
         <v>2064000000</v>
       </c>
-      <c r="F34" s="104" t="n"/>
-      <c r="G34" s="104" t="n"/>
-      <c r="H34" s="104">
+      <c r="F34" s="108" t="n"/>
+      <c r="G34" s="108" t="n"/>
+      <c r="H34" s="108">
         <f>ROUND(H33,-6)</f>
         <v/>
       </c>
-      <c r="I34" s="104">
+      <c r="I34" s="108">
         <f>IF(E34="","",H34-E34)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="99" t="inlineStr">
+      <c r="A36" s="103" t="inlineStr">
         <is>
           <t>B. LỢI NHUẬN PHẦN PCCC (trước thuế)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="100" t="inlineStr">
+      <c r="B37" s="104" t="inlineStr">
         <is>
           <t>Khoản</t>
         </is>
       </c>
-      <c r="C37" s="91" t="n"/>
-      <c r="D37" s="92" t="n"/>
-      <c r="E37" s="100" t="inlineStr">
+      <c r="C37" s="94" t="n"/>
+      <c r="D37" s="95" t="n"/>
+      <c r="E37" s="104" t="inlineStr">
         <is>
           <t>Hiện tại</t>
         </is>
       </c>
-      <c r="F37" s="100" t="inlineStr">
+      <c r="F37" s="104" t="inlineStr">
         <is>
           <t>SAU KHI CHỐT GIÁ</t>
         </is>
       </c>
-      <c r="G37" s="100" t="inlineStr">
+      <c r="G37" s="104" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H37" s="91" t="n"/>
-      <c r="I37" s="91" t="n"/>
-      <c r="J37" s="91" t="n"/>
-      <c r="K37" s="92" t="n"/>
+      <c r="H37" s="94" t="n"/>
+      <c r="I37" s="94" t="n"/>
+      <c r="J37" s="94" t="n"/>
+      <c r="K37" s="95" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="105" t="inlineStr">
+      <c r="B38" s="109" t="inlineStr">
         <is>
           <t>Doanh thu lắp đặt PCCC (Gxdct1)</t>
         </is>
       </c>
-      <c r="C38" s="115" t="n"/>
-      <c r="D38" s="115" t="n"/>
-      <c r="E38" s="107" t="n">
+      <c r="C38" s="121" t="n"/>
+      <c r="D38" s="121" t="n"/>
+      <c r="E38" s="111" t="n">
         <v>1215750394</v>
       </c>
-      <c r="F38" s="107">
+      <c r="F38" s="111">
         <f>F12</f>
         <v/>
       </c>
-      <c r="G38" s="116" t="n"/>
-      <c r="H38" s="115" t="n"/>
-      <c r="I38" s="115" t="n"/>
-      <c r="J38" s="115" t="n"/>
-      <c r="K38" s="115" t="n"/>
+      <c r="G38" s="122" t="n"/>
+      <c r="H38" s="121" t="n"/>
+      <c r="I38" s="121" t="n"/>
+      <c r="J38" s="121" t="n"/>
+      <c r="K38" s="121" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="105" t="inlineStr">
+      <c r="B39" s="109" t="inlineStr">
         <is>
           <t>Nhà tạm phần PCCC (1,1% × Gxdct1)</t>
         </is>
       </c>
-      <c r="C39" s="115" t="n"/>
-      <c r="D39" s="115" t="n"/>
-      <c r="E39" s="107">
+      <c r="C39" s="121" t="n"/>
+      <c r="D39" s="121" t="n"/>
+      <c r="E39" s="111">
         <f>E38*1.1%</f>
         <v/>
       </c>
-      <c r="F39" s="107">
+      <c r="F39" s="111">
         <f>F38*1.1%</f>
         <v/>
       </c>
-      <c r="G39" s="116" t="n"/>
-      <c r="H39" s="115" t="n"/>
-      <c r="I39" s="115" t="n"/>
-      <c r="J39" s="115" t="n"/>
-      <c r="K39" s="115" t="n"/>
+      <c r="G39" s="122" t="n"/>
+      <c r="H39" s="121" t="n"/>
+      <c r="I39" s="121" t="n"/>
+      <c r="J39" s="121" t="n"/>
+      <c r="K39" s="121" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="105" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
         <is>
           <t>Thiết bị (trước thuế)</t>
         </is>
       </c>
-      <c r="C40" s="115" t="n"/>
-      <c r="D40" s="115" t="n"/>
-      <c r="E40" s="107" t="n">
+      <c r="C40" s="121" t="n"/>
+      <c r="D40" s="121" t="n"/>
+      <c r="E40" s="111" t="n">
         <v>17550000</v>
       </c>
-      <c r="F40" s="107">
+      <c r="F40" s="111">
         <f>F21</f>
         <v/>
       </c>
-      <c r="G40" s="116" t="n"/>
-      <c r="H40" s="115" t="n"/>
-      <c r="I40" s="115" t="n"/>
-      <c r="J40" s="115" t="n"/>
-      <c r="K40" s="115" t="n"/>
+      <c r="G40" s="122" t="n"/>
+      <c r="H40" s="121" t="n"/>
+      <c r="I40" s="121" t="n"/>
+      <c r="J40" s="121" t="n"/>
+      <c r="K40" s="121" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="90" t="inlineStr">
+      <c r="B41" s="93" t="inlineStr">
         <is>
           <t>Cộng doanh thu PCCC</t>
         </is>
       </c>
-      <c r="C41" s="117" t="n"/>
-      <c r="D41" s="117" t="n"/>
-      <c r="E41" s="108">
+      <c r="C41" s="123" t="n"/>
+      <c r="D41" s="123" t="n"/>
+      <c r="E41" s="112">
         <f>SUM(E38:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="108">
+      <c r="F41" s="112">
         <f>SUM(F38:F40)</f>
         <v/>
       </c>
-      <c r="G41" s="116" t="n"/>
-      <c r="H41" s="117" t="n"/>
-      <c r="I41" s="117" t="n"/>
-      <c r="J41" s="117" t="n"/>
-      <c r="K41" s="117" t="n"/>
+      <c r="G41" s="122" t="n"/>
+      <c r="H41" s="123" t="n"/>
+      <c r="I41" s="123" t="n"/>
+      <c r="J41" s="123" t="n"/>
+      <c r="K41" s="123" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="105" t="inlineStr">
+      <c r="B42" s="109" t="inlineStr">
         <is>
           <t>Giá vốn – các mục trong báo giá</t>
         </is>
       </c>
-      <c r="C42" s="115" t="n"/>
-      <c r="D42" s="115" t="n"/>
-      <c r="E42" s="107">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="F42" s="107">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="G42" s="116" t="inlineStr">
+      <c r="C42" s="121" t="n"/>
+      <c r="D42" s="121" t="n"/>
+      <c r="E42" s="111">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="F42" s="111">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="G42" s="122" t="inlineStr">
         <is>
           <t>Bảng C: khối lượng dự toán × giá vốn</t>
         </is>
       </c>
-      <c r="H42" s="115" t="n"/>
-      <c r="I42" s="115" t="n"/>
-      <c r="J42" s="115" t="n"/>
-      <c r="K42" s="115" t="n"/>
+      <c r="H42" s="121" t="n"/>
+      <c r="I42" s="121" t="n"/>
+      <c r="J42" s="121" t="n"/>
+      <c r="K42" s="121" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="105" t="inlineStr">
+      <c r="B43" s="109" t="inlineStr">
         <is>
           <t>Giá vốn – ngoài báo giá (ống, cáp, van, vật tư phụ 5%…)</t>
         </is>
       </c>
-      <c r="C43" s="115" t="n"/>
-      <c r="D43" s="115" t="n"/>
-      <c r="E43" s="107">
-        <f>G110</f>
-        <v/>
-      </c>
-      <c r="F43" s="107">
-        <f>G110</f>
-        <v/>
-      </c>
-      <c r="G43" s="116" t="inlineStr">
+      <c r="C43" s="121" t="n"/>
+      <c r="D43" s="121" t="n"/>
+      <c r="E43" s="111">
+        <f>G111</f>
+        <v/>
+      </c>
+      <c r="F43" s="111">
+        <f>G111</f>
+        <v/>
+      </c>
+      <c r="G43" s="122" t="inlineStr">
         <is>
           <t>Bảng D: theo sheet Gia von chi tiet</t>
         </is>
       </c>
-      <c r="H43" s="115" t="n"/>
-      <c r="I43" s="115" t="n"/>
-      <c r="J43" s="115" t="n"/>
-      <c r="K43" s="115" t="n"/>
+      <c r="H43" s="121" t="n"/>
+      <c r="I43" s="121" t="n"/>
+      <c r="J43" s="121" t="n"/>
+      <c r="K43" s="121" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="90" t="inlineStr">
+      <c r="B44" s="93" t="inlineStr">
         <is>
           <t>Cộng giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C44" s="117" t="n"/>
-      <c r="D44" s="117" t="n"/>
-      <c r="E44" s="108">
+      <c r="C44" s="123" t="n"/>
+      <c r="D44" s="123" t="n"/>
+      <c r="E44" s="112">
         <f>E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="108">
+      <c r="F44" s="112">
         <f>F42+F43</f>
         <v/>
       </c>
-      <c r="G44" s="116" t="n"/>
-      <c r="H44" s="117" t="n"/>
-      <c r="I44" s="117" t="n"/>
-      <c r="J44" s="117" t="n"/>
-      <c r="K44" s="117" t="n"/>
+      <c r="G44" s="122" t="n"/>
+      <c r="H44" s="123" t="n"/>
+      <c r="I44" s="123" t="n"/>
+      <c r="J44" s="123" t="n"/>
+      <c r="K44" s="123" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="101" t="inlineStr">
+      <c r="B45" s="105" t="inlineStr">
         <is>
           <t>Trích lại chủ đầu tư (15% × tổng dự toán làm tròn)</t>
         </is>
       </c>
-      <c r="C45" s="118" t="n"/>
-      <c r="D45" s="118" t="n"/>
-      <c r="E45" s="103">
+      <c r="C45" s="124" t="n"/>
+      <c r="D45" s="124" t="n"/>
+      <c r="E45" s="107">
         <f>$E$5*E34</f>
         <v/>
       </c>
-      <c r="F45" s="103">
+      <c r="F45" s="107">
         <f>$E$5*H34</f>
         <v/>
       </c>
-      <c r="G45" s="119" t="inlineStr">
+      <c r="G45" s="125" t="inlineStr">
         <is>
           <t>Trừ vào doanh thu trước thuế (VAT phải nộp nhà nước)</t>
         </is>
       </c>
-      <c r="H45" s="118" t="n"/>
-      <c r="I45" s="118" t="n"/>
-      <c r="J45" s="118" t="n"/>
-      <c r="K45" s="118" t="n"/>
+      <c r="H45" s="124" t="n"/>
+      <c r="I45" s="124" t="n"/>
+      <c r="J45" s="124" t="n"/>
+      <c r="K45" s="124" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="110" t="inlineStr">
+      <c r="B46" s="116" t="inlineStr">
         <is>
           <t>LỢI NHUẬN PCCC</t>
         </is>
       </c>
-      <c r="C46" s="120" t="n"/>
-      <c r="D46" s="120" t="n"/>
-      <c r="E46" s="112">
+      <c r="C46" s="126" t="n"/>
+      <c r="D46" s="126" t="n"/>
+      <c r="E46" s="118">
         <f>E41-E44-E45</f>
         <v/>
       </c>
-      <c r="F46" s="112">
+      <c r="F46" s="118">
         <f>F41-F44-F45</f>
         <v/>
       </c>
-      <c r="G46" s="121" t="n"/>
-      <c r="H46" s="120" t="n"/>
-      <c r="I46" s="120" t="n"/>
-      <c r="J46" s="120" t="n"/>
-      <c r="K46" s="120" t="n"/>
+      <c r="G46" s="127" t="n"/>
+      <c r="H46" s="126" t="n"/>
+      <c r="I46" s="126" t="n"/>
+      <c r="J46" s="126" t="n"/>
+      <c r="K46" s="126" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="110" t="inlineStr">
+      <c r="B47" s="116" t="inlineStr">
         <is>
           <t>% lợi nhuận / giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C47" s="120" t="n"/>
-      <c r="D47" s="120" t="n"/>
-      <c r="E47" s="122">
+      <c r="C47" s="126" t="n"/>
+      <c r="D47" s="126" t="n"/>
+      <c r="E47" s="128">
         <f>E46/E44</f>
         <v/>
       </c>
-      <c r="F47" s="122">
+      <c r="F47" s="128">
         <f>F46/F44</f>
         <v/>
       </c>
-      <c r="G47" s="121" t="n"/>
-      <c r="H47" s="120" t="n"/>
-      <c r="I47" s="120" t="n"/>
-      <c r="J47" s="120" t="n"/>
-      <c r="K47" s="120" t="n"/>
+      <c r="G47" s="127" t="n"/>
+      <c r="H47" s="126" t="n"/>
+      <c r="I47" s="126" t="n"/>
+      <c r="J47" s="126" t="n"/>
+      <c r="K47" s="126" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="90" t="inlineStr">
+      <c r="B48" s="93" t="inlineStr">
         <is>
           <t>Đánh giá so với mức tối thiểu (ô E4)</t>
         </is>
       </c>
-      <c r="C48" s="117" t="n"/>
-      <c r="D48" s="117" t="n"/>
-      <c r="E48" s="117">
+      <c r="C48" s="123" t="n"/>
+      <c r="D48" s="123" t="n"/>
+      <c r="E48" s="123">
         <f>IF(E47&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="F48" s="117">
+      <c r="F48" s="123">
         <f>IF(F47&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="G48" s="116" t="n"/>
-      <c r="H48" s="117" t="n"/>
-      <c r="I48" s="117" t="n"/>
-      <c r="J48" s="117" t="n"/>
-      <c r="K48" s="117" t="n"/>
+      <c r="G48" s="122" t="n"/>
+      <c r="H48" s="123" t="n"/>
+      <c r="I48" s="123" t="n"/>
+      <c r="J48" s="123" t="n"/>
+      <c r="K48" s="123" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="105" t="inlineStr">
+      <c r="B50" s="109" t="inlineStr">
         <is>
           <t>Tham khảo – doanh thu xây dựng (xây lắp + nhà tạm, trước thuế)</t>
         </is>
       </c>
-      <c r="C50" s="115" t="n"/>
-      <c r="D50" s="115" t="n"/>
-      <c r="E50" s="107">
+      <c r="C50" s="121" t="n"/>
+      <c r="D50" s="121" t="n"/>
+      <c r="E50" s="111">
         <f>378842471*1.011</f>
         <v/>
       </c>
-      <c r="F50" s="107">
+      <c r="F50" s="111">
         <f>378842471*1.011</f>
         <v/>
       </c>
-      <c r="G50" s="116" t="inlineStr">
+      <c r="G50" s="122" t="inlineStr">
         <is>
           <t>Giữ nguyên đơn giá dự toán</t>
         </is>
       </c>
-      <c r="H50" s="115" t="n"/>
-      <c r="I50" s="115" t="n"/>
-      <c r="J50" s="115" t="n"/>
-      <c r="K50" s="115" t="n"/>
+      <c r="H50" s="121" t="n"/>
+      <c r="I50" s="121" t="n"/>
+      <c r="J50" s="121" t="n"/>
+      <c r="K50" s="121" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="105" t="inlineStr">
+      <c r="B51" s="109" t="inlineStr">
         <is>
           <t>Tham khảo – giá vốn xây dựng</t>
         </is>
       </c>
-      <c r="C51" s="115" t="n"/>
-      <c r="D51" s="115" t="n"/>
-      <c r="E51" s="107" t="n">
+      <c r="C51" s="121" t="n"/>
+      <c r="D51" s="121" t="n"/>
+      <c r="E51" s="111" t="n">
         <v>110800000</v>
       </c>
-      <c r="F51" s="107" t="n">
+      <c r="F51" s="111" t="n">
         <v>110800000</v>
       </c>
-      <c r="G51" s="116" t="inlineStr">
+      <c r="G51" s="122" t="inlineStr">
         <is>
           <t>Sheet Gia von chi tiet (khối lượng tiên lượng)</t>
         </is>
       </c>
-      <c r="H51" s="115" t="n"/>
-      <c r="I51" s="115" t="n"/>
-      <c r="J51" s="115" t="n"/>
-      <c r="K51" s="115" t="n"/>
+      <c r="H51" s="121" t="n"/>
+      <c r="I51" s="121" t="n"/>
+      <c r="J51" s="121" t="n"/>
+      <c r="K51" s="121" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="90" t="inlineStr">
+      <c r="B52" s="93" t="inlineStr">
         <is>
           <t>Tham khảo – lợi nhuận xây dựng (không dùng bù cho PCCC)</t>
         </is>
       </c>
-      <c r="C52" s="117" t="n"/>
-      <c r="D52" s="117" t="n"/>
-      <c r="E52" s="108">
+      <c r="C52" s="123" t="n"/>
+      <c r="D52" s="123" t="n"/>
+      <c r="E52" s="112">
         <f>E50-E51</f>
         <v/>
       </c>
-      <c r="F52" s="108">
+      <c r="F52" s="112">
         <f>F50-F51</f>
         <v/>
       </c>
-      <c r="G52" s="116" t="n"/>
-      <c r="H52" s="117" t="n"/>
-      <c r="I52" s="117" t="n"/>
-      <c r="J52" s="117" t="n"/>
-      <c r="K52" s="117" t="n"/>
+      <c r="G52" s="122" t="n"/>
+      <c r="H52" s="123" t="n"/>
+      <c r="I52" s="123" t="n"/>
+      <c r="J52" s="123" t="n"/>
+      <c r="K52" s="123" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="99" t="inlineStr">
+      <c r="A60" s="103" t="inlineStr">
         <is>
           <t>C. CHI TIẾT HẠNG MỤC TRONG BÁO GIÁ</t>
         </is>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="100" t="inlineStr">
+      <c r="A61" s="104" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B61" s="100" t="inlineStr">
+      <c r="B61" s="104" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C61" s="100" t="inlineStr">
+      <c r="C61" s="104" t="inlineStr">
         <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="D61" s="100" t="inlineStr">
+      <c r="D61" s="104" t="inlineStr">
         <is>
           <t>Khối lượng</t>
         </is>
       </c>
-      <c r="E61" s="100" t="inlineStr">
-        <is>
-          <t>Giá vốn vật tư</t>
-        </is>
-      </c>
-      <c r="F61" s="100" t="inlineStr">
-        <is>
-          <t>Giá vốn nhân công</t>
-        </is>
-      </c>
-      <c r="G61" s="100" t="inlineStr">
+      <c r="E61" s="104" t="inlineStr">
+        <is>
+          <t>Giá vốn vật tư (từ sheet Bao gia)</t>
+        </is>
+      </c>
+      <c r="F61" s="104" t="inlineStr">
+        <is>
+          <t>Giá vốn nhân công (sheet Gia von chi tiet)</t>
+        </is>
+      </c>
+      <c r="G61" s="104" t="inlineStr">
         <is>
           <t>Giá VT dự toán hiện tại</t>
         </is>
       </c>
-      <c r="H61" s="100" t="inlineStr">
+      <c r="H61" s="104" t="inlineStr">
         <is>
           <t>GIÁ VT ĐỀ XUẤT (CHỐT)</t>
         </is>
       </c>
-      <c r="I61" s="100" t="inlineStr">
+      <c r="I61" s="104" t="inlineStr">
         <is>
           <t>Nhân công theo định mức</t>
         </is>
       </c>
-      <c r="J61" s="100" t="inlineStr">
+      <c r="J61" s="104" t="inlineStr">
         <is>
           <t>Thành tiền giá vốn</t>
         </is>
       </c>
-      <c r="K61" s="100" t="inlineStr">
+      <c r="K61" s="104" t="inlineStr">
         <is>
           <t>Thành tiền VT đề xuất</t>
         </is>
       </c>
-      <c r="L61" s="100" t="inlineStr">
+      <c r="L61" s="104" t="inlineStr">
         <is>
           <t>Phần</t>
         </is>
       </c>
-      <c r="M61" s="100" t="inlineStr">
+      <c r="M61" s="104" t="inlineStr">
         <is>
           <t>SL quy đổi (gồm VL khác)</t>
         </is>
       </c>
-      <c r="N61" s="100" t="inlineStr">
+      <c r="N61" s="104" t="inlineStr">
         <is>
           <t>VL dự toán hiện tại (thành tiền)</t>
         </is>
       </c>
-      <c r="O61" s="100" t="inlineStr">
+      <c r="O61" s="104" t="inlineStr">
         <is>
           <t>Tăng/giảm giá trị XD trước thuế</t>
         </is>
       </c>
-      <c r="P61" s="100" t="inlineStr">
+      <c r="P61" s="104" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="106" t="n">
+      <c r="A62" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="B62" s="105" t="inlineStr">
+      <c r="B62" s="109" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 10 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C62" s="106" t="inlineStr">
+      <c r="C62" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D62" s="123" t="n">
+      <c r="D62" s="129" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="107" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="F62" s="107" t="n">
+      <c r="E62" s="111">
+        <f>'Bao gia'!J4</f>
+        <v/>
+      </c>
+      <c r="F62" s="111" t="n">
         <v>1500000</v>
       </c>
-      <c r="G62" s="107">
+      <c r="G62" s="111">
         <f>IF(M62=0,"",N62/M62)</f>
         <v/>
       </c>
-      <c r="H62" s="104">
+      <c r="H62" s="108">
         <f>ROUNDUP(E62*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I62" s="107" t="n">
+      <c r="I62" s="111" t="n">
         <v>828880</v>
       </c>
-      <c r="J62" s="107">
+      <c r="J62" s="111">
         <f>D62*(E62+F62)</f>
         <v/>
       </c>
-      <c r="K62" s="107">
+      <c r="K62" s="111">
         <f>D62*H62</f>
         <v/>
       </c>
-      <c r="L62" s="106" t="inlineStr">
+      <c r="L62" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M62" s="124" t="n">
+      <c r="M62" s="130" t="n">
         <v>2.1</v>
       </c>
-      <c r="N62" s="107" t="n">
+      <c r="N62" s="111" t="n">
         <v>17850000</v>
       </c>
-      <c r="O62" s="107">
+      <c r="O62" s="111">
         <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
         <v/>
       </c>
-      <c r="P62" s="105" t="n"/>
+      <c r="P62" s="109" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="106" t="n">
+      <c r="A63" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="105" t="inlineStr">
+      <c r="B63" s="109" t="inlineStr">
         <is>
           <t>Còi đèn báo cháy kết hợp</t>
         </is>
       </c>
-      <c r="C63" s="106" t="inlineStr">
+      <c r="C63" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D63" s="123" t="n">
+      <c r="D63" s="129" t="n">
         <v>21</v>
       </c>
-      <c r="E63" s="107" t="n">
-        <v>252000</v>
-      </c>
-      <c r="F63" s="107" t="n">
+      <c r="E63" s="111">
+        <f>'Bao gia'!J5</f>
+        <v/>
+      </c>
+      <c r="F63" s="111" t="n">
         <v>100000</v>
       </c>
-      <c r="G63" s="107">
+      <c r="G63" s="111">
         <f>IF(M63=0,"",N63/M63)</f>
         <v/>
       </c>
-      <c r="H63" s="104">
+      <c r="H63" s="108">
         <f>ROUNDUP(E63*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I63" s="107" t="n">
+      <c r="I63" s="111" t="n">
         <v>74280</v>
       </c>
-      <c r="J63" s="107">
+      <c r="J63" s="111">
         <f>D63*(E63+F63)</f>
         <v/>
       </c>
-      <c r="K63" s="107">
+      <c r="K63" s="111">
         <f>D63*H63</f>
         <v/>
       </c>
-      <c r="L63" s="106" t="inlineStr">
+      <c r="L63" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M63" s="124" t="n">
+      <c r="M63" s="130" t="n">
         <v>21.42</v>
       </c>
-      <c r="N63" s="107" t="n">
+      <c r="N63" s="111" t="n">
         <v>5355000</v>
       </c>
-      <c r="O63" s="107">
+      <c r="O63" s="111">
         <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
         <v/>
       </c>
-      <c r="P63" s="105" t="n"/>
+      <c r="P63" s="109" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="106" t="n">
+      <c r="A64" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="105" t="inlineStr">
+      <c r="B64" s="109" t="inlineStr">
         <is>
           <t>Nút ấn khẩn tròn lắp nổi</t>
         </is>
       </c>
-      <c r="C64" s="106" t="inlineStr">
+      <c r="C64" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D64" s="123" t="n">
+      <c r="D64" s="129" t="n">
         <v>21</v>
       </c>
-      <c r="E64" s="107" t="n">
-        <v>205000</v>
-      </c>
-      <c r="F64" s="107" t="n">
+      <c r="E64" s="111">
+        <f>'Bao gia'!J6</f>
+        <v/>
+      </c>
+      <c r="F64" s="111" t="n">
         <v>100000</v>
       </c>
-      <c r="G64" s="107">
+      <c r="G64" s="111">
         <f>IF(M64=0,"",N64/M64)</f>
         <v/>
       </c>
-      <c r="H64" s="104">
+      <c r="H64" s="108">
         <f>ROUNDUP(E64*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I64" s="107" t="n">
+      <c r="I64" s="111" t="n">
         <v>191280</v>
       </c>
-      <c r="J64" s="107">
+      <c r="J64" s="111">
         <f>D64*(E64+F64)</f>
         <v/>
       </c>
-      <c r="K64" s="107">
+      <c r="K64" s="111">
         <f>D64*H64</f>
         <v/>
       </c>
-      <c r="L64" s="106" t="inlineStr">
+      <c r="L64" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M64" s="124" t="n">
+      <c r="M64" s="130" t="n">
         <v>21.42</v>
       </c>
-      <c r="N64" s="107" t="n">
+      <c r="N64" s="111" t="n">
         <v>4284000</v>
       </c>
-      <c r="O64" s="107">
+      <c r="O64" s="111">
         <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
         <v/>
       </c>
-      <c r="P64" s="105" t="n"/>
+      <c r="P64" s="109" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="106" t="n">
+      <c r="A65" s="110" t="n">
         <v>4</v>
       </c>
-      <c r="B65" s="105" t="inlineStr">
+      <c r="B65" s="109" t="inlineStr">
         <is>
           <t>Đầu báo khói quang 24VDC</t>
         </is>
       </c>
-      <c r="C65" s="106" t="inlineStr">
+      <c r="C65" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D65" s="123" t="n">
+      <c r="D65" s="129" t="n">
         <v>287</v>
       </c>
-      <c r="E65" s="107" t="n">
-        <v>242000</v>
-      </c>
-      <c r="F65" s="107" t="n">
+      <c r="E65" s="111">
+        <f>'Bao gia'!J7</f>
+        <v/>
+      </c>
+      <c r="F65" s="111" t="n">
         <v>100000</v>
       </c>
-      <c r="G65" s="107">
+      <c r="G65" s="111">
         <f>IF(M65=0,"",N65/M65)</f>
         <v/>
       </c>
-      <c r="H65" s="104">
+      <c r="H65" s="108">
         <f>ROUNDUP(E65*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I65" s="107" t="n">
+      <c r="I65" s="111" t="n">
         <v>55471</v>
       </c>
-      <c r="J65" s="107">
+      <c r="J65" s="111">
         <f>D65*(E65+F65)</f>
         <v/>
       </c>
-      <c r="K65" s="107">
+      <c r="K65" s="111">
         <f>D65*H65</f>
         <v/>
       </c>
-      <c r="L65" s="106" t="inlineStr">
+      <c r="L65" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M65" s="124" t="n">
+      <c r="M65" s="130" t="n">
         <v>292.74</v>
       </c>
-      <c r="N65" s="107" t="n">
+      <c r="N65" s="111" t="n">
         <v>73185000</v>
       </c>
-      <c r="O65" s="107">
+      <c r="O65" s="111">
         <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
         <v/>
       </c>
-      <c r="P65" s="105" t="n"/>
+      <c r="P65" s="109" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="106" t="n">
+      <c r="A66" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="B66" s="105" t="inlineStr">
+      <c r="B66" s="109" t="inlineStr">
         <is>
           <t>Đèn báo phòng</t>
         </is>
       </c>
-      <c r="C66" s="106" t="inlineStr">
+      <c r="C66" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D66" s="123" t="n">
+      <c r="D66" s="129" t="n">
         <v>70</v>
       </c>
-      <c r="E66" s="107" t="n">
-        <v>116000</v>
-      </c>
-      <c r="F66" s="107" t="n">
+      <c r="E66" s="111">
+        <f>'Bao gia'!J8</f>
+        <v/>
+      </c>
+      <c r="F66" s="111" t="n">
         <v>100000</v>
       </c>
-      <c r="G66" s="107">
+      <c r="G66" s="111">
         <f>IF(M66=0,"",N66/M66)</f>
         <v/>
       </c>
-      <c r="H66" s="104">
+      <c r="H66" s="108">
         <f>ROUNDUP(E66*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I66" s="107" t="n">
+      <c r="I66" s="111" t="n">
         <v>74280</v>
       </c>
-      <c r="J66" s="107">
+      <c r="J66" s="111">
         <f>D66*(E66+F66)</f>
         <v/>
       </c>
-      <c r="K66" s="107">
+      <c r="K66" s="111">
         <f>D66*H66</f>
         <v/>
       </c>
-      <c r="L66" s="106" t="inlineStr">
+      <c r="L66" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M66" s="124" t="n">
+      <c r="M66" s="130" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="N66" s="107" t="n">
+      <c r="N66" s="111" t="n">
         <v>3570000</v>
       </c>
-      <c r="O66" s="107">
+      <c r="O66" s="111">
         <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
         <v/>
       </c>
-      <c r="P66" s="105" t="n"/>
+      <c r="P66" s="109" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="106" t="n">
+      <c r="A67" s="110" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="105" t="inlineStr">
+      <c r="B67" s="109" t="inlineStr">
         <is>
           <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
         </is>
       </c>
-      <c r="C67" s="106" t="inlineStr">
+      <c r="C67" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D67" s="123" t="n">
+      <c r="D67" s="129" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="107" t="n">
-        <v>252000</v>
-      </c>
-      <c r="F67" s="107" t="n">
+      <c r="E67" s="111">
+        <f>'Bao gia'!J9</f>
+        <v/>
+      </c>
+      <c r="F67" s="111" t="n">
         <v>20000</v>
       </c>
-      <c r="G67" s="107">
+      <c r="G67" s="111">
         <f>IF(M67=0,"",N67/M67)</f>
         <v/>
       </c>
-      <c r="H67" s="104">
+      <c r="H67" s="108">
         <f>ROUNDUP(E67*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I67" s="107" t="n">
+      <c r="I67" s="111" t="n">
         <v>100928</v>
       </c>
-      <c r="J67" s="107">
+      <c r="J67" s="111">
         <f>D67*(E67+F67)</f>
         <v/>
       </c>
-      <c r="K67" s="107">
+      <c r="K67" s="111">
         <f>D67*H67</f>
         <v/>
       </c>
-      <c r="L67" s="106" t="inlineStr">
+      <c r="L67" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M67" s="124" t="n">
+      <c r="M67" s="130" t="n">
         <v>2.02</v>
       </c>
-      <c r="N67" s="107" t="n">
+      <c r="N67" s="111" t="n">
         <v>565600</v>
       </c>
-      <c r="O67" s="107">
+      <c r="O67" s="111">
         <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
         <v/>
       </c>
-      <c r="P67" s="105" t="n"/>
+      <c r="P67" s="109" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="106" t="n">
+      <c r="A68" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="B68" s="105" t="inlineStr">
+      <c r="B68" s="109" t="inlineStr">
         <is>
           <t>Co thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C68" s="106" t="inlineStr">
+      <c r="C68" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D68" s="123" t="n">
+      <c r="D68" s="129" t="n">
         <v>56</v>
       </c>
-      <c r="E68" s="107" t="n">
-        <v>53000</v>
-      </c>
-      <c r="F68" s="107" t="n">
+      <c r="E68" s="111">
+        <f>'Bao gia'!J10</f>
+        <v/>
+      </c>
+      <c r="F68" s="111" t="n">
         <v>25000</v>
       </c>
-      <c r="G68" s="107">
+      <c r="G68" s="111">
         <f>IF(M68=0,"",N68/M68)</f>
         <v/>
       </c>
-      <c r="H68" s="104">
+      <c r="H68" s="108">
         <f>ROUNDUP(E68*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I68" s="107" t="n">
+      <c r="I68" s="111" t="n">
         <v>75696</v>
       </c>
-      <c r="J68" s="107">
+      <c r="J68" s="111">
         <f>D68*(E68+F68)</f>
         <v/>
       </c>
-      <c r="K68" s="107">
+      <c r="K68" s="111">
         <f>D68*H68</f>
         <v/>
       </c>
-      <c r="L68" s="106" t="inlineStr">
+      <c r="L68" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M68" s="124" t="n">
+      <c r="M68" s="130" t="n">
         <v>56.0056</v>
       </c>
-      <c r="N68" s="107" t="n">
+      <c r="N68" s="111" t="n">
         <v>3640364</v>
       </c>
-      <c r="O68" s="107">
+      <c r="O68" s="111">
         <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
         <v/>
       </c>
-      <c r="P68" s="105" t="n"/>
+      <c r="P68" s="109" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="106" t="n">
+      <c r="A69" s="110" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="105" t="inlineStr">
+      <c r="B69" s="109" t="inlineStr">
         <is>
           <t>Co thép đen hàn DN50</t>
         </is>
       </c>
-      <c r="C69" s="106" t="inlineStr">
+      <c r="C69" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D69" s="123" t="n">
+      <c r="D69" s="129" t="n">
         <v>265</v>
       </c>
-      <c r="E69" s="107" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F69" s="107" t="n">
+      <c r="E69" s="111">
+        <f>'Bao gia'!J11</f>
+        <v/>
+      </c>
+      <c r="F69" s="111" t="n">
         <v>25000</v>
       </c>
-      <c r="G69" s="107">
+      <c r="G69" s="111">
         <f>IF(M69=0,"",N69/M69)</f>
         <v/>
       </c>
-      <c r="H69" s="104">
+      <c r="H69" s="108">
         <f>ROUNDUP(E69*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I69" s="107" t="n">
+      <c r="I69" s="111" t="n">
         <v>66234</v>
       </c>
-      <c r="J69" s="107">
+      <c r="J69" s="111">
         <f>D69*(E69+F69)</f>
         <v/>
       </c>
-      <c r="K69" s="107">
+      <c r="K69" s="111">
         <f>D69*H69</f>
         <v/>
       </c>
-      <c r="L69" s="106" t="inlineStr">
+      <c r="L69" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M69" s="124" t="n">
+      <c r="M69" s="130" t="n">
         <v>265.0265</v>
       </c>
-      <c r="N69" s="107" t="n">
+      <c r="N69" s="111" t="n">
         <v>13251325</v>
       </c>
-      <c r="O69" s="107">
+      <c r="O69" s="111">
         <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
         <v/>
       </c>
-      <c r="P69" s="105" t="n"/>
+      <c r="P69" s="109" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="106" t="n">
+      <c r="A70" s="110" t="n">
         <v>9</v>
       </c>
-      <c r="B70" s="105" t="inlineStr">
+      <c r="B70" s="109" t="inlineStr">
         <is>
           <t>Tê thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C70" s="106" t="inlineStr">
+      <c r="C70" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D70" s="123" t="n">
+      <c r="D70" s="129" t="n">
         <v>22</v>
       </c>
-      <c r="E70" s="107" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F70" s="107" t="n">
+      <c r="E70" s="111">
+        <f>'Bao gia'!J12</f>
+        <v/>
+      </c>
+      <c r="F70" s="111" t="n">
         <v>25000</v>
       </c>
-      <c r="G70" s="107">
+      <c r="G70" s="111">
         <f>IF(M70=0,"",N70/M70)</f>
         <v/>
       </c>
-      <c r="H70" s="104">
+      <c r="H70" s="108">
         <f>ROUNDUP(E70*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I70" s="107" t="n">
+      <c r="I70" s="111" t="n">
         <v>75696</v>
       </c>
-      <c r="J70" s="107">
+      <c r="J70" s="111">
         <f>D70*(E70+F70)</f>
         <v/>
       </c>
-      <c r="K70" s="107">
+      <c r="K70" s="111">
         <f>D70*H70</f>
         <v/>
       </c>
-      <c r="L70" s="106" t="inlineStr">
+      <c r="L70" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M70" s="124" t="n">
+      <c r="M70" s="130" t="n">
         <v>22.0022</v>
       </c>
-      <c r="N70" s="107" t="n">
+      <c r="N70" s="111" t="n">
         <v>3630363</v>
       </c>
-      <c r="O70" s="107">
+      <c r="O70" s="111">
         <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
         <v/>
       </c>
-      <c r="P70" s="105" t="n"/>
+      <c r="P70" s="109" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="106" t="n">
+      <c r="A71" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="B71" s="105" t="inlineStr">
+      <c r="B71" s="109" t="inlineStr">
         <is>
           <t>Tê giảm thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C71" s="106" t="inlineStr">
+      <c r="C71" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D71" s="123" t="n">
+      <c r="D71" s="129" t="n">
         <v>10</v>
       </c>
-      <c r="E71" s="107" t="n">
-        <v>190000</v>
-      </c>
-      <c r="F71" s="107" t="n">
+      <c r="E71" s="111">
+        <f>'Bao gia'!J13</f>
+        <v/>
+      </c>
+      <c r="F71" s="111" t="n">
         <v>50000</v>
       </c>
-      <c r="G71" s="107">
+      <c r="G71" s="111">
         <f>IF(M71=0,"",N71/M71)</f>
         <v/>
       </c>
-      <c r="H71" s="104">
+      <c r="H71" s="108">
         <f>ROUNDUP(E71*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I71" s="107" t="n">
+      <c r="I71" s="111" t="n">
         <v>75696</v>
       </c>
-      <c r="J71" s="107">
+      <c r="J71" s="111">
         <f>D71*(E71+F71)</f>
         <v/>
       </c>
-      <c r="K71" s="107">
+      <c r="K71" s="111">
         <f>D71*H71</f>
         <v/>
       </c>
-      <c r="L71" s="106" t="inlineStr">
+      <c r="L71" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M71" s="124" t="n">
+      <c r="M71" s="130" t="n">
         <v>10.001</v>
       </c>
-      <c r="N71" s="107" t="n">
+      <c r="N71" s="111" t="n">
         <v>1650165</v>
       </c>
-      <c r="O71" s="107">
+      <c r="O71" s="111">
         <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
         <v/>
       </c>
-      <c r="P71" s="105" t="n"/>
+      <c r="P71" s="109" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="106" t="n">
+      <c r="A72" s="110" t="n">
         <v>11</v>
       </c>
-      <c r="B72" s="105" t="inlineStr">
+      <c r="B72" s="109" t="inlineStr">
         <is>
           <t>Tê thép hàn tráng kẽm DN50</t>
         </is>
       </c>
-      <c r="C72" s="106" t="inlineStr">
+      <c r="C72" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D72" s="123" t="n">
+      <c r="D72" s="129" t="n">
         <v>52</v>
       </c>
-      <c r="E72" s="107" t="n">
-        <v>75000</v>
-      </c>
-      <c r="F72" s="107" t="n">
+      <c r="E72" s="111">
+        <f>'Bao gia'!J14</f>
+        <v/>
+      </c>
+      <c r="F72" s="111" t="n">
         <v>25000</v>
       </c>
-      <c r="G72" s="107">
+      <c r="G72" s="111">
         <f>IF(M72=0,"",N72/M72)</f>
         <v/>
       </c>
-      <c r="H72" s="104">
+      <c r="H72" s="108">
         <f>ROUNDUP(E72*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I72" s="107" t="n">
+      <c r="I72" s="111" t="n">
         <v>100928</v>
       </c>
-      <c r="J72" s="107">
+      <c r="J72" s="111">
         <f>D72*(E72+F72)</f>
         <v/>
       </c>
-      <c r="K72" s="107">
+      <c r="K72" s="111">
         <f>D72*H72</f>
         <v/>
       </c>
-      <c r="L72" s="106" t="inlineStr">
+      <c r="L72" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M72" s="124" t="n">
+      <c r="M72" s="130" t="n">
         <v>52.0052</v>
       </c>
-      <c r="N72" s="107" t="n">
+      <c r="N72" s="111" t="n">
         <v>7800780</v>
       </c>
-      <c r="O72" s="107">
+      <c r="O72" s="111">
         <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
         <v/>
       </c>
-      <c r="P72" s="105" t="n"/>
+      <c r="P72" s="109" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="106" t="n">
+      <c r="A73" s="110" t="n">
         <v>12</v>
       </c>
-      <c r="B73" s="105" t="inlineStr">
+      <c r="B73" s="109" t="inlineStr">
         <is>
           <t>Tê giảm thép hàn DN100/65</t>
         </is>
       </c>
-      <c r="C73" s="106" t="inlineStr">
+      <c r="C73" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D73" s="123" t="n">
+      <c r="D73" s="129" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="107" t="n">
-        <v>245000</v>
-      </c>
-      <c r="F73" s="107" t="n">
+      <c r="E73" s="111">
+        <f>'Bao gia'!J15</f>
+        <v/>
+      </c>
+      <c r="F73" s="111" t="n">
         <v>50000</v>
       </c>
-      <c r="G73" s="107">
+      <c r="G73" s="111">
         <f>IF(M73=0,"",N73/M73)</f>
         <v/>
       </c>
-      <c r="H73" s="104">
+      <c r="H73" s="108">
         <f>ROUNDUP(E73*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I73" s="107" t="n">
+      <c r="I73" s="111" t="n">
         <v>113544</v>
       </c>
-      <c r="J73" s="107">
+      <c r="J73" s="111">
         <f>D73*(E73+F73)</f>
         <v/>
       </c>
-      <c r="K73" s="107">
+      <c r="K73" s="111">
         <f>D73*H73</f>
         <v/>
       </c>
-      <c r="L73" s="106" t="inlineStr">
+      <c r="L73" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M73" s="124" t="n">
+      <c r="M73" s="130" t="n">
         <v>1.0001</v>
       </c>
-      <c r="N73" s="107" t="n">
+      <c r="N73" s="111" t="n">
         <v>180018</v>
       </c>
-      <c r="O73" s="107">
+      <c r="O73" s="111">
         <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
         <v/>
       </c>
-      <c r="P73" s="105" t="n"/>
+      <c r="P73" s="109" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="106" t="n">
+      <c r="A74" s="110" t="n">
         <v>13</v>
       </c>
-      <c r="B74" s="105" t="inlineStr">
+      <c r="B74" s="109" t="inlineStr">
         <is>
           <t>Tê giảm thép hàn DN65/50</t>
         </is>
       </c>
-      <c r="C74" s="106" t="inlineStr">
+      <c r="C74" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D74" s="123" t="n">
+      <c r="D74" s="129" t="n">
         <v>5</v>
       </c>
-      <c r="E74" s="107" t="n">
-        <v>190000</v>
-      </c>
-      <c r="F74" s="107" t="n">
+      <c r="E74" s="111">
+        <f>'Bao gia'!J16</f>
+        <v/>
+      </c>
+      <c r="F74" s="111" t="n">
         <v>50000</v>
       </c>
-      <c r="G74" s="107">
+      <c r="G74" s="111">
         <f>IF(M74=0,"",N74/M74)</f>
         <v/>
       </c>
-      <c r="H74" s="104">
+      <c r="H74" s="108">
         <f>ROUNDUP(E74*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I74" s="107" t="n">
+      <c r="I74" s="111" t="n">
         <v>75696</v>
       </c>
-      <c r="J74" s="107">
+      <c r="J74" s="111">
         <f>D74*(E74+F74)</f>
         <v/>
       </c>
-      <c r="K74" s="107">
+      <c r="K74" s="111">
         <f>D74*H74</f>
         <v/>
       </c>
-      <c r="L74" s="106" t="inlineStr">
+      <c r="L74" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M74" s="124" t="n">
+      <c r="M74" s="130" t="n">
         <v>5.0005</v>
       </c>
-      <c r="N74" s="107" t="n">
+      <c r="N74" s="111" t="n">
         <v>750075</v>
       </c>
-      <c r="O74" s="107">
+      <c r="O74" s="111">
         <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
         <v/>
       </c>
-      <c r="P74" s="105" t="n"/>
+      <c r="P74" s="109" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="106" t="n">
+      <c r="A75" s="110" t="n">
         <v>14</v>
       </c>
-      <c r="B75" s="105" t="inlineStr">
+      <c r="B75" s="109" t="inlineStr">
         <is>
           <t>Côn giảm thép hàn DN80/65</t>
         </is>
       </c>
-      <c r="C75" s="106" t="inlineStr">
+      <c r="C75" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D75" s="123" t="n">
+      <c r="D75" s="129" t="n">
         <v>1</v>
       </c>
-      <c r="E75" s="107" t="n">
-        <v>231000</v>
-      </c>
-      <c r="F75" s="107" t="n">
+      <c r="E75" s="111">
+        <f>'Bao gia'!J17</f>
+        <v/>
+      </c>
+      <c r="F75" s="111" t="n">
         <v>50000</v>
       </c>
-      <c r="G75" s="107">
+      <c r="G75" s="111">
         <f>IF(M75=0,"",N75/M75)</f>
         <v/>
       </c>
-      <c r="H75" s="104">
+      <c r="H75" s="108">
         <f>ROUNDUP(E75*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I75" s="107" t="n">
+      <c r="I75" s="111" t="n">
         <v>100928</v>
       </c>
-      <c r="J75" s="107">
+      <c r="J75" s="111">
         <f>D75*(E75+F75)</f>
         <v/>
       </c>
-      <c r="K75" s="107">
+      <c r="K75" s="111">
         <f>D75*H75</f>
         <v/>
       </c>
-      <c r="L75" s="106" t="inlineStr">
+      <c r="L75" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M75" s="124" t="n">
+      <c r="M75" s="130" t="n">
         <v>1.0001</v>
       </c>
-      <c r="N75" s="107" t="n">
+      <c r="N75" s="111" t="n">
         <v>80008</v>
       </c>
-      <c r="O75" s="107">
+      <c r="O75" s="111">
         <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
         <v/>
       </c>
-      <c r="P75" s="105" t="n"/>
+      <c r="P75" s="109" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="106" t="n">
+      <c r="A76" s="110" t="n">
         <v>15</v>
       </c>
-      <c r="B76" s="105" t="inlineStr">
+      <c r="B76" s="109" t="inlineStr">
         <is>
           <t>Mặt bích thép DN80</t>
         </is>
       </c>
-      <c r="C76" s="106" t="inlineStr">
+      <c r="C76" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D76" s="123" t="n">
+      <c r="D76" s="129" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="107" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F76" s="107" t="n">
+      <c r="E76" s="111">
+        <f>'Bao gia'!J18</f>
+        <v/>
+      </c>
+      <c r="F76" s="111" t="n">
         <v>50000</v>
       </c>
-      <c r="G76" s="107">
+      <c r="G76" s="111">
         <f>IF(M76=0,"",N76/M76)</f>
         <v/>
       </c>
-      <c r="H76" s="104">
+      <c r="H76" s="108">
         <f>ROUNDUP(E76*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I76" s="107" t="n">
+      <c r="I76" s="111" t="n">
         <v>59926</v>
       </c>
-      <c r="J76" s="107">
+      <c r="J76" s="111">
         <f>D76*(E76+F76)</f>
         <v/>
       </c>
-      <c r="K76" s="107">
+      <c r="K76" s="111">
         <f>D76*H76</f>
         <v/>
       </c>
-      <c r="L76" s="106" t="inlineStr">
+      <c r="L76" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M76" s="124" t="n">
+      <c r="M76" s="130" t="n">
         <v>1.0001</v>
       </c>
-      <c r="N76" s="107" t="n">
+      <c r="N76" s="111" t="n">
         <v>321032.1</v>
       </c>
-      <c r="O76" s="107">
+      <c r="O76" s="111">
         <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
         <v/>
       </c>
-      <c r="P76" s="105" t="n"/>
+      <c r="P76" s="109" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="106" t="n">
+      <c r="A77" s="110" t="n">
         <v>16</v>
       </c>
-      <c r="B77" s="105" t="inlineStr">
+      <c r="B77" s="109" t="inlineStr">
         <is>
           <t>Roăng su DN80</t>
         </is>
       </c>
-      <c r="C77" s="106" t="inlineStr">
+      <c r="C77" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D77" s="123" t="n">
+      <c r="D77" s="129" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="107" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F77" s="107" t="n">
+      <c r="E77" s="111">
+        <f>'Bao gia'!J19</f>
+        <v/>
+      </c>
+      <c r="F77" s="111" t="n">
         <v>11538</v>
       </c>
-      <c r="G77" s="107">
+      <c r="G77" s="111">
         <f>IF(M77=0,"",N77/M77)</f>
         <v/>
       </c>
-      <c r="H77" s="104">
+      <c r="H77" s="108">
         <f>ROUNDUP(E77*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I77" s="107" t="n">
+      <c r="I77" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="107">
+      <c r="J77" s="111">
         <f>D77*(E77+F77)</f>
         <v/>
       </c>
-      <c r="K77" s="107">
+      <c r="K77" s="111">
         <f>D77*H77</f>
         <v/>
       </c>
-      <c r="L77" s="106" t="inlineStr">
+      <c r="L77" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M77" s="124" t="n">
+      <c r="M77" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="N77" s="107" t="n">
+      <c r="N77" s="111" t="n">
         <v>150000</v>
       </c>
-      <c r="O77" s="107">
+      <c r="O77" s="111">
         <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
         <v/>
       </c>
-      <c r="P77" s="105" t="n"/>
+      <c r="P77" s="109" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="106" t="n">
+      <c r="A78" s="110" t="n">
         <v>17</v>
       </c>
-      <c r="B78" s="105" t="inlineStr">
+      <c r="B78" s="109" t="inlineStr">
         <is>
           <t>Van 1 chiều DN80</t>
         </is>
       </c>
-      <c r="C78" s="106" t="inlineStr">
+      <c r="C78" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D78" s="123" t="n">
+      <c r="D78" s="129" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="107" t="n">
+      <c r="E78" s="111">
+        <f>'Bao gia'!J20</f>
+        <v/>
+      </c>
+      <c r="F78" s="111" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G78" s="111">
+        <f>IF(M78=0,"",N78/M78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="108">
+        <f>ROUNDUP(E78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I78" s="111" t="n">
+        <v>97774</v>
+      </c>
+      <c r="J78" s="111">
+        <f>D78*(E78+F78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="111">
+        <f>D78*H78</f>
+        <v/>
+      </c>
+      <c r="L78" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M78" s="130" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N78" s="111" t="n">
+        <v>350035</v>
+      </c>
+      <c r="O78" s="111">
+        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
+        <v/>
+      </c>
+      <c r="P78" s="109" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="110" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" s="109" t="inlineStr">
+        <is>
+          <t>Rơ le kiểm tra mực nước</t>
+        </is>
+      </c>
+      <c r="C79" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D79" s="129" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="111">
+        <f>'Bao gia'!J21</f>
+        <v/>
+      </c>
+      <c r="F79" s="111" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G79" s="111">
+        <f>IF(M79=0,"",N79/M79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="108">
+        <f>ROUNDUP(E79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I79" s="111" t="n">
+        <v>31540</v>
+      </c>
+      <c r="J79" s="111">
+        <f>D79*(E79+F79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="111">
+        <f>D79*H79</f>
+        <v/>
+      </c>
+      <c r="L79" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M79" s="130" t="n">
+        <v>4.0004</v>
+      </c>
+      <c r="N79" s="111" t="n">
+        <v>4600460</v>
+      </c>
+      <c r="O79" s="111">
+        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
+        <v/>
+      </c>
+      <c r="P79" s="109" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="110" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" s="109" t="inlineStr">
+        <is>
+          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
+        </is>
+      </c>
+      <c r="C80" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D80" s="129" t="n">
+        <v>57</v>
+      </c>
+      <c r="E80" s="111">
+        <f>'Bao gia'!J22</f>
+        <v/>
+      </c>
+      <c r="F80" s="111" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G80" s="111">
+        <f>IF(M80=0,"",N80/M80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="108">
+        <f>ROUNDUP(E80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I80" s="111" t="n">
+        <v>94620</v>
+      </c>
+      <c r="J80" s="111">
+        <f>D80*(E80+F80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="111">
+        <f>D80*H80</f>
+        <v/>
+      </c>
+      <c r="L80" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M80" s="130" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="N80" s="111" t="n">
+        <v>19152000</v>
+      </c>
+      <c r="O80" s="111">
+        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
+        <v/>
+      </c>
+      <c r="P80" s="109" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="110" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" s="109" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
+        </is>
+      </c>
+      <c r="C81" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D81" s="129" t="n">
+        <v>70</v>
+      </c>
+      <c r="E81" s="111">
+        <f>'Bao gia'!J23</f>
+        <v/>
+      </c>
+      <c r="F81" s="111" t="n">
+        <v>58022</v>
+      </c>
+      <c r="G81" s="111">
+        <f>IF(M81=0,"",N81/M81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="108">
+        <f>ROUNDUP(E81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I81" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="111">
+        <f>D81*(E81+F81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="111">
+        <f>D81*H81</f>
+        <v/>
+      </c>
+      <c r="L81" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M81" s="130" t="n">
+        <v>70</v>
+      </c>
+      <c r="N81" s="111" t="n">
+        <v>33600000</v>
+      </c>
+      <c r="O81" s="111">
+        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
+        <v/>
+      </c>
+      <c r="P81" s="109" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="110" t="n">
+        <v>21</v>
+      </c>
+      <c r="B82" s="109" t="inlineStr">
+        <is>
+          <t>Lăng phun DN50</t>
+        </is>
+      </c>
+      <c r="C82" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D82" s="129" t="n">
+        <v>70</v>
+      </c>
+      <c r="E82" s="111">
+        <f>'Bao gia'!J24</f>
+        <v/>
+      </c>
+      <c r="F82" s="111" t="n">
+        <v>9670</v>
+      </c>
+      <c r="G82" s="111">
+        <f>IF(M82=0,"",N82/M82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="108">
+        <f>ROUNDUP(E82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I82" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="111">
+        <f>D82*(E82+F82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="111">
+        <f>D82*H82</f>
+        <v/>
+      </c>
+      <c r="L82" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M82" s="130" t="n">
+        <v>70</v>
+      </c>
+      <c r="N82" s="111" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="O82" s="111">
+        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
+        <v/>
+      </c>
+      <c r="P82" s="109" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="110" t="n">
+        <v>22</v>
+      </c>
+      <c r="B83" s="109" t="inlineStr">
+        <is>
+          <t>Van góc FUJI DN50</t>
+        </is>
+      </c>
+      <c r="C83" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D83" s="129" t="n">
+        <v>70</v>
+      </c>
+      <c r="E83" s="111">
+        <f>'Bao gia'!J25</f>
+        <v/>
+      </c>
+      <c r="F83" s="111" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G83" s="111">
+        <f>IF(M83=0,"",N83/M83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="108">
+        <f>ROUNDUP(E83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I83" s="111" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J83" s="111">
+        <f>D83*(E83+F83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="111">
+        <f>D83*H83</f>
+        <v/>
+      </c>
+      <c r="L83" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M83" s="130" t="n">
+        <v>70.00700000000001</v>
+      </c>
+      <c r="N83" s="111" t="n">
+        <v>17501750</v>
+      </c>
+      <c r="O83" s="111">
+        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
+        <v/>
+      </c>
+      <c r="P83" s="109" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="110" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" s="109" t="inlineStr">
+        <is>
+          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
+        </is>
+      </c>
+      <c r="C84" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D84" s="129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="111">
+        <f>'Bao gia'!J26</f>
+        <v/>
+      </c>
+      <c r="F84" s="111" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G84" s="111">
+        <f>IF(M84=0,"",N84/M84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="108">
+        <f>ROUNDUP(E84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I84" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="111">
+        <f>D84*(E84+F84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="111">
+        <f>D84*H84</f>
+        <v/>
+      </c>
+      <c r="L84" s="110" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M84" s="130" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" s="111" t="n">
         <v>200000</v>
       </c>
-      <c r="F78" s="107" t="n">
+      <c r="O84" s="111">
+        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
+        <v/>
+      </c>
+      <c r="P84" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="110" t="n">
+        <v>24</v>
+      </c>
+      <c r="B85" s="109" t="inlineStr">
+        <is>
+          <t>Kệ đỡ bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="C85" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D85" s="129" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" s="111">
+        <f>'Bao gia'!J27</f>
+        <v/>
+      </c>
+      <c r="F85" s="111" t="n">
+        <v>31538</v>
+      </c>
+      <c r="G85" s="111">
+        <f>IF(M85=0,"",N85/M85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="108">
+        <f>ROUNDUP(E85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I85" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="111">
+        <f>D85*(E85+F85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="111">
+        <f>D85*H85</f>
+        <v/>
+      </c>
+      <c r="L85" s="110" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M85" s="130" t="n">
+        <v>10</v>
+      </c>
+      <c r="N85" s="111" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="O85" s="111">
+        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
+        <v/>
+      </c>
+      <c r="P85" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="110" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" s="109" t="inlineStr">
+        <is>
+          <t>BÌNH BỘT ABC 8KG</t>
+        </is>
+      </c>
+      <c r="C86" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D86" s="129" t="n">
+        <v>20</v>
+      </c>
+      <c r="E86" s="111">
+        <f>'Bao gia'!J28</f>
+        <v/>
+      </c>
+      <c r="F86" s="111" t="n">
+        <v>10769</v>
+      </c>
+      <c r="G86" s="111">
+        <f>IF(M86=0,"",N86/M86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="108">
+        <f>ROUNDUP(E86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I86" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="111">
+        <f>D86*(E86+F86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="111">
+        <f>D86*H86</f>
+        <v/>
+      </c>
+      <c r="L86" s="110" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M86" s="130" t="n">
+        <v>20</v>
+      </c>
+      <c r="N86" s="111" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="O86" s="111">
+        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
+        <v/>
+      </c>
+      <c r="P86" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="110" t="n">
+        <v>26</v>
+      </c>
+      <c r="B87" s="109" t="inlineStr">
+        <is>
+          <t>Đèn exit</t>
+        </is>
+      </c>
+      <c r="C87" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D87" s="129" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" s="111">
+        <f>'Bao gia'!J29</f>
+        <v/>
+      </c>
+      <c r="F87" s="111" t="n">
         <v>100000</v>
       </c>
-      <c r="G78" s="107">
-        <f>IF(M78=0,"",N78/M78)</f>
-        <v/>
-      </c>
-      <c r="H78" s="104">
-        <f>ROUNDUP(E78*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I78" s="107" t="n">
-        <v>97774</v>
-      </c>
-      <c r="J78" s="107">
-        <f>D78*(E78+F78)</f>
-        <v/>
-      </c>
-      <c r="K78" s="107">
-        <f>D78*H78</f>
-        <v/>
-      </c>
-      <c r="L78" s="106" t="inlineStr">
+      <c r="G87" s="111">
+        <f>IF(M87=0,"",N87/M87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="108">
+        <f>ROUNDUP(E87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I87" s="111" t="n">
+        <v>93090</v>
+      </c>
+      <c r="J87" s="111">
+        <f>D87*(E87+F87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="111">
+        <f>D87*H87</f>
+        <v/>
+      </c>
+      <c r="L87" s="110" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M78" s="124" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="N78" s="107" t="n">
-        <v>350035</v>
-      </c>
-      <c r="O78" s="107">
-        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
-        <v/>
-      </c>
-      <c r="P78" s="105" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="106" t="n">
-        <v>18</v>
-      </c>
-      <c r="B79" s="105" t="inlineStr">
-        <is>
-          <t>Rơ le kiểm tra mực nước</t>
-        </is>
-      </c>
-      <c r="C79" s="106" t="inlineStr">
+      <c r="M87" s="130" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="N87" s="111" t="n">
+        <v>2310000</v>
+      </c>
+      <c r="O87" s="111">
+        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
+        <v/>
+      </c>
+      <c r="P87" s="109" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="110" t="n">
+        <v>27</v>
+      </c>
+      <c r="B88" s="109" t="inlineStr">
+        <is>
+          <t>Đèn chiếu sáng sự cố</t>
+        </is>
+      </c>
+      <c r="C88" s="110" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D79" s="123" t="n">
+      <c r="D88" s="129" t="n">
+        <v>54</v>
+      </c>
+      <c r="E88" s="111">
+        <f>'Bao gia'!J30</f>
+        <v/>
+      </c>
+      <c r="F88" s="111" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G88" s="111">
+        <f>IF(M88=0,"",N88/M88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="108">
+        <f>ROUNDUP(E88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I88" s="111" t="n">
+        <v>93090</v>
+      </c>
+      <c r="J88" s="111">
+        <f>D88*(E88+F88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="111">
+        <f>D88*H88</f>
+        <v/>
+      </c>
+      <c r="L88" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M88" s="130" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="N88" s="111" t="n">
+        <v>11340000</v>
+      </c>
+      <c r="O88" s="111">
+        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
+        <v/>
+      </c>
+      <c r="P88" s="109" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="110" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" s="109" t="inlineStr">
+        <is>
+          <t>Đèn báo trạm bơm</t>
+        </is>
+      </c>
+      <c r="C89" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D89" s="129">
+        <f>N('Bao gia'!D31)</f>
+        <v/>
+      </c>
+      <c r="E89" s="111">
+        <f>'Bao gia'!J31</f>
+        <v/>
+      </c>
+      <c r="F89" s="111" t="n"/>
+      <c r="G89" s="111">
+        <f>IF(M89=0,"",N89/M89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="108">
+        <f>ROUNDUP(E89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I89" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="111">
+        <f>D89*(E89+F89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="111">
+        <f>D89*H89</f>
+        <v/>
+      </c>
+      <c r="L89" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M89" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="111">
+        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
+        <v/>
+      </c>
+      <c r="P89" s="109" t="inlineStr">
+        <is>
+          <t>Chưa có giá vốn, chưa có trong dự toán – nếu dùng thì điền KL và giá vốn ở sheet Bao gia</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="110" t="n">
+        <v>29</v>
+      </c>
+      <c r="B90" s="109" t="inlineStr">
+        <is>
+          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
+        </is>
+      </c>
+      <c r="C90" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D90" s="129" t="n">
+        <v>35</v>
+      </c>
+      <c r="E90" s="111">
+        <f>'Bao gia'!J32</f>
+        <v/>
+      </c>
+      <c r="F90" s="111" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G90" s="111">
+        <f>IF(M90=0,"",N90/M90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="108">
+        <f>ROUNDUP(E90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I90" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="111">
+        <f>D90*(E90+F90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="111">
+        <f>D90*H90</f>
+        <v/>
+      </c>
+      <c r="L90" s="110" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M90" s="130" t="n">
+        <v>35</v>
+      </c>
+      <c r="N90" s="111" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="O90" s="111">
+        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
+        <v/>
+      </c>
+      <c r="P90" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="110" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" s="109" t="inlineStr">
+        <is>
+          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
+        </is>
+      </c>
+      <c r="C91" s="110" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D91" s="129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" s="111">
+        <f>'Bao gia'!J33</f>
+        <v/>
+      </c>
+      <c r="F91" s="111" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G91" s="111">
+        <f>IF(M91=0,"",N91/M91)</f>
+        <v/>
+      </c>
+      <c r="H91" s="108">
+        <f>ROUNDUP(E91*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I91" s="111" t="n">
+        <v>110390</v>
+      </c>
+      <c r="J91" s="111">
+        <f>D91*(E91+F91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="111">
+        <f>D91*H91</f>
+        <v/>
+      </c>
+      <c r="L91" s="110" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M91" s="130" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="N91" s="111" t="n">
+        <v>2852850</v>
+      </c>
+      <c r="O91" s="111">
+        <f>IF(L91="Thiết bị",0,$E$7*(M91*H91-N91))</f>
+        <v/>
+      </c>
+      <c r="P91" s="109" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="126" t="n"/>
+      <c r="B92" s="126" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C92" s="126" t="n"/>
+      <c r="D92" s="126" t="n"/>
+      <c r="E92" s="126" t="n"/>
+      <c r="F92" s="126" t="n"/>
+      <c r="G92" s="126" t="n"/>
+      <c r="H92" s="126" t="n"/>
+      <c r="I92" s="126" t="n"/>
+      <c r="J92" s="118">
+        <f>SUM(J62:J91)</f>
+        <v/>
+      </c>
+      <c r="K92" s="118">
+        <f>SUM(K62:K91)</f>
+        <v/>
+      </c>
+      <c r="L92" s="126" t="n"/>
+      <c r="M92" s="126" t="n"/>
+      <c r="N92" s="118">
+        <f>SUM(N62:N91)</f>
+        <v/>
+      </c>
+      <c r="O92" s="118">
+        <f>SUM(O62:O91)</f>
+        <v/>
+      </c>
+      <c r="P92" s="126" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="103" t="inlineStr">
+        <is>
+          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="104" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B95" s="104" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C95" s="104" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D95" s="104" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E95" s="104" t="inlineStr">
+        <is>
+          <t>Giá vốn VT</t>
+        </is>
+      </c>
+      <c r="F95" s="104" t="inlineStr">
+        <is>
+          <t>Giá vốn NC</t>
+        </is>
+      </c>
+      <c r="G95" s="104" t="inlineStr">
+        <is>
+          <t>Thành tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" s="109" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN65</t>
+        </is>
+      </c>
+      <c r="C96" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D96" s="129" t="n">
+        <v>860</v>
+      </c>
+      <c r="E96" s="111" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F96" s="111" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G96" s="111" t="n">
+        <v>206400000</v>
+      </c>
+      <c r="H96" s="91" t="inlineStr">
+        <is>
+          <t>Trong đó vật tư phụ 5%:</t>
+        </is>
+      </c>
+      <c r="J96" s="131">
+        <f>SUMIF(C96:C110,"Vật tư phụ",G96:G110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B97" s="109" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C97" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D97" s="129" t="n">
+        <v>570</v>
+      </c>
+      <c r="E97" s="111" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F97" s="111" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G97" s="111" t="n">
+        <v>125400000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" s="109" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN80</t>
+        </is>
+      </c>
+      <c r="C98" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D98" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="111" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F98" s="111" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G98" s="111" t="n">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="121" t="n">
         <v>4</v>
       </c>
-      <c r="E79" s="107" t="n">
-        <v>2205000</v>
-      </c>
-      <c r="F79" s="107" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G79" s="107">
-        <f>IF(M79=0,"",N79/M79)</f>
-        <v/>
-      </c>
-      <c r="H79" s="104">
-        <f>ROUNDUP(E79*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I79" s="107" t="n">
-        <v>31540</v>
-      </c>
-      <c r="J79" s="107">
-        <f>D79*(E79+F79)</f>
-        <v/>
-      </c>
-      <c r="K79" s="107">
-        <f>D79*H79</f>
-        <v/>
-      </c>
-      <c r="L79" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M79" s="124" t="n">
-        <v>4.0004</v>
-      </c>
-      <c r="N79" s="107" t="n">
-        <v>4600460</v>
-      </c>
-      <c r="O79" s="107">
-        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
-        <v/>
-      </c>
-      <c r="P79" s="105" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="106" t="n">
-        <v>19</v>
-      </c>
-      <c r="B80" s="105" t="inlineStr">
-        <is>
-          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
-        </is>
-      </c>
-      <c r="C80" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D80" s="123" t="n">
-        <v>57</v>
-      </c>
-      <c r="E80" s="107" t="n">
-        <v>368000</v>
-      </c>
-      <c r="F80" s="107" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G80" s="107">
-        <f>IF(M80=0,"",N80/M80)</f>
-        <v/>
-      </c>
-      <c r="H80" s="104">
-        <f>ROUNDUP(E80*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I80" s="107" t="n">
-        <v>94620</v>
-      </c>
-      <c r="J80" s="107">
-        <f>D80*(E80+F80)</f>
-        <v/>
-      </c>
-      <c r="K80" s="107">
-        <f>D80*H80</f>
-        <v/>
-      </c>
-      <c r="L80" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M80" s="124" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="N80" s="107" t="n">
-        <v>19152000</v>
-      </c>
-      <c r="O80" s="107">
-        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
-        <v/>
-      </c>
-      <c r="P80" s="105" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="106" t="n">
-        <v>20</v>
-      </c>
-      <c r="B81" s="105" t="inlineStr">
-        <is>
-          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
-        </is>
-      </c>
-      <c r="C81" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D81" s="123" t="n">
-        <v>70</v>
-      </c>
-      <c r="E81" s="107" t="n">
-        <v>514286</v>
-      </c>
-      <c r="F81" s="107" t="n">
-        <v>58022</v>
-      </c>
-      <c r="G81" s="107">
-        <f>IF(M81=0,"",N81/M81)</f>
-        <v/>
-      </c>
-      <c r="H81" s="104">
-        <f>ROUNDUP(E81*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I81" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="107">
-        <f>D81*(E81+F81)</f>
-        <v/>
-      </c>
-      <c r="K81" s="107">
-        <f>D81*H81</f>
-        <v/>
-      </c>
-      <c r="L81" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M81" s="124" t="n">
-        <v>70</v>
-      </c>
-      <c r="N81" s="107" t="n">
-        <v>33600000</v>
-      </c>
-      <c r="O81" s="107">
-        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
-        <v/>
-      </c>
-      <c r="P81" s="105" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="106" t="n">
-        <v>21</v>
-      </c>
-      <c r="B82" s="105" t="inlineStr">
-        <is>
-          <t>Lăng phun DN50</t>
-        </is>
-      </c>
-      <c r="C82" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D82" s="123" t="n">
-        <v>70</v>
-      </c>
-      <c r="E82" s="107" t="n">
-        <v>85714</v>
-      </c>
-      <c r="F82" s="107" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G82" s="107">
-        <f>IF(M82=0,"",N82/M82)</f>
-        <v/>
-      </c>
-      <c r="H82" s="104">
-        <f>ROUNDUP(E82*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I82" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="107">
-        <f>D82*(E82+F82)</f>
-        <v/>
-      </c>
-      <c r="K82" s="107">
-        <f>D82*H82</f>
-        <v/>
-      </c>
-      <c r="L82" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M82" s="124" t="n">
-        <v>70</v>
-      </c>
-      <c r="N82" s="107" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="O82" s="107">
-        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
-        <v/>
-      </c>
-      <c r="P82" s="105" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="106" t="n">
-        <v>22</v>
-      </c>
-      <c r="B83" s="105" t="inlineStr">
-        <is>
-          <t>Van góc FUJI DN50</t>
-        </is>
-      </c>
-      <c r="C83" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D83" s="123" t="n">
-        <v>70</v>
-      </c>
-      <c r="E83" s="107" t="n">
-        <v>166000</v>
-      </c>
-      <c r="F83" s="107" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G83" s="107">
-        <f>IF(M83=0,"",N83/M83)</f>
-        <v/>
-      </c>
-      <c r="H83" s="104">
-        <f>ROUNDUP(E83*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I83" s="107" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J83" s="107">
-        <f>D83*(E83+F83)</f>
-        <v/>
-      </c>
-      <c r="K83" s="107">
-        <f>D83*H83</f>
-        <v/>
-      </c>
-      <c r="L83" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M83" s="124" t="n">
-        <v>70.00700000000001</v>
-      </c>
-      <c r="N83" s="107" t="n">
-        <v>17501750</v>
-      </c>
-      <c r="O83" s="107">
-        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
-        <v/>
-      </c>
-      <c r="P83" s="105" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="106" t="n">
-        <v>23</v>
-      </c>
-      <c r="B84" s="105" t="inlineStr">
-        <is>
-          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
-        </is>
-      </c>
-      <c r="C84" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D84" s="123" t="n">
+      <c r="B99" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C99" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D99" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="111" t="n"/>
+      <c r="F99" s="111" t="n"/>
+      <c r="G99" s="111" t="n">
+        <v>5345662</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="121" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="107" t="n">
-        <v>53000</v>
-      </c>
-      <c r="F84" s="107" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G84" s="107">
-        <f>IF(M84=0,"",N84/M84)</f>
-        <v/>
-      </c>
-      <c r="H84" s="104">
-        <f>ROUNDUP(E84*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I84" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="107">
-        <f>D84*(E84+F84)</f>
-        <v/>
-      </c>
-      <c r="K84" s="107">
-        <f>D84*H84</f>
-        <v/>
-      </c>
-      <c r="L84" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M84" s="124" t="n">
-        <v>5</v>
-      </c>
-      <c r="N84" s="107" t="n">
-        <v>200000</v>
-      </c>
-      <c r="O84" s="107">
-        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
-        <v/>
-      </c>
-      <c r="P84" s="105" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="106" t="n">
-        <v>24</v>
-      </c>
-      <c r="B85" s="105" t="inlineStr">
-        <is>
-          <t>Kệ đỡ bình chữa cháy</t>
-        </is>
-      </c>
-      <c r="C85" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D85" s="123" t="n">
+      <c r="B100" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C100" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D100" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="111" t="n"/>
+      <c r="F100" s="111" t="n"/>
+      <c r="G100" s="111" t="n">
+        <v>4422065</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="121" t="n">
+        <v>6</v>
+      </c>
+      <c r="B101" s="109" t="inlineStr">
+        <is>
+          <t>Dây nguồn đèn exit sự cố 2x0.75mm</t>
+        </is>
+      </c>
+      <c r="C101" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D101" s="129" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E101" s="111" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F101" s="111" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G101" s="111" t="n">
+        <v>21250000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="121" t="n">
+        <v>7</v>
+      </c>
+      <c r="B102" s="109" t="inlineStr">
+        <is>
+          <t>Ống luồn dây PVC D20</t>
+        </is>
+      </c>
+      <c r="C102" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D102" s="129" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E102" s="111" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F102" s="111" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G102" s="111" t="n">
+        <v>117000000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="121" t="n">
+        <v>8</v>
+      </c>
+      <c r="B103" s="109" t="inlineStr">
+        <is>
+          <t>Cáp tín hiệu 2x2x0,5mm2</t>
+        </is>
+      </c>
+      <c r="C103" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D103" s="129" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E103" s="111" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F103" s="111" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G103" s="111" t="n">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="121" t="n">
+        <v>9</v>
+      </c>
+      <c r="B104" s="109" t="inlineStr">
+        <is>
+          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
+        </is>
+      </c>
+      <c r="C104" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D104" s="129" t="n">
+        <v>130</v>
+      </c>
+      <c r="E104" s="111" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F104" s="111" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G104" s="111" t="n">
+        <v>1625000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="121" t="n">
         <v>10</v>
       </c>
-      <c r="E85" s="107" t="n">
-        <v>137000</v>
-      </c>
-      <c r="F85" s="107" t="n">
-        <v>31538</v>
-      </c>
-      <c r="G85" s="107">
-        <f>IF(M85=0,"",N85/M85)</f>
-        <v/>
-      </c>
-      <c r="H85" s="104">
-        <f>ROUNDUP(E85*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I85" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="107">
-        <f>D85*(E85+F85)</f>
-        <v/>
-      </c>
-      <c r="K85" s="107">
-        <f>D85*H85</f>
-        <v/>
-      </c>
-      <c r="L85" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M85" s="124" t="n">
-        <v>10</v>
-      </c>
-      <c r="N85" s="107" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="O85" s="107">
-        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
-        <v/>
-      </c>
-      <c r="P85" s="105" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="106" t="n">
-        <v>25</v>
-      </c>
-      <c r="B86" s="105" t="inlineStr">
-        <is>
-          <t>BÌNH BỘT ABC 8KG</t>
-        </is>
-      </c>
-      <c r="C86" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D86" s="123" t="n">
-        <v>20</v>
-      </c>
-      <c r="E86" s="107" t="n">
-        <v>652000</v>
-      </c>
-      <c r="F86" s="107" t="n">
-        <v>10769</v>
-      </c>
-      <c r="G86" s="107">
-        <f>IF(M86=0,"",N86/M86)</f>
-        <v/>
-      </c>
-      <c r="H86" s="104">
-        <f>ROUNDUP(E86*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I86" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="107">
-        <f>D86*(E86+F86)</f>
-        <v/>
-      </c>
-      <c r="K86" s="107">
-        <f>D86*H86</f>
-        <v/>
-      </c>
-      <c r="L86" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M86" s="124" t="n">
-        <v>20</v>
-      </c>
-      <c r="N86" s="107" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="O86" s="107">
-        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
-        <v/>
-      </c>
-      <c r="P86" s="105" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="106" t="n">
-        <v>26</v>
-      </c>
-      <c r="B87" s="105" t="inlineStr">
-        <is>
-          <t>Đèn exit</t>
-        </is>
-      </c>
-      <c r="C87" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D87" s="123" t="n">
+      <c r="B105" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C105" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D105" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="111" t="n"/>
+      <c r="F105" s="111" t="n"/>
+      <c r="G105" s="111" t="n">
+        <v>7726450</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="121" t="n">
         <v>11</v>
       </c>
-      <c r="E87" s="107" t="n">
-        <v>158000</v>
-      </c>
-      <c r="F87" s="107" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G87" s="107">
-        <f>IF(M87=0,"",N87/M87)</f>
-        <v/>
-      </c>
-      <c r="H87" s="104">
-        <f>ROUNDUP(E87*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I87" s="107" t="n">
-        <v>93090</v>
-      </c>
-      <c r="J87" s="107">
-        <f>D87*(E87+F87)</f>
-        <v/>
-      </c>
-      <c r="K87" s="107">
-        <f>D87*H87</f>
-        <v/>
-      </c>
-      <c r="L87" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M87" s="124" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="N87" s="107" t="n">
-        <v>2310000</v>
-      </c>
-      <c r="O87" s="107">
-        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
-        <v/>
-      </c>
-      <c r="P87" s="105" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="106" t="n">
-        <v>27</v>
-      </c>
-      <c r="B88" s="105" t="inlineStr">
-        <is>
-          <t>Đèn chiếu sáng sự cố</t>
-        </is>
-      </c>
-      <c r="C88" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D88" s="123" t="n">
-        <v>54</v>
-      </c>
-      <c r="E88" s="107" t="n">
-        <v>190000</v>
-      </c>
-      <c r="F88" s="107" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G88" s="107">
-        <f>IF(M88=0,"",N88/M88)</f>
-        <v/>
-      </c>
-      <c r="H88" s="104">
-        <f>ROUNDUP(E88*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I88" s="107" t="n">
-        <v>93090</v>
-      </c>
-      <c r="J88" s="107">
-        <f>D88*(E88+F88)</f>
-        <v/>
-      </c>
-      <c r="K88" s="107">
-        <f>D88*H88</f>
-        <v/>
-      </c>
-      <c r="L88" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M88" s="124" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="N88" s="107" t="n">
-        <v>11340000</v>
-      </c>
-      <c r="O88" s="107">
-        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
-        <v/>
-      </c>
-      <c r="P88" s="105" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="106" t="n">
-        <v>28</v>
-      </c>
-      <c r="B89" s="105" t="inlineStr">
-        <is>
-          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
-        </is>
-      </c>
-      <c r="C89" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D89" s="123" t="n">
-        <v>35</v>
-      </c>
-      <c r="E89" s="107" t="n">
-        <v>442000</v>
-      </c>
-      <c r="F89" s="107" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G89" s="107">
-        <f>IF(M89=0,"",N89/M89)</f>
-        <v/>
-      </c>
-      <c r="H89" s="104">
-        <f>ROUNDUP(E89*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I89" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="107">
-        <f>D89*(E89+F89)</f>
-        <v/>
-      </c>
-      <c r="K89" s="107">
-        <f>D89*H89</f>
-        <v/>
-      </c>
-      <c r="L89" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M89" s="124" t="n">
-        <v>35</v>
-      </c>
-      <c r="N89" s="107" t="n">
-        <v>5250000</v>
-      </c>
-      <c r="O89" s="107">
-        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
-        <v/>
-      </c>
-      <c r="P89" s="105" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="106" t="n">
-        <v>29</v>
-      </c>
-      <c r="B90" s="105" t="inlineStr">
-        <is>
-          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
-        </is>
-      </c>
-      <c r="C90" s="106" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D90" s="123" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" s="107" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="F90" s="107" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G90" s="107">
-        <f>IF(M90=0,"",N90/M90)</f>
-        <v/>
-      </c>
-      <c r="H90" s="104">
-        <f>ROUNDUP(E90*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I90" s="107" t="n">
-        <v>110390</v>
-      </c>
-      <c r="J90" s="107">
-        <f>D90*(E90+F90)</f>
-        <v/>
-      </c>
-      <c r="K90" s="107">
-        <f>D90*H90</f>
-        <v/>
-      </c>
-      <c r="L90" s="106" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M90" s="124" t="n">
-        <v>3.003</v>
-      </c>
-      <c r="N90" s="107" t="n">
-        <v>2852850</v>
-      </c>
-      <c r="O90" s="107">
-        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
-        <v/>
-      </c>
-      <c r="P90" s="105" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="120" t="n"/>
-      <c r="B91" s="120" t="inlineStr">
+      <c r="B106" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C106" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D106" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="111" t="n"/>
+      <c r="F106" s="111" t="n"/>
+      <c r="G106" s="111" t="n">
+        <v>6964392</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="121" t="n">
+        <v>12</v>
+      </c>
+      <c r="B107" s="109" t="inlineStr">
+        <is>
+          <t>Ống nhựa xoắn HDPE 40/30</t>
+        </is>
+      </c>
+      <c r="C107" s="121" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D107" s="129" t="n">
+        <v>200</v>
+      </c>
+      <c r="E107" s="111" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F107" s="111" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G107" s="111" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="121" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C108" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D108" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="111" t="n"/>
+      <c r="F108" s="111" t="n"/>
+      <c r="G108" s="111" t="n">
+        <v>6135550</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="121" t="n">
+        <v>14</v>
+      </c>
+      <c r="B109" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C109" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D109" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="111" t="n"/>
+      <c r="F109" s="111" t="n"/>
+      <c r="G109" s="111" t="n">
+        <v>5017119</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="121" t="n">
+        <v>15</v>
+      </c>
+      <c r="B110" s="109" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C110" s="121" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D110" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="111" t="n"/>
+      <c r="F110" s="111" t="n"/>
+      <c r="G110" s="111" t="n">
+        <v>4482900</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="126" t="n"/>
+      <c r="B111" s="126" t="inlineStr">
         <is>
           <t>CỘNG</t>
         </is>
       </c>
-      <c r="C91" s="120" t="n"/>
-      <c r="D91" s="120" t="n"/>
-      <c r="E91" s="120" t="n"/>
-      <c r="F91" s="120" t="n"/>
-      <c r="G91" s="120" t="n"/>
-      <c r="H91" s="120" t="n"/>
-      <c r="I91" s="120" t="n"/>
-      <c r="J91" s="112">
-        <f>SUM(J62:J90)</f>
-        <v/>
-      </c>
-      <c r="K91" s="112">
-        <f>SUM(K62:K90)</f>
-        <v/>
-      </c>
-      <c r="L91" s="120" t="n"/>
-      <c r="M91" s="120" t="n"/>
-      <c r="N91" s="112">
-        <f>SUM(N62:N90)</f>
-        <v/>
-      </c>
-      <c r="O91" s="112">
-        <f>SUM(O62:O90)</f>
-        <v/>
-      </c>
-      <c r="P91" s="120" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="99" t="inlineStr">
-        <is>
-          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="100" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B94" s="100" t="inlineStr">
-        <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="C94" s="100" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="D94" s="100" t="inlineStr">
-        <is>
-          <t>Khối lượng</t>
-        </is>
-      </c>
-      <c r="E94" s="100" t="inlineStr">
-        <is>
-          <t>Giá vốn VT</t>
-        </is>
-      </c>
-      <c r="F94" s="100" t="inlineStr">
-        <is>
-          <t>Giá vốn NC</t>
-        </is>
-      </c>
-      <c r="G94" s="100" t="inlineStr">
-        <is>
-          <t>Thành tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="115" t="n">
-        <v>1</v>
-      </c>
-      <c r="B95" s="105" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN65</t>
-        </is>
-      </c>
-      <c r="C95" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D95" s="123" t="n">
-        <v>860</v>
-      </c>
-      <c r="E95" s="107" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F95" s="107" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G95" s="107" t="n">
-        <v>206400000</v>
-      </c>
-      <c r="H95" s="89" t="inlineStr">
-        <is>
-          <t>Trong đó vật tư phụ 5%:</t>
-        </is>
-      </c>
-      <c r="J95" s="125">
-        <f>SUMIF(C95:C109,"Vật tư phụ",G95:G109)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="115" t="n">
-        <v>2</v>
-      </c>
-      <c r="B96" s="105" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C96" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D96" s="123" t="n">
-        <v>570</v>
-      </c>
-      <c r="E96" s="107" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F96" s="107" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G96" s="107" t="n">
-        <v>125400000</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="115" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="105" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN80</t>
-        </is>
-      </c>
-      <c r="C97" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D97" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="107" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F97" s="107" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G97" s="107" t="n">
-        <v>280000</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="115" t="n">
-        <v>4</v>
-      </c>
-      <c r="B98" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C98" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D98" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="107" t="n"/>
-      <c r="F98" s="107" t="n"/>
-      <c r="G98" s="107" t="n">
-        <v>5345662</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="115" t="n">
-        <v>5</v>
-      </c>
-      <c r="B99" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C99" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D99" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="107" t="n"/>
-      <c r="F99" s="107" t="n"/>
-      <c r="G99" s="107" t="n">
-        <v>4422065</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="115" t="n">
-        <v>6</v>
-      </c>
-      <c r="B100" s="105" t="inlineStr">
-        <is>
-          <t>Dây nguồn đèn exit sự cố 2x0.75mm</t>
-        </is>
-      </c>
-      <c r="C100" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D100" s="123" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E100" s="107" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F100" s="107" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G100" s="107" t="n">
-        <v>21250000</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="115" t="n">
-        <v>7</v>
-      </c>
-      <c r="B101" s="105" t="inlineStr">
-        <is>
-          <t>Ống luồn dây PVC D20</t>
-        </is>
-      </c>
-      <c r="C101" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D101" s="123" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E101" s="107" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F101" s="107" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G101" s="107" t="n">
-        <v>117000000</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="115" t="n">
-        <v>8</v>
-      </c>
-      <c r="B102" s="105" t="inlineStr">
-        <is>
-          <t>Cáp tín hiệu 2x2x0,5mm2</t>
-        </is>
-      </c>
-      <c r="C102" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D102" s="123" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E102" s="107" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F102" s="107" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G102" s="107" t="n">
-        <v>50000000</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="115" t="n">
-        <v>9</v>
-      </c>
-      <c r="B103" s="105" t="inlineStr">
-        <is>
-          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
-        </is>
-      </c>
-      <c r="C103" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D103" s="123" t="n">
-        <v>130</v>
-      </c>
-      <c r="E103" s="107" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F103" s="107" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G103" s="107" t="n">
-        <v>1625000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="115" t="n">
-        <v>10</v>
-      </c>
-      <c r="B104" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C104" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D104" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="107" t="n"/>
-      <c r="F104" s="107" t="n"/>
-      <c r="G104" s="107" t="n">
-        <v>7726450</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="115" t="n">
-        <v>11</v>
-      </c>
-      <c r="B105" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C105" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D105" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="107" t="n"/>
-      <c r="F105" s="107" t="n"/>
-      <c r="G105" s="107" t="n">
-        <v>6964392</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="115" t="n">
-        <v>12</v>
-      </c>
-      <c r="B106" s="105" t="inlineStr">
-        <is>
-          <t>Ống nhựa xoắn HDPE 40/30</t>
-        </is>
-      </c>
-      <c r="C106" s="115" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D106" s="123" t="n">
-        <v>200</v>
-      </c>
-      <c r="E106" s="107" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F106" s="107" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G106" s="107" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="115" t="n">
-        <v>13</v>
-      </c>
-      <c r="B107" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C107" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D107" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="107" t="n"/>
-      <c r="F107" s="107" t="n"/>
-      <c r="G107" s="107" t="n">
-        <v>6135550</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="115" t="n">
-        <v>14</v>
-      </c>
-      <c r="B108" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C108" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D108" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="107" t="n"/>
-      <c r="F108" s="107" t="n"/>
-      <c r="G108" s="107" t="n">
-        <v>5017119</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="115" t="n">
-        <v>15</v>
-      </c>
-      <c r="B109" s="105" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C109" s="115" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D109" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="107" t="n"/>
-      <c r="F109" s="107" t="n"/>
-      <c r="G109" s="107" t="n">
-        <v>4482900</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="120" t="n"/>
-      <c r="B110" s="120" t="inlineStr">
-        <is>
-          <t>CỘNG</t>
-        </is>
-      </c>
-      <c r="C110" s="120" t="n"/>
-      <c r="D110" s="120" t="n"/>
-      <c r="E110" s="120" t="n"/>
-      <c r="F110" s="120" t="n"/>
-      <c r="G110" s="112">
-        <f>SUM(G95:G109)</f>
+      <c r="C111" s="126" t="n"/>
+      <c r="D111" s="126" t="n"/>
+      <c r="E111" s="126" t="n"/>
+      <c r="F111" s="126" t="n"/>
+      <c r="G111" s="118">
+        <f>SUM(G96:G110)</f>
         <v/>
       </c>
     </row>

--- a/Báo giá 2.xlsx
+++ b/Báo giá 2.xlsx
@@ -14,7 +14,7 @@
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$L$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$M$35</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1" iterateCount="1"/>
 </workbook>
@@ -1002,6 +1002,7 @@
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1089,15 +1090,19 @@
       </c>
       <c r="P3" s="83" t="inlineStr">
         <is>
+          <t>Giá vốn nhân công (lấy từ sheet Bao gia)</t>
+        </is>
+      </c>
+      <c r="Q3" s="83" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="Q3" s="83" t="inlineStr">
-        <is>
-          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
-        </is>
-      </c>
-      <c r="R3" s="82" t="n"/>
+      <c r="R3" s="83" t="inlineStr">
+        <is>
+          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+        </is>
+      </c>
       <c r="S3" s="82" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -1126,7 +1131,7 @@
       <c r="O4" s="84" t="n"/>
       <c r="P4" s="84" t="n"/>
       <c r="Q4" s="84" t="n"/>
-      <c r="R4" s="82" t="n"/>
+      <c r="R4" s="84" t="n"/>
       <c r="S4" s="82" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
@@ -1177,15 +1182,18 @@
         <f>'Bao gia'!J26</f>
         <v/>
       </c>
-      <c r="P5" s="87">
+      <c r="P5" s="86">
+        <f>'Bao gia'!K26</f>
+        <v/>
+      </c>
+      <c r="Q5" s="87">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="Q5" s="88">
+      <c r="R5" s="88">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
-      <c r="R5" s="82" t="n"/>
       <c r="S5" s="82" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -1238,15 +1246,18 @@
         <f>'Bao gia'!J27</f>
         <v/>
       </c>
-      <c r="P6" s="87">
+      <c r="P6" s="86">
+        <f>'Bao gia'!K27</f>
+        <v/>
+      </c>
+      <c r="Q6" s="87">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="Q6" s="88">
+      <c r="R6" s="88">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
-      <c r="R6" s="82" t="n"/>
       <c r="S6" s="82" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -1299,15 +1310,18 @@
         <f>'Bao gia'!J28</f>
         <v/>
       </c>
-      <c r="P7" s="87">
+      <c r="P7" s="86">
+        <f>'Bao gia'!K28</f>
+        <v/>
+      </c>
+      <c r="Q7" s="87">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="Q7" s="88">
+      <c r="R7" s="88">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
-      <c r="R7" s="82" t="n"/>
       <c r="S7" s="82" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -1366,15 +1380,18 @@
         <f>'Bao gia'!J32</f>
         <v/>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="86">
+        <f>'Bao gia'!K32</f>
+        <v/>
+      </c>
+      <c r="Q8" s="87">
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="Q8" s="88">
+      <c r="R8" s="88">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
-      <c r="R8" s="82" t="n"/>
       <c r="S8" s="82" t="n"/>
     </row>
     <row r="9" ht="18.75" customFormat="1" customHeight="1" s="10">
@@ -1412,7 +1429,7 @@
       <c r="O9" s="84" t="n"/>
       <c r="P9" s="84" t="n"/>
       <c r="Q9" s="84" t="n"/>
-      <c r="R9" s="82" t="n"/>
+      <c r="R9" s="84" t="n"/>
       <c r="S9" s="82" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -1439,7 +1456,7 @@
       <c r="O10" s="84" t="n"/>
       <c r="P10" s="84" t="n"/>
       <c r="Q10" s="84" t="n"/>
-      <c r="R10" s="82" t="n"/>
+      <c r="R10" s="84" t="n"/>
       <c r="S10" s="82" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -1481,7 +1498,7 @@
     <col width="22" customWidth="1" style="1" min="10" max="16384"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1555,20 +1572,24 @@
       </c>
       <c r="J3" s="83" t="inlineStr">
         <is>
-          <t>Giá vốn vật tư, thiết bị (điền giá chuẩn)</t>
+          <t>Giá vốn vật tư, thiết bị (điền giá thực tế)</t>
         </is>
       </c>
       <c r="K3" s="83" t="inlineStr">
         <is>
+          <t>Giá vốn nhân công (điền giá thực tế)</t>
+        </is>
+      </c>
+      <c r="L3" s="83" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="L3" s="83" t="inlineStr">
-        <is>
-          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
-        </is>
-      </c>
-      <c r="M3" s="82" t="n"/>
+      <c r="M3" s="83" t="inlineStr">
+        <is>
+          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+        </is>
+      </c>
       <c r="N3" s="82" t="n"/>
     </row>
     <row r="4" ht="37.5" customHeight="1">
@@ -1610,15 +1631,17 @@
       <c r="J4" s="89" t="n">
         <v>8600000</v>
       </c>
-      <c r="K4" s="87">
+      <c r="K4" s="89" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="L4" s="87">
         <f>'Danh gia LN'!H62</f>
         <v/>
       </c>
-      <c r="L4" s="88">
+      <c r="M4" s="88">
         <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
-      <c r="M4" s="82" t="n"/>
       <c r="N4" s="82" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -1660,15 +1683,17 @@
       <c r="J5" s="89" t="n">
         <v>252000</v>
       </c>
-      <c r="K5" s="87">
+      <c r="K5" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L5" s="87">
         <f>'Danh gia LN'!H63</f>
         <v/>
       </c>
-      <c r="L5" s="88">
+      <c r="M5" s="88">
         <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
-      <c r="M5" s="82" t="n"/>
       <c r="N5" s="82" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -1711,15 +1736,17 @@
       <c r="J6" s="89" t="n">
         <v>205000</v>
       </c>
-      <c r="K6" s="87">
+      <c r="K6" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L6" s="87">
         <f>'Danh gia LN'!H64</f>
         <v/>
       </c>
-      <c r="L6" s="88">
+      <c r="M6" s="88">
         <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
-      <c r="M6" s="82" t="n"/>
       <c r="N6" s="82" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -1762,15 +1789,17 @@
       <c r="J7" s="89" t="n">
         <v>242000</v>
       </c>
-      <c r="K7" s="87">
+      <c r="K7" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L7" s="87">
         <f>'Danh gia LN'!H65</f>
         <v/>
       </c>
-      <c r="L7" s="88">
+      <c r="M7" s="88">
         <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
-      <c r="M7" s="82" t="n"/>
       <c r="N7" s="82" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -1813,15 +1842,17 @@
       <c r="J8" s="89" t="n">
         <v>116000</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L8" s="87">
         <f>'Danh gia LN'!H66</f>
         <v/>
       </c>
-      <c r="L8" s="88">
+      <c r="M8" s="88">
         <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
-      <c r="M8" s="82" t="n"/>
       <c r="N8" s="82" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -1864,15 +1895,17 @@
       <c r="J9" s="89" t="n">
         <v>252000</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="89" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L9" s="87">
         <f>'Danh gia LN'!H67</f>
         <v/>
       </c>
-      <c r="L9" s="88">
+      <c r="M9" s="88">
         <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
-      <c r="M9" s="82" t="n"/>
       <c r="N9" s="82" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -1915,15 +1948,17 @@
       <c r="J10" s="89" t="n">
         <v>53000</v>
       </c>
-      <c r="K10" s="87">
+      <c r="K10" s="89" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L10" s="87">
         <f>'Danh gia LN'!H68</f>
         <v/>
       </c>
-      <c r="L10" s="88">
+      <c r="M10" s="88">
         <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
-      <c r="M10" s="82" t="n"/>
       <c r="N10" s="82" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -1966,15 +2001,17 @@
       <c r="J11" s="89" t="n">
         <v>42000</v>
       </c>
-      <c r="K11" s="87">
+      <c r="K11" s="89" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L11" s="87">
         <f>'Danh gia LN'!H69</f>
         <v/>
       </c>
-      <c r="L11" s="88">
+      <c r="M11" s="88">
         <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
-      <c r="M11" s="82" t="n"/>
       <c r="N11" s="82" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -2017,15 +2054,17 @@
       <c r="J12" s="89" t="n">
         <v>95000</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="89" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L12" s="87">
         <f>'Danh gia LN'!H70</f>
         <v/>
       </c>
-      <c r="L12" s="88">
+      <c r="M12" s="88">
         <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
-      <c r="M12" s="82" t="n"/>
       <c r="N12" s="82" t="n"/>
     </row>
     <row r="13" ht="18.75" customFormat="1" customHeight="1" s="69">
@@ -2068,15 +2107,17 @@
       <c r="J13" s="89" t="n">
         <v>190000</v>
       </c>
-      <c r="K13" s="87">
+      <c r="K13" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L13" s="87">
         <f>'Danh gia LN'!H71</f>
         <v/>
       </c>
-      <c r="L13" s="88">
+      <c r="M13" s="88">
         <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
-      <c r="M13" s="82" t="n"/>
       <c r="N13" s="82" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -2119,15 +2160,17 @@
       <c r="J14" s="89" t="n">
         <v>75000</v>
       </c>
-      <c r="K14" s="87">
+      <c r="K14" s="89" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L14" s="87">
         <f>'Danh gia LN'!H72</f>
         <v/>
       </c>
-      <c r="L14" s="88">
+      <c r="M14" s="88">
         <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
-      <c r="M14" s="82" t="n"/>
       <c r="N14" s="82" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
@@ -2170,15 +2213,17 @@
       <c r="J15" s="89" t="n">
         <v>245000</v>
       </c>
-      <c r="K15" s="87">
+      <c r="K15" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L15" s="87">
         <f>'Danh gia LN'!H73</f>
         <v/>
       </c>
-      <c r="L15" s="88">
+      <c r="M15" s="88">
         <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
-      <c r="M15" s="82" t="n"/>
       <c r="N15" s="82" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
@@ -2221,15 +2266,17 @@
       <c r="J16" s="89" t="n">
         <v>190000</v>
       </c>
-      <c r="K16" s="87">
+      <c r="K16" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L16" s="87">
         <f>'Danh gia LN'!H74</f>
         <v/>
       </c>
-      <c r="L16" s="88">
+      <c r="M16" s="88">
         <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
-      <c r="M16" s="82" t="n"/>
       <c r="N16" s="82" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
@@ -2272,15 +2319,17 @@
       <c r="J17" s="89" t="n">
         <v>231000</v>
       </c>
-      <c r="K17" s="87">
+      <c r="K17" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L17" s="87">
         <f>'Danh gia LN'!H75</f>
         <v/>
       </c>
-      <c r="L17" s="88">
+      <c r="M17" s="88">
         <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
-      <c r="M17" s="82" t="n"/>
       <c r="N17" s="82" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
@@ -2323,15 +2372,17 @@
       <c r="J18" s="89" t="n">
         <v>95000</v>
       </c>
-      <c r="K18" s="87">
+      <c r="K18" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L18" s="87">
         <f>'Danh gia LN'!H76</f>
         <v/>
       </c>
-      <c r="L18" s="88">
+      <c r="M18" s="88">
         <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
-      <c r="M18" s="82" t="n"/>
       <c r="N18" s="82" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
@@ -2374,15 +2425,17 @@
       <c r="J19" s="89" t="n">
         <v>17000</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="89" t="n">
+        <v>11538</v>
+      </c>
+      <c r="L19" s="87">
         <f>'Danh gia LN'!H77</f>
         <v/>
       </c>
-      <c r="L19" s="88">
+      <c r="M19" s="88">
         <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
-      <c r="M19" s="82" t="n"/>
       <c r="N19" s="82" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
@@ -2424,15 +2477,17 @@
       <c r="J20" s="89" t="n">
         <v>200000</v>
       </c>
-      <c r="K20" s="87">
+      <c r="K20" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L20" s="87">
         <f>'Danh gia LN'!H78</f>
         <v/>
       </c>
-      <c r="L20" s="88">
+      <c r="M20" s="88">
         <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
-      <c r="M20" s="82" t="n"/>
       <c r="N20" s="82" t="n"/>
     </row>
     <row r="21" ht="18.75" customFormat="1" customHeight="1" s="69">
@@ -2473,15 +2528,17 @@
       <c r="J21" s="89" t="n">
         <v>2205000</v>
       </c>
-      <c r="K21" s="87">
+      <c r="K21" s="89" t="n">
+        <v>150000</v>
+      </c>
+      <c r="L21" s="87">
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="L21" s="88">
+      <c r="M21" s="88">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
-      <c r="M21" s="82" t="n"/>
       <c r="N21" s="82" t="n"/>
     </row>
     <row r="22" ht="37.5" customHeight="1">
@@ -2524,15 +2581,17 @@
       <c r="J22" s="89" t="n">
         <v>368000</v>
       </c>
-      <c r="K22" s="87">
+      <c r="K22" s="89" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L22" s="87">
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="L22" s="88">
+      <c r="M22" s="88">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
-      <c r="M22" s="82" t="n"/>
       <c r="N22" s="82" t="n"/>
     </row>
     <row r="23" ht="37.5" customHeight="1">
@@ -2575,15 +2634,17 @@
       <c r="J23" s="89" t="n">
         <v>514286</v>
       </c>
-      <c r="K23" s="87">
+      <c r="K23" s="89" t="n">
+        <v>58022</v>
+      </c>
+      <c r="L23" s="87">
         <f>'Danh gia LN'!H81</f>
         <v/>
       </c>
-      <c r="L23" s="88">
+      <c r="M23" s="88">
         <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
-      <c r="M23" s="82" t="n"/>
       <c r="N23" s="82" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
@@ -2626,15 +2687,17 @@
       <c r="J24" s="89" t="n">
         <v>85714</v>
       </c>
-      <c r="K24" s="87">
+      <c r="K24" s="89" t="n">
+        <v>9670</v>
+      </c>
+      <c r="L24" s="87">
         <f>'Danh gia LN'!H82</f>
         <v/>
       </c>
-      <c r="L24" s="88">
+      <c r="M24" s="88">
         <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
-      <c r="M24" s="82" t="n"/>
       <c r="N24" s="82" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
@@ -2677,15 +2740,17 @@
       <c r="J25" s="89" t="n">
         <v>166000</v>
       </c>
-      <c r="K25" s="87">
+      <c r="K25" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L25" s="87">
         <f>'Danh gia LN'!H83</f>
         <v/>
       </c>
-      <c r="L25" s="88">
+      <c r="M25" s="88">
         <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
-      <c r="M25" s="82" t="n"/>
       <c r="N25" s="82" t="n"/>
     </row>
     <row r="26" ht="37.5" customHeight="1">
@@ -2729,15 +2794,17 @@
       <c r="J26" s="89" t="n">
         <v>53000</v>
       </c>
-      <c r="K26" s="87">
+      <c r="K26" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L26" s="87">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="L26" s="88">
+      <c r="M26" s="88">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
-      <c r="M26" s="82" t="n"/>
       <c r="N26" s="82" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
@@ -2781,15 +2848,17 @@
       <c r="J27" s="89" t="n">
         <v>137000</v>
       </c>
-      <c r="K27" s="87">
+      <c r="K27" s="89" t="n">
+        <v>31538</v>
+      </c>
+      <c r="L27" s="87">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="L27" s="88">
+      <c r="M27" s="88">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
-      <c r="M27" s="82" t="n"/>
       <c r="N27" s="82" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
@@ -2833,15 +2902,17 @@
       <c r="J28" s="89" t="n">
         <v>652000</v>
       </c>
-      <c r="K28" s="87">
+      <c r="K28" s="89" t="n">
+        <v>10769</v>
+      </c>
+      <c r="L28" s="87">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="L28" s="88">
+      <c r="M28" s="88">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
-      <c r="M28" s="82" t="n"/>
       <c r="N28" s="82" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
@@ -2884,15 +2955,17 @@
       <c r="J29" s="89" t="n">
         <v>158000</v>
       </c>
-      <c r="K29" s="87">
+      <c r="K29" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L29" s="87">
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="L29" s="88">
+      <c r="M29" s="88">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
-      <c r="M29" s="82" t="n"/>
       <c r="N29" s="82" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -2935,15 +3008,17 @@
       <c r="J30" s="89" t="n">
         <v>190000</v>
       </c>
-      <c r="K30" s="87">
+      <c r="K30" s="89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L30" s="87">
         <f>'Danh gia LN'!H88</f>
         <v/>
       </c>
-      <c r="L30" s="88">
+      <c r="M30" s="88">
         <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
-      <c r="M30" s="82" t="n"/>
       <c r="N30" s="82" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -2980,15 +3055,15 @@
         </is>
       </c>
       <c r="J31" s="89" t="n"/>
-      <c r="K31" s="87">
+      <c r="K31" s="89" t="n"/>
+      <c r="L31" s="87">
         <f>'Danh gia LN'!H89</f>
         <v/>
       </c>
-      <c r="L31" s="88">
+      <c r="M31" s="88">
         <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
-      <c r="M31" s="82" t="n"/>
       <c r="N31" s="82" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -3032,15 +3107,17 @@
       <c r="J32" s="89" t="n">
         <v>442000</v>
       </c>
-      <c r="K32" s="87">
+      <c r="K32" s="89" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" s="87">
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="L32" s="88">
+      <c r="M32" s="88">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
-      <c r="M32" s="82" t="n"/>
       <c r="N32" s="82" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -3083,15 +3160,17 @@
       <c r="J33" s="89" t="n">
         <v>1260000</v>
       </c>
-      <c r="K33" s="87">
+      <c r="K33" s="89" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L33" s="87">
         <f>'Danh gia LN'!H91</f>
         <v/>
       </c>
-      <c r="L33" s="88">
+      <c r="M33" s="88">
         <f>'Danh gia LN'!I91</f>
         <v/>
       </c>
-      <c r="M33" s="82" t="n"/>
       <c r="N33" s="82" t="n"/>
     </row>
     <row r="34" customFormat="1" s="46">
@@ -3117,7 +3196,7 @@
       <c r="J34" s="84" t="n"/>
       <c r="K34" s="84" t="n"/>
       <c r="L34" s="84" t="n"/>
-      <c r="M34" s="82" t="n"/>
+      <c r="M34" s="84" t="n"/>
       <c r="N34" s="82" t="n"/>
     </row>
     <row r="35" customFormat="1" s="46">
@@ -3140,7 +3219,7 @@
       <c r="J35" s="84" t="n"/>
       <c r="K35" s="84" t="n"/>
       <c r="L35" s="84" t="n"/>
-      <c r="M35" s="82" t="n"/>
+      <c r="M35" s="84" t="n"/>
       <c r="N35" s="82" t="n"/>
     </row>
   </sheetData>
@@ -4814,7 +4893,7 @@
       </c>
       <c r="F61" s="104" t="inlineStr">
         <is>
-          <t>Giá vốn nhân công (sheet Gia von chi tiet)</t>
+          <t>Giá vốn nhân công (từ sheet Bao gia)</t>
         </is>
       </c>
       <c r="G61" s="104" t="inlineStr">
@@ -4829,7 +4908,7 @@
       </c>
       <c r="I61" s="104" t="inlineStr">
         <is>
-          <t>Nhân công theo định mức</t>
+          <t>Nhân công báo giá (theo dự toán)</t>
         </is>
       </c>
       <c r="J61" s="104" t="inlineStr">
@@ -4889,8 +4968,9 @@
         <f>'Bao gia'!J4</f>
         <v/>
       </c>
-      <c r="F62" s="111" t="n">
-        <v>1500000</v>
+      <c r="F62" s="111">
+        <f>'Bao gia'!K4</f>
+        <v/>
       </c>
       <c r="G62" s="111">
         <f>IF(M62=0,"",N62/M62)</f>
@@ -4949,8 +5029,9 @@
         <f>'Bao gia'!J5</f>
         <v/>
       </c>
-      <c r="F63" s="111" t="n">
-        <v>100000</v>
+      <c r="F63" s="111">
+        <f>'Bao gia'!K5</f>
+        <v/>
       </c>
       <c r="G63" s="111">
         <f>IF(M63=0,"",N63/M63)</f>
@@ -5009,8 +5090,9 @@
         <f>'Bao gia'!J6</f>
         <v/>
       </c>
-      <c r="F64" s="111" t="n">
-        <v>100000</v>
+      <c r="F64" s="111">
+        <f>'Bao gia'!K6</f>
+        <v/>
       </c>
       <c r="G64" s="111">
         <f>IF(M64=0,"",N64/M64)</f>
@@ -5069,8 +5151,9 @@
         <f>'Bao gia'!J7</f>
         <v/>
       </c>
-      <c r="F65" s="111" t="n">
-        <v>100000</v>
+      <c r="F65" s="111">
+        <f>'Bao gia'!K7</f>
+        <v/>
       </c>
       <c r="G65" s="111">
         <f>IF(M65=0,"",N65/M65)</f>
@@ -5129,8 +5212,9 @@
         <f>'Bao gia'!J8</f>
         <v/>
       </c>
-      <c r="F66" s="111" t="n">
-        <v>100000</v>
+      <c r="F66" s="111">
+        <f>'Bao gia'!K8</f>
+        <v/>
       </c>
       <c r="G66" s="111">
         <f>IF(M66=0,"",N66/M66)</f>
@@ -5189,8 +5273,9 @@
         <f>'Bao gia'!J9</f>
         <v/>
       </c>
-      <c r="F67" s="111" t="n">
-        <v>20000</v>
+      <c r="F67" s="111">
+        <f>'Bao gia'!K9</f>
+        <v/>
       </c>
       <c r="G67" s="111">
         <f>IF(M67=0,"",N67/M67)</f>
@@ -5249,8 +5334,9 @@
         <f>'Bao gia'!J10</f>
         <v/>
       </c>
-      <c r="F68" s="111" t="n">
-        <v>25000</v>
+      <c r="F68" s="111">
+        <f>'Bao gia'!K10</f>
+        <v/>
       </c>
       <c r="G68" s="111">
         <f>IF(M68=0,"",N68/M68)</f>
@@ -5309,8 +5395,9 @@
         <f>'Bao gia'!J11</f>
         <v/>
       </c>
-      <c r="F69" s="111" t="n">
-        <v>25000</v>
+      <c r="F69" s="111">
+        <f>'Bao gia'!K11</f>
+        <v/>
       </c>
       <c r="G69" s="111">
         <f>IF(M69=0,"",N69/M69)</f>
@@ -5369,8 +5456,9 @@
         <f>'Bao gia'!J12</f>
         <v/>
       </c>
-      <c r="F70" s="111" t="n">
-        <v>25000</v>
+      <c r="F70" s="111">
+        <f>'Bao gia'!K12</f>
+        <v/>
       </c>
       <c r="G70" s="111">
         <f>IF(M70=0,"",N70/M70)</f>
@@ -5429,8 +5517,9 @@
         <f>'Bao gia'!J13</f>
         <v/>
       </c>
-      <c r="F71" s="111" t="n">
-        <v>50000</v>
+      <c r="F71" s="111">
+        <f>'Bao gia'!K13</f>
+        <v/>
       </c>
       <c r="G71" s="111">
         <f>IF(M71=0,"",N71/M71)</f>
@@ -5489,8 +5578,9 @@
         <f>'Bao gia'!J14</f>
         <v/>
       </c>
-      <c r="F72" s="111" t="n">
-        <v>25000</v>
+      <c r="F72" s="111">
+        <f>'Bao gia'!K14</f>
+        <v/>
       </c>
       <c r="G72" s="111">
         <f>IF(M72=0,"",N72/M72)</f>
@@ -5549,8 +5639,9 @@
         <f>'Bao gia'!J15</f>
         <v/>
       </c>
-      <c r="F73" s="111" t="n">
-        <v>50000</v>
+      <c r="F73" s="111">
+        <f>'Bao gia'!K15</f>
+        <v/>
       </c>
       <c r="G73" s="111">
         <f>IF(M73=0,"",N73/M73)</f>
@@ -5609,8 +5700,9 @@
         <f>'Bao gia'!J16</f>
         <v/>
       </c>
-      <c r="F74" s="111" t="n">
-        <v>50000</v>
+      <c r="F74" s="111">
+        <f>'Bao gia'!K16</f>
+        <v/>
       </c>
       <c r="G74" s="111">
         <f>IF(M74=0,"",N74/M74)</f>
@@ -5669,8 +5761,9 @@
         <f>'Bao gia'!J17</f>
         <v/>
       </c>
-      <c r="F75" s="111" t="n">
-        <v>50000</v>
+      <c r="F75" s="111">
+        <f>'Bao gia'!K17</f>
+        <v/>
       </c>
       <c r="G75" s="111">
         <f>IF(M75=0,"",N75/M75)</f>
@@ -5729,8 +5822,9 @@
         <f>'Bao gia'!J18</f>
         <v/>
       </c>
-      <c r="F76" s="111" t="n">
-        <v>50000</v>
+      <c r="F76" s="111">
+        <f>'Bao gia'!K18</f>
+        <v/>
       </c>
       <c r="G76" s="111">
         <f>IF(M76=0,"",N76/M76)</f>
@@ -5789,8 +5883,9 @@
         <f>'Bao gia'!J19</f>
         <v/>
       </c>
-      <c r="F77" s="111" t="n">
-        <v>11538</v>
+      <c r="F77" s="111">
+        <f>'Bao gia'!K19</f>
+        <v/>
       </c>
       <c r="G77" s="111">
         <f>IF(M77=0,"",N77/M77)</f>
@@ -5849,8 +5944,9 @@
         <f>'Bao gia'!J20</f>
         <v/>
       </c>
-      <c r="F78" s="111" t="n">
-        <v>100000</v>
+      <c r="F78" s="111">
+        <f>'Bao gia'!K20</f>
+        <v/>
       </c>
       <c r="G78" s="111">
         <f>IF(M78=0,"",N78/M78)</f>
@@ -5909,8 +6005,9 @@
         <f>'Bao gia'!J21</f>
         <v/>
       </c>
-      <c r="F79" s="111" t="n">
-        <v>150000</v>
+      <c r="F79" s="111">
+        <f>'Bao gia'!K21</f>
+        <v/>
       </c>
       <c r="G79" s="111">
         <f>IF(M79=0,"",N79/M79)</f>
@@ -5969,8 +6066,9 @@
         <f>'Bao gia'!J22</f>
         <v/>
       </c>
-      <c r="F80" s="111" t="n">
-        <v>400000</v>
+      <c r="F80" s="111">
+        <f>'Bao gia'!K22</f>
+        <v/>
       </c>
       <c r="G80" s="111">
         <f>IF(M80=0,"",N80/M80)</f>
@@ -6029,8 +6127,9 @@
         <f>'Bao gia'!J23</f>
         <v/>
       </c>
-      <c r="F81" s="111" t="n">
-        <v>58022</v>
+      <c r="F81" s="111">
+        <f>'Bao gia'!K23</f>
+        <v/>
       </c>
       <c r="G81" s="111">
         <f>IF(M81=0,"",N81/M81)</f>
@@ -6093,8 +6192,9 @@
         <f>'Bao gia'!J24</f>
         <v/>
       </c>
-      <c r="F82" s="111" t="n">
-        <v>9670</v>
+      <c r="F82" s="111">
+        <f>'Bao gia'!K24</f>
+        <v/>
       </c>
       <c r="G82" s="111">
         <f>IF(M82=0,"",N82/M82)</f>
@@ -6157,8 +6257,9 @@
         <f>'Bao gia'!J25</f>
         <v/>
       </c>
-      <c r="F83" s="111" t="n">
-        <v>100000</v>
+      <c r="F83" s="111">
+        <f>'Bao gia'!K25</f>
+        <v/>
       </c>
       <c r="G83" s="111">
         <f>IF(M83=0,"",N83/M83)</f>
@@ -6217,8 +6318,9 @@
         <f>'Bao gia'!J26</f>
         <v/>
       </c>
-      <c r="F84" s="111" t="n">
-        <v>50000</v>
+      <c r="F84" s="111">
+        <f>'Bao gia'!K26</f>
+        <v/>
       </c>
       <c r="G84" s="111">
         <f>IF(M84=0,"",N84/M84)</f>
@@ -6281,8 +6383,9 @@
         <f>'Bao gia'!J27</f>
         <v/>
       </c>
-      <c r="F85" s="111" t="n">
-        <v>31538</v>
+      <c r="F85" s="111">
+        <f>'Bao gia'!K27</f>
+        <v/>
       </c>
       <c r="G85" s="111">
         <f>IF(M85=0,"",N85/M85)</f>
@@ -6345,8 +6448,9 @@
         <f>'Bao gia'!J28</f>
         <v/>
       </c>
-      <c r="F86" s="111" t="n">
-        <v>10769</v>
+      <c r="F86" s="111">
+        <f>'Bao gia'!K28</f>
+        <v/>
       </c>
       <c r="G86" s="111">
         <f>IF(M86=0,"",N86/M86)</f>
@@ -6409,8 +6513,9 @@
         <f>'Bao gia'!J29</f>
         <v/>
       </c>
-      <c r="F87" s="111" t="n">
-        <v>100000</v>
+      <c r="F87" s="111">
+        <f>'Bao gia'!K29</f>
+        <v/>
       </c>
       <c r="G87" s="111">
         <f>IF(M87=0,"",N87/M87)</f>
@@ -6469,8 +6574,9 @@
         <f>'Bao gia'!J30</f>
         <v/>
       </c>
-      <c r="F88" s="111" t="n">
-        <v>100000</v>
+      <c r="F88" s="111">
+        <f>'Bao gia'!K30</f>
+        <v/>
       </c>
       <c r="G88" s="111">
         <f>IF(M88=0,"",N88/M88)</f>
@@ -6530,7 +6636,10 @@
         <f>'Bao gia'!J31</f>
         <v/>
       </c>
-      <c r="F89" s="111" t="n"/>
+      <c r="F89" s="111">
+        <f>'Bao gia'!K31</f>
+        <v/>
+      </c>
       <c r="G89" s="111">
         <f>IF(M89=0,"",N89/M89)</f>
         <v/>
@@ -6592,8 +6701,9 @@
         <f>'Bao gia'!J32</f>
         <v/>
       </c>
-      <c r="F90" s="111" t="n">
-        <v>50000</v>
+      <c r="F90" s="111">
+        <f>'Bao gia'!K32</f>
+        <v/>
       </c>
       <c r="G90" s="111">
         <f>IF(M90=0,"",N90/M90)</f>
@@ -6656,8 +6766,9 @@
         <f>'Bao gia'!J33</f>
         <v/>
       </c>
-      <c r="F91" s="111" t="n">
-        <v>500000</v>
+      <c r="F91" s="111">
+        <f>'Bao gia'!K33</f>
+        <v/>
       </c>
       <c r="G91" s="111">
         <f>IF(M91=0,"",N91/M91)</f>

--- a/Báo giá 2.xlsx
+++ b/Báo giá 2.xlsx
@@ -299,7 +299,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -492,9 +492,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1100,7 +1097,7 @@
       </c>
       <c r="R3" s="83" t="inlineStr">
         <is>
-          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+          <t>Đơn giá nhân công đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="S3" s="82" t="n"/>
@@ -1190,7 +1187,7 @@
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="R5" s="88">
+      <c r="R5" s="87">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
@@ -1254,7 +1251,7 @@
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="R6" s="88">
+      <c r="R6" s="87">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
@@ -1318,7 +1315,7 @@
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="R7" s="88">
+      <c r="R7" s="87">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
@@ -1388,7 +1385,7 @@
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="87">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
@@ -1587,7 +1584,7 @@
       </c>
       <c r="M3" s="83" t="inlineStr">
         <is>
-          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+          <t>Đơn giá nhân công đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="N3" s="82" t="n"/>
@@ -1628,17 +1625,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J4" s="89" t="n">
+      <c r="J4" s="88" t="n">
         <v>8600000</v>
       </c>
-      <c r="K4" s="89" t="n">
+      <c r="K4" s="88" t="n">
         <v>1500000</v>
       </c>
       <c r="L4" s="87">
         <f>'Danh gia LN'!H62</f>
         <v/>
       </c>
-      <c r="M4" s="88">
+      <c r="M4" s="87">
         <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
@@ -1680,17 +1677,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J5" s="89" t="n">
+      <c r="J5" s="88" t="n">
         <v>252000</v>
       </c>
-      <c r="K5" s="89" t="n">
+      <c r="K5" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L5" s="87">
         <f>'Danh gia LN'!H63</f>
         <v/>
       </c>
-      <c r="M5" s="88">
+      <c r="M5" s="87">
         <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
@@ -1733,17 +1730,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J6" s="89" t="n">
+      <c r="J6" s="88" t="n">
         <v>205000</v>
       </c>
-      <c r="K6" s="89" t="n">
+      <c r="K6" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L6" s="87">
         <f>'Danh gia LN'!H64</f>
         <v/>
       </c>
-      <c r="M6" s="88">
+      <c r="M6" s="87">
         <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
@@ -1786,17 +1783,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J7" s="89" t="n">
+      <c r="J7" s="88" t="n">
         <v>242000</v>
       </c>
-      <c r="K7" s="89" t="n">
+      <c r="K7" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L7" s="87">
         <f>'Danh gia LN'!H65</f>
         <v/>
       </c>
-      <c r="M7" s="88">
+      <c r="M7" s="87">
         <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
@@ -1839,17 +1836,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J8" s="89" t="n">
+      <c r="J8" s="88" t="n">
         <v>116000</v>
       </c>
-      <c r="K8" s="89" t="n">
+      <c r="K8" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L8" s="87">
         <f>'Danh gia LN'!H66</f>
         <v/>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="87">
         <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
@@ -1892,17 +1889,17 @@
           <t>ấn độ</t>
         </is>
       </c>
-      <c r="J9" s="89" t="n">
+      <c r="J9" s="88" t="n">
         <v>252000</v>
       </c>
-      <c r="K9" s="89" t="n">
+      <c r="K9" s="88" t="n">
         <v>20000</v>
       </c>
       <c r="L9" s="87">
         <f>'Danh gia LN'!H67</f>
         <v/>
       </c>
-      <c r="M9" s="88">
+      <c r="M9" s="87">
         <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
@@ -1945,17 +1942,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J10" s="89" t="n">
+      <c r="J10" s="88" t="n">
         <v>53000</v>
       </c>
-      <c r="K10" s="89" t="n">
+      <c r="K10" s="88" t="n">
         <v>25000</v>
       </c>
       <c r="L10" s="87">
         <f>'Danh gia LN'!H68</f>
         <v/>
       </c>
-      <c r="M10" s="88">
+      <c r="M10" s="87">
         <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
@@ -1998,17 +1995,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J11" s="89" t="n">
+      <c r="J11" s="88" t="n">
         <v>42000</v>
       </c>
-      <c r="K11" s="89" t="n">
+      <c r="K11" s="88" t="n">
         <v>25000</v>
       </c>
       <c r="L11" s="87">
         <f>'Danh gia LN'!H69</f>
         <v/>
       </c>
-      <c r="M11" s="88">
+      <c r="M11" s="87">
         <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
@@ -2051,17 +2048,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J12" s="89" t="n">
+      <c r="J12" s="88" t="n">
         <v>95000</v>
       </c>
-      <c r="K12" s="89" t="n">
+      <c r="K12" s="88" t="n">
         <v>25000</v>
       </c>
       <c r="L12" s="87">
         <f>'Danh gia LN'!H70</f>
         <v/>
       </c>
-      <c r="M12" s="88">
+      <c r="M12" s="87">
         <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
@@ -2104,17 +2101,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J13" s="89" t="n">
+      <c r="J13" s="88" t="n">
         <v>190000</v>
       </c>
-      <c r="K13" s="89" t="n">
+      <c r="K13" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L13" s="87">
         <f>'Danh gia LN'!H71</f>
         <v/>
       </c>
-      <c r="M13" s="88">
+      <c r="M13" s="87">
         <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
@@ -2157,17 +2154,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J14" s="89" t="n">
+      <c r="J14" s="88" t="n">
         <v>75000</v>
       </c>
-      <c r="K14" s="89" t="n">
+      <c r="K14" s="88" t="n">
         <v>25000</v>
       </c>
       <c r="L14" s="87">
         <f>'Danh gia LN'!H72</f>
         <v/>
       </c>
-      <c r="M14" s="88">
+      <c r="M14" s="87">
         <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
@@ -2210,17 +2207,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J15" s="89" t="n">
+      <c r="J15" s="88" t="n">
         <v>245000</v>
       </c>
-      <c r="K15" s="89" t="n">
+      <c r="K15" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L15" s="87">
         <f>'Danh gia LN'!H73</f>
         <v/>
       </c>
-      <c r="M15" s="88">
+      <c r="M15" s="87">
         <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
@@ -2263,17 +2260,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J16" s="89" t="n">
+      <c r="J16" s="88" t="n">
         <v>190000</v>
       </c>
-      <c r="K16" s="89" t="n">
+      <c r="K16" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L16" s="87">
         <f>'Danh gia LN'!H74</f>
         <v/>
       </c>
-      <c r="M16" s="88">
+      <c r="M16" s="87">
         <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
@@ -2316,17 +2313,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J17" s="89" t="n">
+      <c r="J17" s="88" t="n">
         <v>231000</v>
       </c>
-      <c r="K17" s="89" t="n">
+      <c r="K17" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L17" s="87">
         <f>'Danh gia LN'!H75</f>
         <v/>
       </c>
-      <c r="M17" s="88">
+      <c r="M17" s="87">
         <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
@@ -2369,17 +2366,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J18" s="89" t="n">
+      <c r="J18" s="88" t="n">
         <v>95000</v>
       </c>
-      <c r="K18" s="89" t="n">
+      <c r="K18" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L18" s="87">
         <f>'Danh gia LN'!H76</f>
         <v/>
       </c>
-      <c r="M18" s="88">
+      <c r="M18" s="87">
         <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
@@ -2422,17 +2419,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J19" s="89" t="n">
+      <c r="J19" s="88" t="n">
         <v>17000</v>
       </c>
-      <c r="K19" s="89" t="n">
+      <c r="K19" s="88" t="n">
         <v>11538</v>
       </c>
       <c r="L19" s="87">
         <f>'Danh gia LN'!H77</f>
         <v/>
       </c>
-      <c r="M19" s="88">
+      <c r="M19" s="87">
         <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
@@ -2474,17 +2471,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J20" s="89" t="n">
+      <c r="J20" s="88" t="n">
         <v>200000</v>
       </c>
-      <c r="K20" s="89" t="n">
+      <c r="K20" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L20" s="87">
         <f>'Danh gia LN'!H78</f>
         <v/>
       </c>
-      <c r="M20" s="88">
+      <c r="M20" s="87">
         <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
@@ -2525,17 +2522,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J21" s="89" t="n">
+      <c r="J21" s="88" t="n">
         <v>2205000</v>
       </c>
-      <c r="K21" s="89" t="n">
+      <c r="K21" s="88" t="n">
         <v>150000</v>
       </c>
       <c r="L21" s="87">
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="M21" s="88">
+      <c r="M21" s="87">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
@@ -2578,17 +2575,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J22" s="89" t="n">
+      <c r="J22" s="88" t="n">
         <v>368000</v>
       </c>
-      <c r="K22" s="89" t="n">
+      <c r="K22" s="88" t="n">
         <v>400000</v>
       </c>
       <c r="L22" s="87">
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="M22" s="88">
+      <c r="M22" s="87">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
@@ -2631,17 +2628,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J23" s="89" t="n">
+      <c r="J23" s="88" t="n">
         <v>514286</v>
       </c>
-      <c r="K23" s="89" t="n">
+      <c r="K23" s="88" t="n">
         <v>58022</v>
       </c>
       <c r="L23" s="87">
         <f>'Danh gia LN'!H81</f>
         <v/>
       </c>
-      <c r="M23" s="88">
+      <c r="M23" s="87">
         <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
@@ -2684,17 +2681,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J24" s="89" t="n">
+      <c r="J24" s="88" t="n">
         <v>85714</v>
       </c>
-      <c r="K24" s="89" t="n">
+      <c r="K24" s="88" t="n">
         <v>9670</v>
       </c>
       <c r="L24" s="87">
         <f>'Danh gia LN'!H82</f>
         <v/>
       </c>
-      <c r="M24" s="88">
+      <c r="M24" s="87">
         <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
@@ -2737,17 +2734,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J25" s="89" t="n">
+      <c r="J25" s="88" t="n">
         <v>166000</v>
       </c>
-      <c r="K25" s="89" t="n">
+      <c r="K25" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L25" s="87">
         <f>'Danh gia LN'!H83</f>
         <v/>
       </c>
-      <c r="M25" s="88">
+      <c r="M25" s="87">
         <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
@@ -2791,17 +2788,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J26" s="89" t="n">
+      <c r="J26" s="88" t="n">
         <v>53000</v>
       </c>
-      <c r="K26" s="89" t="n">
+      <c r="K26" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L26" s="87">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="M26" s="88">
+      <c r="M26" s="87">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
@@ -2845,17 +2842,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J27" s="89" t="n">
+      <c r="J27" s="88" t="n">
         <v>137000</v>
       </c>
-      <c r="K27" s="89" t="n">
+      <c r="K27" s="88" t="n">
         <v>31538</v>
       </c>
       <c r="L27" s="87">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="M27" s="88">
+      <c r="M27" s="87">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
@@ -2899,17 +2896,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J28" s="89" t="n">
+      <c r="J28" s="88" t="n">
         <v>652000</v>
       </c>
-      <c r="K28" s="89" t="n">
+      <c r="K28" s="88" t="n">
         <v>10769</v>
       </c>
       <c r="L28" s="87">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="M28" s="88">
+      <c r="M28" s="87">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
@@ -2952,17 +2949,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J29" s="89" t="n">
+      <c r="J29" s="88" t="n">
         <v>158000</v>
       </c>
-      <c r="K29" s="89" t="n">
+      <c r="K29" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L29" s="87">
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="M29" s="88">
+      <c r="M29" s="87">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
@@ -3005,17 +3002,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J30" s="89" t="n">
+      <c r="J30" s="88" t="n">
         <v>190000</v>
       </c>
-      <c r="K30" s="89" t="n">
+      <c r="K30" s="88" t="n">
         <v>100000</v>
       </c>
       <c r="L30" s="87">
         <f>'Danh gia LN'!H88</f>
         <v/>
       </c>
-      <c r="M30" s="88">
+      <c r="M30" s="87">
         <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
@@ -3054,13 +3051,13 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J31" s="89" t="n"/>
-      <c r="K31" s="89" t="n"/>
+      <c r="J31" s="88" t="n"/>
+      <c r="K31" s="88" t="n"/>
       <c r="L31" s="87">
         <f>'Danh gia LN'!H89</f>
         <v/>
       </c>
-      <c r="M31" s="88">
+      <c r="M31" s="87">
         <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
@@ -3104,17 +3101,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J32" s="89" t="n">
+      <c r="J32" s="88" t="n">
         <v>442000</v>
       </c>
-      <c r="K32" s="89" t="n">
+      <c r="K32" s="88" t="n">
         <v>50000</v>
       </c>
       <c r="L32" s="87">
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="M32" s="88">
+      <c r="M32" s="87">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
@@ -3157,17 +3154,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J33" s="89" t="n">
+      <c r="J33" s="88" t="n">
         <v>1260000</v>
       </c>
-      <c r="K33" s="89" t="n">
+      <c r="K33" s="88" t="n">
         <v>500000</v>
       </c>
       <c r="L33" s="87">
         <f>'Danh gia LN'!H91</f>
         <v/>
       </c>
-      <c r="M33" s="88">
+      <c r="M33" s="87">
         <f>'Danh gia LN'!I91</f>
         <v/>
       </c>
@@ -3257,6 +3254,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
     <col width="44" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -3266,4022 +3264,4161 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>ĐÁNH GIÁ GIÁ CHỐT PHẦN PCCC – HỆ THỐNG PCCC CÁC TRƯỜNG TIỂU HỌC, THCS PHƯỜNG ĐỒNG SƠN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>Chỉ điều chỉnh đơn giá vật tư/thiết bị có trong báo giá; nhân công theo định mức, các hạng mục khác giữ đơn giá dự toán. QLDA, tư vấn, nhà tạm, dự phòng tính lại theo công thức của bảng tổng dự toán. Giá vốn theo sheet 'Gia von chi tiet'.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="R3" s="92" t="inlineStr">
+      <c r="R3" s="91" t="inlineStr">
         <is>
           <t>VÙNG TÍNH HỆ SỐ TỰ ĐỘNG (không cần sửa)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="93" t="inlineStr">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>Lợi nhuận tối thiểu của bên thi công trên giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C4" s="94" t="n"/>
-      <c r="D4" s="95" t="n"/>
-      <c r="E4" s="96" t="n">
+      <c r="C4" s="93" t="n"/>
+      <c r="D4" s="94" t="n"/>
+      <c r="E4" s="95" t="n">
         <v>0.25</v>
       </c>
-      <c r="R4" s="92" t="inlineStr">
+      <c r="R4" s="91" t="inlineStr">
         <is>
           <t>Σ SL quy đổi × giá vốn VT – lắp đặt</t>
         </is>
       </c>
-      <c r="S4" s="97">
+      <c r="S4" s="96">
         <f>SUMPRODUCT((L62:L91="Lắp đặt")*M62:M91*N(+E62:E91))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="92" t="inlineStr">
         <is>
           <t>Tỷ lệ trích lại chủ đầu tư (trên tổng dự toán gói sau VAT, đã làm tròn)</t>
         </is>
       </c>
-      <c r="C5" s="94" t="n"/>
-      <c r="D5" s="95" t="n"/>
-      <c r="E5" s="96" t="n">
+      <c r="C5" s="93" t="n"/>
+      <c r="D5" s="94" t="n"/>
+      <c r="E5" s="95" t="n">
         <v>0.15</v>
       </c>
-      <c r="R5" s="92" t="inlineStr">
+      <c r="R5" s="91" t="inlineStr">
         <is>
           <t>Σ SL × giá vốn – thiết bị</t>
         </is>
       </c>
-      <c r="S5" s="97">
+      <c r="S5" s="96">
         <f>SUMPRODUCT((L62:L91="Thiết bị")*D62:D91*N(+E62:E91))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="93" t="inlineStr">
-        <is>
-          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (tự tính – hệ số nhỏ nhất đạt lợi nhuận ô E4)</t>
-        </is>
-      </c>
-      <c r="C6" s="94" t="n"/>
-      <c r="D6" s="95" t="n"/>
-      <c r="E6" s="98">
+      <c r="B6" s="92" t="inlineStr">
+        <is>
+          <t>Hệ số: giá đề xuất (vật tư và nhân công) = giá vốn × hệ số (tự tính – nhỏ nhất đạt lợi nhuận ô E4)</t>
+        </is>
+      </c>
+      <c r="C6" s="93" t="n"/>
+      <c r="D6" s="94" t="n"/>
+      <c r="E6" s="97">
         <f>ROUNDUP(MAX(1,$W$27),3)</f>
         <v/>
       </c>
-      <c r="F6" s="99" t="inlineStr">
+      <c r="F6" s="98" t="inlineStr">
         <is>
           <t>← tự tính lại khi sửa giá vốn ở sheet Bao gia hoặc sửa ô E4, E5 (vùng tính phụ ở cột R–W)</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="R6" s="91" t="inlineStr">
         <is>
           <t>VL dự toán hiện tại – lắp đặt</t>
         </is>
       </c>
-      <c r="S6" s="97">
+      <c r="S6" s="96">
         <f>SUMIF(L62:L91,"Lắp đặt",N62:N91)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>Hệ số chi phí trực tiếp → chi phí xây dựng trước thuế: (1 + 7,3% + 2,5%) × (1 + 5,5%)</t>
         </is>
       </c>
-      <c r="C7" s="94" t="n"/>
-      <c r="D7" s="95" t="n"/>
-      <c r="E7" s="100">
+      <c r="C7" s="93" t="n"/>
+      <c r="D7" s="94" t="n"/>
+      <c r="E7" s="99">
         <f>(1+7.3%+2.5%)*(1+5.5%)</f>
         <v/>
       </c>
-      <c r="R7" s="92" t="inlineStr">
+      <c r="R7" s="91" t="inlineStr">
         <is>
           <t>Giá vốn PCCC (C)</t>
         </is>
       </c>
-      <c r="S7" s="97">
+      <c r="S7" s="96">
         <f>J92+G111</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="93" t="inlineStr">
+      <c r="B8" s="92" t="inlineStr">
         <is>
           <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – tự tính</t>
         </is>
       </c>
-      <c r="C8" s="94" t="n"/>
-      <c r="D8" s="95" t="n"/>
-      <c r="E8" s="101">
+      <c r="C8" s="93" t="n"/>
+      <c r="D8" s="94" t="n"/>
+      <c r="E8" s="100">
         <f>ROUND(1.05*(H20+H21+H22+H28+500000)/(1-1.05*0.57%),-6)</f>
         <v/>
       </c>
-      <c r="F8" s="102">
+      <c r="F8" s="101">
         <f>IF($E$8=H34,"Khớp tổng làm tròn","⚠ Lệch do làm tròn: tổng = "&amp;TEXT(H34,"#,##0"))</f>
         <v/>
       </c>
-      <c r="R8" s="92" t="inlineStr">
+      <c r="R8" s="91" t="inlineStr">
         <is>
           <t>Gxdct1 hiện tại</t>
         </is>
       </c>
-      <c r="S8" s="97" t="n">
+      <c r="S8" s="96" t="n">
         <v>1215750394</v>
       </c>
     </row>
     <row r="9">
-      <c r="R9" s="92" t="inlineStr">
+      <c r="R9" s="91" t="inlineStr">
         <is>
           <t>Xây lắp các trường (giữ nguyên)</t>
         </is>
       </c>
-      <c r="S9" s="97" t="n">
+      <c r="S9" s="96" t="n">
         <v>378842471</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="103" t="inlineStr">
+      <c r="A10" s="102" t="inlineStr">
         <is>
           <t>A. TỔNG DỰ TOÁN GÓI – HIỆN TẠI VÀ SAU KHI CHỐT GIÁ PCCC</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="R10" s="91" t="inlineStr">
         <is>
           <t>Đệm an toàn cho sai số làm tròn (đ)</t>
         </is>
       </c>
-      <c r="S10" s="97" t="n">
+      <c r="S10" s="96" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="104" t="inlineStr">
+      <c r="B11" s="103" t="inlineStr">
         <is>
           <t>Khoản mục chi phí</t>
         </is>
       </c>
-      <c r="C11" s="104" t="inlineStr">
+      <c r="C11" s="103" t="inlineStr">
         <is>
           <t>Ký hiệu</t>
         </is>
       </c>
-      <c r="D11" s="104" t="inlineStr">
+      <c r="D11" s="103" t="inlineStr">
         <is>
           <t>Cách tính</t>
         </is>
       </c>
-      <c r="E11" s="104" t="inlineStr">
+      <c r="E11" s="103" t="inlineStr">
         <is>
           <t>Hiện tại (sau thuế)</t>
         </is>
       </c>
-      <c r="F11" s="104" t="inlineStr">
+      <c r="F11" s="103" t="inlineStr">
         <is>
           <t>Mới – trước thuế</t>
         </is>
       </c>
-      <c r="G11" s="104" t="inlineStr">
+      <c r="G11" s="103" t="inlineStr">
         <is>
           <t>Thuế VAT 8%</t>
         </is>
       </c>
-      <c r="H11" s="104" t="inlineStr">
+      <c r="H11" s="103" t="inlineStr">
         <is>
           <t>MỚI – SAU THUẾ</t>
         </is>
       </c>
-      <c r="I11" s="104" t="inlineStr">
+      <c r="I11" s="103" t="inlineStr">
         <is>
           <t>Chênh (sau thuế)</t>
         </is>
       </c>
+      <c r="R11" s="91" t="inlineStr">
+        <is>
+          <t>Σ KL × giá vốn NC (S11) | Σ KL × NC dự toán hiện tại (T11)</t>
+        </is>
+      </c>
+      <c r="S11" s="96">
+        <f>SUMPRODUCT(N(+D62:D91),N(+F62:F91))</f>
+        <v/>
+      </c>
+      <c r="T11" s="96">
+        <f>SUMPRODUCT(N(+D62:D91),N(+Q62:Q91))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="105" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>Chi phí xây dựng phần PCCC (lắp đặt)</t>
         </is>
       </c>
-      <c r="C12" s="106" t="inlineStr">
+      <c r="C12" s="105" t="inlineStr">
         <is>
           <t>Gxdct1</t>
         </is>
       </c>
-      <c r="D12" s="105" t="inlineStr">
-        <is>
-          <t>Dự toán hiện tại + hệ số × chênh VT</t>
-        </is>
-      </c>
-      <c r="E12" s="107" t="n">
+      <c r="D12" s="104" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại + hệ số × chênh VT, NC</t>
+        </is>
+      </c>
+      <c r="E12" s="106" t="n">
         <v>1313010000</v>
       </c>
-      <c r="F12" s="107">
+      <c r="F12" s="106">
         <f>1215750394+SUM(O62:O91)</f>
         <v/>
       </c>
-      <c r="G12" s="107">
+      <c r="G12" s="106">
         <f>F12*8%</f>
         <v/>
       </c>
-      <c r="H12" s="108">
+      <c r="H12" s="107">
         <f>ROUND(F12+G12,-3)</f>
         <v/>
       </c>
-      <c r="I12" s="107">
+      <c r="I12" s="106">
         <f>IF(E12="","",H12-E12)</f>
         <v/>
       </c>
-      <c r="R12" s="92" t="inlineStr">
+      <c r="R12" s="91" t="inlineStr">
         <is>
           <t>Điểm thử</t>
         </is>
       </c>
-      <c r="S12" s="92" t="inlineStr">
+      <c r="S12" s="91" t="inlineStr">
         <is>
           <t>m = 1</t>
         </is>
       </c>
-      <c r="T12" s="92" t="inlineStr">
+      <c r="T12" s="91" t="inlineStr">
         <is>
           <t>m = 3</t>
         </is>
       </c>
-      <c r="U12" s="92" t="inlineStr">
+      <c r="U12" s="91" t="inlineStr">
         <is>
           <t>m₃ (dây cung 1)</t>
         </is>
       </c>
-      <c r="V12" s="92" t="inlineStr">
+      <c r="V12" s="91" t="inlineStr">
         <is>
           <t>m₃ + 0,01</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="108" t="inlineStr">
         <is>
           <t>Xây lắp Trường tiểu học Nghĩa Ninh</t>
         </is>
       </c>
-      <c r="C13" s="110" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
         <is>
           <t>Gxdct2</t>
         </is>
       </c>
-      <c r="D13" s="109" t="inlineStr">
+      <c r="D13" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E13" s="111" t="n">
+      <c r="E13" s="110" t="n">
         <v>109257000</v>
       </c>
-      <c r="F13" s="111" t="n">
+      <c r="F13" s="110" t="n">
         <v>101163519</v>
       </c>
-      <c r="G13" s="111">
+      <c r="G13" s="110">
         <f>F13*8%</f>
         <v/>
       </c>
-      <c r="H13" s="112">
+      <c r="H13" s="111">
         <f>ROUND(F13+G13,-3)</f>
         <v/>
       </c>
-      <c r="I13" s="111">
+      <c r="I13" s="110">
         <f>IF(E13="","",H13-E13)</f>
         <v/>
       </c>
-      <c r="R13" s="92" t="inlineStr">
+      <c r="R13" s="91" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S13" s="113" t="n">
+      <c r="S13" s="112" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="113" t="n">
+      <c r="T13" s="112" t="n">
         <v>3</v>
       </c>
-      <c r="U13" s="113">
+      <c r="U13" s="112">
         <f>T13-T23*(T13-S13)/(T23-S23)</f>
         <v/>
       </c>
-      <c r="V13" s="113">
+      <c r="V13" s="112">
         <f>U13+0.01</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="109" t="inlineStr">
+      <c r="B14" s="108" t="inlineStr">
         <is>
           <t>Xây lắp Trường tiểu học số 1 Đồng Sơn</t>
         </is>
       </c>
-      <c r="C14" s="110" t="inlineStr">
+      <c r="C14" s="109" t="inlineStr">
         <is>
           <t>Gxdct3</t>
         </is>
       </c>
-      <c r="D14" s="109" t="inlineStr">
+      <c r="D14" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E14" s="111" t="n">
+      <c r="E14" s="110" t="n">
         <v>42923000</v>
       </c>
-      <c r="F14" s="111" t="n">
+      <c r="F14" s="110" t="n">
         <v>39743608</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G14" s="110">
         <f>F14*8%</f>
         <v/>
       </c>
-      <c r="H14" s="112">
+      <c r="H14" s="111">
         <f>ROUND(F14+G14,-3)</f>
         <v/>
       </c>
-      <c r="I14" s="111">
+      <c r="I14" s="110">
         <f>IF(E14="","",H14-E14)</f>
         <v/>
       </c>
-      <c r="R14" s="92" t="inlineStr">
+      <c r="R14" s="91" t="inlineStr">
         <is>
           <t>Gxdct1</t>
         </is>
       </c>
-      <c r="S14" s="97">
-        <f>$S$8+$E$7*(S13*$S$4-$S$6)</f>
-        <v/>
-      </c>
-      <c r="T14" s="97">
-        <f>$S$8+$E$7*(T13*$S$4-$S$6)</f>
-        <v/>
-      </c>
-      <c r="U14" s="97">
-        <f>$S$8+$E$7*(U13*$S$4-$S$6)</f>
-        <v/>
-      </c>
-      <c r="V14" s="97">
-        <f>$S$8+$E$7*(V13*$S$4-$S$6)</f>
+      <c r="S14" s="96">
+        <f>$S$8+$E$7*(S13*$S$4-$S$6)+$E$7*(S13*$S$11-$T$11)</f>
+        <v/>
+      </c>
+      <c r="T14" s="96">
+        <f>$S$8+$E$7*(T13*$S$4-$S$6)+$E$7*(T13*$S$11-$T$11)</f>
+        <v/>
+      </c>
+      <c r="U14" s="96">
+        <f>$S$8+$E$7*(U13*$S$4-$S$6)+$E$7*(U13*$S$11-$T$11)</f>
+        <v/>
+      </c>
+      <c r="V14" s="96">
+        <f>$S$8+$E$7*(V13*$S$4-$S$6)+$E$7*(V13*$S$11-$T$11)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="108" t="inlineStr">
         <is>
           <t>Xây lắp Trường tiểu học số 2 Đồng Sơn</t>
         </is>
       </c>
-      <c r="C15" s="110" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
         <is>
           <t>Gxdct4</t>
         </is>
       </c>
-      <c r="D15" s="109" t="inlineStr">
+      <c r="D15" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E15" s="111" t="n">
+      <c r="E15" s="110" t="n">
         <v>86464000</v>
       </c>
-      <c r="F15" s="111" t="n">
+      <c r="F15" s="110" t="n">
         <v>80058943</v>
       </c>
-      <c r="G15" s="111">
+      <c r="G15" s="110">
         <f>F15*8%</f>
         <v/>
       </c>
-      <c r="H15" s="112">
+      <c r="H15" s="111">
         <f>ROUND(F15+G15,-3)</f>
         <v/>
       </c>
-      <c r="I15" s="111">
+      <c r="I15" s="110">
         <f>IF(E15="","",H15-E15)</f>
         <v/>
       </c>
-      <c r="R15" s="92" t="inlineStr">
+      <c r="R15" s="91" t="inlineStr">
         <is>
           <t>Gxdct</t>
         </is>
       </c>
-      <c r="S15" s="97">
+      <c r="S15" s="96">
         <f>S14+$S$9</f>
         <v/>
       </c>
-      <c r="T15" s="97">
+      <c r="T15" s="96">
         <f>T14+$S$9</f>
         <v/>
       </c>
-      <c r="U15" s="97">
+      <c r="U15" s="96">
         <f>U14+$S$9</f>
         <v/>
       </c>
-      <c r="V15" s="97">
+      <c r="V15" s="96">
         <f>V14+$S$9</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="109" t="inlineStr">
+      <c r="B16" s="108" t="inlineStr">
         <is>
           <t>Xây lắp Trường THCS số 1 Đồng Sơn</t>
         </is>
       </c>
-      <c r="C16" s="110" t="inlineStr">
+      <c r="C16" s="109" t="inlineStr">
         <is>
           <t>Gxdct5</t>
         </is>
       </c>
-      <c r="D16" s="109" t="inlineStr">
+      <c r="D16" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E16" s="111" t="n">
+      <c r="E16" s="110" t="n">
         <v>127297000</v>
       </c>
-      <c r="F16" s="111" t="n">
+      <c r="F16" s="110" t="n">
         <v>117867626</v>
       </c>
-      <c r="G16" s="111">
+      <c r="G16" s="110">
         <f>F16*8%</f>
         <v/>
       </c>
-      <c r="H16" s="112">
+      <c r="H16" s="111">
         <f>ROUND(F16+G16,-3)</f>
         <v/>
       </c>
-      <c r="I16" s="111">
+      <c r="I16" s="110">
         <f>IF(E16="","",H16-E16)</f>
         <v/>
       </c>
-      <c r="R16" s="92" t="inlineStr">
+      <c r="R16" s="91" t="inlineStr">
         <is>
           <t>GXD trước thuế</t>
         </is>
       </c>
-      <c r="S16" s="97">
+      <c r="S16" s="96">
         <f>S15*1.011</f>
         <v/>
       </c>
-      <c r="T16" s="97">
+      <c r="T16" s="96">
         <f>T15*1.011</f>
         <v/>
       </c>
-      <c r="U16" s="97">
+      <c r="U16" s="96">
         <f>U15*1.011</f>
         <v/>
       </c>
-      <c r="V16" s="97">
+      <c r="V16" s="96">
         <f>V15*1.011</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="109" t="inlineStr">
+      <c r="B17" s="108" t="inlineStr">
         <is>
           <t>Xây lắp Trường THCS Bắc Nghĩa</t>
         </is>
       </c>
-      <c r="C17" s="110" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
         <is>
           <t>Gxdct6</t>
         </is>
       </c>
-      <c r="D17" s="109" t="inlineStr">
+      <c r="D17" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E17" s="111" t="n">
+      <c r="E17" s="110" t="n">
         <v>43209000</v>
       </c>
-      <c r="F17" s="111" t="n">
+      <c r="F17" s="110" t="n">
         <v>40008775</v>
       </c>
-      <c r="G17" s="111">
+      <c r="G17" s="110">
         <f>F17*8%</f>
         <v/>
       </c>
-      <c r="H17" s="112">
+      <c r="H17" s="111">
         <f>ROUND(F17+G17,-3)</f>
         <v/>
       </c>
-      <c r="I17" s="111">
+      <c r="I17" s="110">
         <f>IF(E17="","",H17-E17)</f>
         <v/>
       </c>
-      <c r="R17" s="92" t="inlineStr">
+      <c r="R17" s="91" t="inlineStr">
         <is>
           <t>Thiết bị trước thuế</t>
         </is>
       </c>
-      <c r="S17" s="97">
+      <c r="S17" s="96">
         <f>S13*$S$5</f>
         <v/>
       </c>
-      <c r="T17" s="97">
+      <c r="T17" s="96">
         <f>T13*$S$5</f>
         <v/>
       </c>
-      <c r="U17" s="97">
+      <c r="U17" s="96">
         <f>U13*$S$5</f>
         <v/>
       </c>
-      <c r="V17" s="97">
+      <c r="V17" s="96">
         <f>V13*$S$5</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="109" t="inlineStr">
+      <c r="B18" s="108" t="inlineStr">
         <is>
           <t>Chi phí xây dựng của công trình</t>
         </is>
       </c>
-      <c r="C18" s="110" t="inlineStr">
+      <c r="C18" s="109" t="inlineStr">
         <is>
           <t>Gxdct</t>
         </is>
       </c>
-      <c r="D18" s="109" t="inlineStr">
+      <c r="D18" s="108" t="inlineStr">
         <is>
           <t>Cộng</t>
         </is>
       </c>
-      <c r="E18" s="111" t="n"/>
-      <c r="F18" s="111">
+      <c r="E18" s="110" t="n"/>
+      <c r="F18" s="110">
         <f>SUM(F12:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="111">
+      <c r="G18" s="110">
         <f>F18*8%</f>
         <v/>
       </c>
-      <c r="H18" s="112">
+      <c r="H18" s="111">
         <f>ROUND(F18+G18,-3)</f>
         <v/>
       </c>
-      <c r="I18" s="111">
+      <c r="I18" s="110">
         <f>IF(E18="","",H18-E18)</f>
         <v/>
       </c>
-      <c r="R18" s="92" t="inlineStr">
+      <c r="R18" s="91" t="inlineStr">
         <is>
           <t>QLDA</t>
         </is>
       </c>
-      <c r="S18" s="97">
+      <c r="S18" s="96">
         <f>(S16+S17)*3.446%</f>
         <v/>
       </c>
-      <c r="T18" s="97">
+      <c r="T18" s="96">
         <f>(T16+T17)*3.446%</f>
         <v/>
       </c>
-      <c r="U18" s="97">
+      <c r="U18" s="96">
         <f>(U16+U17)*3.446%</f>
         <v/>
       </c>
-      <c r="V18" s="97">
+      <c r="V18" s="96">
         <f>(V16+V17)*3.446%</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="109" t="inlineStr">
+      <c r="B19" s="108" t="inlineStr">
         <is>
           <t>Chi phí nhà tạm để ở và điều hành thi công</t>
         </is>
       </c>
-      <c r="C19" s="110" t="inlineStr">
+      <c r="C19" s="109" t="inlineStr">
         <is>
           <t>Glt</t>
         </is>
       </c>
-      <c r="D19" s="109" t="inlineStr">
+      <c r="D19" s="108" t="inlineStr">
         <is>
           <t>1,1% × Gxdct</t>
         </is>
       </c>
-      <c r="E19" s="111" t="n"/>
-      <c r="F19" s="111">
+      <c r="E19" s="110" t="n"/>
+      <c r="F19" s="110">
         <f>F18*1.1%</f>
         <v/>
       </c>
-      <c r="G19" s="111">
+      <c r="G19" s="110">
         <f>F19*8%</f>
         <v/>
       </c>
-      <c r="H19" s="112">
+      <c r="H19" s="111">
         <f>ROUND(F19+G19,-3)</f>
         <v/>
       </c>
-      <c r="I19" s="111">
+      <c r="I19" s="110">
         <f>IF(E19="","",H19-E19)</f>
         <v/>
       </c>
-      <c r="R19" s="92" t="inlineStr">
+      <c r="R19" s="91" t="inlineStr">
         <is>
           <t>Tư vấn (sau thuế)</t>
         </is>
       </c>
-      <c r="S19" s="97">
+      <c r="S19" s="96">
         <f>25000000+1.08*((S15+S17)*((3-(S16+S17)/10^9)*0.9+4.7)/100+S15*0.508%)</f>
         <v/>
       </c>
-      <c r="T19" s="97">
+      <c r="T19" s="96">
         <f>25000000+1.08*((T15+T17)*((3-(T16+T17)/10^9)*0.9+4.7)/100+T15*0.508%)</f>
         <v/>
       </c>
-      <c r="U19" s="97">
+      <c r="U19" s="96">
         <f>25000000+1.08*((U15+U17)*((3-(U16+U17)/10^9)*0.9+4.7)/100+U15*0.508%)</f>
         <v/>
       </c>
-      <c r="V19" s="97">
+      <c r="V19" s="96">
         <f>25000000+1.08*((V15+V17)*((3-(V16+V17)/10^9)*0.9+4.7)/100+V15*0.508%)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="93" t="inlineStr">
+      <c r="B20" s="92" t="inlineStr">
         <is>
           <t>I. CHI PHÍ XÂY LẮP</t>
         </is>
       </c>
-      <c r="C20" s="114" t="inlineStr">
+      <c r="C20" s="113" t="inlineStr">
         <is>
           <t>GXD</t>
         </is>
       </c>
-      <c r="D20" s="93" t="inlineStr">
+      <c r="D20" s="92" t="inlineStr">
         <is>
           <t>Gxdct + Glt</t>
         </is>
       </c>
-      <c r="E20" s="112" t="n">
+      <c r="E20" s="111" t="n">
         <v>1741104000</v>
       </c>
-      <c r="F20" s="112">
+      <c r="F20" s="111">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G20" s="112">
+      <c r="G20" s="111">
         <f>F20*8%</f>
         <v/>
       </c>
-      <c r="H20" s="112">
+      <c r="H20" s="111">
         <f>ROUND(F20+G20,-3)</f>
         <v/>
       </c>
-      <c r="I20" s="112">
+      <c r="I20" s="111">
         <f>IF(E20="","",H20-E20)</f>
         <v/>
       </c>
-      <c r="R20" s="92" t="inlineStr">
+      <c r="R20" s="91" t="inlineStr">
         <is>
           <t>Tổng gói (ước)</t>
         </is>
       </c>
-      <c r="S20" s="97">
+      <c r="S20" s="96">
         <f>1.05*(1.08*S16+1.08*S17+S18+S19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
-      <c r="T20" s="97">
+      <c r="T20" s="96">
         <f>1.05*(1.08*T16+1.08*T17+T18+T19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
-      <c r="U20" s="97">
+      <c r="U20" s="96">
         <f>1.05*(1.08*U16+1.08*U17+U18+U19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
-      <c r="V20" s="97">
+      <c r="V20" s="96">
         <f>1.05*(1.08*V16+1.08*V17+V18+V19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="92" t="inlineStr">
         <is>
           <t>II. CHI PHÍ THIẾT BỊ</t>
         </is>
       </c>
-      <c r="C21" s="114" t="inlineStr">
+      <c r="C21" s="113" t="inlineStr">
         <is>
           <t>Gtb</t>
         </is>
       </c>
-      <c r="D21" s="93" t="inlineStr">
+      <c r="D21" s="92" t="inlineStr">
         <is>
           <t>Σ thiết bị × giá chốt</t>
         </is>
       </c>
-      <c r="E21" s="112" t="n">
+      <c r="E21" s="111" t="n">
         <v>18954000</v>
       </c>
-      <c r="F21" s="112">
+      <c r="F21" s="111">
         <f>SUMIF(L62:L91,"Thiết bị",K62:K91)</f>
         <v/>
       </c>
-      <c r="G21" s="112">
+      <c r="G21" s="111">
         <f>F21*8%</f>
         <v/>
       </c>
-      <c r="H21" s="112">
+      <c r="H21" s="111">
         <f>F21*1.08</f>
         <v/>
       </c>
-      <c r="I21" s="112">
+      <c r="I21" s="111">
         <f>IF(E21="","",H21-E21)</f>
         <v/>
       </c>
-      <c r="R21" s="92" t="inlineStr">
+      <c r="R21" s="91" t="inlineStr">
         <is>
           <t>Doanh thu PCCC</t>
         </is>
       </c>
-      <c r="S21" s="97">
+      <c r="S21" s="96">
         <f>S14*1.011+S17</f>
         <v/>
       </c>
-      <c r="T21" s="97">
+      <c r="T21" s="96">
         <f>T14*1.011+T17</f>
         <v/>
       </c>
-      <c r="U21" s="97">
+      <c r="U21" s="96">
         <f>U14*1.011+U17</f>
         <v/>
       </c>
-      <c r="V21" s="97">
+      <c r="V21" s="96">
         <f>V14*1.011+V17</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="93" t="inlineStr">
+      <c r="B22" s="92" t="inlineStr">
         <is>
           <t>III. CHI PHÍ QUẢN LÝ DỰ ÁN</t>
         </is>
       </c>
-      <c r="C22" s="114" t="inlineStr">
+      <c r="C22" s="113" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="D22" s="93" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
         <is>
           <t>3,446% × (GXD + Gtb)</t>
         </is>
       </c>
-      <c r="E22" s="112" t="n">
+      <c r="E22" s="111" t="n">
         <v>56159000</v>
       </c>
-      <c r="F22" s="112">
+      <c r="F22" s="111">
         <f>(F20+F21)*3.446%</f>
         <v/>
       </c>
-      <c r="G22" s="112" t="n"/>
-      <c r="H22" s="112">
+      <c r="G22" s="111" t="n"/>
+      <c r="H22" s="111">
         <f>ROUND(F22,-3)</f>
         <v/>
       </c>
-      <c r="I22" s="112">
+      <c r="I22" s="111">
         <f>IF(E22="","",H22-E22)</f>
         <v/>
       </c>
-      <c r="R22" s="92" t="inlineStr">
+      <c r="R22" s="91" t="inlineStr">
         <is>
           <t>Trích CĐT</t>
         </is>
       </c>
-      <c r="S22" s="97">
+      <c r="S22" s="96">
         <f>$E$5*S20</f>
         <v/>
       </c>
-      <c r="T22" s="97">
+      <c r="T22" s="96">
         <f>$E$5*T20</f>
         <v/>
       </c>
-      <c r="U22" s="97">
+      <c r="U22" s="96">
         <f>$E$5*U20</f>
         <v/>
       </c>
-      <c r="V22" s="97">
+      <c r="V22" s="96">
         <f>$E$5*V20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí đo vẽ hiện trạng</t>
         </is>
       </c>
-      <c r="C23" s="110" t="inlineStr">
+      <c r="C23" s="109" t="inlineStr">
         <is>
           <t>TV1</t>
         </is>
       </c>
-      <c r="D23" s="109" t="inlineStr">
+      <c r="D23" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E23" s="111" t="n">
+      <c r="E23" s="110" t="n">
         <v>15000000</v>
       </c>
-      <c r="F23" s="111">
+      <c r="F23" s="110">
         <f>15000000/1.08</f>
         <v/>
       </c>
-      <c r="G23" s="111">
+      <c r="G23" s="110">
         <f>F23*8%</f>
         <v/>
       </c>
-      <c r="H23" s="112">
+      <c r="H23" s="111">
         <f>15000000</f>
         <v/>
       </c>
-      <c r="I23" s="111">
+      <c r="I23" s="110">
         <f>IF(E23="","",H23-E23)</f>
         <v/>
       </c>
-      <c r="R23" s="92" t="inlineStr">
+      <c r="R23" s="91" t="inlineStr">
         <is>
           <t>f(m) = DT − C − trích − LN tối thiểu</t>
         </is>
       </c>
-      <c r="S23" s="97">
+      <c r="S23" s="96">
         <f>S21-$S$7-S22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
-      <c r="T23" s="97">
+      <c r="T23" s="96">
         <f>T21-$S$7-T22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
-      <c r="U23" s="97">
+      <c r="U23" s="96">
         <f>U21-$S$7-U22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
-      <c r="V23" s="97">
+      <c r="V23" s="96">
         <f>V21-$S$7-V22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí lập báo cáo KTKT (nội suy theo quy mô)</t>
         </is>
       </c>
-      <c r="C24" s="110" t="inlineStr">
+      <c r="C24" s="109" t="inlineStr">
         <is>
           <t>TV2</t>
         </is>
       </c>
-      <c r="D24" s="109" t="inlineStr">
+      <c r="D24" s="108" t="inlineStr">
         <is>
           <t>(Gxdct + Gtb) × tỷ lệ nội suy</t>
         </is>
       </c>
-      <c r="E24" s="111" t="n"/>
-      <c r="F24" s="111">
+      <c r="E24" s="110" t="n"/>
+      <c r="F24" s="110">
         <f>(F18+F21)*(((3-(F20+F21)/10^9)*(6.5-4.7)/(3-1)+4.7)/100)</f>
         <v/>
       </c>
-      <c r="G24" s="111">
+      <c r="G24" s="110">
         <f>F24*8%</f>
         <v/>
       </c>
-      <c r="H24" s="112">
+      <c r="H24" s="111">
         <f>ROUND(F24+G24,-3)</f>
         <v/>
       </c>
-      <c r="I24" s="111">
+      <c r="I24" s="110">
         <f>IF(E24="","",H24-E24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra thiết kế BVTC</t>
         </is>
       </c>
-      <c r="C25" s="110" t="inlineStr">
+      <c r="C25" s="109" t="inlineStr">
         <is>
           <t>TV3</t>
         </is>
       </c>
-      <c r="D25" s="109" t="inlineStr">
+      <c r="D25" s="108" t="inlineStr">
         <is>
           <t>0,258% × Gxdct</t>
         </is>
       </c>
-      <c r="E25" s="111" t="n"/>
-      <c r="F25" s="111">
+      <c r="E25" s="110" t="n"/>
+      <c r="F25" s="110">
         <f>F18*0.258%</f>
         <v/>
       </c>
-      <c r="G25" s="111">
+      <c r="G25" s="110">
         <f>F25*8%</f>
         <v/>
       </c>
-      <c r="H25" s="112">
+      <c r="H25" s="111">
         <f>ROUND(F25+G25,-3)</f>
         <v/>
       </c>
-      <c r="I25" s="111">
+      <c r="I25" s="110">
         <f>IF(E25="","",H25-E25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="109" t="inlineStr">
+      <c r="B26" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra dự toán</t>
         </is>
       </c>
-      <c r="C26" s="110" t="inlineStr">
+      <c r="C26" s="109" t="inlineStr">
         <is>
           <t>TV4</t>
         </is>
       </c>
-      <c r="D26" s="109" t="inlineStr">
+      <c r="D26" s="108" t="inlineStr">
         <is>
           <t>0,25% × Gxdct</t>
         </is>
       </c>
-      <c r="E26" s="111" t="n"/>
-      <c r="F26" s="111">
+      <c r="E26" s="110" t="n"/>
+      <c r="F26" s="110">
         <f>F18*0.25%</f>
         <v/>
       </c>
-      <c r="G26" s="111">
+      <c r="G26" s="110">
         <f>F26*8%</f>
         <v/>
       </c>
-      <c r="H26" s="112">
+      <c r="H26" s="111">
         <f>ROUND(F26+G26,-3)</f>
         <v/>
       </c>
-      <c r="I26" s="111">
+      <c r="I26" s="110">
         <f>IF(E26="","",H26-E26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="109" t="inlineStr">
+      <c r="B27" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm định giá</t>
         </is>
       </c>
-      <c r="C27" s="110" t="inlineStr">
+      <c r="C27" s="109" t="inlineStr">
         <is>
           <t>TV5</t>
         </is>
       </c>
-      <c r="D27" s="109" t="inlineStr">
+      <c r="D27" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E27" s="111" t="n">
+      <c r="E27" s="110" t="n">
         <v>10000000</v>
       </c>
-      <c r="F27" s="111">
+      <c r="F27" s="110">
         <f>10000000/1.08</f>
         <v/>
       </c>
-      <c r="G27" s="111">
+      <c r="G27" s="110">
         <f>F27*8%</f>
         <v/>
       </c>
-      <c r="H27" s="112">
+      <c r="H27" s="111">
         <f>10000000</f>
         <v/>
       </c>
-      <c r="I27" s="111">
+      <c r="I27" s="110">
         <f>IF(E27="","",H27-E27)</f>
         <v/>
       </c>
-      <c r="R27" s="92" t="inlineStr">
+      <c r="R27" s="91" t="inlineStr">
         <is>
           <t>Hệ số tối thiểu (dây cung lần 2)</t>
         </is>
       </c>
-      <c r="W27" s="115">
+      <c r="W27" s="114">
         <f>U13-U23*(V13-U13)/(V23-U23)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="93" t="inlineStr">
+      <c r="B28" s="92" t="inlineStr">
         <is>
           <t>IV. CHI PHÍ TƯ VẤN</t>
         </is>
       </c>
-      <c r="C28" s="114" t="inlineStr">
+      <c r="C28" s="113" t="inlineStr">
         <is>
           <t>GTV</t>
         </is>
       </c>
-      <c r="D28" s="93" t="inlineStr">
+      <c r="D28" s="92" t="inlineStr">
         <is>
           <t>Cộng TV1–TV5</t>
         </is>
       </c>
-      <c r="E28" s="112" t="n">
+      <c r="E28" s="111" t="n">
         <v>137053000</v>
       </c>
-      <c r="F28" s="112" t="n"/>
-      <c r="G28" s="112" t="n"/>
-      <c r="H28" s="112">
+      <c r="F28" s="111" t="n"/>
+      <c r="G28" s="111" t="n"/>
+      <c r="H28" s="111">
         <f>ROUND(SUM(H23:H27),-3)</f>
         <v/>
       </c>
-      <c r="I28" s="112">
+      <c r="I28" s="111">
         <f>IF(E28="","",H28-E28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="109" t="inlineStr">
+      <c r="B29" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra phê duyệt quyết toán</t>
         </is>
       </c>
-      <c r="C29" s="110" t="inlineStr">
+      <c r="C29" s="109" t="inlineStr">
         <is>
           <t>CK1</t>
         </is>
       </c>
-      <c r="D29" s="109" t="inlineStr">
+      <c r="D29" s="108" t="inlineStr">
         <is>
           <t>0,57% × TM (ô E8)</t>
         </is>
       </c>
-      <c r="E29" s="111" t="n"/>
-      <c r="F29" s="111">
+      <c r="E29" s="110" t="n"/>
+      <c r="F29" s="110">
         <f>0.57%*$E$8</f>
         <v/>
       </c>
-      <c r="G29" s="111" t="n"/>
-      <c r="H29" s="112">
+      <c r="G29" s="110" t="n"/>
+      <c r="H29" s="111">
         <f>ROUND(F29,-3)</f>
         <v/>
       </c>
-      <c r="I29" s="111">
+      <c r="I29" s="110">
         <f>IF(E29="","",H29-E29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="109" t="inlineStr">
+      <c r="B30" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">   Phí thẩm định báo cáo KTKT</t>
         </is>
       </c>
-      <c r="C30" s="110" t="inlineStr">
+      <c r="C30" s="109" t="inlineStr">
         <is>
           <t>CK2</t>
         </is>
       </c>
-      <c r="D30" s="109" t="inlineStr">
+      <c r="D30" s="108" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E30" s="111" t="n">
+      <c r="E30" s="110" t="n">
         <v>500000</v>
       </c>
-      <c r="F30" s="111" t="n">
+      <c r="F30" s="110" t="n">
         <v>500000</v>
       </c>
-      <c r="G30" s="111" t="n"/>
-      <c r="H30" s="112">
+      <c r="G30" s="110" t="n"/>
+      <c r="H30" s="111">
         <f>ROUND(F30,-3)</f>
         <v/>
       </c>
-      <c r="I30" s="111">
+      <c r="I30" s="110">
         <f>IF(E30="","",H30-E30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="93" t="inlineStr">
+      <c r="B31" s="92" t="inlineStr">
         <is>
           <t>V. CHI PHÍ KHÁC</t>
         </is>
       </c>
-      <c r="C31" s="114" t="inlineStr">
+      <c r="C31" s="113" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="D31" s="93" t="inlineStr">
+      <c r="D31" s="92" t="inlineStr">
         <is>
           <t>CK1 + CK2</t>
         </is>
       </c>
-      <c r="E31" s="112" t="n">
+      <c r="E31" s="111" t="n">
         <v>12265000</v>
       </c>
-      <c r="F31" s="112" t="n"/>
-      <c r="G31" s="112" t="n"/>
-      <c r="H31" s="112">
+      <c r="F31" s="111" t="n"/>
+      <c r="G31" s="111" t="n"/>
+      <c r="H31" s="111">
         <f>ROUND(H29+H30,-3)</f>
         <v/>
       </c>
-      <c r="I31" s="112">
+      <c r="I31" s="111">
         <f>IF(E31="","",H31-E31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="93" t="inlineStr">
+      <c r="B32" s="92" t="inlineStr">
         <is>
           <t>VI. CHI PHÍ DỰ PHÒNG</t>
         </is>
       </c>
-      <c r="C32" s="114" t="inlineStr">
+      <c r="C32" s="113" t="inlineStr">
         <is>
           <t>GDP</t>
         </is>
       </c>
-      <c r="D32" s="93" t="inlineStr">
+      <c r="D32" s="92" t="inlineStr">
         <is>
           <t>5% × (GXD + Gtb + QL + GTV + GK)</t>
         </is>
       </c>
-      <c r="E32" s="112" t="n">
+      <c r="E32" s="111" t="n">
         <v>98277000</v>
       </c>
-      <c r="F32" s="112" t="n"/>
-      <c r="G32" s="112" t="n"/>
-      <c r="H32" s="112">
+      <c r="F32" s="111" t="n"/>
+      <c r="G32" s="111" t="n"/>
+      <c r="H32" s="111">
         <f>ROUND(5%*(H20+H21+H22+H28+H31),-3)</f>
         <v/>
       </c>
-      <c r="I32" s="112">
+      <c r="I32" s="111">
         <f>IF(E32="","",H32-E32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="116" t="inlineStr">
+      <c r="B33" s="115" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI</t>
         </is>
       </c>
-      <c r="C33" s="117" t="inlineStr">
+      <c r="C33" s="116" t="inlineStr">
         <is>
           <t>VTM</t>
         </is>
       </c>
-      <c r="D33" s="116" t="inlineStr">
+      <c r="D33" s="115" t="inlineStr">
         <is>
           <t>I + … + VI</t>
         </is>
       </c>
-      <c r="E33" s="118" t="n">
+      <c r="E33" s="117" t="n">
         <v>2063812000</v>
       </c>
-      <c r="F33" s="118" t="n"/>
-      <c r="G33" s="118" t="n"/>
-      <c r="H33" s="118">
+      <c r="F33" s="117" t="n"/>
+      <c r="G33" s="117" t="n"/>
+      <c r="H33" s="117">
         <f>ROUND(H20+H21+H22+H28+H31+H32,-3)</f>
         <v/>
       </c>
-      <c r="I33" s="118">
+      <c r="I33" s="117">
         <f>IF(E33="","",H33-E33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="119" t="inlineStr">
+      <c r="B34" s="118" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI – LÀM TRÒN (báo chủ đầu tư)</t>
         </is>
       </c>
-      <c r="C34" s="120" t="inlineStr"/>
-      <c r="D34" s="119" t="inlineStr">
+      <c r="C34" s="119" t="inlineStr"/>
+      <c r="D34" s="118" t="inlineStr">
         <is>
           <t>Làm tròn triệu</t>
         </is>
       </c>
-      <c r="E34" s="108" t="n">
+      <c r="E34" s="107" t="n">
         <v>2064000000</v>
       </c>
-      <c r="F34" s="108" t="n"/>
-      <c r="G34" s="108" t="n"/>
-      <c r="H34" s="108">
+      <c r="F34" s="107" t="n"/>
+      <c r="G34" s="107" t="n"/>
+      <c r="H34" s="107">
         <f>ROUND(H33,-6)</f>
         <v/>
       </c>
-      <c r="I34" s="108">
+      <c r="I34" s="107">
         <f>IF(E34="","",H34-E34)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="103" t="inlineStr">
+      <c r="A36" s="102" t="inlineStr">
         <is>
           <t>B. LỢI NHUẬN PHẦN PCCC (trước thuế)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="104" t="inlineStr">
+      <c r="B37" s="103" t="inlineStr">
         <is>
           <t>Khoản</t>
         </is>
       </c>
-      <c r="C37" s="94" t="n"/>
-      <c r="D37" s="95" t="n"/>
-      <c r="E37" s="104" t="inlineStr">
+      <c r="C37" s="93" t="n"/>
+      <c r="D37" s="94" t="n"/>
+      <c r="E37" s="103" t="inlineStr">
         <is>
           <t>Hiện tại</t>
         </is>
       </c>
-      <c r="F37" s="104" t="inlineStr">
+      <c r="F37" s="103" t="inlineStr">
         <is>
           <t>SAU KHI CHỐT GIÁ</t>
         </is>
       </c>
-      <c r="G37" s="104" t="inlineStr">
+      <c r="G37" s="103" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H37" s="94" t="n"/>
-      <c r="I37" s="94" t="n"/>
-      <c r="J37" s="94" t="n"/>
-      <c r="K37" s="95" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="93" t="n"/>
+      <c r="J37" s="93" t="n"/>
+      <c r="K37" s="94" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="109" t="inlineStr">
+      <c r="B38" s="108" t="inlineStr">
         <is>
           <t>Doanh thu lắp đặt PCCC (Gxdct1)</t>
         </is>
       </c>
-      <c r="C38" s="121" t="n"/>
-      <c r="D38" s="121" t="n"/>
-      <c r="E38" s="111" t="n">
+      <c r="C38" s="120" t="n"/>
+      <c r="D38" s="120" t="n"/>
+      <c r="E38" s="110" t="n">
         <v>1215750394</v>
       </c>
-      <c r="F38" s="111">
+      <c r="F38" s="110">
         <f>F12</f>
         <v/>
       </c>
-      <c r="G38" s="122" t="n"/>
-      <c r="H38" s="121" t="n"/>
-      <c r="I38" s="121" t="n"/>
-      <c r="J38" s="121" t="n"/>
-      <c r="K38" s="121" t="n"/>
+      <c r="G38" s="121" t="n"/>
+      <c r="H38" s="120" t="n"/>
+      <c r="I38" s="120" t="n"/>
+      <c r="J38" s="120" t="n"/>
+      <c r="K38" s="120" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="109" t="inlineStr">
+      <c r="B39" s="108" t="inlineStr">
         <is>
           <t>Nhà tạm phần PCCC (1,1% × Gxdct1)</t>
         </is>
       </c>
-      <c r="C39" s="121" t="n"/>
-      <c r="D39" s="121" t="n"/>
-      <c r="E39" s="111">
+      <c r="C39" s="120" t="n"/>
+      <c r="D39" s="120" t="n"/>
+      <c r="E39" s="110">
         <f>E38*1.1%</f>
         <v/>
       </c>
-      <c r="F39" s="111">
+      <c r="F39" s="110">
         <f>F38*1.1%</f>
         <v/>
       </c>
-      <c r="G39" s="122" t="n"/>
-      <c r="H39" s="121" t="n"/>
-      <c r="I39" s="121" t="n"/>
-      <c r="J39" s="121" t="n"/>
-      <c r="K39" s="121" t="n"/>
+      <c r="G39" s="121" t="n"/>
+      <c r="H39" s="120" t="n"/>
+      <c r="I39" s="120" t="n"/>
+      <c r="J39" s="120" t="n"/>
+      <c r="K39" s="120" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="109" t="inlineStr">
+      <c r="B40" s="108" t="inlineStr">
         <is>
           <t>Thiết bị (trước thuế)</t>
         </is>
       </c>
-      <c r="C40" s="121" t="n"/>
-      <c r="D40" s="121" t="n"/>
-      <c r="E40" s="111" t="n">
+      <c r="C40" s="120" t="n"/>
+      <c r="D40" s="120" t="n"/>
+      <c r="E40" s="110" t="n">
         <v>17550000</v>
       </c>
-      <c r="F40" s="111">
+      <c r="F40" s="110">
         <f>F21</f>
         <v/>
       </c>
-      <c r="G40" s="122" t="n"/>
-      <c r="H40" s="121" t="n"/>
-      <c r="I40" s="121" t="n"/>
-      <c r="J40" s="121" t="n"/>
-      <c r="K40" s="121" t="n"/>
+      <c r="G40" s="121" t="n"/>
+      <c r="H40" s="120" t="n"/>
+      <c r="I40" s="120" t="n"/>
+      <c r="J40" s="120" t="n"/>
+      <c r="K40" s="120" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="93" t="inlineStr">
+      <c r="B41" s="92" t="inlineStr">
         <is>
           <t>Cộng doanh thu PCCC</t>
         </is>
       </c>
-      <c r="C41" s="123" t="n"/>
-      <c r="D41" s="123" t="n"/>
-      <c r="E41" s="112">
+      <c r="C41" s="122" t="n"/>
+      <c r="D41" s="122" t="n"/>
+      <c r="E41" s="111">
         <f>SUM(E38:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="112">
+      <c r="F41" s="111">
         <f>SUM(F38:F40)</f>
         <v/>
       </c>
-      <c r="G41" s="122" t="n"/>
-      <c r="H41" s="123" t="n"/>
-      <c r="I41" s="123" t="n"/>
-      <c r="J41" s="123" t="n"/>
-      <c r="K41" s="123" t="n"/>
+      <c r="G41" s="121" t="n"/>
+      <c r="H41" s="122" t="n"/>
+      <c r="I41" s="122" t="n"/>
+      <c r="J41" s="122" t="n"/>
+      <c r="K41" s="122" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="109" t="inlineStr">
+      <c r="B42" s="108" t="inlineStr">
         <is>
           <t>Giá vốn – các mục trong báo giá</t>
         </is>
       </c>
-      <c r="C42" s="121" t="n"/>
-      <c r="D42" s="121" t="n"/>
-      <c r="E42" s="111">
+      <c r="C42" s="120" t="n"/>
+      <c r="D42" s="120" t="n"/>
+      <c r="E42" s="110">
         <f>J92</f>
         <v/>
       </c>
-      <c r="F42" s="111">
+      <c r="F42" s="110">
         <f>J92</f>
         <v/>
       </c>
-      <c r="G42" s="122" t="inlineStr">
+      <c r="G42" s="121" t="inlineStr">
         <is>
           <t>Bảng C: khối lượng dự toán × giá vốn</t>
         </is>
       </c>
-      <c r="H42" s="121" t="n"/>
-      <c r="I42" s="121" t="n"/>
-      <c r="J42" s="121" t="n"/>
-      <c r="K42" s="121" t="n"/>
+      <c r="H42" s="120" t="n"/>
+      <c r="I42" s="120" t="n"/>
+      <c r="J42" s="120" t="n"/>
+      <c r="K42" s="120" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="109" t="inlineStr">
+      <c r="B43" s="108" t="inlineStr">
         <is>
           <t>Giá vốn – ngoài báo giá (ống, cáp, van, vật tư phụ 5%…)</t>
         </is>
       </c>
-      <c r="C43" s="121" t="n"/>
-      <c r="D43" s="121" t="n"/>
-      <c r="E43" s="111">
+      <c r="C43" s="120" t="n"/>
+      <c r="D43" s="120" t="n"/>
+      <c r="E43" s="110">
         <f>G111</f>
         <v/>
       </c>
-      <c r="F43" s="111">
+      <c r="F43" s="110">
         <f>G111</f>
         <v/>
       </c>
-      <c r="G43" s="122" t="inlineStr">
+      <c r="G43" s="121" t="inlineStr">
         <is>
           <t>Bảng D: theo sheet Gia von chi tiet</t>
         </is>
       </c>
-      <c r="H43" s="121" t="n"/>
-      <c r="I43" s="121" t="n"/>
-      <c r="J43" s="121" t="n"/>
-      <c r="K43" s="121" t="n"/>
+      <c r="H43" s="120" t="n"/>
+      <c r="I43" s="120" t="n"/>
+      <c r="J43" s="120" t="n"/>
+      <c r="K43" s="120" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="93" t="inlineStr">
+      <c r="B44" s="92" t="inlineStr">
         <is>
           <t>Cộng giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C44" s="123" t="n"/>
-      <c r="D44" s="123" t="n"/>
-      <c r="E44" s="112">
+      <c r="C44" s="122" t="n"/>
+      <c r="D44" s="122" t="n"/>
+      <c r="E44" s="111">
         <f>E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="112">
+      <c r="F44" s="111">
         <f>F42+F43</f>
         <v/>
       </c>
-      <c r="G44" s="122" t="n"/>
-      <c r="H44" s="123" t="n"/>
-      <c r="I44" s="123" t="n"/>
-      <c r="J44" s="123" t="n"/>
-      <c r="K44" s="123" t="n"/>
+      <c r="G44" s="121" t="n"/>
+      <c r="H44" s="122" t="n"/>
+      <c r="I44" s="122" t="n"/>
+      <c r="J44" s="122" t="n"/>
+      <c r="K44" s="122" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="105" t="inlineStr">
+      <c r="B45" s="104" t="inlineStr">
         <is>
           <t>Trích lại chủ đầu tư (15% × tổng dự toán làm tròn)</t>
         </is>
       </c>
-      <c r="C45" s="124" t="n"/>
-      <c r="D45" s="124" t="n"/>
-      <c r="E45" s="107">
+      <c r="C45" s="123" t="n"/>
+      <c r="D45" s="123" t="n"/>
+      <c r="E45" s="106">
         <f>$E$5*E34</f>
         <v/>
       </c>
-      <c r="F45" s="107">
+      <c r="F45" s="106">
         <f>$E$5*H34</f>
         <v/>
       </c>
-      <c r="G45" s="125" t="inlineStr">
+      <c r="G45" s="124" t="inlineStr">
         <is>
           <t>Trừ vào doanh thu trước thuế (VAT phải nộp nhà nước)</t>
         </is>
       </c>
-      <c r="H45" s="124" t="n"/>
-      <c r="I45" s="124" t="n"/>
-      <c r="J45" s="124" t="n"/>
-      <c r="K45" s="124" t="n"/>
+      <c r="H45" s="123" t="n"/>
+      <c r="I45" s="123" t="n"/>
+      <c r="J45" s="123" t="n"/>
+      <c r="K45" s="123" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="116" t="inlineStr">
+      <c r="B46" s="115" t="inlineStr">
         <is>
           <t>LỢI NHUẬN PCCC</t>
         </is>
       </c>
-      <c r="C46" s="126" t="n"/>
-      <c r="D46" s="126" t="n"/>
-      <c r="E46" s="118">
+      <c r="C46" s="125" t="n"/>
+      <c r="D46" s="125" t="n"/>
+      <c r="E46" s="117">
         <f>E41-E44-E45</f>
         <v/>
       </c>
-      <c r="F46" s="118">
+      <c r="F46" s="117">
         <f>F41-F44-F45</f>
         <v/>
       </c>
-      <c r="G46" s="127" t="n"/>
-      <c r="H46" s="126" t="n"/>
-      <c r="I46" s="126" t="n"/>
-      <c r="J46" s="126" t="n"/>
-      <c r="K46" s="126" t="n"/>
+      <c r="G46" s="126" t="n"/>
+      <c r="H46" s="125" t="n"/>
+      <c r="I46" s="125" t="n"/>
+      <c r="J46" s="125" t="n"/>
+      <c r="K46" s="125" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="116" t="inlineStr">
+      <c r="B47" s="115" t="inlineStr">
         <is>
           <t>% lợi nhuận / giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C47" s="126" t="n"/>
-      <c r="D47" s="126" t="n"/>
-      <c r="E47" s="128">
+      <c r="C47" s="125" t="n"/>
+      <c r="D47" s="125" t="n"/>
+      <c r="E47" s="127">
         <f>E46/E44</f>
         <v/>
       </c>
-      <c r="F47" s="128">
+      <c r="F47" s="127">
         <f>F46/F44</f>
         <v/>
       </c>
-      <c r="G47" s="127" t="n"/>
-      <c r="H47" s="126" t="n"/>
-      <c r="I47" s="126" t="n"/>
-      <c r="J47" s="126" t="n"/>
-      <c r="K47" s="126" t="n"/>
+      <c r="G47" s="126" t="n"/>
+      <c r="H47" s="125" t="n"/>
+      <c r="I47" s="125" t="n"/>
+      <c r="J47" s="125" t="n"/>
+      <c r="K47" s="125" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="93" t="inlineStr">
+      <c r="B48" s="92" t="inlineStr">
         <is>
           <t>Đánh giá so với mức tối thiểu (ô E4)</t>
         </is>
       </c>
-      <c r="C48" s="123" t="n"/>
-      <c r="D48" s="123" t="n"/>
-      <c r="E48" s="123">
+      <c r="C48" s="122" t="n"/>
+      <c r="D48" s="122" t="n"/>
+      <c r="E48" s="122">
         <f>IF(E47&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="F48" s="123">
+      <c r="F48" s="122">
         <f>IF(F47&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="G48" s="122" t="n"/>
-      <c r="H48" s="123" t="n"/>
-      <c r="I48" s="123" t="n"/>
-      <c r="J48" s="123" t="n"/>
-      <c r="K48" s="123" t="n"/>
+      <c r="G48" s="121" t="n"/>
+      <c r="H48" s="122" t="n"/>
+      <c r="I48" s="122" t="n"/>
+      <c r="J48" s="122" t="n"/>
+      <c r="K48" s="122" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="109" t="inlineStr">
+      <c r="B50" s="108" t="inlineStr">
         <is>
           <t>Tham khảo – doanh thu xây dựng (xây lắp + nhà tạm, trước thuế)</t>
         </is>
       </c>
-      <c r="C50" s="121" t="n"/>
-      <c r="D50" s="121" t="n"/>
-      <c r="E50" s="111">
+      <c r="C50" s="120" t="n"/>
+      <c r="D50" s="120" t="n"/>
+      <c r="E50" s="110">
         <f>378842471*1.011</f>
         <v/>
       </c>
-      <c r="F50" s="111">
+      <c r="F50" s="110">
         <f>378842471*1.011</f>
         <v/>
       </c>
-      <c r="G50" s="122" t="inlineStr">
+      <c r="G50" s="121" t="inlineStr">
         <is>
           <t>Giữ nguyên đơn giá dự toán</t>
         </is>
       </c>
-      <c r="H50" s="121" t="n"/>
-      <c r="I50" s="121" t="n"/>
-      <c r="J50" s="121" t="n"/>
-      <c r="K50" s="121" t="n"/>
+      <c r="H50" s="120" t="n"/>
+      <c r="I50" s="120" t="n"/>
+      <c r="J50" s="120" t="n"/>
+      <c r="K50" s="120" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="109" t="inlineStr">
+      <c r="B51" s="108" t="inlineStr">
         <is>
           <t>Tham khảo – giá vốn xây dựng</t>
         </is>
       </c>
-      <c r="C51" s="121" t="n"/>
-      <c r="D51" s="121" t="n"/>
-      <c r="E51" s="111" t="n">
+      <c r="C51" s="120" t="n"/>
+      <c r="D51" s="120" t="n"/>
+      <c r="E51" s="110" t="n">
         <v>110800000</v>
       </c>
-      <c r="F51" s="111" t="n">
+      <c r="F51" s="110" t="n">
         <v>110800000</v>
       </c>
-      <c r="G51" s="122" t="inlineStr">
+      <c r="G51" s="121" t="inlineStr">
         <is>
           <t>Sheet Gia von chi tiet (khối lượng tiên lượng)</t>
         </is>
       </c>
-      <c r="H51" s="121" t="n"/>
-      <c r="I51" s="121" t="n"/>
-      <c r="J51" s="121" t="n"/>
-      <c r="K51" s="121" t="n"/>
+      <c r="H51" s="120" t="n"/>
+      <c r="I51" s="120" t="n"/>
+      <c r="J51" s="120" t="n"/>
+      <c r="K51" s="120" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="93" t="inlineStr">
+      <c r="B52" s="92" t="inlineStr">
         <is>
           <t>Tham khảo – lợi nhuận xây dựng (không dùng bù cho PCCC)</t>
         </is>
       </c>
-      <c r="C52" s="123" t="n"/>
-      <c r="D52" s="123" t="n"/>
-      <c r="E52" s="112">
+      <c r="C52" s="122" t="n"/>
+      <c r="D52" s="122" t="n"/>
+      <c r="E52" s="111">
         <f>E50-E51</f>
         <v/>
       </c>
-      <c r="F52" s="112">
+      <c r="F52" s="111">
         <f>F50-F51</f>
         <v/>
       </c>
-      <c r="G52" s="122" t="n"/>
-      <c r="H52" s="123" t="n"/>
-      <c r="I52" s="123" t="n"/>
-      <c r="J52" s="123" t="n"/>
-      <c r="K52" s="123" t="n"/>
+      <c r="G52" s="121" t="n"/>
+      <c r="H52" s="122" t="n"/>
+      <c r="I52" s="122" t="n"/>
+      <c r="J52" s="122" t="n"/>
+      <c r="K52" s="122" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="103" t="inlineStr">
+      <c r="A60" s="102" t="inlineStr">
         <is>
           <t>C. CHI TIẾT HẠNG MỤC TRONG BÁO GIÁ</t>
         </is>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="104" t="inlineStr">
+      <c r="A61" s="103" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B61" s="104" t="inlineStr">
+      <c r="B61" s="103" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C61" s="104" t="inlineStr">
+      <c r="C61" s="103" t="inlineStr">
         <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="D61" s="104" t="inlineStr">
+      <c r="D61" s="103" t="inlineStr">
         <is>
           <t>Khối lượng</t>
         </is>
       </c>
-      <c r="E61" s="104" t="inlineStr">
+      <c r="E61" s="103" t="inlineStr">
         <is>
           <t>Giá vốn vật tư (từ sheet Bao gia)</t>
         </is>
       </c>
-      <c r="F61" s="104" t="inlineStr">
+      <c r="F61" s="103" t="inlineStr">
         <is>
           <t>Giá vốn nhân công (từ sheet Bao gia)</t>
         </is>
       </c>
-      <c r="G61" s="104" t="inlineStr">
+      <c r="G61" s="103" t="inlineStr">
         <is>
           <t>Giá VT dự toán hiện tại</t>
         </is>
       </c>
-      <c r="H61" s="104" t="inlineStr">
+      <c r="H61" s="103" t="inlineStr">
         <is>
           <t>GIÁ VT ĐỀ XUẤT (CHỐT)</t>
         </is>
       </c>
-      <c r="I61" s="104" t="inlineStr">
-        <is>
-          <t>Nhân công báo giá (theo dự toán)</t>
-        </is>
-      </c>
-      <c r="J61" s="104" t="inlineStr">
+      <c r="I61" s="103" t="inlineStr">
+        <is>
+          <t>GIÁ NC ĐỀ XUẤT</t>
+        </is>
+      </c>
+      <c r="J61" s="103" t="inlineStr">
         <is>
           <t>Thành tiền giá vốn</t>
         </is>
       </c>
-      <c r="K61" s="104" t="inlineStr">
+      <c r="K61" s="103" t="inlineStr">
         <is>
           <t>Thành tiền VT đề xuất</t>
         </is>
       </c>
-      <c r="L61" s="104" t="inlineStr">
+      <c r="L61" s="103" t="inlineStr">
         <is>
           <t>Phần</t>
         </is>
       </c>
-      <c r="M61" s="104" t="inlineStr">
+      <c r="M61" s="103" t="inlineStr">
         <is>
           <t>SL quy đổi (gồm VL khác)</t>
         </is>
       </c>
-      <c r="N61" s="104" t="inlineStr">
+      <c r="N61" s="103" t="inlineStr">
         <is>
           <t>VL dự toán hiện tại (thành tiền)</t>
         </is>
       </c>
-      <c r="O61" s="104" t="inlineStr">
+      <c r="O61" s="103" t="inlineStr">
         <is>
           <t>Tăng/giảm giá trị XD trước thuế</t>
         </is>
       </c>
-      <c r="P61" s="104" t="inlineStr">
+      <c r="P61" s="103" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="Q61" s="103" t="inlineStr">
+        <is>
+          <t>NC dự toán hiện tại (định mức)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="110" t="n">
+      <c r="A62" s="109" t="n">
         <v>1</v>
       </c>
-      <c r="B62" s="109" t="inlineStr">
+      <c r="B62" s="108" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 10 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C62" s="110" t="inlineStr">
+      <c r="C62" s="109" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D62" s="129" t="n">
+      <c r="D62" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="111">
+      <c r="E62" s="110">
         <f>'Bao gia'!J4</f>
         <v/>
       </c>
-      <c r="F62" s="111">
+      <c r="F62" s="110">
         <f>'Bao gia'!K4</f>
         <v/>
       </c>
-      <c r="G62" s="111">
+      <c r="G62" s="110">
         <f>IF(M62=0,"",N62/M62)</f>
         <v/>
       </c>
-      <c r="H62" s="108">
+      <c r="H62" s="107">
         <f>ROUNDUP(E62*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I62" s="111" t="n">
+      <c r="I62" s="107">
+        <f>ROUNDUP(F62*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J62" s="110">
+        <f>D62*(E62+F62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="110">
+        <f>D62*H62</f>
+        <v/>
+      </c>
+      <c r="L62" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M62" s="129" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" s="110" t="n">
+        <v>17850000</v>
+      </c>
+      <c r="O62" s="110">
+        <f>$E$7*D62*(I62-Q62)+IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
+        <v/>
+      </c>
+      <c r="P62" s="108" t="n"/>
+      <c r="Q62" s="110" t="n">
         <v>828880</v>
       </c>
-      <c r="J62" s="111">
-        <f>D62*(E62+F62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="111">
-        <f>D62*H62</f>
-        <v/>
-      </c>
-      <c r="L62" s="110" t="inlineStr">
+    </row>
+    <row r="63">
+      <c r="A63" s="109" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="108" t="inlineStr">
+        <is>
+          <t>Còi đèn báo cháy kết hợp</t>
+        </is>
+      </c>
+      <c r="C63" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D63" s="128" t="n">
+        <v>21</v>
+      </c>
+      <c r="E63" s="110">
+        <f>'Bao gia'!J5</f>
+        <v/>
+      </c>
+      <c r="F63" s="110">
+        <f>'Bao gia'!K5</f>
+        <v/>
+      </c>
+      <c r="G63" s="110">
+        <f>IF(M63=0,"",N63/M63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="107">
+        <f>ROUNDUP(E63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I63" s="107">
+        <f>ROUNDUP(F63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J63" s="110">
+        <f>D63*(E63+F63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="110">
+        <f>D63*H63</f>
+        <v/>
+      </c>
+      <c r="L63" s="109" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M62" s="130" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N62" s="111" t="n">
-        <v>17850000</v>
-      </c>
-      <c r="O62" s="111">
-        <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
-        <v/>
-      </c>
-      <c r="P62" s="109" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="110" t="n">
+      <c r="M63" s="129" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="N63" s="110" t="n">
+        <v>5355000</v>
+      </c>
+      <c r="O63" s="110">
+        <f>$E$7*D63*(I63-Q63)+IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
+        <v/>
+      </c>
+      <c r="P63" s="108" t="n"/>
+      <c r="Q63" s="110" t="n">
+        <v>74280</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="109" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="108" t="inlineStr">
+        <is>
+          <t>Nút ấn khẩn tròn lắp nổi</t>
+        </is>
+      </c>
+      <c r="C64" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D64" s="128" t="n">
+        <v>21</v>
+      </c>
+      <c r="E64" s="110">
+        <f>'Bao gia'!J6</f>
+        <v/>
+      </c>
+      <c r="F64" s="110">
+        <f>'Bao gia'!K6</f>
+        <v/>
+      </c>
+      <c r="G64" s="110">
+        <f>IF(M64=0,"",N64/M64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="107">
+        <f>ROUNDUP(E64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I64" s="107">
+        <f>ROUNDUP(F64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J64" s="110">
+        <f>D64*(E64+F64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="110">
+        <f>D64*H64</f>
+        <v/>
+      </c>
+      <c r="L64" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M64" s="129" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="N64" s="110" t="n">
+        <v>4284000</v>
+      </c>
+      <c r="O64" s="110">
+        <f>$E$7*D64*(I64-Q64)+IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
+        <v/>
+      </c>
+      <c r="P64" s="108" t="n"/>
+      <c r="Q64" s="110" t="n">
+        <v>191280</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="109" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="108" t="inlineStr">
+        <is>
+          <t>Đầu báo khói quang 24VDC</t>
+        </is>
+      </c>
+      <c r="C65" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D65" s="128" t="n">
+        <v>287</v>
+      </c>
+      <c r="E65" s="110">
+        <f>'Bao gia'!J7</f>
+        <v/>
+      </c>
+      <c r="F65" s="110">
+        <f>'Bao gia'!K7</f>
+        <v/>
+      </c>
+      <c r="G65" s="110">
+        <f>IF(M65=0,"",N65/M65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="107">
+        <f>ROUNDUP(E65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I65" s="107">
+        <f>ROUNDUP(F65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J65" s="110">
+        <f>D65*(E65+F65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="110">
+        <f>D65*H65</f>
+        <v/>
+      </c>
+      <c r="L65" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M65" s="129" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="N65" s="110" t="n">
+        <v>73185000</v>
+      </c>
+      <c r="O65" s="110">
+        <f>$E$7*D65*(I65-Q65)+IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
+        <v/>
+      </c>
+      <c r="P65" s="108" t="n"/>
+      <c r="Q65" s="110" t="n">
+        <v>55471</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="109" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="108" t="inlineStr">
+        <is>
+          <t>Đèn báo phòng</t>
+        </is>
+      </c>
+      <c r="C66" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D66" s="128" t="n">
+        <v>70</v>
+      </c>
+      <c r="E66" s="110">
+        <f>'Bao gia'!J8</f>
+        <v/>
+      </c>
+      <c r="F66" s="110">
+        <f>'Bao gia'!K8</f>
+        <v/>
+      </c>
+      <c r="G66" s="110">
+        <f>IF(M66=0,"",N66/M66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="107">
+        <f>ROUNDUP(E66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I66" s="107">
+        <f>ROUNDUP(F66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J66" s="110">
+        <f>D66*(E66+F66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="110">
+        <f>D66*H66</f>
+        <v/>
+      </c>
+      <c r="L66" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M66" s="129" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N66" s="110" t="n">
+        <v>3570000</v>
+      </c>
+      <c r="O66" s="110">
+        <f>$E$7*D66*(I66-Q66)+IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
+        <v/>
+      </c>
+      <c r="P66" s="108" t="n"/>
+      <c r="Q66" s="110" t="n">
+        <v>74280</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="109" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="108" t="inlineStr">
+        <is>
+          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
+        </is>
+      </c>
+      <c r="C67" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D67" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="109" t="inlineStr">
-        <is>
-          <t>Còi đèn báo cháy kết hợp</t>
-        </is>
-      </c>
-      <c r="C63" s="110" t="inlineStr">
+      <c r="E67" s="110">
+        <f>'Bao gia'!J9</f>
+        <v/>
+      </c>
+      <c r="F67" s="110">
+        <f>'Bao gia'!K9</f>
+        <v/>
+      </c>
+      <c r="G67" s="110">
+        <f>IF(M67=0,"",N67/M67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="107">
+        <f>ROUNDUP(E67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I67" s="107">
+        <f>ROUNDUP(F67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J67" s="110">
+        <f>D67*(E67+F67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="110">
+        <f>D67*H67</f>
+        <v/>
+      </c>
+      <c r="L67" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M67" s="129" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N67" s="110" t="n">
+        <v>565600</v>
+      </c>
+      <c r="O67" s="110">
+        <f>$E$7*D67*(I67-Q67)+IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
+        <v/>
+      </c>
+      <c r="P67" s="108" t="n"/>
+      <c r="Q67" s="110" t="n">
+        <v>100928</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="109" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="108" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C68" s="109" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D63" s="129" t="n">
+      <c r="D68" s="128" t="n">
+        <v>56</v>
+      </c>
+      <c r="E68" s="110">
+        <f>'Bao gia'!J10</f>
+        <v/>
+      </c>
+      <c r="F68" s="110">
+        <f>'Bao gia'!K10</f>
+        <v/>
+      </c>
+      <c r="G68" s="110">
+        <f>IF(M68=0,"",N68/M68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="107">
+        <f>ROUNDUP(E68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I68" s="107">
+        <f>ROUNDUP(F68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J68" s="110">
+        <f>D68*(E68+F68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="110">
+        <f>D68*H68</f>
+        <v/>
+      </c>
+      <c r="L68" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M68" s="129" t="n">
+        <v>56.0056</v>
+      </c>
+      <c r="N68" s="110" t="n">
+        <v>3640364</v>
+      </c>
+      <c r="O68" s="110">
+        <f>$E$7*D68*(I68-Q68)+IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
+        <v/>
+      </c>
+      <c r="P68" s="108" t="n"/>
+      <c r="Q68" s="110" t="n">
+        <v>75696</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="109" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="108" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN50</t>
+        </is>
+      </c>
+      <c r="C69" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D69" s="128" t="n">
+        <v>265</v>
+      </c>
+      <c r="E69" s="110">
+        <f>'Bao gia'!J11</f>
+        <v/>
+      </c>
+      <c r="F69" s="110">
+        <f>'Bao gia'!K11</f>
+        <v/>
+      </c>
+      <c r="G69" s="110">
+        <f>IF(M69=0,"",N69/M69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="107">
+        <f>ROUNDUP(E69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I69" s="107">
+        <f>ROUNDUP(F69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J69" s="110">
+        <f>D69*(E69+F69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="110">
+        <f>D69*H69</f>
+        <v/>
+      </c>
+      <c r="L69" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M69" s="129" t="n">
+        <v>265.0265</v>
+      </c>
+      <c r="N69" s="110" t="n">
+        <v>13251325</v>
+      </c>
+      <c r="O69" s="110">
+        <f>$E$7*D69*(I69-Q69)+IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
+        <v/>
+      </c>
+      <c r="P69" s="108" t="n"/>
+      <c r="Q69" s="110" t="n">
+        <v>66234</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="109" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="108" t="inlineStr">
+        <is>
+          <t>Tê thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C70" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D70" s="128" t="n">
+        <v>22</v>
+      </c>
+      <c r="E70" s="110">
+        <f>'Bao gia'!J12</f>
+        <v/>
+      </c>
+      <c r="F70" s="110">
+        <f>'Bao gia'!K12</f>
+        <v/>
+      </c>
+      <c r="G70" s="110">
+        <f>IF(M70=0,"",N70/M70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="107">
+        <f>ROUNDUP(E70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I70" s="107">
+        <f>ROUNDUP(F70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J70" s="110">
+        <f>D70*(E70+F70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="110">
+        <f>D70*H70</f>
+        <v/>
+      </c>
+      <c r="L70" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M70" s="129" t="n">
+        <v>22.0022</v>
+      </c>
+      <c r="N70" s="110" t="n">
+        <v>3630363</v>
+      </c>
+      <c r="O70" s="110">
+        <f>$E$7*D70*(I70-Q70)+IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
+        <v/>
+      </c>
+      <c r="P70" s="108" t="n"/>
+      <c r="Q70" s="110" t="n">
+        <v>75696</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="109" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="108" t="inlineStr">
+        <is>
+          <t>Tê giảm thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C71" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D71" s="128" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="110">
+        <f>'Bao gia'!J13</f>
+        <v/>
+      </c>
+      <c r="F71" s="110">
+        <f>'Bao gia'!K13</f>
+        <v/>
+      </c>
+      <c r="G71" s="110">
+        <f>IF(M71=0,"",N71/M71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="107">
+        <f>ROUNDUP(E71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I71" s="107">
+        <f>ROUNDUP(F71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J71" s="110">
+        <f>D71*(E71+F71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="110">
+        <f>D71*H71</f>
+        <v/>
+      </c>
+      <c r="L71" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M71" s="129" t="n">
+        <v>10.001</v>
+      </c>
+      <c r="N71" s="110" t="n">
+        <v>1650165</v>
+      </c>
+      <c r="O71" s="110">
+        <f>$E$7*D71*(I71-Q71)+IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
+        <v/>
+      </c>
+      <c r="P71" s="108" t="n"/>
+      <c r="Q71" s="110" t="n">
+        <v>75696</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="109" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" s="108" t="inlineStr">
+        <is>
+          <t>Tê thép hàn tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C72" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D72" s="128" t="n">
+        <v>52</v>
+      </c>
+      <c r="E72" s="110">
+        <f>'Bao gia'!J14</f>
+        <v/>
+      </c>
+      <c r="F72" s="110">
+        <f>'Bao gia'!K14</f>
+        <v/>
+      </c>
+      <c r="G72" s="110">
+        <f>IF(M72=0,"",N72/M72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="107">
+        <f>ROUNDUP(E72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I72" s="107">
+        <f>ROUNDUP(F72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J72" s="110">
+        <f>D72*(E72+F72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="110">
+        <f>D72*H72</f>
+        <v/>
+      </c>
+      <c r="L72" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M72" s="129" t="n">
+        <v>52.0052</v>
+      </c>
+      <c r="N72" s="110" t="n">
+        <v>7800780</v>
+      </c>
+      <c r="O72" s="110">
+        <f>$E$7*D72*(I72-Q72)+IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
+        <v/>
+      </c>
+      <c r="P72" s="108" t="n"/>
+      <c r="Q72" s="110" t="n">
+        <v>100928</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="109" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" s="108" t="inlineStr">
+        <is>
+          <t>Tê giảm thép hàn DN100/65</t>
+        </is>
+      </c>
+      <c r="C73" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D73" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="110">
+        <f>'Bao gia'!J15</f>
+        <v/>
+      </c>
+      <c r="F73" s="110">
+        <f>'Bao gia'!K15</f>
+        <v/>
+      </c>
+      <c r="G73" s="110">
+        <f>IF(M73=0,"",N73/M73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="107">
+        <f>ROUNDUP(E73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I73" s="107">
+        <f>ROUNDUP(F73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J73" s="110">
+        <f>D73*(E73+F73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="110">
+        <f>D73*H73</f>
+        <v/>
+      </c>
+      <c r="L73" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M73" s="129" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N73" s="110" t="n">
+        <v>180018</v>
+      </c>
+      <c r="O73" s="110">
+        <f>$E$7*D73*(I73-Q73)+IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
+        <v/>
+      </c>
+      <c r="P73" s="108" t="n"/>
+      <c r="Q73" s="110" t="n">
+        <v>113544</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="109" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" s="108" t="inlineStr">
+        <is>
+          <t>Tê giảm thép hàn DN65/50</t>
+        </is>
+      </c>
+      <c r="C74" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D74" s="128" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="110">
+        <f>'Bao gia'!J16</f>
+        <v/>
+      </c>
+      <c r="F74" s="110">
+        <f>'Bao gia'!K16</f>
+        <v/>
+      </c>
+      <c r="G74" s="110">
+        <f>IF(M74=0,"",N74/M74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="107">
+        <f>ROUNDUP(E74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I74" s="107">
+        <f>ROUNDUP(F74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J74" s="110">
+        <f>D74*(E74+F74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="110">
+        <f>D74*H74</f>
+        <v/>
+      </c>
+      <c r="L74" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M74" s="129" t="n">
+        <v>5.0005</v>
+      </c>
+      <c r="N74" s="110" t="n">
+        <v>750075</v>
+      </c>
+      <c r="O74" s="110">
+        <f>$E$7*D74*(I74-Q74)+IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
+        <v/>
+      </c>
+      <c r="P74" s="108" t="n"/>
+      <c r="Q74" s="110" t="n">
+        <v>75696</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="109" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" s="108" t="inlineStr">
+        <is>
+          <t>Côn giảm thép hàn DN80/65</t>
+        </is>
+      </c>
+      <c r="C75" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D75" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="110">
+        <f>'Bao gia'!J17</f>
+        <v/>
+      </c>
+      <c r="F75" s="110">
+        <f>'Bao gia'!K17</f>
+        <v/>
+      </c>
+      <c r="G75" s="110">
+        <f>IF(M75=0,"",N75/M75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="107">
+        <f>ROUNDUP(E75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I75" s="107">
+        <f>ROUNDUP(F75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J75" s="110">
+        <f>D75*(E75+F75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="110">
+        <f>D75*H75</f>
+        <v/>
+      </c>
+      <c r="L75" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M75" s="129" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N75" s="110" t="n">
+        <v>80008</v>
+      </c>
+      <c r="O75" s="110">
+        <f>$E$7*D75*(I75-Q75)+IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
+        <v/>
+      </c>
+      <c r="P75" s="108" t="n"/>
+      <c r="Q75" s="110" t="n">
+        <v>100928</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="109" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" s="108" t="inlineStr">
+        <is>
+          <t>Mặt bích thép DN80</t>
+        </is>
+      </c>
+      <c r="C76" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D76" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="110">
+        <f>'Bao gia'!J18</f>
+        <v/>
+      </c>
+      <c r="F76" s="110">
+        <f>'Bao gia'!K18</f>
+        <v/>
+      </c>
+      <c r="G76" s="110">
+        <f>IF(M76=0,"",N76/M76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="107">
+        <f>ROUNDUP(E76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I76" s="107">
+        <f>ROUNDUP(F76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J76" s="110">
+        <f>D76*(E76+F76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="110">
+        <f>D76*H76</f>
+        <v/>
+      </c>
+      <c r="L76" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M76" s="129" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N76" s="110" t="n">
+        <v>321032.1</v>
+      </c>
+      <c r="O76" s="110">
+        <f>$E$7*D76*(I76-Q76)+IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
+        <v/>
+      </c>
+      <c r="P76" s="108" t="n"/>
+      <c r="Q76" s="110" t="n">
+        <v>59926</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="109" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" s="108" t="inlineStr">
+        <is>
+          <t>Roăng su DN80</t>
+        </is>
+      </c>
+      <c r="C77" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D77" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="110">
+        <f>'Bao gia'!J19</f>
+        <v/>
+      </c>
+      <c r="F77" s="110">
+        <f>'Bao gia'!K19</f>
+        <v/>
+      </c>
+      <c r="G77" s="110">
+        <f>IF(M77=0,"",N77/M77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="107">
+        <f>ROUNDUP(E77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I77" s="107">
+        <f>ROUNDUP(F77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J77" s="110">
+        <f>D77*(E77+F77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="110">
+        <f>D77*H77</f>
+        <v/>
+      </c>
+      <c r="L77" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M77" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="110" t="n">
+        <v>150000</v>
+      </c>
+      <c r="O77" s="110">
+        <f>$E$7*D77*(I77-Q77)+IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
+        <v/>
+      </c>
+      <c r="P77" s="108" t="n"/>
+      <c r="Q77" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="109" t="n">
+        <v>17</v>
+      </c>
+      <c r="B78" s="108" t="inlineStr">
+        <is>
+          <t>Van 1 chiều DN80</t>
+        </is>
+      </c>
+      <c r="C78" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D78" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="110">
+        <f>'Bao gia'!J20</f>
+        <v/>
+      </c>
+      <c r="F78" s="110">
+        <f>'Bao gia'!K20</f>
+        <v/>
+      </c>
+      <c r="G78" s="110">
+        <f>IF(M78=0,"",N78/M78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="107">
+        <f>ROUNDUP(E78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I78" s="107">
+        <f>ROUNDUP(F78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J78" s="110">
+        <f>D78*(E78+F78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="110">
+        <f>D78*H78</f>
+        <v/>
+      </c>
+      <c r="L78" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M78" s="129" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="N78" s="110" t="n">
+        <v>350035</v>
+      </c>
+      <c r="O78" s="110">
+        <f>$E$7*D78*(I78-Q78)+IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
+        <v/>
+      </c>
+      <c r="P78" s="108" t="n"/>
+      <c r="Q78" s="110" t="n">
+        <v>97774</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="109" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" s="108" t="inlineStr">
+        <is>
+          <t>Rơ le kiểm tra mực nước</t>
+        </is>
+      </c>
+      <c r="C79" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D79" s="128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="110">
+        <f>'Bao gia'!J21</f>
+        <v/>
+      </c>
+      <c r="F79" s="110">
+        <f>'Bao gia'!K21</f>
+        <v/>
+      </c>
+      <c r="G79" s="110">
+        <f>IF(M79=0,"",N79/M79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="107">
+        <f>ROUNDUP(E79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I79" s="107">
+        <f>ROUNDUP(F79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J79" s="110">
+        <f>D79*(E79+F79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="110">
+        <f>D79*H79</f>
+        <v/>
+      </c>
+      <c r="L79" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M79" s="129" t="n">
+        <v>4.0004</v>
+      </c>
+      <c r="N79" s="110" t="n">
+        <v>4600460</v>
+      </c>
+      <c r="O79" s="110">
+        <f>$E$7*D79*(I79-Q79)+IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
+        <v/>
+      </c>
+      <c r="P79" s="108" t="n"/>
+      <c r="Q79" s="110" t="n">
+        <v>31540</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="109" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" s="108" t="inlineStr">
+        <is>
+          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
+        </is>
+      </c>
+      <c r="C80" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D80" s="128" t="n">
+        <v>57</v>
+      </c>
+      <c r="E80" s="110">
+        <f>'Bao gia'!J22</f>
+        <v/>
+      </c>
+      <c r="F80" s="110">
+        <f>'Bao gia'!K22</f>
+        <v/>
+      </c>
+      <c r="G80" s="110">
+        <f>IF(M80=0,"",N80/M80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="107">
+        <f>ROUNDUP(E80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I80" s="107">
+        <f>ROUNDUP(F80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J80" s="110">
+        <f>D80*(E80+F80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="110">
+        <f>D80*H80</f>
+        <v/>
+      </c>
+      <c r="L80" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M80" s="129" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="N80" s="110" t="n">
+        <v>19152000</v>
+      </c>
+      <c r="O80" s="110">
+        <f>$E$7*D80*(I80-Q80)+IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
+        <v/>
+      </c>
+      <c r="P80" s="108" t="n"/>
+      <c r="Q80" s="110" t="n">
+        <v>94620</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="109" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" s="108" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
+        </is>
+      </c>
+      <c r="C81" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D81" s="128" t="n">
+        <v>70</v>
+      </c>
+      <c r="E81" s="110">
+        <f>'Bao gia'!J23</f>
+        <v/>
+      </c>
+      <c r="F81" s="110">
+        <f>'Bao gia'!K23</f>
+        <v/>
+      </c>
+      <c r="G81" s="110">
+        <f>IF(M81=0,"",N81/M81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="107">
+        <f>ROUNDUP(E81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I81" s="107">
+        <f>ROUNDUP(F81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J81" s="110">
+        <f>D81*(E81+F81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="110">
+        <f>D81*H81</f>
+        <v/>
+      </c>
+      <c r="L81" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M81" s="129" t="n">
+        <v>70</v>
+      </c>
+      <c r="N81" s="110" t="n">
+        <v>33600000</v>
+      </c>
+      <c r="O81" s="110">
+        <f>$E$7*D81*(I81-Q81)+IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
+        <v/>
+      </c>
+      <c r="P81" s="108" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+      <c r="Q81" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="109" t="n">
         <v>21</v>
       </c>
-      <c r="E63" s="111">
-        <f>'Bao gia'!J5</f>
-        <v/>
-      </c>
-      <c r="F63" s="111">
-        <f>'Bao gia'!K5</f>
-        <v/>
-      </c>
-      <c r="G63" s="111">
-        <f>IF(M63=0,"",N63/M63)</f>
-        <v/>
-      </c>
-      <c r="H63" s="108">
-        <f>ROUNDUP(E63*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I63" s="111" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J63" s="111">
-        <f>D63*(E63+F63)</f>
-        <v/>
-      </c>
-      <c r="K63" s="111">
-        <f>D63*H63</f>
-        <v/>
-      </c>
-      <c r="L63" s="110" t="inlineStr">
+      <c r="B82" s="108" t="inlineStr">
+        <is>
+          <t>Lăng phun DN50</t>
+        </is>
+      </c>
+      <c r="C82" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D82" s="128" t="n">
+        <v>70</v>
+      </c>
+      <c r="E82" s="110">
+        <f>'Bao gia'!J24</f>
+        <v/>
+      </c>
+      <c r="F82" s="110">
+        <f>'Bao gia'!K24</f>
+        <v/>
+      </c>
+      <c r="G82" s="110">
+        <f>IF(M82=0,"",N82/M82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="107">
+        <f>ROUNDUP(E82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I82" s="107">
+        <f>ROUNDUP(F82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J82" s="110">
+        <f>D82*(E82+F82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="110">
+        <f>D82*H82</f>
+        <v/>
+      </c>
+      <c r="L82" s="109" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M63" s="130" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="N63" s="111" t="n">
-        <v>5355000</v>
-      </c>
-      <c r="O63" s="111">
-        <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
-        <v/>
-      </c>
-      <c r="P63" s="109" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="110" t="n">
+      <c r="M82" s="129" t="n">
+        <v>70</v>
+      </c>
+      <c r="N82" s="110" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="O82" s="110">
+        <f>$E$7*D82*(I82-Q82)+IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
+        <v/>
+      </c>
+      <c r="P82" s="108" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+      <c r="Q82" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="109" t="n">
+        <v>22</v>
+      </c>
+      <c r="B83" s="108" t="inlineStr">
+        <is>
+          <t>Van góc FUJI DN50</t>
+        </is>
+      </c>
+      <c r="C83" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D83" s="128" t="n">
+        <v>70</v>
+      </c>
+      <c r="E83" s="110">
+        <f>'Bao gia'!J25</f>
+        <v/>
+      </c>
+      <c r="F83" s="110">
+        <f>'Bao gia'!K25</f>
+        <v/>
+      </c>
+      <c r="G83" s="110">
+        <f>IF(M83=0,"",N83/M83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="107">
+        <f>ROUNDUP(E83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I83" s="107">
+        <f>ROUNDUP(F83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J83" s="110">
+        <f>D83*(E83+F83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="110">
+        <f>D83*H83</f>
+        <v/>
+      </c>
+      <c r="L83" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M83" s="129" t="n">
+        <v>70.00700000000001</v>
+      </c>
+      <c r="N83" s="110" t="n">
+        <v>17501750</v>
+      </c>
+      <c r="O83" s="110">
+        <f>$E$7*D83*(I83-Q83)+IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
+        <v/>
+      </c>
+      <c r="P83" s="108" t="n"/>
+      <c r="Q83" s="110" t="n">
+        <v>66234</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="109" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" s="108" t="inlineStr">
+        <is>
+          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
+        </is>
+      </c>
+      <c r="C84" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D84" s="128" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="110">
+        <f>'Bao gia'!J26</f>
+        <v/>
+      </c>
+      <c r="F84" s="110">
+        <f>'Bao gia'!K26</f>
+        <v/>
+      </c>
+      <c r="G84" s="110">
+        <f>IF(M84=0,"",N84/M84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="107">
+        <f>ROUNDUP(E84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I84" s="107">
+        <f>ROUNDUP(F84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J84" s="110">
+        <f>D84*(E84+F84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="110">
+        <f>D84*H84</f>
+        <v/>
+      </c>
+      <c r="L84" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M84" s="129" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" s="110" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O84" s="110">
+        <f>$E$7*D84*(I84-Q84)+IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
+        <v/>
+      </c>
+      <c r="P84" s="108" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q84" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="109" t="n">
+        <v>24</v>
+      </c>
+      <c r="B85" s="108" t="inlineStr">
+        <is>
+          <t>Kệ đỡ bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="C85" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D85" s="128" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" s="110">
+        <f>'Bao gia'!J27</f>
+        <v/>
+      </c>
+      <c r="F85" s="110">
+        <f>'Bao gia'!K27</f>
+        <v/>
+      </c>
+      <c r="G85" s="110">
+        <f>IF(M85=0,"",N85/M85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="107">
+        <f>ROUNDUP(E85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I85" s="107">
+        <f>ROUNDUP(F85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J85" s="110">
+        <f>D85*(E85+F85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="110">
+        <f>D85*H85</f>
+        <v/>
+      </c>
+      <c r="L85" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M85" s="129" t="n">
+        <v>10</v>
+      </c>
+      <c r="N85" s="110" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="O85" s="110">
+        <f>$E$7*D85*(I85-Q85)+IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
+        <v/>
+      </c>
+      <c r="P85" s="108" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q85" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="109" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" s="108" t="inlineStr">
+        <is>
+          <t>BÌNH BỘT ABC 8KG</t>
+        </is>
+      </c>
+      <c r="C86" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D86" s="128" t="n">
+        <v>20</v>
+      </c>
+      <c r="E86" s="110">
+        <f>'Bao gia'!J28</f>
+        <v/>
+      </c>
+      <c r="F86" s="110">
+        <f>'Bao gia'!K28</f>
+        <v/>
+      </c>
+      <c r="G86" s="110">
+        <f>IF(M86=0,"",N86/M86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="107">
+        <f>ROUNDUP(E86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I86" s="107">
+        <f>ROUNDUP(F86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J86" s="110">
+        <f>D86*(E86+F86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="110">
+        <f>D86*H86</f>
+        <v/>
+      </c>
+      <c r="L86" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M86" s="129" t="n">
+        <v>20</v>
+      </c>
+      <c r="N86" s="110" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="O86" s="110">
+        <f>$E$7*D86*(I86-Q86)+IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
+        <v/>
+      </c>
+      <c r="P86" s="108" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q86" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="109" t="n">
+        <v>26</v>
+      </c>
+      <c r="B87" s="108" t="inlineStr">
+        <is>
+          <t>Đèn exit</t>
+        </is>
+      </c>
+      <c r="C87" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D87" s="128" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" s="110">
+        <f>'Bao gia'!J29</f>
+        <v/>
+      </c>
+      <c r="F87" s="110">
+        <f>'Bao gia'!K29</f>
+        <v/>
+      </c>
+      <c r="G87" s="110">
+        <f>IF(M87=0,"",N87/M87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="107">
+        <f>ROUNDUP(E87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I87" s="107">
+        <f>ROUNDUP(F87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J87" s="110">
+        <f>D87*(E87+F87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="110">
+        <f>D87*H87</f>
+        <v/>
+      </c>
+      <c r="L87" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M87" s="129" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="N87" s="110" t="n">
+        <v>2310000</v>
+      </c>
+      <c r="O87" s="110">
+        <f>$E$7*D87*(I87-Q87)+IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
+        <v/>
+      </c>
+      <c r="P87" s="108" t="n"/>
+      <c r="Q87" s="110" t="n">
+        <v>93090</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="109" t="n">
+        <v>27</v>
+      </c>
+      <c r="B88" s="108" t="inlineStr">
+        <is>
+          <t>Đèn chiếu sáng sự cố</t>
+        </is>
+      </c>
+      <c r="C88" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D88" s="128" t="n">
+        <v>54</v>
+      </c>
+      <c r="E88" s="110">
+        <f>'Bao gia'!J30</f>
+        <v/>
+      </c>
+      <c r="F88" s="110">
+        <f>'Bao gia'!K30</f>
+        <v/>
+      </c>
+      <c r="G88" s="110">
+        <f>IF(M88=0,"",N88/M88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="107">
+        <f>ROUNDUP(E88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I88" s="107">
+        <f>ROUNDUP(F88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J88" s="110">
+        <f>D88*(E88+F88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="110">
+        <f>D88*H88</f>
+        <v/>
+      </c>
+      <c r="L88" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M88" s="129" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="N88" s="110" t="n">
+        <v>11340000</v>
+      </c>
+      <c r="O88" s="110">
+        <f>$E$7*D88*(I88-Q88)+IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
+        <v/>
+      </c>
+      <c r="P88" s="108" t="n"/>
+      <c r="Q88" s="110" t="n">
+        <v>93090</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="109" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" s="108" t="inlineStr">
+        <is>
+          <t>Đèn báo trạm bơm</t>
+        </is>
+      </c>
+      <c r="C89" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D89" s="128">
+        <f>N('Bao gia'!D31)</f>
+        <v/>
+      </c>
+      <c r="E89" s="110">
+        <f>'Bao gia'!J31</f>
+        <v/>
+      </c>
+      <c r="F89" s="110">
+        <f>'Bao gia'!K31</f>
+        <v/>
+      </c>
+      <c r="G89" s="110">
+        <f>IF(M89=0,"",N89/M89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="107">
+        <f>ROUNDUP(E89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I89" s="107">
+        <f>ROUNDUP(F89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J89" s="110">
+        <f>D89*(E89+F89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="110">
+        <f>D89*H89</f>
+        <v/>
+      </c>
+      <c r="L89" s="109" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M89" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="110">
+        <f>$E$7*D89*(I89-Q89)+IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
+        <v/>
+      </c>
+      <c r="P89" s="108" t="inlineStr">
+        <is>
+          <t>Chưa có giá vốn, chưa có trong dự toán – nếu dùng thì điền KL và giá vốn ở sheet Bao gia</t>
+        </is>
+      </c>
+      <c r="Q89" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="109" t="n">
+        <v>29</v>
+      </c>
+      <c r="B90" s="108" t="inlineStr">
+        <is>
+          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
+        </is>
+      </c>
+      <c r="C90" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D90" s="128" t="n">
+        <v>35</v>
+      </c>
+      <c r="E90" s="110">
+        <f>'Bao gia'!J32</f>
+        <v/>
+      </c>
+      <c r="F90" s="110">
+        <f>'Bao gia'!K32</f>
+        <v/>
+      </c>
+      <c r="G90" s="110">
+        <f>IF(M90=0,"",N90/M90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="107">
+        <f>ROUNDUP(E90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I90" s="107">
+        <f>ROUNDUP(F90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J90" s="110">
+        <f>D90*(E90+F90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="110">
+        <f>D90*H90</f>
+        <v/>
+      </c>
+      <c r="L90" s="109" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M90" s="129" t="n">
+        <v>35</v>
+      </c>
+      <c r="N90" s="110" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="O90" s="110">
+        <f>$E$7*D90*(I90-Q90)+IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
+        <v/>
+      </c>
+      <c r="P90" s="108" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q90" s="110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="109" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" s="108" t="inlineStr">
+        <is>
+          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
+        </is>
+      </c>
+      <c r="C91" s="109" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D91" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="109" t="inlineStr">
-        <is>
-          <t>Nút ấn khẩn tròn lắp nổi</t>
-        </is>
-      </c>
-      <c r="C64" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D64" s="129" t="n">
-        <v>21</v>
-      </c>
-      <c r="E64" s="111">
-        <f>'Bao gia'!J6</f>
-        <v/>
-      </c>
-      <c r="F64" s="111">
-        <f>'Bao gia'!K6</f>
-        <v/>
-      </c>
-      <c r="G64" s="111">
-        <f>IF(M64=0,"",N64/M64)</f>
-        <v/>
-      </c>
-      <c r="H64" s="108">
-        <f>ROUNDUP(E64*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I64" s="111" t="n">
-        <v>191280</v>
-      </c>
-      <c r="J64" s="111">
-        <f>D64*(E64+F64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="111">
-        <f>D64*H64</f>
-        <v/>
-      </c>
-      <c r="L64" s="110" t="inlineStr">
+      <c r="E91" s="110">
+        <f>'Bao gia'!J33</f>
+        <v/>
+      </c>
+      <c r="F91" s="110">
+        <f>'Bao gia'!K33</f>
+        <v/>
+      </c>
+      <c r="G91" s="110">
+        <f>IF(M91=0,"",N91/M91)</f>
+        <v/>
+      </c>
+      <c r="H91" s="107">
+        <f>ROUNDUP(E91*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I91" s="107">
+        <f>ROUNDUP(F91*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J91" s="110">
+        <f>D91*(E91+F91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="110">
+        <f>D91*H91</f>
+        <v/>
+      </c>
+      <c r="L91" s="109" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M64" s="130" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="N64" s="111" t="n">
-        <v>4284000</v>
-      </c>
-      <c r="O64" s="111">
-        <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
-        <v/>
-      </c>
-      <c r="P64" s="109" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="110" t="n">
+      <c r="M91" s="129" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="N91" s="110" t="n">
+        <v>2852850</v>
+      </c>
+      <c r="O91" s="110">
+        <f>$E$7*D91*(I91-Q91)+IF(L91="Thiết bị",0,$E$7*(M91*H91-N91))</f>
+        <v/>
+      </c>
+      <c r="P91" s="108" t="n"/>
+      <c r="Q91" s="110" t="n">
+        <v>110390</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="125" t="n"/>
+      <c r="B92" s="125" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C92" s="125" t="n"/>
+      <c r="D92" s="125" t="n"/>
+      <c r="E92" s="125" t="n"/>
+      <c r="F92" s="125" t="n"/>
+      <c r="G92" s="125" t="n"/>
+      <c r="H92" s="125" t="n"/>
+      <c r="I92" s="125" t="n"/>
+      <c r="J92" s="117">
+        <f>SUM(J62:J91)</f>
+        <v/>
+      </c>
+      <c r="K92" s="117">
+        <f>SUM(K62:K91)</f>
+        <v/>
+      </c>
+      <c r="L92" s="125" t="n"/>
+      <c r="M92" s="125" t="n"/>
+      <c r="N92" s="117">
+        <f>SUM(N62:N91)</f>
+        <v/>
+      </c>
+      <c r="O92" s="117">
+        <f>SUM(O62:O91)</f>
+        <v/>
+      </c>
+      <c r="P92" s="125" t="n"/>
+      <c r="Q92" s="125" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="102" t="inlineStr">
+        <is>
+          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="103" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B95" s="103" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C95" s="103" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D95" s="103" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E95" s="103" t="inlineStr">
+        <is>
+          <t>Giá vốn VT</t>
+        </is>
+      </c>
+      <c r="F95" s="103" t="inlineStr">
+        <is>
+          <t>Giá vốn NC</t>
+        </is>
+      </c>
+      <c r="G95" s="103" t="inlineStr">
+        <is>
+          <t>Thành tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" s="108" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN65</t>
+        </is>
+      </c>
+      <c r="C96" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D96" s="128" t="n">
+        <v>860</v>
+      </c>
+      <c r="E96" s="110" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F96" s="110" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G96" s="110" t="n">
+        <v>206400000</v>
+      </c>
+      <c r="H96" s="90" t="inlineStr">
+        <is>
+          <t>Trong đó vật tư phụ 5%:</t>
+        </is>
+      </c>
+      <c r="J96" s="130">
+        <f>SUMIF(C96:C110,"Vật tư phụ",G96:G110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="120" t="n">
+        <v>2</v>
+      </c>
+      <c r="B97" s="108" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C97" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D97" s="128" t="n">
+        <v>570</v>
+      </c>
+      <c r="E97" s="110" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F97" s="110" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G97" s="110" t="n">
+        <v>125400000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" s="108" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN80</t>
+        </is>
+      </c>
+      <c r="C98" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D98" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="110" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F98" s="110" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G98" s="110" t="n">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="120" t="n">
         <v>4</v>
       </c>
-      <c r="B65" s="109" t="inlineStr">
-        <is>
-          <t>Đầu báo khói quang 24VDC</t>
-        </is>
-      </c>
-      <c r="C65" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D65" s="129" t="n">
-        <v>287</v>
-      </c>
-      <c r="E65" s="111">
-        <f>'Bao gia'!J7</f>
-        <v/>
-      </c>
-      <c r="F65" s="111">
-        <f>'Bao gia'!K7</f>
-        <v/>
-      </c>
-      <c r="G65" s="111">
-        <f>IF(M65=0,"",N65/M65)</f>
-        <v/>
-      </c>
-      <c r="H65" s="108">
-        <f>ROUNDUP(E65*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I65" s="111" t="n">
-        <v>55471</v>
-      </c>
-      <c r="J65" s="111">
-        <f>D65*(E65+F65)</f>
-        <v/>
-      </c>
-      <c r="K65" s="111">
-        <f>D65*H65</f>
-        <v/>
-      </c>
-      <c r="L65" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M65" s="130" t="n">
-        <v>292.74</v>
-      </c>
-      <c r="N65" s="111" t="n">
-        <v>73185000</v>
-      </c>
-      <c r="O65" s="111">
-        <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
-        <v/>
-      </c>
-      <c r="P65" s="109" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="110" t="n">
+      <c r="B99" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C99" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D99" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="110" t="n"/>
+      <c r="F99" s="110" t="n"/>
+      <c r="G99" s="110" t="n">
+        <v>5345662</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="120" t="n">
         <v>5</v>
       </c>
-      <c r="B66" s="109" t="inlineStr">
-        <is>
-          <t>Đèn báo phòng</t>
-        </is>
-      </c>
-      <c r="C66" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D66" s="129" t="n">
-        <v>70</v>
-      </c>
-      <c r="E66" s="111">
-        <f>'Bao gia'!J8</f>
-        <v/>
-      </c>
-      <c r="F66" s="111">
-        <f>'Bao gia'!K8</f>
-        <v/>
-      </c>
-      <c r="G66" s="111">
-        <f>IF(M66=0,"",N66/M66)</f>
-        <v/>
-      </c>
-      <c r="H66" s="108">
-        <f>ROUNDUP(E66*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I66" s="111" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J66" s="111">
-        <f>D66*(E66+F66)</f>
-        <v/>
-      </c>
-      <c r="K66" s="111">
-        <f>D66*H66</f>
-        <v/>
-      </c>
-      <c r="L66" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M66" s="130" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="N66" s="111" t="n">
-        <v>3570000</v>
-      </c>
-      <c r="O66" s="111">
-        <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
-        <v/>
-      </c>
-      <c r="P66" s="109" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="110" t="n">
+      <c r="B100" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C100" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D100" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="110" t="n"/>
+      <c r="F100" s="110" t="n"/>
+      <c r="G100" s="110" t="n">
+        <v>4422065</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="120" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="109" t="inlineStr">
-        <is>
-          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
-        </is>
-      </c>
-      <c r="C67" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D67" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="111">
-        <f>'Bao gia'!J9</f>
-        <v/>
-      </c>
-      <c r="F67" s="111">
-        <f>'Bao gia'!K9</f>
-        <v/>
-      </c>
-      <c r="G67" s="111">
-        <f>IF(M67=0,"",N67/M67)</f>
-        <v/>
-      </c>
-      <c r="H67" s="108">
-        <f>ROUNDUP(E67*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I67" s="111" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J67" s="111">
-        <f>D67*(E67+F67)</f>
-        <v/>
-      </c>
-      <c r="K67" s="111">
-        <f>D67*H67</f>
-        <v/>
-      </c>
-      <c r="L67" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M67" s="130" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N67" s="111" t="n">
-        <v>565600</v>
-      </c>
-      <c r="O67" s="111">
-        <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
-        <v/>
-      </c>
-      <c r="P67" s="109" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="110" t="n">
+      <c r="B101" s="108" t="inlineStr">
+        <is>
+          <t>Dây nguồn đèn exit sự cố 2x0.75mm</t>
+        </is>
+      </c>
+      <c r="C101" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D101" s="128" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E101" s="110" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F101" s="110" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G101" s="110" t="n">
+        <v>21250000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="120" t="n">
         <v>7</v>
       </c>
-      <c r="B68" s="109" t="inlineStr">
-        <is>
-          <t>Co thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C68" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D68" s="129" t="n">
-        <v>56</v>
-      </c>
-      <c r="E68" s="111">
-        <f>'Bao gia'!J10</f>
-        <v/>
-      </c>
-      <c r="F68" s="111">
-        <f>'Bao gia'!K10</f>
-        <v/>
-      </c>
-      <c r="G68" s="111">
-        <f>IF(M68=0,"",N68/M68)</f>
-        <v/>
-      </c>
-      <c r="H68" s="108">
-        <f>ROUNDUP(E68*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I68" s="111" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J68" s="111">
-        <f>D68*(E68+F68)</f>
-        <v/>
-      </c>
-      <c r="K68" s="111">
-        <f>D68*H68</f>
-        <v/>
-      </c>
-      <c r="L68" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M68" s="130" t="n">
-        <v>56.0056</v>
-      </c>
-      <c r="N68" s="111" t="n">
-        <v>3640364</v>
-      </c>
-      <c r="O68" s="111">
-        <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
-        <v/>
-      </c>
-      <c r="P68" s="109" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="110" t="n">
+      <c r="B102" s="108" t="inlineStr">
+        <is>
+          <t>Ống luồn dây PVC D20</t>
+        </is>
+      </c>
+      <c r="C102" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D102" s="128" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E102" s="110" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F102" s="110" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G102" s="110" t="n">
+        <v>117000000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="120" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="109" t="inlineStr">
-        <is>
-          <t>Co thép đen hàn DN50</t>
-        </is>
-      </c>
-      <c r="C69" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D69" s="129" t="n">
-        <v>265</v>
-      </c>
-      <c r="E69" s="111">
-        <f>'Bao gia'!J11</f>
-        <v/>
-      </c>
-      <c r="F69" s="111">
-        <f>'Bao gia'!K11</f>
-        <v/>
-      </c>
-      <c r="G69" s="111">
-        <f>IF(M69=0,"",N69/M69)</f>
-        <v/>
-      </c>
-      <c r="H69" s="108">
-        <f>ROUNDUP(E69*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I69" s="111" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J69" s="111">
-        <f>D69*(E69+F69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="111">
-        <f>D69*H69</f>
-        <v/>
-      </c>
-      <c r="L69" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M69" s="130" t="n">
-        <v>265.0265</v>
-      </c>
-      <c r="N69" s="111" t="n">
-        <v>13251325</v>
-      </c>
-      <c r="O69" s="111">
-        <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
-        <v/>
-      </c>
-      <c r="P69" s="109" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="110" t="n">
+      <c r="B103" s="108" t="inlineStr">
+        <is>
+          <t>Cáp tín hiệu 2x2x0,5mm2</t>
+        </is>
+      </c>
+      <c r="C103" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D103" s="128" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E103" s="110" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F103" s="110" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G103" s="110" t="n">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="120" t="n">
         <v>9</v>
       </c>
-      <c r="B70" s="109" t="inlineStr">
-        <is>
-          <t>Tê thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C70" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D70" s="129" t="n">
-        <v>22</v>
-      </c>
-      <c r="E70" s="111">
-        <f>'Bao gia'!J12</f>
-        <v/>
-      </c>
-      <c r="F70" s="111">
-        <f>'Bao gia'!K12</f>
-        <v/>
-      </c>
-      <c r="G70" s="111">
-        <f>IF(M70=0,"",N70/M70)</f>
-        <v/>
-      </c>
-      <c r="H70" s="108">
-        <f>ROUNDUP(E70*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I70" s="111" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J70" s="111">
-        <f>D70*(E70+F70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="111">
-        <f>D70*H70</f>
-        <v/>
-      </c>
-      <c r="L70" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M70" s="130" t="n">
-        <v>22.0022</v>
-      </c>
-      <c r="N70" s="111" t="n">
-        <v>3630363</v>
-      </c>
-      <c r="O70" s="111">
-        <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
-        <v/>
-      </c>
-      <c r="P70" s="109" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="110" t="n">
+      <c r="B104" s="108" t="inlineStr">
+        <is>
+          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
+        </is>
+      </c>
+      <c r="C104" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D104" s="128" t="n">
+        <v>130</v>
+      </c>
+      <c r="E104" s="110" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F104" s="110" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G104" s="110" t="n">
+        <v>1625000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="120" t="n">
         <v>10</v>
       </c>
-      <c r="B71" s="109" t="inlineStr">
-        <is>
-          <t>Tê giảm thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C71" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D71" s="129" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" s="111">
-        <f>'Bao gia'!J13</f>
-        <v/>
-      </c>
-      <c r="F71" s="111">
-        <f>'Bao gia'!K13</f>
-        <v/>
-      </c>
-      <c r="G71" s="111">
-        <f>IF(M71=0,"",N71/M71)</f>
-        <v/>
-      </c>
-      <c r="H71" s="108">
-        <f>ROUNDUP(E71*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I71" s="111" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J71" s="111">
-        <f>D71*(E71+F71)</f>
-        <v/>
-      </c>
-      <c r="K71" s="111">
-        <f>D71*H71</f>
-        <v/>
-      </c>
-      <c r="L71" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M71" s="130" t="n">
-        <v>10.001</v>
-      </c>
-      <c r="N71" s="111" t="n">
-        <v>1650165</v>
-      </c>
-      <c r="O71" s="111">
-        <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
-        <v/>
-      </c>
-      <c r="P71" s="109" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="110" t="n">
+      <c r="B105" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C105" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D105" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="110" t="n"/>
+      <c r="F105" s="110" t="n"/>
+      <c r="G105" s="110" t="n">
+        <v>7726450</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="120" t="n">
         <v>11</v>
       </c>
-      <c r="B72" s="109" t="inlineStr">
-        <is>
-          <t>Tê thép hàn tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C72" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D72" s="129" t="n">
-        <v>52</v>
-      </c>
-      <c r="E72" s="111">
-        <f>'Bao gia'!J14</f>
-        <v/>
-      </c>
-      <c r="F72" s="111">
-        <f>'Bao gia'!K14</f>
-        <v/>
-      </c>
-      <c r="G72" s="111">
-        <f>IF(M72=0,"",N72/M72)</f>
-        <v/>
-      </c>
-      <c r="H72" s="108">
-        <f>ROUNDUP(E72*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I72" s="111" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J72" s="111">
-        <f>D72*(E72+F72)</f>
-        <v/>
-      </c>
-      <c r="K72" s="111">
-        <f>D72*H72</f>
-        <v/>
-      </c>
-      <c r="L72" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M72" s="130" t="n">
-        <v>52.0052</v>
-      </c>
-      <c r="N72" s="111" t="n">
-        <v>7800780</v>
-      </c>
-      <c r="O72" s="111">
-        <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
-        <v/>
-      </c>
-      <c r="P72" s="109" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="110" t="n">
+      <c r="B106" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C106" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D106" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="110" t="n"/>
+      <c r="F106" s="110" t="n"/>
+      <c r="G106" s="110" t="n">
+        <v>6964392</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="120" t="n">
         <v>12</v>
       </c>
-      <c r="B73" s="109" t="inlineStr">
-        <is>
-          <t>Tê giảm thép hàn DN100/65</t>
-        </is>
-      </c>
-      <c r="C73" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D73" s="129" t="n">
+      <c r="B107" s="108" t="inlineStr">
+        <is>
+          <t>Ống nhựa xoắn HDPE 40/30</t>
+        </is>
+      </c>
+      <c r="C107" s="120" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D107" s="128" t="n">
+        <v>200</v>
+      </c>
+      <c r="E107" s="110" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F107" s="110" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G107" s="110" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="120" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C108" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D108" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="111">
-        <f>'Bao gia'!J15</f>
-        <v/>
-      </c>
-      <c r="F73" s="111">
-        <f>'Bao gia'!K15</f>
-        <v/>
-      </c>
-      <c r="G73" s="111">
-        <f>IF(M73=0,"",N73/M73)</f>
-        <v/>
-      </c>
-      <c r="H73" s="108">
-        <f>ROUNDUP(E73*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I73" s="111" t="n">
-        <v>113544</v>
-      </c>
-      <c r="J73" s="111">
-        <f>D73*(E73+F73)</f>
-        <v/>
-      </c>
-      <c r="K73" s="111">
-        <f>D73*H73</f>
-        <v/>
-      </c>
-      <c r="L73" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M73" s="130" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="N73" s="111" t="n">
-        <v>180018</v>
-      </c>
-      <c r="O73" s="111">
-        <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
-        <v/>
-      </c>
-      <c r="P73" s="109" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="110" t="n">
-        <v>13</v>
-      </c>
-      <c r="B74" s="109" t="inlineStr">
-        <is>
-          <t>Tê giảm thép hàn DN65/50</t>
-        </is>
-      </c>
-      <c r="C74" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D74" s="129" t="n">
-        <v>5</v>
-      </c>
-      <c r="E74" s="111">
-        <f>'Bao gia'!J16</f>
-        <v/>
-      </c>
-      <c r="F74" s="111">
-        <f>'Bao gia'!K16</f>
-        <v/>
-      </c>
-      <c r="G74" s="111">
-        <f>IF(M74=0,"",N74/M74)</f>
-        <v/>
-      </c>
-      <c r="H74" s="108">
-        <f>ROUNDUP(E74*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I74" s="111" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J74" s="111">
-        <f>D74*(E74+F74)</f>
-        <v/>
-      </c>
-      <c r="K74" s="111">
-        <f>D74*H74</f>
-        <v/>
-      </c>
-      <c r="L74" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M74" s="130" t="n">
-        <v>5.0005</v>
-      </c>
-      <c r="N74" s="111" t="n">
-        <v>750075</v>
-      </c>
-      <c r="O74" s="111">
-        <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
-        <v/>
-      </c>
-      <c r="P74" s="109" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="110" t="n">
+      <c r="E108" s="110" t="n"/>
+      <c r="F108" s="110" t="n"/>
+      <c r="G108" s="110" t="n">
+        <v>6135550</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="120" t="n">
         <v>14</v>
       </c>
-      <c r="B75" s="109" t="inlineStr">
-        <is>
-          <t>Côn giảm thép hàn DN80/65</t>
-        </is>
-      </c>
-      <c r="C75" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D75" s="129" t="n">
+      <c r="B109" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C109" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D109" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="E75" s="111">
-        <f>'Bao gia'!J17</f>
-        <v/>
-      </c>
-      <c r="F75" s="111">
-        <f>'Bao gia'!K17</f>
-        <v/>
-      </c>
-      <c r="G75" s="111">
-        <f>IF(M75=0,"",N75/M75)</f>
-        <v/>
-      </c>
-      <c r="H75" s="108">
-        <f>ROUNDUP(E75*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I75" s="111" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J75" s="111">
-        <f>D75*(E75+F75)</f>
-        <v/>
-      </c>
-      <c r="K75" s="111">
-        <f>D75*H75</f>
-        <v/>
-      </c>
-      <c r="L75" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M75" s="130" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="N75" s="111" t="n">
-        <v>80008</v>
-      </c>
-      <c r="O75" s="111">
-        <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
-        <v/>
-      </c>
-      <c r="P75" s="109" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="110" t="n">
+      <c r="E109" s="110" t="n"/>
+      <c r="F109" s="110" t="n"/>
+      <c r="G109" s="110" t="n">
+        <v>5017119</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="120" t="n">
         <v>15</v>
       </c>
-      <c r="B76" s="109" t="inlineStr">
-        <is>
-          <t>Mặt bích thép DN80</t>
-        </is>
-      </c>
-      <c r="C76" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D76" s="129" t="n">
+      <c r="B110" s="108" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C110" s="120" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D110" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="111">
-        <f>'Bao gia'!J18</f>
-        <v/>
-      </c>
-      <c r="F76" s="111">
-        <f>'Bao gia'!K18</f>
-        <v/>
-      </c>
-      <c r="G76" s="111">
-        <f>IF(M76=0,"",N76/M76)</f>
-        <v/>
-      </c>
-      <c r="H76" s="108">
-        <f>ROUNDUP(E76*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I76" s="111" t="n">
-        <v>59926</v>
-      </c>
-      <c r="J76" s="111">
-        <f>D76*(E76+F76)</f>
-        <v/>
-      </c>
-      <c r="K76" s="111">
-        <f>D76*H76</f>
-        <v/>
-      </c>
-      <c r="L76" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M76" s="130" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="N76" s="111" t="n">
-        <v>321032.1</v>
-      </c>
-      <c r="O76" s="111">
-        <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
-        <v/>
-      </c>
-      <c r="P76" s="109" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="110" t="n">
-        <v>16</v>
-      </c>
-      <c r="B77" s="109" t="inlineStr">
-        <is>
-          <t>Roăng su DN80</t>
-        </is>
-      </c>
-      <c r="C77" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D77" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="111">
-        <f>'Bao gia'!J19</f>
-        <v/>
-      </c>
-      <c r="F77" s="111">
-        <f>'Bao gia'!K19</f>
-        <v/>
-      </c>
-      <c r="G77" s="111">
-        <f>IF(M77=0,"",N77/M77)</f>
-        <v/>
-      </c>
-      <c r="H77" s="108">
-        <f>ROUNDUP(E77*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I77" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="111">
-        <f>D77*(E77+F77)</f>
-        <v/>
-      </c>
-      <c r="K77" s="111">
-        <f>D77*H77</f>
-        <v/>
-      </c>
-      <c r="L77" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M77" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" s="111" t="n">
-        <v>150000</v>
-      </c>
-      <c r="O77" s="111">
-        <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
-        <v/>
-      </c>
-      <c r="P77" s="109" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="110" t="n">
-        <v>17</v>
-      </c>
-      <c r="B78" s="109" t="inlineStr">
-        <is>
-          <t>Van 1 chiều DN80</t>
-        </is>
-      </c>
-      <c r="C78" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D78" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="111">
-        <f>'Bao gia'!J20</f>
-        <v/>
-      </c>
-      <c r="F78" s="111">
-        <f>'Bao gia'!K20</f>
-        <v/>
-      </c>
-      <c r="G78" s="111">
-        <f>IF(M78=0,"",N78/M78)</f>
-        <v/>
-      </c>
-      <c r="H78" s="108">
-        <f>ROUNDUP(E78*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I78" s="111" t="n">
-        <v>97774</v>
-      </c>
-      <c r="J78" s="111">
-        <f>D78*(E78+F78)</f>
-        <v/>
-      </c>
-      <c r="K78" s="111">
-        <f>D78*H78</f>
-        <v/>
-      </c>
-      <c r="L78" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M78" s="130" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="N78" s="111" t="n">
-        <v>350035</v>
-      </c>
-      <c r="O78" s="111">
-        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
-        <v/>
-      </c>
-      <c r="P78" s="109" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="110" t="n">
-        <v>18</v>
-      </c>
-      <c r="B79" s="109" t="inlineStr">
-        <is>
-          <t>Rơ le kiểm tra mực nước</t>
-        </is>
-      </c>
-      <c r="C79" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D79" s="129" t="n">
-        <v>4</v>
-      </c>
-      <c r="E79" s="111">
-        <f>'Bao gia'!J21</f>
-        <v/>
-      </c>
-      <c r="F79" s="111">
-        <f>'Bao gia'!K21</f>
-        <v/>
-      </c>
-      <c r="G79" s="111">
-        <f>IF(M79=0,"",N79/M79)</f>
-        <v/>
-      </c>
-      <c r="H79" s="108">
-        <f>ROUNDUP(E79*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I79" s="111" t="n">
-        <v>31540</v>
-      </c>
-      <c r="J79" s="111">
-        <f>D79*(E79+F79)</f>
-        <v/>
-      </c>
-      <c r="K79" s="111">
-        <f>D79*H79</f>
-        <v/>
-      </c>
-      <c r="L79" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M79" s="130" t="n">
-        <v>4.0004</v>
-      </c>
-      <c r="N79" s="111" t="n">
-        <v>4600460</v>
-      </c>
-      <c r="O79" s="111">
-        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
-        <v/>
-      </c>
-      <c r="P79" s="109" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="110" t="n">
-        <v>19</v>
-      </c>
-      <c r="B80" s="109" t="inlineStr">
-        <is>
-          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
-        </is>
-      </c>
-      <c r="C80" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D80" s="129" t="n">
-        <v>57</v>
-      </c>
-      <c r="E80" s="111">
-        <f>'Bao gia'!J22</f>
-        <v/>
-      </c>
-      <c r="F80" s="111">
-        <f>'Bao gia'!K22</f>
-        <v/>
-      </c>
-      <c r="G80" s="111">
-        <f>IF(M80=0,"",N80/M80)</f>
-        <v/>
-      </c>
-      <c r="H80" s="108">
-        <f>ROUNDUP(E80*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I80" s="111" t="n">
-        <v>94620</v>
-      </c>
-      <c r="J80" s="111">
-        <f>D80*(E80+F80)</f>
-        <v/>
-      </c>
-      <c r="K80" s="111">
-        <f>D80*H80</f>
-        <v/>
-      </c>
-      <c r="L80" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M80" s="130" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="N80" s="111" t="n">
-        <v>19152000</v>
-      </c>
-      <c r="O80" s="111">
-        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
-        <v/>
-      </c>
-      <c r="P80" s="109" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="110" t="n">
-        <v>20</v>
-      </c>
-      <c r="B81" s="109" t="inlineStr">
-        <is>
-          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
-        </is>
-      </c>
-      <c r="C81" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D81" s="129" t="n">
-        <v>70</v>
-      </c>
-      <c r="E81" s="111">
-        <f>'Bao gia'!J23</f>
-        <v/>
-      </c>
-      <c r="F81" s="111">
-        <f>'Bao gia'!K23</f>
-        <v/>
-      </c>
-      <c r="G81" s="111">
-        <f>IF(M81=0,"",N81/M81)</f>
-        <v/>
-      </c>
-      <c r="H81" s="108">
-        <f>ROUNDUP(E81*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I81" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="111">
-        <f>D81*(E81+F81)</f>
-        <v/>
-      </c>
-      <c r="K81" s="111">
-        <f>D81*H81</f>
-        <v/>
-      </c>
-      <c r="L81" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M81" s="130" t="n">
-        <v>70</v>
-      </c>
-      <c r="N81" s="111" t="n">
-        <v>33600000</v>
-      </c>
-      <c r="O81" s="111">
-        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
-        <v/>
-      </c>
-      <c r="P81" s="109" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="110" t="n">
-        <v>21</v>
-      </c>
-      <c r="B82" s="109" t="inlineStr">
-        <is>
-          <t>Lăng phun DN50</t>
-        </is>
-      </c>
-      <c r="C82" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D82" s="129" t="n">
-        <v>70</v>
-      </c>
-      <c r="E82" s="111">
-        <f>'Bao gia'!J24</f>
-        <v/>
-      </c>
-      <c r="F82" s="111">
-        <f>'Bao gia'!K24</f>
-        <v/>
-      </c>
-      <c r="G82" s="111">
-        <f>IF(M82=0,"",N82/M82)</f>
-        <v/>
-      </c>
-      <c r="H82" s="108">
-        <f>ROUNDUP(E82*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I82" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="111">
-        <f>D82*(E82+F82)</f>
-        <v/>
-      </c>
-      <c r="K82" s="111">
-        <f>D82*H82</f>
-        <v/>
-      </c>
-      <c r="L82" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M82" s="130" t="n">
-        <v>70</v>
-      </c>
-      <c r="N82" s="111" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="O82" s="111">
-        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
-        <v/>
-      </c>
-      <c r="P82" s="109" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="110" t="n">
-        <v>22</v>
-      </c>
-      <c r="B83" s="109" t="inlineStr">
-        <is>
-          <t>Van góc FUJI DN50</t>
-        </is>
-      </c>
-      <c r="C83" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D83" s="129" t="n">
-        <v>70</v>
-      </c>
-      <c r="E83" s="111">
-        <f>'Bao gia'!J25</f>
-        <v/>
-      </c>
-      <c r="F83" s="111">
-        <f>'Bao gia'!K25</f>
-        <v/>
-      </c>
-      <c r="G83" s="111">
-        <f>IF(M83=0,"",N83/M83)</f>
-        <v/>
-      </c>
-      <c r="H83" s="108">
-        <f>ROUNDUP(E83*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I83" s="111" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J83" s="111">
-        <f>D83*(E83+F83)</f>
-        <v/>
-      </c>
-      <c r="K83" s="111">
-        <f>D83*H83</f>
-        <v/>
-      </c>
-      <c r="L83" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M83" s="130" t="n">
-        <v>70.00700000000001</v>
-      </c>
-      <c r="N83" s="111" t="n">
-        <v>17501750</v>
-      </c>
-      <c r="O83" s="111">
-        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
-        <v/>
-      </c>
-      <c r="P83" s="109" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="110" t="n">
-        <v>23</v>
-      </c>
-      <c r="B84" s="109" t="inlineStr">
-        <is>
-          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
-        </is>
-      </c>
-      <c r="C84" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D84" s="129" t="n">
-        <v>5</v>
-      </c>
-      <c r="E84" s="111">
-        <f>'Bao gia'!J26</f>
-        <v/>
-      </c>
-      <c r="F84" s="111">
-        <f>'Bao gia'!K26</f>
-        <v/>
-      </c>
-      <c r="G84" s="111">
-        <f>IF(M84=0,"",N84/M84)</f>
-        <v/>
-      </c>
-      <c r="H84" s="108">
-        <f>ROUNDUP(E84*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I84" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="111">
-        <f>D84*(E84+F84)</f>
-        <v/>
-      </c>
-      <c r="K84" s="111">
-        <f>D84*H84</f>
-        <v/>
-      </c>
-      <c r="L84" s="110" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M84" s="130" t="n">
-        <v>5</v>
-      </c>
-      <c r="N84" s="111" t="n">
-        <v>200000</v>
-      </c>
-      <c r="O84" s="111">
-        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
-        <v/>
-      </c>
-      <c r="P84" s="109" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="110" t="n">
-        <v>24</v>
-      </c>
-      <c r="B85" s="109" t="inlineStr">
-        <is>
-          <t>Kệ đỡ bình chữa cháy</t>
-        </is>
-      </c>
-      <c r="C85" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D85" s="129" t="n">
-        <v>10</v>
-      </c>
-      <c r="E85" s="111">
-        <f>'Bao gia'!J27</f>
-        <v/>
-      </c>
-      <c r="F85" s="111">
-        <f>'Bao gia'!K27</f>
-        <v/>
-      </c>
-      <c r="G85" s="111">
-        <f>IF(M85=0,"",N85/M85)</f>
-        <v/>
-      </c>
-      <c r="H85" s="108">
-        <f>ROUNDUP(E85*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I85" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="111">
-        <f>D85*(E85+F85)</f>
-        <v/>
-      </c>
-      <c r="K85" s="111">
-        <f>D85*H85</f>
-        <v/>
-      </c>
-      <c r="L85" s="110" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M85" s="130" t="n">
-        <v>10</v>
-      </c>
-      <c r="N85" s="111" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="O85" s="111">
-        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
-        <v/>
-      </c>
-      <c r="P85" s="109" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="110" t="n">
-        <v>25</v>
-      </c>
-      <c r="B86" s="109" t="inlineStr">
-        <is>
-          <t>BÌNH BỘT ABC 8KG</t>
-        </is>
-      </c>
-      <c r="C86" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D86" s="129" t="n">
-        <v>20</v>
-      </c>
-      <c r="E86" s="111">
-        <f>'Bao gia'!J28</f>
-        <v/>
-      </c>
-      <c r="F86" s="111">
-        <f>'Bao gia'!K28</f>
-        <v/>
-      </c>
-      <c r="G86" s="111">
-        <f>IF(M86=0,"",N86/M86)</f>
-        <v/>
-      </c>
-      <c r="H86" s="108">
-        <f>ROUNDUP(E86*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I86" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="111">
-        <f>D86*(E86+F86)</f>
-        <v/>
-      </c>
-      <c r="K86" s="111">
-        <f>D86*H86</f>
-        <v/>
-      </c>
-      <c r="L86" s="110" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M86" s="130" t="n">
-        <v>20</v>
-      </c>
-      <c r="N86" s="111" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="O86" s="111">
-        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
-        <v/>
-      </c>
-      <c r="P86" s="109" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="110" t="n">
-        <v>26</v>
-      </c>
-      <c r="B87" s="109" t="inlineStr">
-        <is>
-          <t>Đèn exit</t>
-        </is>
-      </c>
-      <c r="C87" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D87" s="129" t="n">
-        <v>11</v>
-      </c>
-      <c r="E87" s="111">
-        <f>'Bao gia'!J29</f>
-        <v/>
-      </c>
-      <c r="F87" s="111">
-        <f>'Bao gia'!K29</f>
-        <v/>
-      </c>
-      <c r="G87" s="111">
-        <f>IF(M87=0,"",N87/M87)</f>
-        <v/>
-      </c>
-      <c r="H87" s="108">
-        <f>ROUNDUP(E87*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I87" s="111" t="n">
-        <v>93090</v>
-      </c>
-      <c r="J87" s="111">
-        <f>D87*(E87+F87)</f>
-        <v/>
-      </c>
-      <c r="K87" s="111">
-        <f>D87*H87</f>
-        <v/>
-      </c>
-      <c r="L87" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M87" s="130" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="N87" s="111" t="n">
-        <v>2310000</v>
-      </c>
-      <c r="O87" s="111">
-        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
-        <v/>
-      </c>
-      <c r="P87" s="109" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="110" t="n">
-        <v>27</v>
-      </c>
-      <c r="B88" s="109" t="inlineStr">
-        <is>
-          <t>Đèn chiếu sáng sự cố</t>
-        </is>
-      </c>
-      <c r="C88" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D88" s="129" t="n">
-        <v>54</v>
-      </c>
-      <c r="E88" s="111">
-        <f>'Bao gia'!J30</f>
-        <v/>
-      </c>
-      <c r="F88" s="111">
-        <f>'Bao gia'!K30</f>
-        <v/>
-      </c>
-      <c r="G88" s="111">
-        <f>IF(M88=0,"",N88/M88)</f>
-        <v/>
-      </c>
-      <c r="H88" s="108">
-        <f>ROUNDUP(E88*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I88" s="111" t="n">
-        <v>93090</v>
-      </c>
-      <c r="J88" s="111">
-        <f>D88*(E88+F88)</f>
-        <v/>
-      </c>
-      <c r="K88" s="111">
-        <f>D88*H88</f>
-        <v/>
-      </c>
-      <c r="L88" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M88" s="130" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="N88" s="111" t="n">
-        <v>11340000</v>
-      </c>
-      <c r="O88" s="111">
-        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
-        <v/>
-      </c>
-      <c r="P88" s="109" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="110" t="n">
-        <v>28</v>
-      </c>
-      <c r="B89" s="109" t="inlineStr">
-        <is>
-          <t>Đèn báo trạm bơm</t>
-        </is>
-      </c>
-      <c r="C89" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D89" s="129">
-        <f>N('Bao gia'!D31)</f>
-        <v/>
-      </c>
-      <c r="E89" s="111">
-        <f>'Bao gia'!J31</f>
-        <v/>
-      </c>
-      <c r="F89" s="111">
-        <f>'Bao gia'!K31</f>
-        <v/>
-      </c>
-      <c r="G89" s="111">
-        <f>IF(M89=0,"",N89/M89)</f>
-        <v/>
-      </c>
-      <c r="H89" s="108">
-        <f>ROUNDUP(E89*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I89" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="111">
-        <f>D89*(E89+F89)</f>
-        <v/>
-      </c>
-      <c r="K89" s="111">
-        <f>D89*H89</f>
-        <v/>
-      </c>
-      <c r="L89" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M89" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="111">
-        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
-        <v/>
-      </c>
-      <c r="P89" s="109" t="inlineStr">
-        <is>
-          <t>Chưa có giá vốn, chưa có trong dự toán – nếu dùng thì điền KL và giá vốn ở sheet Bao gia</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="110" t="n">
-        <v>29</v>
-      </c>
-      <c r="B90" s="109" t="inlineStr">
-        <is>
-          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
-        </is>
-      </c>
-      <c r="C90" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D90" s="129" t="n">
-        <v>35</v>
-      </c>
-      <c r="E90" s="111">
-        <f>'Bao gia'!J32</f>
-        <v/>
-      </c>
-      <c r="F90" s="111">
-        <f>'Bao gia'!K32</f>
-        <v/>
-      </c>
-      <c r="G90" s="111">
-        <f>IF(M90=0,"",N90/M90)</f>
-        <v/>
-      </c>
-      <c r="H90" s="108">
-        <f>ROUNDUP(E90*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I90" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="111">
-        <f>D90*(E90+F90)</f>
-        <v/>
-      </c>
-      <c r="K90" s="111">
-        <f>D90*H90</f>
-        <v/>
-      </c>
-      <c r="L90" s="110" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M90" s="130" t="n">
-        <v>35</v>
-      </c>
-      <c r="N90" s="111" t="n">
-        <v>5250000</v>
-      </c>
-      <c r="O90" s="111">
-        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
-        <v/>
-      </c>
-      <c r="P90" s="109" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="110" t="n">
-        <v>30</v>
-      </c>
-      <c r="B91" s="109" t="inlineStr">
-        <is>
-          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
-        </is>
-      </c>
-      <c r="C91" s="110" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D91" s="129" t="n">
-        <v>3</v>
-      </c>
-      <c r="E91" s="111">
-        <f>'Bao gia'!J33</f>
-        <v/>
-      </c>
-      <c r="F91" s="111">
-        <f>'Bao gia'!K33</f>
-        <v/>
-      </c>
-      <c r="G91" s="111">
-        <f>IF(M91=0,"",N91/M91)</f>
-        <v/>
-      </c>
-      <c r="H91" s="108">
-        <f>ROUNDUP(E91*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I91" s="111" t="n">
-        <v>110390</v>
-      </c>
-      <c r="J91" s="111">
-        <f>D91*(E91+F91)</f>
-        <v/>
-      </c>
-      <c r="K91" s="111">
-        <f>D91*H91</f>
-        <v/>
-      </c>
-      <c r="L91" s="110" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M91" s="130" t="n">
-        <v>3.003</v>
-      </c>
-      <c r="N91" s="111" t="n">
-        <v>2852850</v>
-      </c>
-      <c r="O91" s="111">
-        <f>IF(L91="Thiết bị",0,$E$7*(M91*H91-N91))</f>
-        <v/>
-      </c>
-      <c r="P91" s="109" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="126" t="n"/>
-      <c r="B92" s="126" t="inlineStr">
+      <c r="E110" s="110" t="n"/>
+      <c r="F110" s="110" t="n"/>
+      <c r="G110" s="110" t="n">
+        <v>4482900</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="125" t="n"/>
+      <c r="B111" s="125" t="inlineStr">
         <is>
           <t>CỘNG</t>
         </is>
       </c>
-      <c r="C92" s="126" t="n"/>
-      <c r="D92" s="126" t="n"/>
-      <c r="E92" s="126" t="n"/>
-      <c r="F92" s="126" t="n"/>
-      <c r="G92" s="126" t="n"/>
-      <c r="H92" s="126" t="n"/>
-      <c r="I92" s="126" t="n"/>
-      <c r="J92" s="118">
-        <f>SUM(J62:J91)</f>
-        <v/>
-      </c>
-      <c r="K92" s="118">
-        <f>SUM(K62:K91)</f>
-        <v/>
-      </c>
-      <c r="L92" s="126" t="n"/>
-      <c r="M92" s="126" t="n"/>
-      <c r="N92" s="118">
-        <f>SUM(N62:N91)</f>
-        <v/>
-      </c>
-      <c r="O92" s="118">
-        <f>SUM(O62:O91)</f>
-        <v/>
-      </c>
-      <c r="P92" s="126" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="103" t="inlineStr">
-        <is>
-          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="104" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B95" s="104" t="inlineStr">
-        <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="C95" s="104" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="D95" s="104" t="inlineStr">
-        <is>
-          <t>Khối lượng</t>
-        </is>
-      </c>
-      <c r="E95" s="104" t="inlineStr">
-        <is>
-          <t>Giá vốn VT</t>
-        </is>
-      </c>
-      <c r="F95" s="104" t="inlineStr">
-        <is>
-          <t>Giá vốn NC</t>
-        </is>
-      </c>
-      <c r="G95" s="104" t="inlineStr">
-        <is>
-          <t>Thành tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="121" t="n">
-        <v>1</v>
-      </c>
-      <c r="B96" s="109" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN65</t>
-        </is>
-      </c>
-      <c r="C96" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D96" s="129" t="n">
-        <v>860</v>
-      </c>
-      <c r="E96" s="111" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F96" s="111" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G96" s="111" t="n">
-        <v>206400000</v>
-      </c>
-      <c r="H96" s="91" t="inlineStr">
-        <is>
-          <t>Trong đó vật tư phụ 5%:</t>
-        </is>
-      </c>
-      <c r="J96" s="131">
-        <f>SUMIF(C96:C110,"Vật tư phụ",G96:G110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="B97" s="109" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C97" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D97" s="129" t="n">
-        <v>570</v>
-      </c>
-      <c r="E97" s="111" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F97" s="111" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G97" s="111" t="n">
-        <v>125400000</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="121" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" s="109" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN80</t>
-        </is>
-      </c>
-      <c r="C98" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D98" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="111" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F98" s="111" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G98" s="111" t="n">
-        <v>280000</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="B99" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C99" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D99" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="111" t="n"/>
-      <c r="F99" s="111" t="n"/>
-      <c r="G99" s="111" t="n">
-        <v>5345662</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="121" t="n">
-        <v>5</v>
-      </c>
-      <c r="B100" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C100" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D100" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="111" t="n"/>
-      <c r="F100" s="111" t="n"/>
-      <c r="G100" s="111" t="n">
-        <v>4422065</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="121" t="n">
-        <v>6</v>
-      </c>
-      <c r="B101" s="109" t="inlineStr">
-        <is>
-          <t>Dây nguồn đèn exit sự cố 2x0.75mm</t>
-        </is>
-      </c>
-      <c r="C101" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D101" s="129" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E101" s="111" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F101" s="111" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G101" s="111" t="n">
-        <v>21250000</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="121" t="n">
-        <v>7</v>
-      </c>
-      <c r="B102" s="109" t="inlineStr">
-        <is>
-          <t>Ống luồn dây PVC D20</t>
-        </is>
-      </c>
-      <c r="C102" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D102" s="129" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E102" s="111" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F102" s="111" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G102" s="111" t="n">
-        <v>117000000</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="121" t="n">
-        <v>8</v>
-      </c>
-      <c r="B103" s="109" t="inlineStr">
-        <is>
-          <t>Cáp tín hiệu 2x2x0,5mm2</t>
-        </is>
-      </c>
-      <c r="C103" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D103" s="129" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E103" s="111" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F103" s="111" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G103" s="111" t="n">
-        <v>50000000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="121" t="n">
-        <v>9</v>
-      </c>
-      <c r="B104" s="109" t="inlineStr">
-        <is>
-          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
-        </is>
-      </c>
-      <c r="C104" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D104" s="129" t="n">
-        <v>130</v>
-      </c>
-      <c r="E104" s="111" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F104" s="111" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G104" s="111" t="n">
-        <v>1625000</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="121" t="n">
-        <v>10</v>
-      </c>
-      <c r="B105" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C105" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D105" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="111" t="n"/>
-      <c r="F105" s="111" t="n"/>
-      <c r="G105" s="111" t="n">
-        <v>7726450</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="121" t="n">
-        <v>11</v>
-      </c>
-      <c r="B106" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C106" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D106" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="111" t="n"/>
-      <c r="F106" s="111" t="n"/>
-      <c r="G106" s="111" t="n">
-        <v>6964392</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="121" t="n">
-        <v>12</v>
-      </c>
-      <c r="B107" s="109" t="inlineStr">
-        <is>
-          <t>Ống nhựa xoắn HDPE 40/30</t>
-        </is>
-      </c>
-      <c r="C107" s="121" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D107" s="129" t="n">
-        <v>200</v>
-      </c>
-      <c r="E107" s="111" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F107" s="111" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G107" s="111" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="121" t="n">
-        <v>13</v>
-      </c>
-      <c r="B108" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C108" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D108" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="111" t="n"/>
-      <c r="F108" s="111" t="n"/>
-      <c r="G108" s="111" t="n">
-        <v>6135550</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="121" t="n">
-        <v>14</v>
-      </c>
-      <c r="B109" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C109" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D109" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="111" t="n"/>
-      <c r="F109" s="111" t="n"/>
-      <c r="G109" s="111" t="n">
-        <v>5017119</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="121" t="n">
-        <v>15</v>
-      </c>
-      <c r="B110" s="109" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C110" s="121" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D110" s="129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="111" t="n"/>
-      <c r="F110" s="111" t="n"/>
-      <c r="G110" s="111" t="n">
-        <v>4482900</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="126" t="n"/>
-      <c r="B111" s="126" t="inlineStr">
-        <is>
-          <t>CỘNG</t>
-        </is>
-      </c>
-      <c r="C111" s="126" t="n"/>
-      <c r="D111" s="126" t="n"/>
-      <c r="E111" s="126" t="n"/>
-      <c r="F111" s="126" t="n"/>
-      <c r="G111" s="118">
+      <c r="C111" s="125" t="n"/>
+      <c r="D111" s="125" t="n"/>
+      <c r="E111" s="125" t="n"/>
+      <c r="F111" s="125" t="n"/>
+      <c r="G111" s="117">
         <f>SUM(G96:G110)</f>
         <v/>
       </c>
